--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="F+azpmG0khTOUh9lmv7nF419EtSuw9ks8zCQ8idIRWM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="tPWFPHOyBKhfIXtBW1J3Bo/enSDTuC0nEN9xYB6V3lw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="58">
   <si>
     <t>Semana</t>
   </si>
@@ -50,7 +50,10 @@
     <t>Inicio</t>
   </si>
   <si>
-    <t>Elaboración-Iteración 1</t>
+    <t>Inicio /Etapa de Elaboración Iteración 1</t>
+  </si>
+  <si>
+    <t>Elaboración Iteración 2</t>
   </si>
   <si>
     <t>Elaboración-Iteración 2</t>
@@ -62,31 +65,127 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Tarea</t>
+  </si>
+  <si>
     <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Modelo de negocio</t>
+  </si>
+  <si>
+    <t>Creación de repositorio</t>
+  </si>
+  <si>
+    <t>desgrabación entrevista</t>
+  </si>
+  <si>
+    <t>Pasar en limpio notas de la entrevista 1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>documento Resumen entrevista</t>
+  </si>
+  <si>
+    <t>Estudio de Factibilidad</t>
+  </si>
+  <si>
+    <t>Estudio Factibilidad</t>
+  </si>
+  <si>
+    <t>Estandares</t>
+  </si>
+  <si>
+    <t>documento de entrevistas y presentación</t>
+  </si>
+  <si>
+    <t>desgrabacion</t>
+  </si>
+  <si>
+    <t>Desgrabacion de entrevista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis </t>
   </si>
   <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>Creación de repositorio - Ramas</t>
+  </si>
+  <si>
+    <t>Revisión de documentos</t>
+  </si>
+  <si>
+    <t>Uargflow a Spring</t>
+  </si>
+  <si>
+    <t>Grabar uargflow</t>
+  </si>
+  <si>
+    <t>Pasar correcciones</t>
+  </si>
+  <si>
     <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Plan SQA</t>
+  </si>
+  <si>
+    <t>Pasado de notas reunion</t>
+  </si>
+  <si>
+    <t>Primer Reunión</t>
+  </si>
+  <si>
+    <t>HASTA ACA ETAPA DE INICIO</t>
   </si>
   <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>Revisión</t>
+  </si>
+  <si>
+    <t>Realizando el documento</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t xml:space="preserve">1:30:00	</t>
+    <t>Estimación fase de elaboración iteración 2</t>
+  </si>
+  <si>
+    <t>Primer prototipo funcional</t>
+  </si>
+  <si>
+    <t>Modelo de casos de uso</t>
+  </si>
+  <si>
+    <t>Estudio y análisis de Toggl Track API</t>
+  </si>
+  <si>
+    <t>Redefinición de Métricas</t>
+  </si>
+  <si>
+    <t>Redefinición de casos de uso</t>
+  </si>
+  <si>
+    <t>Identificación y evaluación de riesgos</t>
   </si>
   <si>
     <t>Semana 6</t>
   </si>
   <si>
-    <t xml:space="preserve">Semana 7 </t>
+    <t>Semana 7</t>
   </si>
   <si>
     <t>Semana 8</t>
+  </si>
+  <si>
+    <t>Semana 9</t>
   </si>
   <si>
     <t>Fecha de inicio</t>
@@ -104,7 +203,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -144,9 +243,27 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font/>
     <font>
       <b/>
       <color theme="1"/>
@@ -154,7 +271,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,8 +280,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,12 +310,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF84E291"/>
-        <bgColor rgb="FF84E291"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -196,11 +337,41 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="68">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -210,96 +381,150 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="164" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="46" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -640,26 +865,32 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="4">
-        <v>0.4509722222222222</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.0</v>
+        <f>Registro!B15</f>
+        <v>0.4929050926</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <f>Registro!D14</f>
+        <v/>
       </c>
       <c r="D2" s="5">
-        <v>0.03487268518518519</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0.0</v>
+        <f>Registro!F3</f>
+        <v>0.03487268519</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>Registro!H15</f>
+        <v/>
       </c>
       <c r="F2" s="7">
-        <v>0.13819444444444445</v>
+        <f>Registro!J15</f>
+        <v>0.4366898148</v>
       </c>
       <c r="G2" s="5">
-        <v>0.08333333333333333</v>
+        <f>Registro!L15</f>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
         <f>SUM(Total!$B2:$G2)</f>
-        <v>0.7073726852</v>
+        <v>0.9644675926</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>9</v>
@@ -670,29 +901,34 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="4">
-        <v>0.38710648148148147</v>
+        <f>Registro!B38</f>
+        <v>0.4042824074</v>
       </c>
       <c r="C3" s="5">
         <v>0.0</v>
       </c>
       <c r="D3" s="5">
-        <v>0.26229166666666665</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.02414351851851852</v>
+        <f>Registro!F38</f>
+        <v>0.2622916667</v>
+      </c>
+      <c r="E3" s="9">
+        <f>Registro!H38</f>
+        <v>0.02414351852</v>
       </c>
       <c r="F3" s="7">
-        <v>0.02648148148148148</v>
+        <f>Registro!J38</f>
+        <v>0.02648148148</v>
       </c>
       <c r="G3" s="5">
-        <v>0.25</v>
+        <f>Registro!L38</f>
+        <v>0.03163194444</v>
       </c>
       <c r="H3" s="5">
         <f>SUM(Total!$B3:$G3)</f>
-        <v>0.9500231481</v>
+        <v>0.7488310185</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -700,63 +936,77 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4879513888888889</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1.1574074074074075E-4</v>
+        <f>Registro!B59</f>
+        <v>0.4879513889</v>
+      </c>
+      <c r="C4" s="5" t="str">
+        <f>Registro!D59</f>
+        <v/>
       </c>
       <c r="D4" s="5">
-        <v>0.19166666666666668</v>
+        <f>Registro!F59</f>
+        <v>0.1916666667</v>
       </c>
       <c r="E4" s="5">
-        <v>0.0</v>
+        <f>Registro!H59</f>
+        <v>0</v>
       </c>
       <c r="F4" s="7">
-        <v>0.21858796296296296</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.4166666666666667</v>
+        <f>Registro!J59</f>
+        <v>0.218587963</v>
+      </c>
+      <c r="G4" s="9">
+        <f>Registro!L59</f>
+        <v>0.161875</v>
       </c>
       <c r="H4" s="5">
         <f>SUM(Total!$B4:$G4)</f>
-        <v>1.314988426</v>
-      </c>
-      <c r="I4" s="9"/>
+        <v>1.060081019</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3">
         <v>4.0</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6286805555555556</v>
+        <f>Registro!B75</f>
+        <v>0.6286805556</v>
       </c>
       <c r="C5" s="5">
-        <v>0.024305555555555556</v>
+        <f>Registro!D75</f>
+        <v>0.0244212963</v>
       </c>
       <c r="D5" s="5">
-        <v>0.09237268518518518</v>
+        <f>Registro!F75</f>
+        <v>0.09237268519</v>
       </c>
       <c r="E5" s="5">
-        <v>0.17800925925925926</v>
+        <f>Registro!H75</f>
+        <v>0.1780092593</v>
       </c>
       <c r="F5" s="7">
-        <v>0.16809027777777777</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.5833333333333334</v>
-      </c>
+        <f>Registro!J75</f>
+        <v>0.2304861111</v>
+      </c>
+      <c r="G5" s="10"/>
       <c r="H5" s="5">
         <f>SUM(Total!$B5:$G5)</f>
-        <v>1.674791667</v>
-      </c>
-      <c r="I5" s="9"/>
+        <v>1.153969907</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3">
         <v>5.0</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6159722222222223</v>
+        <f>Registro!B86</f>
+        <v>0.3979166667</v>
       </c>
       <c r="C6" s="6">
         <v>1.5628356481481482</v>
@@ -765,16 +1015,20 @@
       <c r="E6" s="5">
         <v>0.013888888888888888</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="7">
+        <f>Registro!J86</f>
+        <v>0.2180555556</v>
+      </c>
       <c r="G6" s="5">
-        <v>1.0107523148148148</v>
+        <f>Registro!L86</f>
+        <v>0.03333333333</v>
       </c>
       <c r="H6" s="5">
         <f>SUM(Total!$B6:$G6)</f>
-        <v>3.203449074</v>
+        <v>2.226030093</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -804,7 +1058,7 @@
         <v>1.634814815</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -827,13 +1081,13 @@
         <f t="shared" ref="H8:H9" si="1">SUM(B8:G8)</f>
         <v>0.9558912037</v>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="12">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="9">
         <v>0.06805555555555555</v>
       </c>
       <c r="C9" s="14">
@@ -841,7 +1095,7 @@
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="13">
+      <c r="F9" s="9">
         <v>0.2222222222222222</v>
       </c>
       <c r="G9" s="6">
@@ -852,47 +1106,47 @@
         <v>1.189918981</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="16">
         <f t="shared" ref="B10:C10" si="2">SUM(B2:B9)</f>
-        <v>2.769293981</v>
-      </c>
-      <c r="C10" s="5">
+        <v>2.610347222</v>
+      </c>
+      <c r="C10" s="16">
         <f t="shared" si="2"/>
         <v>3.172037037</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="16">
         <f t="shared" ref="D10:E10" si="3">SUM(D2:D7)</f>
         <v>1.458287037</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="16">
         <f t="shared" si="3"/>
         <v>0.5231481481</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="16">
         <f t="shared" ref="F10:G10" si="4">SUM(F2:F9)</f>
-        <v>1.058842593</v>
-      </c>
-      <c r="G10" s="5">
+        <v>1.637789352</v>
+      </c>
+      <c r="G10" s="16">
         <f t="shared" si="4"/>
-        <v>2.649641204</v>
-      </c>
-      <c r="H10" s="5">
+        <v>0.5323958333</v>
+      </c>
+      <c r="H10" s="16">
         <f>SUM(Total!$B10:$G10)</f>
-        <v>11.63125</v>
-      </c>
-      <c r="I10" s="9"/>
+        <v>9.93400463</v>
+      </c>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="H13" s="15"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" ht="14.25" customHeight="1"/>
     <row r="15" ht="14.25" customHeight="1"/>
@@ -1901,1382 +2155,2803 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="10.63"/>
-    <col customWidth="1" min="3" max="3" width="39.5"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="6" width="27.63"/>
-    <col customWidth="1" min="7" max="7" width="20.0"/>
-    <col customWidth="1" min="8" max="26" width="10.63"/>
+    <col customWidth="1" min="1" max="1" width="41.0"/>
+    <col customWidth="1" min="2" max="2" width="24.88"/>
+    <col customWidth="1" min="3" max="3" width="30.38"/>
+    <col customWidth="1" min="4" max="4" width="39.5"/>
+    <col customWidth="1" min="5" max="5" width="27.63"/>
+    <col customWidth="1" min="6" max="6" width="17.75"/>
+    <col customWidth="1" min="7" max="8" width="27.63"/>
+    <col customWidth="1" min="9" max="9" width="35.88"/>
+    <col customWidth="1" min="10" max="10" width="27.63"/>
+    <col customWidth="1" min="11" max="11" width="31.75"/>
+    <col customWidth="1" min="12" max="12" width="20.0"/>
+    <col customWidth="1" min="13" max="31" width="10.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="19"/>
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="I1" s="23"/>
+      <c r="J1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="K1" s="24"/>
+      <c r="L1" s="22" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="28"/>
+      <c r="G2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="28"/>
+      <c r="I2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="28"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.05783564814814815</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.03487268518518519</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.07708333333333334</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.06111111111111111</v>
+      </c>
+      <c r="K4" s="31"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.04273148148148148</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.019791666666666666</v>
+      </c>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.002939814814814815</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.039780092592592596</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.06607638888888889</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0.0798611111111111</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.06518518518518518</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="14">
+        <v>0.03515046296296296</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.0798611111111111</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.06607638888888889</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.019791666666666666</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0.05783564814814815</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.039780092592592596</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.028356481481481483</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.013148148148148148</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="7">
+        <v>0.07708333333333334</v>
+      </c>
+      <c r="C14" s="34"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="20">
-        <v>0.05783564814814815</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="20">
-        <v>0.07708333333333334</v>
-      </c>
-      <c r="G3" s="21"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="20">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="20">
-        <v>0.06111111111111111</v>
-      </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="16"/>
-      <c r="B5" s="20">
-        <v>0.04273148148148148</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="20">
-        <v>0.002939814814814815</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="16"/>
-      <c r="B7" s="20">
-        <v>0.06607638888888889</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="20">
-        <v>0.06518518518518518</v>
-      </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" s="20">
-        <v>0.0798611111111111</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20">
-        <v>0.019791666666666666</v>
-      </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="20">
-        <v>0.039780092592592596</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="20">
-        <v>0.028356481481481483</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="20">
-        <v>0.013148148148148148</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="22">
-        <v>0.03515046296296296</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="24">
+      <c r="B15" s="36">
         <f>SUM(B3:B14)</f>
-        <v>0.4509722222</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26">
+        <v>0.4929050926</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="37">
         <f>SUM(F3:F14)</f>
-        <v>0.1381944444</v>
-      </c>
-      <c r="G15" s="25"/>
+        <v>0.03487268519</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="37">
+        <f>SUM(J3:J14)</f>
+        <v>0.4366898148</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="37">
+        <f>SUM(L3:L14)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="27"/>
+      <c r="H16" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I16" s="27"/>
+      <c r="J16" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="27"/>
+      <c r="L16" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" s="20">
+      <c r="B17" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="20">
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="7">
         <v>0.08034722222222222</v>
       </c>
-      <c r="E17" s="20">
+      <c r="G18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="20">
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="20">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="7">
         <v>0.18194444444444444</v>
       </c>
-      <c r="E18" s="20">
+      <c r="G19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="7">
         <v>0.003414351851851852</v>
       </c>
-      <c r="F18" s="20">
+      <c r="I19" s="7"/>
+      <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="G18" s="20">
+      <c r="K19" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="7">
         <v>0.03150462962962963</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="20">
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="20">
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="F19" s="20">
+      <c r="I20" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="G19" s="20">
+      <c r="K20" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="7">
         <v>1.273148148148148E-4</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="20">
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="20">
-        <v>0.01892361111111111</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="16"/>
-      <c r="B21" s="20">
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="20">
-        <v>0.04101851851851852</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="20">
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="20">
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+    </row>
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="20">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" s="20">
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+    </row>
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="20">
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+    </row>
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="16"/>
-      <c r="B27" s="20">
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+    </row>
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="16"/>
-      <c r="B28" s="20">
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="16"/>
-      <c r="B29" s="20">
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="16"/>
-      <c r="B30" s="20">
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="16"/>
-      <c r="B31" s="20">
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" s="20">
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="16"/>
-      <c r="B33" s="20">
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="16"/>
-      <c r="B34" s="20">
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="16"/>
-      <c r="B35" s="20">
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="26">
-        <f>SUM(B17:B35)</f>
-        <v>0.3871064815</v>
-      </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="28">
-        <f>SUM(D16:D35)</f>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="A37" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.017175925925925924</v>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="A38" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="37">
+        <f>SUM(B18:B37)</f>
+        <v>0.4042824074</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41">
+        <f>SUM(F17:F36)</f>
         <v>0.2622916667</v>
       </c>
-      <c r="E36" s="26">
-        <f t="shared" ref="E36:G36" si="1">SUM(E17:E35)</f>
+      <c r="G38" s="3"/>
+      <c r="H38" s="37">
+        <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="F36" s="28">
-        <f t="shared" si="1"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41">
+        <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="G36" s="28">
-        <f t="shared" si="1"/>
-        <v>0.09157407407</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="16"/>
-      <c r="B37" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="16"/>
-      <c r="B38" s="20">
+      <c r="K38" s="41"/>
+      <c r="L38" s="41">
+        <f>SUM(L18:L36)</f>
+        <v>0.03163194444</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1">
+      <c r="A39" s="25"/>
+      <c r="B39" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="27"/>
+      <c r="D39" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="27"/>
+      <c r="F39" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="27"/>
+      <c r="H39" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I39" s="27"/>
+      <c r="J39" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K39" s="27"/>
+      <c r="L39" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="A40" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="28"/>
+      <c r="I40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="28"/>
+      <c r="K40" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="28"/>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="A41" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="29">
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5">
         <v>0.19166666666666668</v>
       </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="20">
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="7">
         <v>0.0575462962962963</v>
       </c>
-      <c r="G38" s="20">
+      <c r="K41" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="7">
         <v>0.016446759259259258</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="16"/>
-      <c r="B39" s="20">
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="A42" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="20">
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="7">
         <v>0.019178240740740742</v>
       </c>
-      <c r="G39" s="20">
+      <c r="K42" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L42" s="7">
         <v>0.10934027777777777</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="16"/>
-      <c r="B40" s="20">
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="20">
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="7">
         <v>0.01525462962962963</v>
       </c>
-      <c r="G40" s="20">
+      <c r="K43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="7">
         <v>0.03608796296296296</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="16"/>
-      <c r="B41" s="20">
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="20">
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="G41" s="21"/>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="16"/>
-      <c r="B42" s="20">
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="20">
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="G42" s="21"/>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="16"/>
-      <c r="B43" s="20">
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="20">
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="G43" s="21"/>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="16"/>
-      <c r="B44" s="20">
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="20">
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="G44" s="21"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="16"/>
-      <c r="B45" s="20">
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="A48" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="20">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="G45" s="21"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="16"/>
-      <c r="B46" s="20">
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="A49" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="20">
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="G46" s="21"/>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="16"/>
-      <c r="B47" s="20">
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="A50" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="20">
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="G47" s="21"/>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="16"/>
-      <c r="B48" s="20">
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
+      <c r="A51" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="20">
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="G48" s="21"/>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="16"/>
-      <c r="B49" s="20">
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
+      <c r="A52" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="16"/>
-      <c r="B50" s="20">
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+    </row>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="45"/>
+    </row>
+    <row r="54" ht="14.25" customHeight="1">
+      <c r="A54" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="16"/>
-      <c r="B51" s="20">
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+    </row>
+    <row r="55" ht="14.25" customHeight="1">
+      <c r="A55" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="16"/>
-      <c r="B52" s="20">
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+    </row>
+    <row r="56" ht="14.25" customHeight="1">
+      <c r="A56" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="16"/>
-      <c r="B53" s="20">
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+    </row>
+    <row r="57" ht="14.25" customHeight="1">
+      <c r="A57" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="16"/>
-      <c r="B54" s="20">
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+    </row>
+    <row r="58" ht="14.25" customHeight="1">
+      <c r="A58" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="30">
-        <f>SUM(B38:B54)</f>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+    </row>
+    <row r="59" ht="14.25" customHeight="1">
+      <c r="A59" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="37">
+        <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
-      <c r="C55" s="31"/>
-      <c r="D55" s="32">
-        <f>SUM(D38:D54)</f>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="41">
+        <f>SUM(F41:F58)</f>
         <v>0.1916666667</v>
       </c>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="16"/>
-      <c r="B56" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="16"/>
-      <c r="B57" s="20">
+      <c r="G59" s="3"/>
+      <c r="H59" s="3">
+        <f>SUM(H41:H51)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="37">
+        <f>SUM(J41:J58)</f>
+        <v>0.218587963</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="37">
+        <f>SUM(L41:L58)</f>
+        <v>0.161875</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customHeight="1">
+      <c r="A60" s="25"/>
+      <c r="B60" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="27"/>
+      <c r="D60" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="27"/>
+      <c r="F60" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="27"/>
+      <c r="H60" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="27"/>
+      <c r="J60" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="27"/>
+      <c r="L60" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1">
+      <c r="A61" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="28"/>
+      <c r="E61" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="28"/>
+      <c r="G61" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="28"/>
+      <c r="I61" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="28"/>
+      <c r="K61" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" s="28"/>
+    </row>
+    <row r="62" ht="14.25" customHeight="1">
+      <c r="A62" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" s="7">
         <v>0.0028703703703703703</v>
       </c>
-      <c r="C57" s="20">
+      <c r="C62" s="7"/>
+      <c r="D62" s="7">
         <v>0.024421296296296295</v>
       </c>
-      <c r="D57" s="20">
+      <c r="E62" s="7"/>
+      <c r="F62" s="7">
         <v>0.09237268518518518</v>
       </c>
-      <c r="E57" s="20">
+      <c r="G62" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="7">
         <v>0.16012731481481482</v>
       </c>
-      <c r="F57" s="20">
+      <c r="I62" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="G57" s="21"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="16"/>
-      <c r="B58" s="20">
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+    </row>
+    <row r="63" ht="14.25" customHeight="1">
+      <c r="A63" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="20">
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="7">
         <v>0.017881944444444443</v>
       </c>
-      <c r="F58" s="20">
+      <c r="I63" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="G58" s="21"/>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="16"/>
-      <c r="B59" s="20">
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+    </row>
+    <row r="64" ht="14.25" customHeight="1">
+      <c r="A64" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="16"/>
-      <c r="B60" s="20">
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="J64" s="7">
+        <v>0.06239583333333333</v>
+      </c>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+    </row>
+    <row r="65" ht="14.25" customHeight="1">
+      <c r="A65" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="16"/>
-      <c r="B61" s="20">
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+    </row>
+    <row r="66" ht="14.25" customHeight="1">
+      <c r="A66" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="16"/>
-      <c r="B62" s="20">
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+    </row>
+    <row r="67" ht="14.25" customHeight="1">
+      <c r="A67" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="16"/>
-      <c r="B63" s="20">
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+    </row>
+    <row r="68" ht="14.25" customHeight="1">
+      <c r="A68" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="16"/>
-      <c r="B64" s="20">
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+    </row>
+    <row r="69" ht="14.25" customHeight="1">
+      <c r="A69" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="16"/>
-      <c r="B65" s="20">
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+    </row>
+    <row r="70" ht="14.25" customHeight="1">
+      <c r="A70" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="16"/>
-      <c r="B66" s="20">
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+    </row>
+    <row r="71" ht="14.25" customHeight="1">
+      <c r="A71" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="16"/>
-      <c r="B67" s="20">
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+    </row>
+    <row r="72" ht="14.25" customHeight="1">
+      <c r="A72" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-    </row>
-    <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="16"/>
-      <c r="B68" s="20">
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
+    </row>
+    <row r="73" ht="14.25" customHeight="1">
+      <c r="A73" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="16"/>
-      <c r="B69" s="20">
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
+    </row>
+    <row r="74" ht="14.25" customHeight="1">
+      <c r="A74" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B70" s="25"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="16"/>
-      <c r="B71" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="16"/>
-      <c r="B72" s="20">
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
+    </row>
+    <row r="75" ht="14.25" customHeight="1">
+      <c r="A75" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="37">
+        <f>SUM(B62:B74)</f>
+        <v>0.6286805556</v>
+      </c>
+      <c r="C75" s="46"/>
+      <c r="D75" s="36">
+        <f>SUM(D62:D74)</f>
+        <v>0.0244212963</v>
+      </c>
+      <c r="E75" s="47"/>
+      <c r="F75" s="37">
+        <f>SUM(F62:F74)</f>
+        <v>0.09237268519</v>
+      </c>
+      <c r="G75" s="47"/>
+      <c r="H75" s="37">
+        <f>SUM(H62:H74)</f>
+        <v>0.1780092593</v>
+      </c>
+      <c r="I75" s="47"/>
+      <c r="J75" s="37">
+        <f>SUM(J62:J74)</f>
+        <v>0.2304861111</v>
+      </c>
+      <c r="K75" s="47"/>
+      <c r="L75" s="47"/>
+    </row>
+    <row r="76" ht="14.25" customHeight="1">
+      <c r="A76" s="25"/>
+      <c r="B76" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="27"/>
+      <c r="D76" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="27"/>
+      <c r="F76" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="27"/>
+      <c r="H76" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="27"/>
+      <c r="J76" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="27"/>
+      <c r="L76" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" ht="14.25" customHeight="1">
+      <c r="A77" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="28"/>
+      <c r="E77" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="28"/>
+      <c r="G77" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="28"/>
+      <c r="I77" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" s="28"/>
+      <c r="K77" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" s="28"/>
+    </row>
+    <row r="78" ht="14.25" customHeight="1">
+      <c r="A78" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="7">
+        <v>0.125</v>
+      </c>
+      <c r="C78" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D78" s="49">
+        <v>0.11513888888888889</v>
+      </c>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="I78" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J78" s="7">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="9">
+        <v>0.03333333333333333</v>
+      </c>
+    </row>
+    <row r="79" ht="14.25" customHeight="1">
+      <c r="A79" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79" s="7">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="C79" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="49">
+        <v>0.5638888888888889</v>
+      </c>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J79" s="51">
+        <v>0.09305555555555556</v>
+      </c>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+    </row>
+    <row r="80" ht="14.25" customHeight="1">
+      <c r="A80" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="52">
+        <v>0.0625</v>
+      </c>
+      <c r="C80" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D80" s="53">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J80" s="14">
         <v>0.041666666666666664</v>
       </c>
-      <c r="C72" s="22">
-        <v>0.11513888888888889</v>
-      </c>
-      <c r="D72" s="35"/>
-      <c r="E72" s="22">
-        <v>0.013888888888888888</v>
-      </c>
-      <c r="F72" s="35"/>
-      <c r="G72" s="20">
-        <v>0.024305555555555556</v>
-      </c>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="16"/>
-      <c r="B73" s="20">
+      <c r="K80" s="50"/>
+      <c r="L80" s="50"/>
+    </row>
+    <row r="81" ht="14.25" customHeight="1">
+      <c r="A81" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="54">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C73" s="22">
-        <v>0.5638888888888889</v>
-      </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="20">
-        <v>0.9864467592592593</v>
-      </c>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="16"/>
-      <c r="B74" s="20">
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="49"/>
+      <c r="L81" s="49"/>
+    </row>
+    <row r="82" ht="14.25" customHeight="1">
+      <c r="A82" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B82" s="9">
+        <v>0.05763888888888889</v>
+      </c>
+      <c r="C82" s="49"/>
+      <c r="D82" s="49"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
+    </row>
+    <row r="83" ht="14.25" customHeight="1">
+      <c r="A83" s="55"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49">
+        <v>0.32806712962962964</v>
+      </c>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="50"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="50"/>
+      <c r="L83" s="50"/>
+    </row>
+    <row r="84" ht="14.25" customHeight="1">
+      <c r="A84" s="55"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="50"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="50"/>
+      <c r="L84" s="50"/>
+    </row>
+    <row r="85" ht="14.25" customHeight="1">
+      <c r="A85" s="55"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="56"/>
+      <c r="L85" s="56"/>
+    </row>
+    <row r="86" ht="14.25" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="57">
+        <f>SUM(B78:B85)</f>
+        <v>0.3979166667</v>
+      </c>
+      <c r="C86" s="58"/>
+      <c r="D86" s="58">
+        <f>SUM(D78:D83)</f>
+        <v>1.201539352</v>
+      </c>
+      <c r="E86" s="46"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="46"/>
+      <c r="H86" s="59">
+        <f>SUM(H78:H85)</f>
+        <v>0.01388888889</v>
+      </c>
+      <c r="I86" s="46"/>
+      <c r="J86" s="59">
+        <f>SUM(J78:J85)</f>
+        <v>0.2180555556</v>
+      </c>
+      <c r="K86" s="57"/>
+      <c r="L86" s="57">
+        <f>SUM(L78:L80)</f>
+        <v>0.03333333333</v>
+      </c>
+    </row>
+    <row r="87" ht="14.25" customHeight="1">
+      <c r="A87" s="25"/>
+      <c r="B87" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="27"/>
+      <c r="D87" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="27"/>
+      <c r="F87" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G87" s="27"/>
+      <c r="H87" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I87" s="27"/>
+      <c r="J87" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K87" s="27"/>
+      <c r="L87" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="28"/>
+      <c r="E88" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="28"/>
+      <c r="G88" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="28"/>
+      <c r="I88" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="28"/>
+      <c r="K88" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L88" s="28"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="A89" s="55"/>
+      <c r="B89" s="7">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="C89" s="49"/>
+      <c r="D89" s="14">
+        <v>0.17631944444444445</v>
+      </c>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7">
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7">
+        <v>0.10641203703703704</v>
+      </c>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7">
         <v>0.125</v>
       </c>
-      <c r="C74" s="22">
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="55"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="16"/>
-      <c r="B75" s="20">
-        <v>0.06944444444444445</v>
-      </c>
-      <c r="C75" s="22">
-        <v>0.19444444444444445</v>
-      </c>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="22"/>
-    </row>
-    <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="16"/>
-      <c r="B76" s="20">
-        <v>0.09305555555555556</v>
-      </c>
-      <c r="C76" s="22"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="16"/>
-      <c r="B77" s="20">
+      <c r="E90" s="7"/>
+      <c r="F90" s="7">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="G90" s="7"/>
+      <c r="H90" s="7">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7">
         <v>0.0625</v>
       </c>
-      <c r="C77" s="22">
-        <v>0.32806712962962964</v>
-      </c>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-    </row>
-    <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="16"/>
-      <c r="B78" s="20">
-        <v>0.05763888888888889</v>
-      </c>
-      <c r="C78" s="22"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-    </row>
-    <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="16"/>
-      <c r="B79" s="20">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="C79" s="36"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="36"/>
-    </row>
-    <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="28">
-        <f>SUM(B72:B79)</f>
-        <v>0.6159722222</v>
-      </c>
-      <c r="C80" s="37">
-        <f>SUM(C72:C77)</f>
-        <v>1.368206019</v>
-      </c>
-      <c r="D80" s="33"/>
-      <c r="E80" s="24">
-        <f>SUM(E72:E79)</f>
-        <v>0.01388888889</v>
-      </c>
-      <c r="F80" s="33"/>
-      <c r="G80" s="28">
-        <f>SUM(G72:G74)</f>
-        <v>1.010752315</v>
-      </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="16"/>
-      <c r="B81" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="34"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="16"/>
-      <c r="B82" s="20">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="C82" s="22">
-        <v>0.17631944444444445</v>
-      </c>
-      <c r="D82" s="20">
-        <v>0.39791666666666664</v>
-      </c>
-      <c r="E82" s="20">
-        <v>0.10641203703703704</v>
-      </c>
-      <c r="F82" s="20">
-        <v>0.003472222222222222</v>
-      </c>
-      <c r="G82" s="20">
+    </row>
+    <row r="91" ht="14.25" customHeight="1">
+      <c r="A91" s="55"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="50"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7">
         <v>0.125</v>
       </c>
-    </row>
-    <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="16"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="20">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="E83" s="20">
-        <v>0.13541666666666666</v>
-      </c>
-      <c r="F83" s="21"/>
-      <c r="G83" s="20">
+      <c r="G91" s="7"/>
+      <c r="H91" s="7">
+        <v>0.06527777777777778</v>
+      </c>
+      <c r="I91" s="30"/>
+      <c r="J91" s="30"/>
+      <c r="K91" s="30"/>
+      <c r="L91" s="30"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="55"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="50"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="30"/>
+      <c r="K92" s="30"/>
+      <c r="L92" s="30"/>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="57">
+        <f>SUM(B89)</f>
+        <v>0.08333333333</v>
+      </c>
+      <c r="C93" s="58"/>
+      <c r="D93" s="58">
+        <f>SUM(D89)</f>
+        <v>0.1763194444</v>
+      </c>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57">
+        <f>SUM(F89:F91)</f>
+        <v>0.8770833333</v>
+      </c>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57">
+        <f>SUM(H89:H91)</f>
+        <v>0.3071064815</v>
+      </c>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57">
+        <f>SUM(J89)</f>
+        <v>0.003472222222</v>
+      </c>
+      <c r="K93" s="57"/>
+      <c r="L93" s="57">
+        <f>SUM(L89:L90)</f>
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c r="A94" s="25"/>
+      <c r="B94" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="27"/>
+      <c r="F94" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="27"/>
+      <c r="H94" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="27"/>
+      <c r="J94" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="27"/>
+      <c r="L94" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="30"/>
+      <c r="E95" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="30"/>
+      <c r="G95" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="30"/>
+      <c r="I95" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" s="30"/>
+      <c r="K95" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" s="30"/>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
+      <c r="A96" s="55"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="K96" s="30"/>
+      <c r="L96" s="30"/>
+    </row>
+    <row r="97" ht="14.25" customHeight="1">
+      <c r="A97" s="55"/>
+      <c r="B97" s="9">
+        <v>0.04722222222222222</v>
+      </c>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51">
+        <v>0.03420138888888889</v>
+      </c>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9">
+        <v>0.06859953703703704</v>
+      </c>
+      <c r="K97" s="30"/>
+      <c r="L97" s="30"/>
+    </row>
+    <row r="98" ht="14.25" customHeight="1">
+      <c r="A98" s="55"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="14"/>
+      <c r="D98" s="14">
+        <v>0.03017361111111111</v>
+      </c>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6">
+        <v>0.1909722222222222</v>
+      </c>
+      <c r="K98" s="30"/>
+      <c r="L98" s="30"/>
+    </row>
+    <row r="99" ht="14.25" customHeight="1">
+      <c r="A99" s="55"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14">
         <v>0.0625</v>
       </c>
-    </row>
-    <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="16"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="20">
-        <v>0.125</v>
-      </c>
-      <c r="E84" s="20">
-        <v>0.06527777777777778</v>
-      </c>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-    </row>
-    <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="16"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="35"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-    </row>
-    <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="28">
-        <f t="shared" ref="B86:C86" si="2">SUM(B82)</f>
-        <v>0.08333333333</v>
-      </c>
-      <c r="C86" s="37">
-        <f t="shared" si="2"/>
-        <v>0.1763194444</v>
-      </c>
-      <c r="D86" s="28">
-        <f t="shared" ref="D86:E86" si="3">SUM(D82:D84)</f>
-        <v>0.8770833333</v>
-      </c>
-      <c r="E86" s="28">
-        <f t="shared" si="3"/>
-        <v>0.3071064815</v>
-      </c>
-      <c r="F86" s="28">
-        <f>SUM(F82)</f>
-        <v>0.003472222222</v>
-      </c>
-      <c r="G86" s="28">
-        <f>SUM(G82:G83)</f>
-        <v>0.1875</v>
-      </c>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="16"/>
-      <c r="B87" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C87" s="34"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="16"/>
-      <c r="B88" s="39"/>
-      <c r="C88" s="40">
-        <v>0.5</v>
-      </c>
-      <c r="D88" s="21"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="39">
-        <v>0.022222222222222223</v>
-      </c>
-      <c r="G88" s="21"/>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="16"/>
-      <c r="B89" s="39">
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="30"/>
+      <c r="K99" s="30"/>
+      <c r="L99" s="30"/>
+    </row>
+    <row r="100" ht="14.25" customHeight="1">
+      <c r="A100" s="29"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="30"/>
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
+    </row>
+    <row r="101" ht="14.25" customHeight="1">
+      <c r="A101" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" s="63">
+        <f>SUM(B96:B100)</f>
+        <v>0.04722222222</v>
+      </c>
+      <c r="C101" s="46"/>
+      <c r="D101" s="59">
+        <f>SUM(D96:D100)</f>
+        <v>0.626875</v>
+      </c>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
+      <c r="J101" s="63">
+        <f>SUM(J96:J100)</f>
+        <v>0.2817939815</v>
+      </c>
+      <c r="K101" s="47"/>
+      <c r="L101" s="47"/>
+    </row>
+    <row r="102" ht="14.25" customHeight="1">
+      <c r="A102" s="25"/>
+      <c r="B102" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" s="27"/>
+      <c r="D102" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E102" s="27"/>
+      <c r="F102" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="27"/>
+      <c r="H102" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="27"/>
+      <c r="J102" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="27"/>
+      <c r="L102" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25" customHeight="1">
+      <c r="A103" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C103" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" s="30"/>
+      <c r="E103" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="30"/>
+      <c r="G103" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="30"/>
+      <c r="I103" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="30"/>
+      <c r="K103" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L103" s="30"/>
+    </row>
+    <row r="104" ht="14.25" customHeight="1">
+      <c r="A104" s="55"/>
+      <c r="B104" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C89" s="41">
+      <c r="C104" s="51"/>
+      <c r="D104" s="51">
         <v>0.03420138888888889</v>
       </c>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="39">
-        <v>0.06859953703703704</v>
-      </c>
-      <c r="G89" s="21"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="16"/>
-      <c r="B90" s="39"/>
-      <c r="C90" s="40">
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="51"/>
+      <c r="J104" s="51">
+        <v>0.1909722222222222</v>
+      </c>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9">
+        <v>0.0763888888888889</v>
+      </c>
+    </row>
+    <row r="105" ht="14.25" customHeight="1">
+      <c r="A105" s="55"/>
+      <c r="B105" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14">
         <v>0.03017361111111111</v>
       </c>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="42">
-        <v>0.1909722222222222</v>
-      </c>
-      <c r="G90" s="21"/>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="16"/>
-      <c r="B91" s="39"/>
-      <c r="C91" s="40">
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" customHeight="1">
+      <c r="A106" s="55"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14">
         <v>0.0625</v>
       </c>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21"/>
-      <c r="G91" s="21"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="43"/>
-      <c r="B92" s="39"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B93" s="26">
-        <f t="shared" ref="B93:C93" si="4">SUM(B88:B92)</f>
-        <v>0.04722222222</v>
-      </c>
-      <c r="C93" s="24">
-        <f t="shared" si="4"/>
-        <v>0.626875</v>
-      </c>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="26">
-        <f>SUM(F88:F92)</f>
-        <v>0.2817939815</v>
-      </c>
-      <c r="G93" s="25"/>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="16"/>
-      <c r="B94" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" s="34"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="19"/>
-      <c r="G94" s="19"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="16"/>
-      <c r="B95" s="42">
-        <v>0.04722222222222222</v>
-      </c>
-      <c r="C95" s="41">
-        <v>0.03420138888888889</v>
-      </c>
-      <c r="D95" s="21"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="41">
-        <v>0.1909722222222222</v>
-      </c>
-      <c r="G95" s="39">
-        <v>0.0763888888888889</v>
-      </c>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="16"/>
-      <c r="B96" s="39">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="C96" s="40">
-        <v>0.03017361111111111</v>
-      </c>
-      <c r="D96" s="21"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="39">
-        <v>0.03125</v>
-      </c>
-      <c r="G96" s="39">
-        <v>0.041666666666666664</v>
-      </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="16"/>
-      <c r="B97" s="21"/>
-      <c r="C97" s="40">
-        <v>0.0625</v>
-      </c>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="21"/>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="16"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="40">
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
+      <c r="I106" s="30"/>
+      <c r="J106" s="30"/>
+      <c r="K106" s="30"/>
+      <c r="L106" s="30"/>
+    </row>
+    <row r="107" ht="14.25" customHeight="1">
+      <c r="A107" s="55"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14">
         <v>0.3076388888888889</v>
       </c>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="16"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="40">
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+      <c r="H107" s="30"/>
+      <c r="I107" s="30"/>
+      <c r="J107" s="30"/>
+      <c r="K107" s="30"/>
+      <c r="L107" s="30"/>
+    </row>
+    <row r="108" ht="14.25" customHeight="1">
+      <c r="A108" s="55"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14">
         <v>0.24097222222222223</v>
       </c>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="21"/>
-      <c r="G99" s="21"/>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="16"/>
-      <c r="B100" s="21"/>
-      <c r="C100" s="40">
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="30"/>
+      <c r="H108" s="30"/>
+      <c r="I108" s="30"/>
+      <c r="J108" s="30"/>
+      <c r="K108" s="30"/>
+      <c r="L108" s="30"/>
+    </row>
+    <row r="109" ht="14.25" customHeight="1">
+      <c r="A109" s="55"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14">
         <v>0.10609953703703703</v>
       </c>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21"/>
-      <c r="G100" s="21"/>
-    </row>
-    <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="16"/>
-      <c r="B101" s="21"/>
-      <c r="C101" s="35"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-    </row>
-    <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="16"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-    </row>
-    <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B103" s="28">
-        <f t="shared" ref="B103:C103" si="5">SUM(B95:B102)</f>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
+      <c r="I109" s="30"/>
+      <c r="J109" s="30"/>
+      <c r="K109" s="30"/>
+      <c r="L109" s="30"/>
+    </row>
+    <row r="110" ht="14.25" customHeight="1">
+      <c r="A110" s="55"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="50"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+      <c r="H110" s="30"/>
+      <c r="I110" s="30"/>
+      <c r="J110" s="30"/>
+      <c r="K110" s="30"/>
+      <c r="L110" s="30"/>
+    </row>
+    <row r="111" ht="14.25" customHeight="1">
+      <c r="A111" s="55"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="50"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
+      <c r="I111" s="30"/>
+      <c r="J111" s="30"/>
+      <c r="K111" s="30"/>
+      <c r="L111" s="30"/>
+    </row>
+    <row r="112" ht="14.25" customHeight="1">
+      <c r="A112" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" s="57">
+        <f>SUM(B104:B111)</f>
         <v>0.06805555556</v>
       </c>
-      <c r="C103" s="37">
-        <f t="shared" si="5"/>
+      <c r="C112" s="46"/>
+      <c r="D112" s="58">
+        <f>SUM(D104:D111)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="28">
-        <f t="shared" ref="F103:G103" si="6">SUM(F95:F102)</f>
+      <c r="E112" s="47"/>
+      <c r="F112" s="47"/>
+      <c r="G112" s="47"/>
+      <c r="H112" s="47"/>
+      <c r="I112" s="47"/>
+      <c r="J112" s="57">
+        <f>SUM(J104:J111)</f>
         <v>0.2222222222</v>
       </c>
-      <c r="G103" s="26">
-        <f t="shared" si="6"/>
+      <c r="K112" s="47"/>
+      <c r="L112" s="63">
+        <f>SUM(L104:L111)</f>
         <v>0.1180555556</v>
       </c>
     </row>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1">
+      <c r="A113" s="25"/>
+      <c r="B113" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" s="27"/>
+      <c r="D113" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E113" s="27"/>
+      <c r="F113" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G113" s="27"/>
+      <c r="H113" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="I113" s="27"/>
+      <c r="J113" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K113" s="27"/>
+      <c r="L113" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25" customHeight="1">
+      <c r="A114" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="28"/>
+      <c r="E114" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="28"/>
+      <c r="G114" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="28"/>
+      <c r="I114" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="28"/>
+      <c r="K114" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L114" s="28"/>
+    </row>
+    <row r="115" ht="14.25" customHeight="1">
+      <c r="A115" s="19"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="19"/>
+      <c r="E115" s="19"/>
+      <c r="F115" s="19"/>
+      <c r="G115" s="19"/>
+      <c r="H115" s="19"/>
+      <c r="I115" s="19"/>
+      <c r="J115" s="19"/>
+      <c r="K115" s="19"/>
+      <c r="L115" s="19"/>
+    </row>
+    <row r="116" ht="14.25" customHeight="1">
+      <c r="A116" s="19"/>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19"/>
+      <c r="F116" s="19"/>
+      <c r="G116" s="19"/>
+      <c r="H116" s="19"/>
+      <c r="I116" s="19"/>
+      <c r="J116" s="19"/>
+      <c r="K116" s="19"/>
+      <c r="L116" s="19"/>
+    </row>
+    <row r="117" ht="14.25" customHeight="1">
+      <c r="A117" s="19"/>
+      <c r="B117" s="19"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="19"/>
+      <c r="G117" s="19"/>
+      <c r="H117" s="19"/>
+      <c r="I117" s="19"/>
+      <c r="J117" s="19"/>
+      <c r="K117" s="19"/>
+      <c r="L117" s="19"/>
+    </row>
+    <row r="118" ht="14.25" customHeight="1">
+      <c r="A118" s="19"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="19"/>
+      <c r="J118" s="19"/>
+      <c r="K118" s="19"/>
+      <c r="L118" s="19"/>
+    </row>
+    <row r="119" ht="14.25" customHeight="1">
+      <c r="A119" s="19"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="19"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="19"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="19"/>
+    </row>
+    <row r="120" ht="14.25" customHeight="1">
+      <c r="A120" s="19"/>
+      <c r="B120" s="19"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="19"/>
+      <c r="F120" s="19"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="19"/>
+      <c r="J120" s="19"/>
+      <c r="K120" s="19"/>
+      <c r="L120" s="19"/>
+    </row>
+    <row r="121" ht="14.25" customHeight="1">
+      <c r="A121" s="19"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="19"/>
+      <c r="E121" s="19"/>
+      <c r="F121" s="19"/>
+      <c r="G121" s="19"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="19"/>
+      <c r="J121" s="19"/>
+      <c r="K121" s="19"/>
+      <c r="L121" s="19"/>
+    </row>
+    <row r="122" ht="14.25" customHeight="1">
+      <c r="A122" s="19"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="19"/>
+      <c r="D122" s="19"/>
+      <c r="E122" s="19"/>
+      <c r="F122" s="19"/>
+      <c r="G122" s="19"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="19"/>
+      <c r="J122" s="19"/>
+      <c r="K122" s="19"/>
+      <c r="L122" s="19"/>
+    </row>
+    <row r="123" ht="14.25" customHeight="1">
+      <c r="A123" s="19"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="19"/>
+      <c r="D123" s="19"/>
+      <c r="E123" s="19"/>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19"/>
+      <c r="H123" s="19"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="19"/>
+      <c r="K123" s="19"/>
+      <c r="L123" s="19"/>
+    </row>
+    <row r="124" ht="14.25" customHeight="1">
+      <c r="A124" s="19"/>
+      <c r="B124" s="19"/>
+      <c r="C124" s="19"/>
+      <c r="D124" s="19"/>
+      <c r="E124" s="19"/>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="19"/>
+      <c r="K124" s="19"/>
+      <c r="L124" s="19"/>
+    </row>
+    <row r="125" ht="14.25" customHeight="1">
+      <c r="A125" s="19"/>
+      <c r="B125" s="19"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="19"/>
+      <c r="E125" s="19"/>
+      <c r="F125" s="19"/>
+      <c r="G125" s="19"/>
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="19"/>
+      <c r="K125" s="19"/>
+      <c r="L125" s="19"/>
+    </row>
+    <row r="126" ht="14.25" customHeight="1">
+      <c r="A126" s="19"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="19"/>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19"/>
+      <c r="K126" s="19"/>
+      <c r="L126" s="19"/>
+    </row>
+    <row r="127" ht="14.25" customHeight="1">
+      <c r="A127" s="19"/>
+      <c r="B127" s="19"/>
+      <c r="C127" s="19"/>
+      <c r="D127" s="19"/>
+      <c r="E127" s="19"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="19"/>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="19"/>
+      <c r="K127" s="19"/>
+      <c r="L127" s="19"/>
+    </row>
+    <row r="128" ht="14.25" customHeight="1">
+      <c r="A128" s="19"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="19"/>
+      <c r="K128" s="19"/>
+      <c r="L128" s="19"/>
+    </row>
+    <row r="129" ht="14.25" customHeight="1">
+      <c r="A129" s="19"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="19"/>
+      <c r="D129" s="19"/>
+      <c r="E129" s="19"/>
+      <c r="F129" s="19"/>
+      <c r="G129" s="19"/>
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="19"/>
+      <c r="K129" s="19"/>
+      <c r="L129" s="19"/>
+    </row>
+    <row r="130" ht="14.25" customHeight="1">
+      <c r="A130" s="19"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="19"/>
+      <c r="D130" s="19"/>
+      <c r="E130" s="19"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+      <c r="L130" s="19"/>
+    </row>
+    <row r="131" ht="14.25" customHeight="1">
+      <c r="A131" s="19"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="19"/>
+      <c r="D131" s="19"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+      <c r="L131" s="19"/>
+    </row>
+    <row r="132" ht="14.25" customHeight="1">
+      <c r="A132" s="19"/>
+      <c r="B132" s="19"/>
+      <c r="C132" s="19"/>
+      <c r="D132" s="19"/>
+      <c r="E132" s="19"/>
+      <c r="F132" s="19"/>
+      <c r="G132" s="19"/>
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="19"/>
+      <c r="K132" s="19"/>
+      <c r="L132" s="19"/>
+    </row>
+    <row r="133" ht="14.25" customHeight="1">
+      <c r="A133" s="19"/>
+      <c r="B133" s="19"/>
+      <c r="C133" s="19"/>
+      <c r="D133" s="19"/>
+      <c r="E133" s="19"/>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="19"/>
+      <c r="K133" s="19"/>
+      <c r="L133" s="19"/>
+    </row>
+    <row r="134" ht="14.25" customHeight="1">
+      <c r="A134" s="19"/>
+      <c r="B134" s="19"/>
+      <c r="C134" s="19"/>
+      <c r="D134" s="19"/>
+      <c r="E134" s="19"/>
+      <c r="F134" s="19"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="19"/>
+      <c r="K134" s="19"/>
+      <c r="L134" s="19"/>
+    </row>
+    <row r="135" ht="14.25" customHeight="1">
+      <c r="A135" s="19"/>
+      <c r="B135" s="19"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="19"/>
+      <c r="E135" s="19"/>
+      <c r="F135" s="19"/>
+      <c r="G135" s="19"/>
+      <c r="H135" s="19"/>
+      <c r="I135" s="19"/>
+      <c r="J135" s="19"/>
+      <c r="K135" s="19"/>
+      <c r="L135" s="19"/>
+    </row>
+    <row r="136" ht="14.25" customHeight="1">
+      <c r="A136" s="19"/>
+      <c r="B136" s="19"/>
+      <c r="C136" s="19"/>
+      <c r="D136" s="19"/>
+      <c r="E136" s="19"/>
+      <c r="F136" s="19"/>
+      <c r="G136" s="19"/>
+      <c r="H136" s="19"/>
+      <c r="I136" s="19"/>
+      <c r="J136" s="19"/>
+      <c r="K136" s="19"/>
+      <c r="L136" s="19"/>
+    </row>
     <row r="137" ht="14.25" customHeight="1"/>
     <row r="138" ht="14.25" customHeight="1"/>
     <row r="139" ht="14.25" customHeight="1"/>
@@ -4153,7 +5828,19 @@
     <row r="1010" ht="14.25" customHeight="1"/>
     <row r="1011" ht="14.25" customHeight="1"/>
     <row r="1012" ht="14.25" customHeight="1"/>
+    <row r="1013" ht="14.25" customHeight="1"/>
+    <row r="1014" ht="14.25" customHeight="1"/>
+    <row r="1015" ht="14.25" customHeight="1"/>
+    <row r="1016" ht="14.25" customHeight="1"/>
+    <row r="1017" ht="14.25" customHeight="1"/>
+    <row r="1018" ht="14.25" customHeight="1"/>
+    <row r="1019" ht="14.25" customHeight="1"/>
+    <row r="1020" ht="14.25" customHeight="1"/>
+    <row r="1021" ht="14.25" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A53:L53"/>
+  </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
@@ -4172,130 +5859,130 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>24</v>
+      <c r="C3" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="45">
+      <c r="B4" s="65">
         <v>1.0</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="66">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="66">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="45">
+      <c r="B5" s="65">
         <v>2.0</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="66">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="66">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="45">
+      <c r="B6" s="65">
         <v>3.0</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="66">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="66">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="45">
+      <c r="B7" s="65">
         <v>4.0</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="66">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="66">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="45">
+      <c r="B8" s="65">
         <v>5.0</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="66">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="66">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="45">
+      <c r="B9" s="65">
         <v>6.0</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="66">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="66">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="45">
+      <c r="B10" s="65">
         <v>7.0</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="66">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="67">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="45">
+      <c r="B11" s="65">
         <v>8.0</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="67">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="67">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="45">
+      <c r="B12" s="65">
         <v>9.0</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="67">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="67">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="45">
+      <c r="B13" s="65">
         <v>10.0</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="67">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="66">
         <v>45965.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="tPWFPHOyBKhfIXtBW1J3Bo/enSDTuC0nEN9xYB6V3lw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="OKNazMu+baFD34LkA3mPGAXypLuJqsk+3PIO95RjQ9c="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="82">
   <si>
     <t>Semana</t>
   </si>
@@ -53,12 +53,15 @@
     <t>Inicio /Etapa de Elaboración Iteración 1</t>
   </si>
   <si>
-    <t>Elaboración Iteración 2</t>
+    <t>Elaboración Iteración 1</t>
   </si>
   <si>
     <t>Elaboración-Iteración 2</t>
   </si>
   <si>
+    <t>Elaboración-Iteración 2 - Construcción iteración 1</t>
+  </si>
+  <si>
     <t>Construcción-Iteración 1</t>
   </si>
   <si>
@@ -179,10 +182,79 @@
     <t>Semana 6</t>
   </si>
   <si>
+    <t>Inicio de modelo de diseño</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementación UARGFlow Funcional </t>
+  </si>
+  <si>
+    <t>Plan de pruebas</t>
+  </si>
+  <si>
+    <t>Implementación UARGFlow Funcional (Video)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitación sobre el uso de lenguajes, tecnologías y herramientas a implementar. </t>
+  </si>
+  <si>
+    <t>Modelo de datoos (BD)</t>
+  </si>
+  <si>
+    <t>Revisión Técnica Formal: Plan de Pruebas</t>
+  </si>
+  <si>
+    <t>Modelo de datos (BD)</t>
+  </si>
+  <si>
+    <t>Realización de excel de registro de tiempos y gráficos</t>
+  </si>
+  <si>
     <t>Semana 7</t>
   </si>
   <si>
+    <t>Estimación</t>
+  </si>
+  <si>
+    <t>Prototipo final</t>
+  </si>
+  <si>
+    <t>Cierre Fase Elaboración - Iteración 2</t>
+  </si>
+  <si>
+    <t>Riesgos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo Arquitectonico </t>
+  </si>
+  <si>
+    <t>Plan de Iteración Fase Construcción Iteración 1</t>
+  </si>
+  <si>
+    <t>Modelo Arquitectónico</t>
+  </si>
+  <si>
     <t>Semana 8</t>
+  </si>
+  <si>
+    <t>Aplicando angular al CU 01</t>
+  </si>
+  <si>
+    <t>Diagrama de componentes</t>
+  </si>
+  <si>
+    <t>Creación y modificación de gráficos obligatorios</t>
+  </si>
+  <si>
+    <t>Priorización e Inicio del Diseño – 1° tanda Casos de Uso</t>
+  </si>
+  <si>
+    <t>Modificación de excel para gráfico de registro de tiempos</t>
+  </si>
+  <si>
+    <t>Modelo de Diseño (Clases y Componentes)</t>
+  </si>
+  <si>
+    <t>Mejora dashboard prototipo</t>
   </si>
   <si>
     <t>Semana 9</t>
@@ -403,9 +475,6 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="1" fillId="4" fontId="4" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -507,12 +576,14 @@
     <xf borderId="1" fillId="4" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -523,7 +594,12 @@
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -909,7 +985,7 @@
       </c>
       <c r="D3" s="5">
         <f>Registro!F38</f>
-        <v>0.2622916667</v>
+        <v>0.689375</v>
       </c>
       <c r="E3" s="9">
         <f>Registro!H38</f>
@@ -925,7 +1001,7 @@
       </c>
       <c r="H3" s="5">
         <f>SUM(Total!$B3:$G3)</f>
-        <v>0.7488310185</v>
+        <v>1.175914352</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>9</v>
@@ -945,7 +1021,7 @@
       </c>
       <c r="D4" s="5">
         <f>Registro!F59</f>
-        <v>0.1916666667</v>
+        <v>0.2333333333</v>
       </c>
       <c r="E4" s="5">
         <f>Registro!H59</f>
@@ -961,7 +1037,7 @@
       </c>
       <c r="H4" s="5">
         <f>SUM(Total!$B4:$G4)</f>
-        <v>1.060081019</v>
+        <v>1.101747685</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>10</v>
@@ -1036,26 +1112,32 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="11">
-        <v>0.08333333333333333</v>
+        <f>Registro!B93</f>
+        <v>0.08333333333</v>
       </c>
       <c r="C7" s="5">
-        <v>0.17631944444444445</v>
+        <f>Registro!D93</f>
+        <v>0.6710532407</v>
       </c>
       <c r="D7" s="5">
-        <v>0.8770833333333333</v>
+        <f>Registro!F93</f>
+        <v>0.8770833333</v>
       </c>
       <c r="E7" s="5">
-        <v>0.3071064814814815</v>
+        <f>Registro!H93</f>
+        <v>0.3071064815</v>
       </c>
       <c r="F7" s="7">
-        <v>0.003472222222222222</v>
+        <f>Registro!J93</f>
+        <v>0.003472222222</v>
       </c>
       <c r="G7" s="5">
-        <v>0.1875</v>
+        <f>Registro!L93</f>
+        <v>0.4239467593</v>
       </c>
       <c r="H7" s="5">
         <f>SUM(Total!$B7:$G7)</f>
-        <v>1.634814815</v>
+        <v>2.36599537</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>12</v>
@@ -1066,87 +1148,99 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="6">
-        <v>0.04722222222222222</v>
+        <f>Registro!B102</f>
+        <v>0.06805555556</v>
       </c>
       <c r="C8" s="6">
-        <v>0.626875</v>
+        <f>Registro!D102</f>
+        <v>0.8178472222</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="6">
-        <v>0.2817939814814815</v>
+        <f>Registro!J102</f>
+        <v>0.4086689815</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f t="shared" ref="H8:H9" si="1">SUM(B8:G8)</f>
-        <v>0.9558912037</v>
-      </c>
-      <c r="I8" s="13"/>
+        <v>1.294571759</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="12">
         <v>8.0</v>
       </c>
       <c r="B9" s="9">
-        <v>0.06805555555555555</v>
-      </c>
-      <c r="C9" s="14">
-        <v>0.7815856481481481</v>
-      </c>
-      <c r="D9" s="5"/>
+        <f>Registro!B113</f>
+        <v>0.2798611111</v>
+      </c>
+      <c r="C9" s="13">
+        <f>Registro!D113</f>
+        <v>0.7815856481</v>
+      </c>
+      <c r="D9" s="5">
+        <f>Registro!F113</f>
+        <v>0.2756944444</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="9">
-        <v>0.2222222222222222</v>
+        <f>Registro!J113</f>
+        <v>0.5817361111</v>
       </c>
       <c r="G9" s="6">
-        <v>0.11805555555555555</v>
+        <f>Registro!L113</f>
+        <v>0.3125</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="1"/>
-        <v>1.189918981</v>
+        <v>2.231377315</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="16">
-        <f t="shared" ref="B10:C10" si="2">SUM(B2:B9)</f>
-        <v>2.610347222</v>
-      </c>
-      <c r="C10" s="16">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="15">
+        <f t="shared" ref="B10:D10" si="2">SUM(B2:B9)</f>
+        <v>2.842986111</v>
+      </c>
+      <c r="C10" s="15">
         <f t="shared" si="2"/>
-        <v>3.172037037</v>
-      </c>
-      <c r="D10" s="16">
-        <f t="shared" ref="D10:E10" si="3">SUM(D2:D7)</f>
-        <v>1.458287037</v>
-      </c>
-      <c r="E10" s="16">
+        <v>3.857743056</v>
+      </c>
+      <c r="D10" s="15">
+        <f t="shared" si="2"/>
+        <v>2.202731481</v>
+      </c>
+      <c r="E10" s="15">
+        <f>SUM(E2:E7)</f>
+        <v>0.5231481481</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" ref="F10:G10" si="3">SUM(F2:F9)</f>
+        <v>2.124178241</v>
+      </c>
+      <c r="G10" s="15">
         <f t="shared" si="3"/>
-        <v>0.5231481481</v>
-      </c>
-      <c r="F10" s="16">
-        <f t="shared" ref="F10:G10" si="4">SUM(F2:F9)</f>
-        <v>1.637789352</v>
-      </c>
-      <c r="G10" s="16">
-        <f t="shared" si="4"/>
-        <v>0.5323958333</v>
-      </c>
-      <c r="H10" s="16">
+        <v>0.963287037</v>
+      </c>
+      <c r="H10" s="15">
         <f>SUM(Total!$B10:$G10)</f>
-        <v>9.93400463</v>
-      </c>
-      <c r="I10" s="17"/>
+        <v>12.51407407</v>
+      </c>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="H13" s="18"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" ht="14.25" customHeight="1"/>
     <row r="15" ht="14.25" customHeight="1"/>
@@ -2155,451 +2249,452 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="41.0"/>
+    <col customWidth="1" min="1" max="1" width="49.13"/>
     <col customWidth="1" min="2" max="2" width="24.88"/>
-    <col customWidth="1" min="3" max="3" width="30.38"/>
+    <col customWidth="1" min="3" max="3" width="39.38"/>
     <col customWidth="1" min="4" max="4" width="39.5"/>
     <col customWidth="1" min="5" max="5" width="27.63"/>
     <col customWidth="1" min="6" max="6" width="17.75"/>
-    <col customWidth="1" min="7" max="8" width="27.63"/>
-    <col customWidth="1" min="9" max="9" width="35.88"/>
+    <col customWidth="1" min="7" max="7" width="38.75"/>
+    <col customWidth="1" min="8" max="8" width="27.63"/>
+    <col customWidth="1" min="9" max="9" width="54.63"/>
     <col customWidth="1" min="10" max="10" width="27.63"/>
-    <col customWidth="1" min="11" max="11" width="31.75"/>
+    <col customWidth="1" min="11" max="11" width="71.63"/>
     <col customWidth="1" min="12" max="12" width="20.0"/>
     <col customWidth="1" min="13" max="31" width="10.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="20" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="22" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="22" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="24"/>
-      <c r="L1" s="22" t="s">
+      <c r="K1" s="23"/>
+      <c r="L1" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="28"/>
+      <c r="B2" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="27"/>
+      <c r="I2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="27"/>
+      <c r="K2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>17</v>
+      <c r="A3" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="B3" s="6">
         <v>0.05783564814814815</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
       <c r="E3" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="9">
         <v>0.03487268518518519</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
       <c r="I3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="K3" s="31"/>
+      <c r="K3" s="30"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>17</v>
+      <c r="A4" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="B4" s="5">
         <v>1.1574074074074075E-4</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
       <c r="I4" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="7">
         <v>0.06111111111111111</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="30"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="29" t="s">
-        <v>21</v>
+      <c r="A5" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B5" s="5">
         <v>0.04273148148148148</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
       <c r="I5" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="7">
         <v>0.019791666666666666</v>
       </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="29" t="s">
-        <v>21</v>
+      <c r="A6" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="5">
         <v>0.002939814814814815</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
       <c r="I6" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="7">
         <v>0.039780092592592596</v>
       </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="29" t="s">
-        <v>23</v>
+      <c r="A7" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="B7" s="5">
         <v>0.06607638888888889</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
       <c r="I7" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" s="9">
         <v>0.0798611111111111</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="29" t="s">
-        <v>25</v>
+      <c r="A8" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="B8" s="5">
         <v>0.06518518518518518</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="13">
         <v>0.03515046296296296</v>
       </c>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="29" t="s">
-        <v>24</v>
+      <c r="A9" s="28" t="s">
+        <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>0.0798611111111111</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
       <c r="I9" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="7">
         <v>0.06607638888888889</v>
       </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>22</v>
+      <c r="A10" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="B10" s="5">
         <v>0.019791666666666666</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
       <c r="I10" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" s="9">
         <v>0.05783564814814815</v>
       </c>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="33" t="s">
-        <v>22</v>
+      <c r="A11" s="32" t="s">
+        <v>23</v>
       </c>
       <c r="B11" s="5">
         <v>0.039780092592592596</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>27</v>
+      <c r="A12" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="B12" s="5">
         <v>0.028356481481481483</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>28</v>
+      <c r="A13" s="28" t="s">
+        <v>29</v>
       </c>
       <c r="B13" s="5">
         <v>0.013148148148148148</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="36">
+      <c r="A15" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="35">
         <f>SUM(B3:B14)</f>
         <v>0.4929050926</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="37">
+      <c r="F15" s="36">
         <f>SUM(F3:F14)</f>
         <v>0.03487268519</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="37">
+      <c r="J15" s="36">
         <f>SUM(J3:J14)</f>
         <v>0.4366898148</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="37">
+      <c r="L15" s="36">
         <f>SUM(L3:L14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="22" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="22" t="s">
+      <c r="E16" s="26"/>
+      <c r="F16" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="22" t="s">
+      <c r="G16" s="26"/>
+      <c r="H16" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="27"/>
-      <c r="J16" s="22" t="s">
+      <c r="I16" s="26"/>
+      <c r="J16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="27"/>
-      <c r="L16" s="22" t="s">
+      <c r="K16" s="26"/>
+      <c r="L16" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" s="28"/>
+      <c r="A17" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="27"/>
+      <c r="K17" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="27"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="29" t="s">
-        <v>17</v>
+      <c r="A18" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
       <c r="E18" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" s="7">
         <v>0.08034722222222222</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="29" t="s">
-        <v>21</v>
+      <c r="A19" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.6090277777777777</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="F19" s="7">
-        <v>0.18194444444444444</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="H19" s="7">
         <v>0.003414351851851852</v>
@@ -2608,828 +2703,828 @@
       <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="K19" s="39" t="s">
-        <v>34</v>
+      <c r="K19" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="L19" s="7">
         <v>0.03150462962962963</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>21</v>
+      <c r="A20" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
       <c r="G20" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="I20" s="40" t="s">
-        <v>35</v>
+      <c r="I20" s="39" t="s">
+        <v>36</v>
       </c>
       <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="K20" s="39" t="s">
-        <v>34</v>
+      <c r="K20" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="L20" s="7">
         <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>21</v>
+      <c r="A21" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>21</v>
+      <c r="A22" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>21</v>
+      <c r="A23" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>21</v>
+      <c r="A24" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>21</v>
+      <c r="A25" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>21</v>
+      <c r="A26" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>21</v>
+      <c r="A27" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>21</v>
+      <c r="A28" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>21</v>
+      <c r="A29" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>21</v>
+      <c r="A30" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>21</v>
+      <c r="A31" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>21</v>
+      <c r="A32" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>21</v>
+      <c r="A33" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>21</v>
+      <c r="A34" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>21</v>
+      <c r="A35" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>21</v>
+      <c r="A36" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>17</v>
+      <c r="A37" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="B37" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="37">
+      <c r="A38" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="36">
         <f>SUM(B18:B37)</f>
         <v>0.4042824074</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41">
+      <c r="E38" s="40"/>
+      <c r="F38" s="40">
         <f>SUM(F17:F36)</f>
-        <v>0.2622916667</v>
+        <v>0.689375</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="37">
+      <c r="H38" s="36">
         <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41">
+      <c r="I38" s="40"/>
+      <c r="J38" s="40">
         <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41">
+      <c r="K38" s="40"/>
+      <c r="L38" s="40">
         <f>SUM(L18:L36)</f>
         <v>0.03163194444</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="25"/>
-      <c r="B39" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="27"/>
-      <c r="D39" s="22" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="26"/>
+      <c r="D39" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="27"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="26"/>
+      <c r="F39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="27"/>
-      <c r="H39" s="22" t="s">
+      <c r="G39" s="26"/>
+      <c r="H39" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="27"/>
-      <c r="J39" s="22" t="s">
+      <c r="I39" s="26"/>
+      <c r="J39" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="27"/>
-      <c r="L39" s="22" t="s">
+      <c r="K39" s="26"/>
+      <c r="L39" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="28"/>
-      <c r="G40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="28"/>
-      <c r="I40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="28"/>
-      <c r="K40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" s="28"/>
+      <c r="A40" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="27"/>
+      <c r="E40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="27"/>
+      <c r="G40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="27"/>
+      <c r="I40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="27"/>
+      <c r="K40" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="27"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>21</v>
+      <c r="A41" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="5">
-        <v>0.19166666666666668</v>
-      </c>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
+      <c r="F41" s="6">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
       <c r="I41" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J41" s="7">
         <v>0.0575462962962963</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L41" s="7">
         <v>0.016446759259259258</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>21</v>
+      <c r="A42" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
       <c r="I42" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J42" s="7">
         <v>0.019178240740740742</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L42" s="7">
         <v>0.10934027777777777</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>21</v>
+      <c r="A43" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
       <c r="I43" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J43" s="7">
         <v>0.01525462962962963</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L43" s="7">
         <v>0.03608796296296296</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>21</v>
+      <c r="A44" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
       <c r="I44" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>21</v>
+      <c r="A45" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
       <c r="I45" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>21</v>
+      <c r="A46" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
       <c r="I46" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>21</v>
+      <c r="A47" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
       <c r="I47" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>21</v>
+      <c r="A48" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
       <c r="I48" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>21</v>
+      <c r="A49" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>21</v>
+      <c r="A50" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
       <c r="I50" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="K50" s="30"/>
-      <c r="L50" s="30"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>21</v>
+      <c r="A51" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
       <c r="I51" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>21</v>
+      <c r="A52" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="44"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="44"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="44"/>
-      <c r="L53" s="45"/>
+      <c r="A53" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="43"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="44"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>21</v>
+      <c r="A54" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>21</v>
+      <c r="A55" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>21</v>
+      <c r="A56" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
-      <c r="L56" s="30"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>21</v>
+      <c r="A57" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="30"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>21</v>
+      <c r="A58" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="37">
+      <c r="A59" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="36">
         <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="41">
+      <c r="F59" s="40">
         <f>SUM(F41:F58)</f>
-        <v>0.1916666667</v>
+        <v>0.2333333333</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3">
@@ -3437,73 +3532,73 @@
         <v>0</v>
       </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="37">
+      <c r="J59" s="36">
         <f>SUM(J41:J58)</f>
         <v>0.218587963</v>
       </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="37">
+      <c r="L59" s="36">
         <f>SUM(L41:L58)</f>
         <v>0.161875</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="25"/>
-      <c r="B60" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="22" t="s">
+      <c r="A60" s="24"/>
+      <c r="B60" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="27"/>
-      <c r="F60" s="22" t="s">
+      <c r="E60" s="26"/>
+      <c r="F60" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="27"/>
-      <c r="H60" s="22" t="s">
+      <c r="G60" s="26"/>
+      <c r="H60" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="27"/>
-      <c r="J60" s="22" t="s">
+      <c r="I60" s="26"/>
+      <c r="J60" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="27"/>
-      <c r="L60" s="22" t="s">
+      <c r="K60" s="26"/>
+      <c r="L60" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="28"/>
-      <c r="E61" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="28"/>
-      <c r="G61" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="28"/>
-      <c r="I61" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" s="28"/>
-      <c r="K61" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" s="28"/>
+      <c r="A61" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="27"/>
+      <c r="E61" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="27"/>
+      <c r="G61" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="27"/>
+      <c r="I61" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="27"/>
+      <c r="K61" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L61" s="27"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>21</v>
+      <c r="A62" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B62" s="7">
         <v>0.0028703703703703703</v>
@@ -3517,1442 +3612,1568 @@
         <v>0.09237268518518518</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H62" s="7">
         <v>0.16012731481481482</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="K62" s="30"/>
-      <c r="L62" s="30"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>21</v>
+      <c r="A63" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
       <c r="G63" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H63" s="7">
         <v>0.017881944444444443</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="K63" s="30"/>
-      <c r="L63" s="30"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>21</v>
+      <c r="A64" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="29" t="s">
-        <v>43</v>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="J64" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>21</v>
+      <c r="A65" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
-      <c r="L65" s="30"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="29"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>43</v>
+      <c r="A66" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
-      <c r="J66" s="30"/>
-      <c r="K66" s="30"/>
-      <c r="L66" s="30"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="29"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>21</v>
+      <c r="A67" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>21</v>
+      <c r="A68" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="30"/>
-      <c r="K68" s="30"/>
-      <c r="L68" s="30"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>21</v>
+      <c r="A69" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="30"/>
-      <c r="K69" s="30"/>
-      <c r="L69" s="30"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>21</v>
+      <c r="A70" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>21</v>
+      <c r="A71" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-      <c r="J71" s="30"/>
-      <c r="K71" s="30"/>
-      <c r="L71" s="30"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
+      <c r="L71" s="29"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="29" t="s">
-        <v>21</v>
+      <c r="A72" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-      <c r="J72" s="30"/>
-      <c r="K72" s="30"/>
-      <c r="L72" s="30"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="29"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="29"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="29" t="s">
-        <v>21</v>
+      <c r="A73" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="30"/>
-      <c r="K73" s="30"/>
-      <c r="L73" s="30"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
+      <c r="E73" s="29"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="29"/>
+      <c r="J73" s="29"/>
+      <c r="K73" s="29"/>
+      <c r="L73" s="29"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="29" t="s">
-        <v>21</v>
+      <c r="A74" s="28" t="s">
+        <v>22</v>
       </c>
       <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="30"/>
-      <c r="K74" s="30"/>
-      <c r="L74" s="30"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="29"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="29"/>
+      <c r="J74" s="29"/>
+      <c r="K74" s="29"/>
+      <c r="L74" s="29"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B75" s="37">
+      <c r="A75" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="36">
         <f>SUM(B62:B74)</f>
         <v>0.6286805556</v>
       </c>
-      <c r="C75" s="46"/>
-      <c r="D75" s="36">
+      <c r="C75" s="45"/>
+      <c r="D75" s="35">
         <f>SUM(D62:D74)</f>
         <v>0.0244212963</v>
       </c>
-      <c r="E75" s="47"/>
-      <c r="F75" s="37">
+      <c r="E75" s="46"/>
+      <c r="F75" s="36">
         <f>SUM(F62:F74)</f>
         <v>0.09237268519</v>
       </c>
-      <c r="G75" s="47"/>
-      <c r="H75" s="37">
+      <c r="G75" s="46"/>
+      <c r="H75" s="36">
         <f>SUM(H62:H74)</f>
         <v>0.1780092593</v>
       </c>
-      <c r="I75" s="47"/>
-      <c r="J75" s="37">
+      <c r="I75" s="46"/>
+      <c r="J75" s="36">
         <f>SUM(J62:J74)</f>
         <v>0.2304861111</v>
       </c>
-      <c r="K75" s="47"/>
-      <c r="L75" s="47"/>
+      <c r="K75" s="46"/>
+      <c r="L75" s="46"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="25"/>
-      <c r="B76" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="27"/>
-      <c r="D76" s="22" t="s">
+      <c r="A76" s="24"/>
+      <c r="B76" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C76" s="26"/>
+      <c r="D76" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="27"/>
-      <c r="F76" s="22" t="s">
+      <c r="E76" s="26"/>
+      <c r="F76" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="27"/>
-      <c r="H76" s="22" t="s">
+      <c r="G76" s="26"/>
+      <c r="H76" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="27"/>
-      <c r="J76" s="22" t="s">
+      <c r="I76" s="26"/>
+      <c r="J76" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="27"/>
-      <c r="L76" s="22" t="s">
+      <c r="K76" s="26"/>
+      <c r="L76" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77" s="28"/>
-      <c r="E77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" s="28"/>
-      <c r="G77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="28"/>
-      <c r="I77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" s="28"/>
-      <c r="K77" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" s="28"/>
+      <c r="A77" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="27"/>
+      <c r="E77" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" s="27"/>
+      <c r="G77" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="27"/>
+      <c r="I77" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="27"/>
+      <c r="K77" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L77" s="27"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="29" t="s">
-        <v>45</v>
+      <c r="A78" s="28" t="s">
+        <v>46</v>
       </c>
       <c r="B78" s="7">
         <v>0.125</v>
       </c>
-      <c r="C78" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="D78" s="49">
+      <c r="C78" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D78" s="48">
         <v>0.11513888888888889</v>
       </c>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49">
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48">
         <v>0.013888888888888888</v>
       </c>
-      <c r="I78" s="29" t="s">
-        <v>47</v>
+      <c r="I78" s="28" t="s">
+        <v>48</v>
       </c>
       <c r="J78" s="7">
         <v>0.08333333333333333</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L78" s="9">
         <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="29" t="s">
-        <v>49</v>
+      <c r="A79" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="B79" s="7">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C79" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="D79" s="49">
+      <c r="C79" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D79" s="48">
         <v>0.5638888888888889</v>
       </c>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="J79" s="51">
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="50">
         <v>0.09305555555555556</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="52">
+      <c r="A80" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" s="51">
         <v>0.0625</v>
       </c>
-      <c r="C80" s="48" t="s">
+      <c r="C80" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" s="52">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J80" s="13">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="K80" s="49"/>
+      <c r="L80" s="49"/>
+    </row>
+    <row r="81" ht="14.25" customHeight="1">
+      <c r="A81" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D80" s="53">
-        <v>0.19444444444444445</v>
-      </c>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="J80" s="14">
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="K80" s="50"/>
-      <c r="L80" s="50"/>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="54">
+      <c r="B81" s="53">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C81" s="49"/>
-      <c r="D81" s="49"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="50"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="49"/>
-      <c r="L81" s="49"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
+      <c r="H81" s="49"/>
+      <c r="I81" s="49"/>
+      <c r="J81" s="49"/>
+      <c r="K81" s="48"/>
+      <c r="L81" s="48"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="29" t="s">
-        <v>51</v>
+      <c r="A82" s="28" t="s">
+        <v>52</v>
       </c>
       <c r="B82" s="9">
         <v>0.05763888888888889</v>
       </c>
-      <c r="C82" s="49"/>
-      <c r="D82" s="49"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="50"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="48"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="49"/>
+      <c r="H82" s="49"/>
+      <c r="I82" s="49"/>
+      <c r="J82" s="49"/>
+      <c r="K82" s="49"/>
+      <c r="L82" s="49"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="55"/>
+      <c r="A83" s="54"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="49"/>
-      <c r="D83" s="49">
-        <v>0.32806712962962964</v>
-      </c>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="50"/>
-      <c r="I83" s="50"/>
-      <c r="J83" s="50"/>
-      <c r="K83" s="50"/>
-      <c r="L83" s="50"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
+      <c r="H83" s="49"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="49"/>
+      <c r="K83" s="49"/>
+      <c r="L83" s="49"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="55"/>
+      <c r="A84" s="54"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
-      <c r="H84" s="50"/>
-      <c r="I84" s="50"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="50"/>
-      <c r="L84" s="50"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
+      <c r="L84" s="49"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="55"/>
+      <c r="A85" s="54"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="56"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="50"/>
-      <c r="H85" s="50"/>
-      <c r="I85" s="50"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="56"/>
-      <c r="L85" s="56"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="55"/>
+      <c r="L85" s="55"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="57">
+        <v>15</v>
+      </c>
+      <c r="B86" s="40">
         <f>SUM(B78:B85)</f>
         <v>0.3979166667</v>
       </c>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58">
+      <c r="C86" s="56"/>
+      <c r="D86" s="56">
         <f>SUM(D78:D83)</f>
-        <v>1.201539352</v>
-      </c>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="59">
+        <v>0.8734722222</v>
+      </c>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="35">
         <f>SUM(H78:H85)</f>
         <v>0.01388888889</v>
       </c>
-      <c r="I86" s="46"/>
-      <c r="J86" s="59">
+      <c r="I86" s="57"/>
+      <c r="J86" s="35">
         <f>SUM(J78:J85)</f>
         <v>0.2180555556</v>
       </c>
-      <c r="K86" s="57"/>
-      <c r="L86" s="57">
+      <c r="K86" s="40"/>
+      <c r="L86" s="40">
         <f>SUM(L78:L80)</f>
         <v>0.03333333333</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="25"/>
-      <c r="B87" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C87" s="27"/>
-      <c r="D87" s="22" t="s">
+      <c r="A87" s="24"/>
+      <c r="B87" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C87" s="26"/>
+      <c r="D87" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="27"/>
-      <c r="F87" s="22" t="s">
+      <c r="E87" s="26"/>
+      <c r="F87" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="27"/>
-      <c r="H87" s="22" t="s">
+      <c r="G87" s="26"/>
+      <c r="H87" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I87" s="27"/>
-      <c r="J87" s="22" t="s">
+      <c r="I87" s="26"/>
+      <c r="J87" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="27"/>
-      <c r="L87" s="22" t="s">
+      <c r="K87" s="26"/>
+      <c r="L87" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" s="28"/>
-      <c r="E88" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="28"/>
-      <c r="G88" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="28"/>
-      <c r="I88" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" s="28"/>
-      <c r="K88" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L88" s="28"/>
+      <c r="A88" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B88" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" s="27"/>
+      <c r="E88" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" s="27"/>
+      <c r="G88" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="27"/>
+      <c r="I88" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="27"/>
+      <c r="K88" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L88" s="27"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="55"/>
+      <c r="A89" s="54"/>
       <c r="B89" s="7">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C89" s="49"/>
-      <c r="D89" s="14">
+      <c r="C89" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D89" s="13">
         <v>0.17631944444444445</v>
       </c>
-      <c r="E89" s="7"/>
+      <c r="E89" s="58" t="s">
+        <v>55</v>
+      </c>
       <c r="F89" s="7">
         <v>0.39791666666666664</v>
       </c>
-      <c r="G89" s="7"/>
+      <c r="G89" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="H89" s="7">
         <v>0.10641203703703704</v>
       </c>
-      <c r="I89" s="7"/>
+      <c r="I89" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="J89" s="7">
         <v>0.003472222222222222</v>
       </c>
-      <c r="K89" s="7"/>
+      <c r="K89" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="L89" s="7">
         <v>0.125</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="55"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="49"/>
-      <c r="D90" s="14">
+      <c r="A90" s="54"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" s="13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E90" s="7"/>
+      <c r="E90" s="58" t="s">
+        <v>55</v>
+      </c>
       <c r="F90" s="7">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G90" s="7"/>
+      <c r="G90" s="39" t="s">
+        <v>60</v>
+      </c>
       <c r="H90" s="7">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I90" s="30"/>
-      <c r="J90" s="30"/>
-      <c r="K90" s="7"/>
+      <c r="I90" s="29"/>
+      <c r="J90" s="29"/>
+      <c r="K90" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="L90" s="7">
         <v>0.0625</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="55"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="50"/>
-      <c r="D91" s="50"/>
-      <c r="E91" s="7"/>
+      <c r="A91" s="54"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" s="50">
+        <v>0.32806712962962964</v>
+      </c>
+      <c r="E91" s="58" t="s">
+        <v>55</v>
+      </c>
       <c r="F91" s="7">
         <v>0.125</v>
       </c>
-      <c r="G91" s="7"/>
+      <c r="G91" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="H91" s="7">
         <v>0.06527777777777778</v>
       </c>
-      <c r="I91" s="30"/>
-      <c r="J91" s="30"/>
-      <c r="K91" s="30"/>
-      <c r="L91" s="30"/>
+      <c r="I91" s="29"/>
+      <c r="J91" s="29"/>
+      <c r="K91" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L91" s="9">
+        <v>0.23644675925925926</v>
+      </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="55"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="50"/>
-      <c r="D92" s="50"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="30"/>
-      <c r="J92" s="30"/>
-      <c r="K92" s="30"/>
-      <c r="L92" s="30"/>
+      <c r="A92" s="54"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49"/>
+      <c r="E92" s="29"/>
+      <c r="F92" s="29"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="29"/>
+      <c r="I92" s="29"/>
+      <c r="J92" s="29"/>
+      <c r="K92" s="29"/>
+      <c r="L92" s="29"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" s="57">
+        <v>15</v>
+      </c>
+      <c r="B93" s="40">
         <f>SUM(B89)</f>
         <v>0.08333333333</v>
       </c>
-      <c r="C93" s="58"/>
-      <c r="D93" s="58">
-        <f>SUM(D89)</f>
-        <v>0.1763194444</v>
-      </c>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57">
+      <c r="C93" s="56"/>
+      <c r="D93" s="56">
+        <f>SUM(D89:D92)</f>
+        <v>0.6710532407</v>
+      </c>
+      <c r="E93" s="40"/>
+      <c r="F93" s="40">
         <f>SUM(F89:F91)</f>
         <v>0.8770833333</v>
       </c>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57">
+      <c r="G93" s="40"/>
+      <c r="H93" s="40">
         <f>SUM(H89:H91)</f>
         <v>0.3071064815</v>
       </c>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57">
+      <c r="I93" s="40"/>
+      <c r="J93" s="40">
         <f>SUM(J89)</f>
         <v>0.003472222222</v>
       </c>
-      <c r="K93" s="57"/>
-      <c r="L93" s="57">
-        <f>SUM(L89:L90)</f>
-        <v>0.1875</v>
+      <c r="K93" s="40"/>
+      <c r="L93" s="40">
+        <f>SUM(L89:L91)</f>
+        <v>0.4239467593</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="25"/>
-      <c r="B94" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C94" s="27"/>
-      <c r="D94" s="22" t="s">
+      <c r="A94" s="24"/>
+      <c r="B94" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="26"/>
+      <c r="D94" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E94" s="27"/>
-      <c r="F94" s="22" t="s">
+      <c r="E94" s="26"/>
+      <c r="F94" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="27"/>
-      <c r="H94" s="22" t="s">
+      <c r="G94" s="26"/>
+      <c r="H94" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="27"/>
-      <c r="J94" s="22" t="s">
+      <c r="I94" s="26"/>
+      <c r="J94" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="27"/>
-      <c r="L94" s="22" t="s">
+      <c r="K94" s="26"/>
+      <c r="L94" s="21" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="C95" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" s="30"/>
-      <c r="E95" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="30"/>
-      <c r="G95" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="30"/>
-      <c r="I95" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J95" s="30"/>
-      <c r="K95" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L95" s="30"/>
+      <c r="A95" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C95" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="29"/>
+      <c r="E95" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="29"/>
+      <c r="G95" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" s="29"/>
+      <c r="I95" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="29"/>
+      <c r="K95" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="L95" s="29"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="55"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14">
+      <c r="A96" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B96" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="C96" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D96" s="13">
         <v>0.5</v>
       </c>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="9"/>
+      <c r="E96" s="29"/>
+      <c r="F96" s="29"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+      <c r="I96" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="J96" s="9">
         <v>0.022222222222222223</v>
       </c>
-      <c r="K96" s="30"/>
-      <c r="L96" s="30"/>
+      <c r="K96" s="29"/>
+      <c r="L96" s="29"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="55"/>
+      <c r="A97" s="28" t="s">
+        <v>67</v>
+      </c>
       <c r="B97" s="9">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51">
+      <c r="C97" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" s="50">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="9"/>
+      <c r="E97" s="29"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+      <c r="I97" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="J97" s="9">
         <v>0.06859953703703704</v>
       </c>
-      <c r="K97" s="30"/>
-      <c r="L97" s="30"/>
+      <c r="K97" s="29"/>
+      <c r="L97" s="29"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="55"/>
+      <c r="A98" s="54"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14">
+      <c r="C98" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="6"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+      <c r="I98" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="J98" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="K98" s="30"/>
-      <c r="L98" s="30"/>
+      <c r="K98" s="29"/>
+      <c r="L98" s="29"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="55"/>
+      <c r="A99" s="54"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="14">
+      <c r="C99" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
-      <c r="J99" s="30"/>
-      <c r="K99" s="30"/>
-      <c r="L99" s="30"/>
+      <c r="E99" s="29"/>
+      <c r="F99" s="29"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+      <c r="I99" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J99" s="50">
+        <v>0.03420138888888889</v>
+      </c>
+      <c r="K99" s="29"/>
+      <c r="L99" s="29"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="29"/>
+      <c r="A100" s="28"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
-      <c r="J100" s="30"/>
-      <c r="K100" s="30"/>
-      <c r="L100" s="30"/>
+      <c r="C100" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D100" s="6">
+        <v>0.1909722222222222</v>
+      </c>
+      <c r="E100" s="29"/>
+      <c r="F100" s="29"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+      <c r="I100" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J100" s="13">
+        <v>0.03017361111111111</v>
+      </c>
+      <c r="K100" s="29"/>
+      <c r="L100" s="29"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B101" s="63">
-        <f>SUM(B96:B100)</f>
-        <v>0.04722222222</v>
-      </c>
-      <c r="C101" s="46"/>
-      <c r="D101" s="59">
-        <f>SUM(D96:D100)</f>
-        <v>0.626875</v>
-      </c>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
-      <c r="J101" s="63">
-        <f>SUM(J96:J100)</f>
-        <v>0.2817939815</v>
-      </c>
-      <c r="K101" s="47"/>
-      <c r="L101" s="47"/>
+      <c r="A101" s="28"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="49"/>
+      <c r="D101" s="62"/>
+      <c r="E101" s="29"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="29"/>
+      <c r="H101" s="29"/>
+      <c r="I101" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J101" s="13">
+        <v>0.0625</v>
+      </c>
+      <c r="K101" s="29"/>
+      <c r="L101" s="29"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="25"/>
-      <c r="B102" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C102" s="27"/>
-      <c r="D102" s="22" t="s">
+      <c r="A102" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" s="36">
+        <f>SUM(B96:B101)</f>
+        <v>0.06805555556</v>
+      </c>
+      <c r="C102" s="45"/>
+      <c r="D102" s="35">
+        <f>SUM(D96:D101)</f>
+        <v>0.8178472222</v>
+      </c>
+      <c r="E102" s="46"/>
+      <c r="F102" s="46"/>
+      <c r="G102" s="46"/>
+      <c r="H102" s="46"/>
+      <c r="I102" s="46"/>
+      <c r="J102" s="36">
+        <f>SUM(J96:J101)</f>
+        <v>0.4086689815</v>
+      </c>
+      <c r="K102" s="46"/>
+      <c r="L102" s="46"/>
+    </row>
+    <row r="103" ht="14.25" customHeight="1">
+      <c r="A103" s="24"/>
+      <c r="B103" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103" s="26"/>
+      <c r="D103" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E102" s="27"/>
-      <c r="F102" s="22" t="s">
+      <c r="E103" s="26"/>
+      <c r="F103" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G102" s="27"/>
-      <c r="H102" s="22" t="s">
+      <c r="G103" s="26"/>
+      <c r="H103" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I102" s="27"/>
-      <c r="J102" s="22" t="s">
+      <c r="I103" s="26"/>
+      <c r="J103" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="27"/>
-      <c r="L102" s="22" t="s">
+      <c r="K103" s="26"/>
+      <c r="L103" s="21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="C103" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="D103" s="30"/>
-      <c r="E103" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="30"/>
-      <c r="G103" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="30"/>
-      <c r="I103" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J103" s="30"/>
-      <c r="K103" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L103" s="30"/>
-    </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="55"/>
-      <c r="B104" s="6">
+      <c r="A104" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" s="29"/>
+      <c r="E104" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" s="63"/>
+      <c r="G104" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" s="29"/>
+      <c r="I104" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="29"/>
+      <c r="K104" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="L104" s="29"/>
+    </row>
+    <row r="105" ht="14.25" customHeight="1">
+      <c r="A105" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B105" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51">
+      <c r="C105" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" s="50">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="30"/>
-      <c r="I104" s="51"/>
-      <c r="J104" s="51">
+      <c r="E105" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F105" s="6">
+        <v>0.27569444444444446</v>
+      </c>
+      <c r="G105" s="29"/>
+      <c r="H105" s="29"/>
+      <c r="I105" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="J105" s="50">
         <v>0.1909722222222222</v>
-      </c>
-      <c r="K104" s="9"/>
-      <c r="L104" s="9">
-        <v>0.0763888888888889</v>
-      </c>
-    </row>
-    <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="55"/>
-      <c r="B105" s="9">
-        <v>0.020833333333333332</v>
-      </c>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14">
-        <v>0.03017361111111111</v>
-      </c>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="9"/>
-      <c r="J105" s="9">
-        <v>0.03125</v>
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="9">
+        <v>0.0763888888888889</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" customHeight="1">
+      <c r="A106" s="28"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" s="13">
+        <v>0.03017361111111111</v>
+      </c>
+      <c r="E106" s="29"/>
+      <c r="F106" s="29"/>
+      <c r="G106" s="29"/>
+      <c r="H106" s="29"/>
+      <c r="I106" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J106" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="K106" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L106" s="9">
         <v>0.041666666666666664</v>
       </c>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="55"/>
-      <c r="B106" s="30"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14">
+    <row r="107" ht="14.25" customHeight="1">
+      <c r="A107" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B107" s="9">
+        <v>0.2326388888888889</v>
+      </c>
+      <c r="C107" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E106" s="30"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-      <c r="H106" s="30"/>
-      <c r="I106" s="30"/>
-      <c r="J106" s="30"/>
-      <c r="K106" s="30"/>
-      <c r="L106" s="30"/>
-    </row>
-    <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="55"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14">
+      <c r="E107" s="29"/>
+      <c r="F107" s="29"/>
+      <c r="G107" s="29"/>
+      <c r="H107" s="29"/>
+      <c r="I107" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J107" s="50">
+        <v>0.03420138888888889</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L107" s="9">
+        <v>0.19444444444444445</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" customHeight="1">
+      <c r="A108" s="54"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="D108" s="13">
         <v>0.3076388888888889</v>
       </c>
-      <c r="E107" s="30"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="30"/>
-      <c r="J107" s="30"/>
-      <c r="K107" s="30"/>
-      <c r="L107" s="30"/>
-    </row>
-    <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="55"/>
-      <c r="B108" s="30"/>
-      <c r="C108" s="14"/>
-      <c r="D108" s="14">
+      <c r="E108" s="29"/>
+      <c r="F108" s="29"/>
+      <c r="G108" s="29"/>
+      <c r="H108" s="29"/>
+      <c r="I108" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J108" s="13">
+        <v>0.03017361111111111</v>
+      </c>
+      <c r="K108" s="29"/>
+      <c r="L108" s="29"/>
+    </row>
+    <row r="109" ht="14.25" customHeight="1">
+      <c r="A109" s="54"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="D109" s="13">
         <v>0.24097222222222223</v>
       </c>
-      <c r="E108" s="30"/>
-      <c r="F108" s="30"/>
-      <c r="G108" s="30"/>
-      <c r="H108" s="30"/>
-      <c r="I108" s="30"/>
-      <c r="J108" s="30"/>
-      <c r="K108" s="30"/>
-      <c r="L108" s="30"/>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="55"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14">
+      <c r="E109" s="29"/>
+      <c r="F109" s="29"/>
+      <c r="G109" s="29"/>
+      <c r="H109" s="29"/>
+      <c r="I109" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J109" s="13">
+        <v>0.0625</v>
+      </c>
+      <c r="K109" s="29"/>
+      <c r="L109" s="29"/>
+    </row>
+    <row r="110" ht="14.25" customHeight="1">
+      <c r="A110" s="54"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="D110" s="13">
         <v>0.10609953703703703</v>
       </c>
-      <c r="E109" s="30"/>
-      <c r="F109" s="30"/>
-      <c r="G109" s="30"/>
-      <c r="H109" s="30"/>
-      <c r="I109" s="30"/>
-      <c r="J109" s="30"/>
-      <c r="K109" s="30"/>
-      <c r="L109" s="30"/>
-    </row>
-    <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="55"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="50"/>
-      <c r="D110" s="50"/>
-      <c r="E110" s="30"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="30"/>
-      <c r="H110" s="30"/>
-      <c r="I110" s="30"/>
-      <c r="J110" s="30"/>
-      <c r="K110" s="30"/>
-      <c r="L110" s="30"/>
+      <c r="E110" s="29"/>
+      <c r="F110" s="29"/>
+      <c r="G110" s="29"/>
+      <c r="H110" s="29"/>
+      <c r="I110" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="J110" s="9">
+        <v>0.2326388888888889</v>
+      </c>
+      <c r="K110" s="29"/>
+      <c r="L110" s="29"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="55"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="50"/>
-      <c r="D111" s="50"/>
-      <c r="E111" s="30"/>
-      <c r="F111" s="30"/>
-      <c r="G111" s="30"/>
-      <c r="H111" s="30"/>
-      <c r="I111" s="30"/>
-      <c r="J111" s="30"/>
-      <c r="K111" s="30"/>
-      <c r="L111" s="30"/>
+      <c r="A111" s="54"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="29"/>
+      <c r="F111" s="29"/>
+      <c r="G111" s="29"/>
+      <c r="H111" s="29"/>
+      <c r="I111" s="29"/>
+      <c r="J111" s="29"/>
+      <c r="K111" s="29"/>
+      <c r="L111" s="29"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B112" s="57">
-        <f>SUM(B104:B111)</f>
-        <v>0.06805555556</v>
-      </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="58">
-        <f>SUM(D104:D111)</f>
+      <c r="A112" s="54"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="29"/>
+      <c r="F112" s="29"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+      <c r="I112" s="29"/>
+      <c r="J112" s="29"/>
+      <c r="K112" s="29"/>
+      <c r="L112" s="29"/>
+    </row>
+    <row r="113" ht="14.25" customHeight="1">
+      <c r="A113" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="40">
+        <f>SUM(B105:B112)</f>
+        <v>0.2798611111</v>
+      </c>
+      <c r="C113" s="45"/>
+      <c r="D113" s="56">
+        <f>SUM(D105:D112)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="E112" s="47"/>
-      <c r="F112" s="47"/>
-      <c r="G112" s="47"/>
-      <c r="H112" s="47"/>
-      <c r="I112" s="47"/>
-      <c r="J112" s="57">
-        <f>SUM(J104:J111)</f>
-        <v>0.2222222222</v>
-      </c>
-      <c r="K112" s="47"/>
-      <c r="L112" s="63">
-        <f>SUM(L104:L111)</f>
-        <v>0.1180555556</v>
-      </c>
-    </row>
-    <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="25"/>
-      <c r="B113" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C113" s="27"/>
-      <c r="D113" s="22" t="s">
+      <c r="E113" s="46"/>
+      <c r="F113" s="40">
+        <f>SUM(F105:F112)</f>
+        <v>0.2756944444</v>
+      </c>
+      <c r="G113" s="46"/>
+      <c r="H113" s="46"/>
+      <c r="I113" s="46"/>
+      <c r="J113" s="40">
+        <f>SUM(J105:J112)</f>
+        <v>0.5817361111</v>
+      </c>
+      <c r="K113" s="46"/>
+      <c r="L113" s="36">
+        <f>SUM(L105:L112)</f>
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25" customHeight="1">
+      <c r="A114" s="24"/>
+      <c r="B114" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114" s="26"/>
+      <c r="D114" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E113" s="27"/>
-      <c r="F113" s="22" t="s">
+      <c r="E114" s="26"/>
+      <c r="F114" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G113" s="27"/>
-      <c r="H113" s="22" t="s">
+      <c r="G114" s="26"/>
+      <c r="H114" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I113" s="27"/>
-      <c r="J113" s="22" t="s">
+      <c r="I114" s="26"/>
+      <c r="J114" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K113" s="27"/>
-      <c r="L113" s="22" t="s">
+      <c r="K114" s="26"/>
+      <c r="L114" s="21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C114" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D114" s="28"/>
-      <c r="E114" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" s="28"/>
-      <c r="G114" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H114" s="28"/>
-      <c r="I114" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J114" s="28"/>
-      <c r="K114" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L114" s="28"/>
-    </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="19"/>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="19"/>
-      <c r="F115" s="19"/>
-      <c r="G115" s="19"/>
-      <c r="H115" s="19"/>
-      <c r="I115" s="19"/>
-      <c r="J115" s="19"/>
-      <c r="K115" s="19"/>
-      <c r="L115" s="19"/>
+      <c r="A115" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B115" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" s="27"/>
+      <c r="E115" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" s="27"/>
+      <c r="G115" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H115" s="27"/>
+      <c r="I115" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="27"/>
+      <c r="K115" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L115" s="27"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="19"/>
-      <c r="B116" s="19"/>
-      <c r="C116" s="19"/>
-      <c r="D116" s="19"/>
-      <c r="E116" s="19"/>
-      <c r="F116" s="19"/>
-      <c r="G116" s="19"/>
-      <c r="H116" s="19"/>
-      <c r="I116" s="19"/>
-      <c r="J116" s="19"/>
-      <c r="K116" s="19"/>
-      <c r="L116" s="19"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18"/>
+      <c r="J116" s="18"/>
+      <c r="K116" s="18"/>
+      <c r="L116" s="18"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="19"/>
-      <c r="B117" s="19"/>
-      <c r="C117" s="19"/>
-      <c r="D117" s="19"/>
-      <c r="E117" s="19"/>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
-      <c r="H117" s="19"/>
-      <c r="I117" s="19"/>
-      <c r="J117" s="19"/>
-      <c r="K117" s="19"/>
-      <c r="L117" s="19"/>
+      <c r="A117" s="18"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="18"/>
+      <c r="H117" s="18"/>
+      <c r="I117" s="18"/>
+      <c r="J117" s="18"/>
+      <c r="K117" s="18"/>
+      <c r="L117" s="18"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="19"/>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
-      <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19"/>
-      <c r="I118" s="19"/>
-      <c r="J118" s="19"/>
-      <c r="K118" s="19"/>
-      <c r="L118" s="19"/>
+      <c r="A118" s="18"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="18"/>
+      <c r="G118" s="18"/>
+      <c r="H118" s="18"/>
+      <c r="I118" s="18"/>
+      <c r="J118" s="18"/>
+      <c r="K118" s="18"/>
+      <c r="L118" s="18"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="19"/>
-      <c r="B119" s="19"/>
-      <c r="C119" s="19"/>
-      <c r="D119" s="19"/>
-      <c r="E119" s="19"/>
-      <c r="F119" s="19"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="19"/>
-      <c r="I119" s="19"/>
-      <c r="J119" s="19"/>
-      <c r="K119" s="19"/>
-      <c r="L119" s="19"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="18"/>
+      <c r="I119" s="18"/>
+      <c r="J119" s="18"/>
+      <c r="K119" s="18"/>
+      <c r="L119" s="18"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="19"/>
-      <c r="B120" s="19"/>
-      <c r="C120" s="19"/>
-      <c r="D120" s="19"/>
-      <c r="E120" s="19"/>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="19"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="19"/>
-      <c r="K120" s="19"/>
-      <c r="L120" s="19"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="18"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="18"/>
+      <c r="J120" s="18"/>
+      <c r="K120" s="18"/>
+      <c r="L120" s="18"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="19"/>
-      <c r="B121" s="19"/>
-      <c r="C121" s="19"/>
-      <c r="D121" s="19"/>
-      <c r="E121" s="19"/>
-      <c r="F121" s="19"/>
-      <c r="G121" s="19"/>
-      <c r="H121" s="19"/>
-      <c r="I121" s="19"/>
-      <c r="J121" s="19"/>
-      <c r="K121" s="19"/>
-      <c r="L121" s="19"/>
+      <c r="A121" s="18"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="18"/>
+      <c r="H121" s="18"/>
+      <c r="I121" s="18"/>
+      <c r="J121" s="18"/>
+      <c r="K121" s="18"/>
+      <c r="L121" s="18"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="19"/>
-      <c r="B122" s="19"/>
-      <c r="C122" s="19"/>
-      <c r="D122" s="19"/>
-      <c r="E122" s="19"/>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="19"/>
-      <c r="I122" s="19"/>
-      <c r="J122" s="19"/>
-      <c r="K122" s="19"/>
-      <c r="L122" s="19"/>
+      <c r="A122" s="18"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
+      <c r="G122" s="18"/>
+      <c r="H122" s="18"/>
+      <c r="I122" s="18"/>
+      <c r="J122" s="18"/>
+      <c r="K122" s="18"/>
+      <c r="L122" s="18"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="19"/>
-      <c r="B123" s="19"/>
-      <c r="C123" s="19"/>
-      <c r="D123" s="19"/>
-      <c r="E123" s="19"/>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
-      <c r="H123" s="19"/>
-      <c r="I123" s="19"/>
-      <c r="J123" s="19"/>
-      <c r="K123" s="19"/>
-      <c r="L123" s="19"/>
+      <c r="A123" s="18"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="18"/>
+      <c r="H123" s="18"/>
+      <c r="I123" s="18"/>
+      <c r="J123" s="18"/>
+      <c r="K123" s="18"/>
+      <c r="L123" s="18"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="19"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
-      <c r="D124" s="19"/>
-      <c r="E124" s="19"/>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
-      <c r="H124" s="19"/>
-      <c r="I124" s="19"/>
-      <c r="J124" s="19"/>
-      <c r="K124" s="19"/>
-      <c r="L124" s="19"/>
+      <c r="A124" s="18"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="18"/>
+      <c r="H124" s="18"/>
+      <c r="I124" s="18"/>
+      <c r="J124" s="18"/>
+      <c r="K124" s="18"/>
+      <c r="L124" s="18"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="19"/>
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-      <c r="D125" s="19"/>
-      <c r="E125" s="19"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="19"/>
-      <c r="I125" s="19"/>
-      <c r="J125" s="19"/>
-      <c r="K125" s="19"/>
-      <c r="L125" s="19"/>
+      <c r="A125" s="18"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="18"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18"/>
+      <c r="G125" s="18"/>
+      <c r="H125" s="18"/>
+      <c r="I125" s="18"/>
+      <c r="J125" s="18"/>
+      <c r="K125" s="18"/>
+      <c r="L125" s="18"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="19"/>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="19"/>
-      <c r="E126" s="19"/>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
-      <c r="H126" s="19"/>
-      <c r="I126" s="19"/>
-      <c r="J126" s="19"/>
-      <c r="K126" s="19"/>
-      <c r="L126" s="19"/>
+      <c r="A126" s="18"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="18"/>
+      <c r="E126" s="18"/>
+      <c r="F126" s="18"/>
+      <c r="G126" s="18"/>
+      <c r="H126" s="18"/>
+      <c r="I126" s="18"/>
+      <c r="J126" s="18"/>
+      <c r="K126" s="18"/>
+      <c r="L126" s="18"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="19"/>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
-      <c r="I127" s="19"/>
-      <c r="J127" s="19"/>
-      <c r="K127" s="19"/>
-      <c r="L127" s="19"/>
+      <c r="A127" s="18"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="18"/>
+      <c r="H127" s="18"/>
+      <c r="I127" s="18"/>
+      <c r="J127" s="18"/>
+      <c r="K127" s="18"/>
+      <c r="L127" s="18"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="19"/>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
-      <c r="I128" s="19"/>
-      <c r="J128" s="19"/>
-      <c r="K128" s="19"/>
-      <c r="L128" s="19"/>
+      <c r="A128" s="18"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="18"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="18"/>
+      <c r="J128" s="18"/>
+      <c r="K128" s="18"/>
+      <c r="L128" s="18"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="19"/>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
-      <c r="G129" s="19"/>
-      <c r="H129" s="19"/>
-      <c r="I129" s="19"/>
-      <c r="J129" s="19"/>
-      <c r="K129" s="19"/>
-      <c r="L129" s="19"/>
+      <c r="A129" s="18"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="18"/>
+      <c r="H129" s="18"/>
+      <c r="I129" s="18"/>
+      <c r="J129" s="18"/>
+      <c r="K129" s="18"/>
+      <c r="L129" s="18"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="19"/>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="19"/>
-      <c r="E130" s="19"/>
-      <c r="F130" s="19"/>
-      <c r="G130" s="19"/>
-      <c r="H130" s="19"/>
-      <c r="I130" s="19"/>
-      <c r="J130" s="19"/>
-      <c r="K130" s="19"/>
-      <c r="L130" s="19"/>
+      <c r="A130" s="18"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
+      <c r="H130" s="18"/>
+      <c r="I130" s="18"/>
+      <c r="J130" s="18"/>
+      <c r="K130" s="18"/>
+      <c r="L130" s="18"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="19"/>
-      <c r="B131" s="19"/>
-      <c r="C131" s="19"/>
-      <c r="D131" s="19"/>
-      <c r="E131" s="19"/>
-      <c r="F131" s="19"/>
-      <c r="G131" s="19"/>
-      <c r="H131" s="19"/>
-      <c r="I131" s="19"/>
-      <c r="J131" s="19"/>
-      <c r="K131" s="19"/>
-      <c r="L131" s="19"/>
+      <c r="A131" s="18"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
+      <c r="G131" s="18"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="18"/>
+      <c r="J131" s="18"/>
+      <c r="K131" s="18"/>
+      <c r="L131" s="18"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="19"/>
-      <c r="B132" s="19"/>
-      <c r="C132" s="19"/>
-      <c r="D132" s="19"/>
-      <c r="E132" s="19"/>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
-      <c r="H132" s="19"/>
-      <c r="I132" s="19"/>
-      <c r="J132" s="19"/>
-      <c r="K132" s="19"/>
-      <c r="L132" s="19"/>
+      <c r="A132" s="18"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="18"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="18"/>
+      <c r="J132" s="18"/>
+      <c r="K132" s="18"/>
+      <c r="L132" s="18"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="19"/>
-      <c r="B133" s="19"/>
-      <c r="C133" s="19"/>
-      <c r="D133" s="19"/>
-      <c r="E133" s="19"/>
-      <c r="F133" s="19"/>
-      <c r="G133" s="19"/>
-      <c r="H133" s="19"/>
-      <c r="I133" s="19"/>
-      <c r="J133" s="19"/>
-      <c r="K133" s="19"/>
-      <c r="L133" s="19"/>
+      <c r="A133" s="18"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="18"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="18"/>
+      <c r="J133" s="18"/>
+      <c r="K133" s="18"/>
+      <c r="L133" s="18"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="19"/>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
-      <c r="D134" s="19"/>
-      <c r="E134" s="19"/>
-      <c r="F134" s="19"/>
-      <c r="G134" s="19"/>
-      <c r="H134" s="19"/>
-      <c r="I134" s="19"/>
-      <c r="J134" s="19"/>
-      <c r="K134" s="19"/>
-      <c r="L134" s="19"/>
+      <c r="A134" s="18"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="18"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="18"/>
+      <c r="J134" s="18"/>
+      <c r="K134" s="18"/>
+      <c r="L134" s="18"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="19"/>
-      <c r="B135" s="19"/>
-      <c r="C135" s="19"/>
-      <c r="D135" s="19"/>
-      <c r="E135" s="19"/>
-      <c r="F135" s="19"/>
-      <c r="G135" s="19"/>
-      <c r="H135" s="19"/>
-      <c r="I135" s="19"/>
-      <c r="J135" s="19"/>
-      <c r="K135" s="19"/>
-      <c r="L135" s="19"/>
+      <c r="A135" s="18"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="18"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="18"/>
+      <c r="J135" s="18"/>
+      <c r="K135" s="18"/>
+      <c r="L135" s="18"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="19"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
-      <c r="D136" s="19"/>
-      <c r="E136" s="19"/>
-      <c r="F136" s="19"/>
-      <c r="G136" s="19"/>
-      <c r="H136" s="19"/>
-      <c r="I136" s="19"/>
-      <c r="J136" s="19"/>
-      <c r="K136" s="19"/>
-      <c r="L136" s="19"/>
-    </row>
-    <row r="137" ht="14.25" customHeight="1"/>
+      <c r="A136" s="18"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
+      <c r="G136" s="18"/>
+      <c r="H136" s="18"/>
+      <c r="I136" s="18"/>
+      <c r="J136" s="18"/>
+      <c r="K136" s="18"/>
+      <c r="L136" s="18"/>
+    </row>
+    <row r="137" ht="14.25" customHeight="1">
+      <c r="A137" s="18"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="18"/>
+      <c r="I137" s="18"/>
+      <c r="J137" s="18"/>
+      <c r="K137" s="18"/>
+      <c r="L137" s="18"/>
+    </row>
     <row r="138" ht="14.25" customHeight="1"/>
     <row r="139" ht="14.25" customHeight="1"/>
     <row r="140" ht="14.25" customHeight="1"/>
@@ -5837,6 +6058,7 @@
     <row r="1019" ht="14.25" customHeight="1"/>
     <row r="1020" ht="14.25" customHeight="1"/>
     <row r="1021" ht="14.25" customHeight="1"/>
+    <row r="1022" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A53:L53"/>
@@ -5863,10 +6085,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -5980,9 +6202,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="OKNazMu+baFD34LkA3mPGAXypLuJqsk+3PIO95RjQ9c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="eWdMrhJoTS4M4QFoS5GozNlFDlzJzdV0I1r1+OHyOmg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="88">
   <si>
     <t>Semana</t>
   </si>
@@ -258,6 +258,24 @@
   </si>
   <si>
     <t>Semana 9</t>
+  </si>
+  <si>
+    <t>Especificación CU20</t>
+  </si>
+  <si>
+    <t>Revisión de Especificación de Casos de Uso a implementar / Modelo de Datos</t>
+  </si>
+  <si>
+    <t>Especificación CU12</t>
+  </si>
+  <si>
+    <t>Revisión de Especificación de CU 09 y 20</t>
+  </si>
+  <si>
+    <t>Reunión 23/10</t>
+  </si>
+  <si>
+    <t>Especificación CU09</t>
   </si>
   <si>
     <t>Fecha de inicio</t>
@@ -275,7 +293,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -337,6 +355,10 @@
     </font>
     <font/>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Docs-Roboto"/>
+    </font>
+    <font>
       <b/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -393,7 +415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -439,11 +461,19 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -600,7 +630,21 @@
     <xf borderId="1" fillId="4" fontId="3" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="12" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -678,7 +722,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I10" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I11" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="Semana" id="1"/>
     <tableColumn name="Análisis" id="2"/>
@@ -1163,7 +1207,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <f t="shared" ref="H8:H9" si="1">SUM(B8:G8)</f>
+        <f t="shared" ref="H8:H10" si="1">SUM(B8:G8)</f>
         <v>1.294571759</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -1204,45 +1248,77 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="5">
+        <f>Registro!B137</f>
+        <v>0.2326388889</v>
+      </c>
+      <c r="C10" s="5">
+        <f>Registro!D137</f>
+        <v>0.2292361111</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5">
+        <f>Registro!H137</f>
+        <v>0.02300925926</v>
+      </c>
+      <c r="F10" s="5">
+        <f>Registro!J137</f>
+        <v>0.2292361111</v>
+      </c>
+      <c r="G10" s="5">
+        <f>Registro!L137</f>
+        <v>0.3020833333</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="1"/>
+        <v>1.016203704</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="15">
-        <f t="shared" ref="B10:D10" si="2">SUM(B2:B9)</f>
-        <v>2.842986111</v>
-      </c>
-      <c r="C10" s="15">
+      <c r="B11" s="15">
+        <f t="shared" ref="B11:C11" si="2">SUM(B2:B10)</f>
+        <v>3.075625</v>
+      </c>
+      <c r="C11" s="15">
         <f t="shared" si="2"/>
-        <v>3.857743056</v>
-      </c>
-      <c r="D10" s="15">
-        <f t="shared" si="2"/>
+        <v>4.086979167</v>
+      </c>
+      <c r="D11" s="15">
+        <f>SUM(D2:D9)</f>
         <v>2.202731481</v>
       </c>
-      <c r="E10" s="15">
-        <f>SUM(E2:E7)</f>
-        <v>0.5231481481</v>
-      </c>
-      <c r="F10" s="15">
-        <f t="shared" ref="F10:G10" si="3">SUM(F2:F9)</f>
-        <v>2.124178241</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="E11" s="15">
+        <f t="shared" ref="E11:G11" si="3">SUM(E2:E10)</f>
+        <v>0.5461574074</v>
+      </c>
+      <c r="F11" s="15">
         <f t="shared" si="3"/>
-        <v>0.963287037</v>
-      </c>
-      <c r="H10" s="15">
-        <f>SUM(Total!$B10:$G10)</f>
-        <v>12.51407407</v>
-      </c>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1"/>
+        <v>2.353414352</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="3"/>
+        <v>1.26537037</v>
+      </c>
+      <c r="H11" s="15">
+        <f>SUM(Total!$B11:$G11)</f>
+        <v>13.53027778</v>
+      </c>
+      <c r="I11" s="16"/>
+    </row>
     <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="H14" s="17"/>
+    </row>
     <row r="15" ht="14.25" customHeight="1"/>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
@@ -2231,6 +2307,7 @@
     <row r="1000" ht="14.25" customHeight="1"/>
     <row r="1001" ht="14.25" customHeight="1"/>
     <row r="1002" ht="14.25" customHeight="1"/>
+    <row r="1003" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4867,312 +4944,373 @@
       <c r="L115" s="27"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="18"/>
-      <c r="B116" s="18"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="18"/>
-      <c r="F116" s="18"/>
-      <c r="G116" s="18"/>
-      <c r="H116" s="18"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="18"/>
-      <c r="K116" s="18"/>
-      <c r="L116" s="18"/>
+      <c r="A116" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="9">
+        <v>0.2326388888888889</v>
+      </c>
+      <c r="C116" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D116" s="64">
+        <v>0.09930555555555555</v>
+      </c>
+      <c r="E116" s="54"/>
+      <c r="F116" s="54"/>
+      <c r="G116" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="H116" s="66">
+        <v>0.008726851851851852</v>
+      </c>
+      <c r="I116" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="J116" s="64">
+        <v>0.09930555555555555</v>
+      </c>
+      <c r="K116" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L116" s="9">
+        <v>0.19444444444444445</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="18"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="18"/>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="18"/>
-      <c r="G117" s="18"/>
-      <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
-      <c r="K117" s="18"/>
-      <c r="L117" s="18"/>
+      <c r="A117" s="54"/>
+      <c r="B117" s="54"/>
+      <c r="C117" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D117" s="67">
+        <v>0.05625</v>
+      </c>
+      <c r="E117" s="54"/>
+      <c r="F117" s="54"/>
+      <c r="G117" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="H117" s="67">
+        <v>0.014282407407407407</v>
+      </c>
+      <c r="I117" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J117" s="67">
+        <v>0.05625</v>
+      </c>
+      <c r="K117" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L117" s="9">
+        <v>0.1076388888888889</v>
+      </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="18"/>
-      <c r="B118" s="18"/>
-      <c r="C118" s="18"/>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="18"/>
-      <c r="G118" s="18"/>
-      <c r="H118" s="18"/>
-      <c r="I118" s="18"/>
-      <c r="J118" s="18"/>
-      <c r="K118" s="18"/>
-      <c r="L118" s="18"/>
+      <c r="A118" s="54"/>
+      <c r="B118" s="54"/>
+      <c r="C118" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D118" s="64">
+        <v>0.07368055555555555</v>
+      </c>
+      <c r="E118" s="54"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="54"/>
+      <c r="H118" s="54"/>
+      <c r="I118" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="J118" s="64">
+        <v>0.07368055555555555</v>
+      </c>
+      <c r="K118" s="54"/>
+      <c r="L118" s="54"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="18"/>
-      <c r="B119" s="18"/>
-      <c r="C119" s="18"/>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18"/>
-      <c r="F119" s="18"/>
-      <c r="G119" s="18"/>
-      <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="18"/>
+      <c r="A119" s="54"/>
+      <c r="B119" s="54"/>
+      <c r="C119" s="54"/>
+      <c r="D119" s="54"/>
+      <c r="E119" s="54"/>
+      <c r="F119" s="54"/>
+      <c r="G119" s="54"/>
+      <c r="H119" s="54"/>
+      <c r="I119" s="54"/>
+      <c r="J119" s="54"/>
+      <c r="K119" s="54"/>
+      <c r="L119" s="54"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="18"/>
-      <c r="B120" s="18"/>
-      <c r="C120" s="18"/>
-      <c r="D120" s="18"/>
-      <c r="E120" s="18"/>
-      <c r="F120" s="18"/>
-      <c r="G120" s="18"/>
-      <c r="H120" s="18"/>
-      <c r="I120" s="18"/>
-      <c r="J120" s="18"/>
-      <c r="K120" s="18"/>
-      <c r="L120" s="18"/>
+      <c r="A120" s="54"/>
+      <c r="B120" s="54"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="54"/>
+      <c r="E120" s="54"/>
+      <c r="F120" s="54"/>
+      <c r="G120" s="54"/>
+      <c r="H120" s="54"/>
+      <c r="I120" s="54"/>
+      <c r="J120" s="54"/>
+      <c r="K120" s="54"/>
+      <c r="L120" s="54"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="18"/>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="18"/>
-      <c r="H121" s="18"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="18"/>
-      <c r="K121" s="18"/>
-      <c r="L121" s="18"/>
+      <c r="A121" s="54"/>
+      <c r="B121" s="54"/>
+      <c r="C121" s="54"/>
+      <c r="D121" s="54"/>
+      <c r="E121" s="54"/>
+      <c r="F121" s="54"/>
+      <c r="G121" s="54"/>
+      <c r="H121" s="54"/>
+      <c r="I121" s="54"/>
+      <c r="J121" s="54"/>
+      <c r="K121" s="54"/>
+      <c r="L121" s="54"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="18"/>
-      <c r="B122" s="18"/>
-      <c r="C122" s="18"/>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="18"/>
-      <c r="H122" s="18"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="18"/>
-      <c r="K122" s="18"/>
-      <c r="L122" s="18"/>
+      <c r="A122" s="54"/>
+      <c r="B122" s="54"/>
+      <c r="C122" s="54"/>
+      <c r="D122" s="54"/>
+      <c r="E122" s="54"/>
+      <c r="F122" s="54"/>
+      <c r="G122" s="54"/>
+      <c r="H122" s="54"/>
+      <c r="I122" s="54"/>
+      <c r="J122" s="54"/>
+      <c r="K122" s="54"/>
+      <c r="L122" s="54"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="18"/>
-      <c r="B123" s="18"/>
-      <c r="C123" s="18"/>
-      <c r="D123" s="18"/>
-      <c r="E123" s="18"/>
-      <c r="F123" s="18"/>
-      <c r="G123" s="18"/>
-      <c r="H123" s="18"/>
-      <c r="I123" s="18"/>
-      <c r="J123" s="18"/>
-      <c r="K123" s="18"/>
-      <c r="L123" s="18"/>
+      <c r="A123" s="54"/>
+      <c r="B123" s="54"/>
+      <c r="C123" s="54"/>
+      <c r="D123" s="54"/>
+      <c r="E123" s="54"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="54"/>
+      <c r="H123" s="54"/>
+      <c r="I123" s="54"/>
+      <c r="J123" s="54"/>
+      <c r="K123" s="54"/>
+      <c r="L123" s="54"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="18"/>
-      <c r="B124" s="18"/>
-      <c r="C124" s="18"/>
-      <c r="D124" s="18"/>
-      <c r="E124" s="18"/>
-      <c r="F124" s="18"/>
-      <c r="G124" s="18"/>
-      <c r="H124" s="18"/>
-      <c r="I124" s="18"/>
-      <c r="J124" s="18"/>
-      <c r="K124" s="18"/>
-      <c r="L124" s="18"/>
+      <c r="A124" s="54"/>
+      <c r="B124" s="54"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="54"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="54"/>
+      <c r="H124" s="54"/>
+      <c r="I124" s="54"/>
+      <c r="J124" s="54"/>
+      <c r="K124" s="54"/>
+      <c r="L124" s="54"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="18"/>
-      <c r="B125" s="18"/>
-      <c r="C125" s="18"/>
-      <c r="D125" s="18"/>
-      <c r="E125" s="18"/>
-      <c r="F125" s="18"/>
-      <c r="G125" s="18"/>
-      <c r="H125" s="18"/>
-      <c r="I125" s="18"/>
-      <c r="J125" s="18"/>
-      <c r="K125" s="18"/>
-      <c r="L125" s="18"/>
+      <c r="A125" s="54"/>
+      <c r="B125" s="54"/>
+      <c r="C125" s="54"/>
+      <c r="D125" s="54"/>
+      <c r="E125" s="54"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="54"/>
+      <c r="H125" s="54"/>
+      <c r="I125" s="54"/>
+      <c r="J125" s="54"/>
+      <c r="K125" s="54"/>
+      <c r="L125" s="54"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="18"/>
-      <c r="B126" s="18"/>
-      <c r="C126" s="18"/>
-      <c r="D126" s="18"/>
-      <c r="E126" s="18"/>
-      <c r="F126" s="18"/>
-      <c r="G126" s="18"/>
-      <c r="H126" s="18"/>
-      <c r="I126" s="18"/>
-      <c r="J126" s="18"/>
-      <c r="K126" s="18"/>
-      <c r="L126" s="18"/>
+      <c r="A126" s="54"/>
+      <c r="B126" s="54"/>
+      <c r="C126" s="54"/>
+      <c r="D126" s="54"/>
+      <c r="E126" s="54"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="54"/>
+      <c r="H126" s="54"/>
+      <c r="I126" s="54"/>
+      <c r="J126" s="54"/>
+      <c r="K126" s="54"/>
+      <c r="L126" s="54"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="18"/>
-      <c r="B127" s="18"/>
-      <c r="C127" s="18"/>
-      <c r="D127" s="18"/>
-      <c r="E127" s="18"/>
-      <c r="F127" s="18"/>
-      <c r="G127" s="18"/>
-      <c r="H127" s="18"/>
-      <c r="I127" s="18"/>
-      <c r="J127" s="18"/>
-      <c r="K127" s="18"/>
-      <c r="L127" s="18"/>
+      <c r="A127" s="54"/>
+      <c r="B127" s="54"/>
+      <c r="C127" s="54"/>
+      <c r="D127" s="54"/>
+      <c r="E127" s="54"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="54"/>
+      <c r="H127" s="54"/>
+      <c r="I127" s="54"/>
+      <c r="J127" s="54"/>
+      <c r="K127" s="54"/>
+      <c r="L127" s="54"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="18"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="18"/>
-      <c r="F128" s="18"/>
-      <c r="G128" s="18"/>
-      <c r="H128" s="18"/>
-      <c r="I128" s="18"/>
-      <c r="J128" s="18"/>
-      <c r="K128" s="18"/>
-      <c r="L128" s="18"/>
+      <c r="A128" s="54"/>
+      <c r="B128" s="54"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="54"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="54"/>
+      <c r="J128" s="54"/>
+      <c r="K128" s="54"/>
+      <c r="L128" s="54"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="18"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
-      <c r="F129" s="18"/>
-      <c r="G129" s="18"/>
-      <c r="H129" s="18"/>
-      <c r="I129" s="18"/>
-      <c r="J129" s="18"/>
-      <c r="K129" s="18"/>
-      <c r="L129" s="18"/>
+      <c r="A129" s="54"/>
+      <c r="B129" s="54"/>
+      <c r="C129" s="54"/>
+      <c r="D129" s="54"/>
+      <c r="E129" s="54"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="54"/>
+      <c r="I129" s="54"/>
+      <c r="J129" s="54"/>
+      <c r="K129" s="54"/>
+      <c r="L129" s="54"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="18"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
-      <c r="F130" s="18"/>
-      <c r="G130" s="18"/>
-      <c r="H130" s="18"/>
-      <c r="I130" s="18"/>
-      <c r="J130" s="18"/>
-      <c r="K130" s="18"/>
-      <c r="L130" s="18"/>
+      <c r="A130" s="54"/>
+      <c r="B130" s="54"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="54"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
+      <c r="H130" s="54"/>
+      <c r="I130" s="54"/>
+      <c r="J130" s="54"/>
+      <c r="K130" s="54"/>
+      <c r="L130" s="54"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="18"/>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="18"/>
+      <c r="A131" s="54"/>
+      <c r="B131" s="54"/>
+      <c r="C131" s="54"/>
+      <c r="D131" s="54"/>
+      <c r="E131" s="54"/>
+      <c r="F131" s="54"/>
+      <c r="G131" s="54"/>
+      <c r="H131" s="54"/>
+      <c r="I131" s="54"/>
+      <c r="J131" s="54"/>
+      <c r="K131" s="54"/>
+      <c r="L131" s="54"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="18"/>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="18"/>
-      <c r="H132" s="18"/>
-      <c r="I132" s="18"/>
-      <c r="J132" s="18"/>
-      <c r="K132" s="18"/>
-      <c r="L132" s="18"/>
+      <c r="A132" s="54"/>
+      <c r="B132" s="54"/>
+      <c r="C132" s="54"/>
+      <c r="D132" s="54"/>
+      <c r="E132" s="54"/>
+      <c r="F132" s="54"/>
+      <c r="G132" s="54"/>
+      <c r="H132" s="54"/>
+      <c r="I132" s="54"/>
+      <c r="J132" s="54"/>
+      <c r="K132" s="54"/>
+      <c r="L132" s="54"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="18"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="18"/>
-      <c r="H133" s="18"/>
-      <c r="I133" s="18"/>
-      <c r="J133" s="18"/>
-      <c r="K133" s="18"/>
-      <c r="L133" s="18"/>
+      <c r="A133" s="54"/>
+      <c r="B133" s="54"/>
+      <c r="C133" s="54"/>
+      <c r="D133" s="54"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="54"/>
+      <c r="H133" s="54"/>
+      <c r="I133" s="54"/>
+      <c r="J133" s="54"/>
+      <c r="K133" s="54"/>
+      <c r="L133" s="54"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="18"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="18"/>
-      <c r="H134" s="18"/>
-      <c r="I134" s="18"/>
-      <c r="J134" s="18"/>
-      <c r="K134" s="18"/>
-      <c r="L134" s="18"/>
+      <c r="A134" s="54"/>
+      <c r="B134" s="54"/>
+      <c r="C134" s="54"/>
+      <c r="D134" s="54"/>
+      <c r="E134" s="54"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="54"/>
+      <c r="H134" s="54"/>
+      <c r="I134" s="54"/>
+      <c r="J134" s="54"/>
+      <c r="K134" s="54"/>
+      <c r="L134" s="54"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="18"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="18"/>
-      <c r="H135" s="18"/>
-      <c r="I135" s="18"/>
-      <c r="J135" s="18"/>
-      <c r="K135" s="18"/>
-      <c r="L135" s="18"/>
+      <c r="A135" s="54"/>
+      <c r="B135" s="54"/>
+      <c r="C135" s="54"/>
+      <c r="D135" s="54"/>
+      <c r="E135" s="54"/>
+      <c r="F135" s="54"/>
+      <c r="G135" s="54"/>
+      <c r="H135" s="54"/>
+      <c r="I135" s="54"/>
+      <c r="J135" s="54"/>
+      <c r="K135" s="54"/>
+      <c r="L135" s="54"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="18"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="18"/>
-      <c r="H136" s="18"/>
-      <c r="I136" s="18"/>
-      <c r="J136" s="18"/>
-      <c r="K136" s="18"/>
-      <c r="L136" s="18"/>
+      <c r="A136" s="68"/>
+      <c r="B136" s="68"/>
+      <c r="C136" s="68"/>
+      <c r="D136" s="68"/>
+      <c r="E136" s="68"/>
+      <c r="F136" s="68"/>
+      <c r="G136" s="68"/>
+      <c r="H136" s="68"/>
+      <c r="I136" s="68"/>
+      <c r="J136" s="68"/>
+      <c r="K136" s="68"/>
+      <c r="L136" s="68"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="18"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
-      <c r="K137" s="18"/>
-      <c r="L137" s="18"/>
+      <c r="A137" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="69">
+        <f>SUM(B116:B136)</f>
+        <v>0.2326388889</v>
+      </c>
+      <c r="C137" s="68"/>
+      <c r="D137" s="69">
+        <f>SUM(D116:D118)</f>
+        <v>0.2292361111</v>
+      </c>
+      <c r="E137" s="68"/>
+      <c r="F137" s="68"/>
+      <c r="G137" s="68"/>
+      <c r="H137" s="69">
+        <f>SUM(H116:H135)</f>
+        <v>0.02300925926</v>
+      </c>
+      <c r="I137" s="68"/>
+      <c r="J137" s="69">
+        <f>SUM(J116:J136)</f>
+        <v>0.2292361111</v>
+      </c>
+      <c r="K137" s="68"/>
+      <c r="L137" s="69">
+        <f>SUM(L116:L135)</f>
+        <v>0.3020833333</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1"/>
     <row r="139" ht="14.25" customHeight="1"/>
@@ -6081,123 +6219,123 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>81</v>
+      <c r="C3" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="65">
+      <c r="B4" s="71">
         <v>1.0</v>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="72">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="66">
+      <c r="D4" s="72">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="65">
+      <c r="B5" s="71">
         <v>2.0</v>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="72">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="72">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="65">
+      <c r="B6" s="71">
         <v>3.0</v>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="72">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="72">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="65">
+      <c r="B7" s="71">
         <v>4.0</v>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="72">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="66">
+      <c r="D7" s="72">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="65">
+      <c r="B8" s="71">
         <v>5.0</v>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="72">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="66">
+      <c r="D8" s="72">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="65">
+      <c r="B9" s="71">
         <v>6.0</v>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="72">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="72">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="65">
+      <c r="B10" s="71">
         <v>7.0</v>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="72">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="67">
+      <c r="D10" s="73">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="65">
+      <c r="B11" s="71">
         <v>8.0</v>
       </c>
-      <c r="C11" s="67">
+      <c r="C11" s="73">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="67">
+      <c r="D11" s="73">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="65">
+      <c r="B12" s="71">
         <v>9.0</v>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="73">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="67">
+      <c r="D12" s="73">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="65">
+      <c r="B13" s="71">
         <v>10.0</v>
       </c>
-      <c r="C13" s="67">
+      <c r="C13" s="73">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="72">
         <v>45965.0</v>
       </c>
     </row>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="89">
   <si>
     <t>Semana</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>Revisión de Especificación de Casos de Uso a implementar / Modelo de Datos</t>
+  </si>
+  <si>
+    <t>Riesgos 24/10</t>
   </si>
   <si>
     <t>Especificación CU12</t>
@@ -1253,7 +1256,7 @@
       </c>
       <c r="B10" s="5">
         <f>Registro!B137</f>
-        <v>0.2326388889</v>
+        <v>0.2935185185</v>
       </c>
       <c r="C10" s="5">
         <f>Registro!D137</f>
@@ -1274,7 +1277,7 @@
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>1.016203704</v>
+        <v>1.077083333</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>14</v>
@@ -1286,7 +1289,7 @@
       </c>
       <c r="B11" s="15">
         <f t="shared" ref="B11:C11" si="2">SUM(B2:B10)</f>
-        <v>3.075625</v>
+        <v>3.13650463</v>
       </c>
       <c r="C11" s="15">
         <f t="shared" si="2"/>
@@ -1310,7 +1313,7 @@
       </c>
       <c r="H11" s="15">
         <f>SUM(Total!$B11:$G11)</f>
-        <v>13.53027778</v>
+        <v>13.59115741</v>
       </c>
       <c r="I11" s="16"/>
     </row>
@@ -4978,10 +4981,14 @@
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="54"/>
-      <c r="B117" s="54"/>
+      <c r="A117" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B117" s="64">
+        <v>0.06087962962962963</v>
+      </c>
       <c r="C117" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D117" s="67">
         <v>0.05625</v>
@@ -4989,19 +4996,19 @@
       <c r="E117" s="54"/>
       <c r="F117" s="54"/>
       <c r="G117" s="32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H117" s="67">
         <v>0.014282407407407407</v>
       </c>
       <c r="I117" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J117" s="67">
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L117" s="9">
         <v>0.1076388888888889</v>
@@ -5011,7 +5018,7 @@
       <c r="A118" s="54"/>
       <c r="B118" s="54"/>
       <c r="C118" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D118" s="64">
         <v>0.07368055555555555</v>
@@ -5021,7 +5028,7 @@
       <c r="G118" s="54"/>
       <c r="H118" s="54"/>
       <c r="I118" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J118" s="64">
         <v>0.07368055555555555</v>
@@ -5287,7 +5294,7 @@
       </c>
       <c r="B137" s="69">
         <f>SUM(B116:B136)</f>
-        <v>0.2326388889</v>
+        <v>0.2935185185</v>
       </c>
       <c r="C137" s="68"/>
       <c r="D137" s="69">
@@ -6223,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
   <si>
     <t>Semana</t>
   </si>
@@ -272,6 +272,9 @@
     <t>Especificación CU12</t>
   </si>
   <si>
+    <t>Implementación CU09,CU12</t>
+  </si>
+  <si>
     <t>Revisión de Especificación de CU 09 y 20</t>
   </si>
   <si>
@@ -279,6 +282,18 @@
   </si>
   <si>
     <t>Especificación CU09</t>
+  </si>
+  <si>
+    <t>Implementación CU20</t>
+  </si>
+  <si>
+    <t>Casos de prueba CU's primera tanda</t>
+  </si>
+  <si>
+    <t>Ejecución Casos de prueba CU's primera tanda</t>
+  </si>
+  <si>
+    <t>Revisión casos de prueba</t>
   </si>
   <si>
     <t>Fecha de inicio</t>
@@ -476,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -647,6 +662,7 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -1256,20 +1272,23 @@
       </c>
       <c r="B10" s="5">
         <f>Registro!B137</f>
-        <v>0.2935185185</v>
+        <v>0.3587962963</v>
       </c>
       <c r="C10" s="5">
         <f>Registro!D137</f>
         <v>0.2292361111</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="5">
+        <f>Registro!F137</f>
+        <v>1.383240741</v>
+      </c>
       <c r="E10" s="5">
         <f>Registro!H137</f>
-        <v>0.02300925926</v>
+        <v>0.4480324074</v>
       </c>
       <c r="F10" s="5">
         <f>Registro!J137</f>
-        <v>0.2292361111</v>
+        <v>0.4821180556</v>
       </c>
       <c r="G10" s="5">
         <f>Registro!L137</f>
@@ -1277,7 +1296,7 @@
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>1.077083333</v>
+        <v>3.203506944</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>14</v>
@@ -1288,32 +1307,32 @@
         <v>15</v>
       </c>
       <c r="B11" s="15">
-        <f t="shared" ref="B11:C11" si="2">SUM(B2:B10)</f>
-        <v>3.13650463</v>
+        <f t="shared" ref="B11:G11" si="2">SUM(B2:B10)</f>
+        <v>3.201782407</v>
       </c>
       <c r="C11" s="15">
         <f t="shared" si="2"/>
         <v>4.086979167</v>
       </c>
       <c r="D11" s="15">
-        <f>SUM(D2:D9)</f>
-        <v>2.202731481</v>
+        <f t="shared" si="2"/>
+        <v>3.585972222</v>
       </c>
       <c r="E11" s="15">
-        <f t="shared" ref="E11:G11" si="3">SUM(E2:E10)</f>
-        <v>0.5461574074</v>
+        <f t="shared" si="2"/>
+        <v>0.9711805556</v>
       </c>
       <c r="F11" s="15">
-        <f t="shared" si="3"/>
-        <v>2.353414352</v>
+        <f t="shared" si="2"/>
+        <v>2.606296296</v>
       </c>
       <c r="G11" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1.26537037</v>
       </c>
       <c r="H11" s="15">
         <f>SUM(Total!$B11:$G11)</f>
-        <v>13.59115741</v>
+        <v>15.71758102</v>
       </c>
       <c r="I11" s="16"/>
     </row>
@@ -2335,7 +2354,7 @@
     <col customWidth="1" min="4" max="4" width="39.5"/>
     <col customWidth="1" min="5" max="5" width="27.63"/>
     <col customWidth="1" min="6" max="6" width="17.75"/>
-    <col customWidth="1" min="7" max="7" width="38.75"/>
+    <col customWidth="1" min="7" max="7" width="40.25"/>
     <col customWidth="1" min="8" max="8" width="27.63"/>
     <col customWidth="1" min="9" max="9" width="54.63"/>
     <col customWidth="1" min="10" max="10" width="27.63"/>
@@ -4993,10 +5012,14 @@
       <c r="D117" s="67">
         <v>0.05625</v>
       </c>
-      <c r="E117" s="54"/>
-      <c r="F117" s="54"/>
+      <c r="E117" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F117" s="67">
+        <v>0.6346296296296297</v>
+      </c>
       <c r="G117" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H117" s="67">
         <v>0.014282407407407407</v>
@@ -5008,27 +5031,39 @@
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L117" s="9">
         <v>0.1076388888888889</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="54"/>
-      <c r="B118" s="54"/>
+      <c r="A118" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B118" s="64">
+        <v>0.06527777777777778</v>
+      </c>
       <c r="C118" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D118" s="64">
         <v>0.07368055555555555</v>
       </c>
-      <c r="E118" s="54"/>
-      <c r="F118" s="54"/>
-      <c r="G118" s="54"/>
-      <c r="H118" s="54"/>
+      <c r="E118" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F118" s="67">
+        <v>0.04513888888888889</v>
+      </c>
+      <c r="G118" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H118" s="67">
+        <v>0.18760416666666666</v>
+      </c>
       <c r="I118" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J118" s="64">
         <v>0.07368055555555555</v>
@@ -5041,12 +5076,24 @@
       <c r="B119" s="54"/>
       <c r="C119" s="54"/>
       <c r="D119" s="54"/>
-      <c r="E119" s="54"/>
-      <c r="F119" s="54"/>
-      <c r="G119" s="54"/>
-      <c r="H119" s="54"/>
-      <c r="I119" s="54"/>
-      <c r="J119" s="54"/>
+      <c r="E119" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F119" s="67">
+        <v>0.225</v>
+      </c>
+      <c r="G119" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="H119" s="67">
+        <v>0.08680555555555555</v>
+      </c>
+      <c r="I119" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="J119" s="67">
+        <v>0.18760416666666666</v>
+      </c>
       <c r="K119" s="54"/>
       <c r="L119" s="54"/>
     </row>
@@ -5055,12 +5102,24 @@
       <c r="B120" s="54"/>
       <c r="C120" s="54"/>
       <c r="D120" s="54"/>
-      <c r="E120" s="54"/>
-      <c r="F120" s="54"/>
-      <c r="G120" s="54"/>
-      <c r="H120" s="54"/>
-      <c r="I120" s="54"/>
-      <c r="J120" s="54"/>
+      <c r="E120" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F120" s="67">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="G120" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H120" s="67">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I120" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="J120" s="64">
+        <v>0.06527777777777778</v>
+      </c>
       <c r="K120" s="54"/>
       <c r="L120" s="54"/>
     </row>
@@ -5069,10 +5128,18 @@
       <c r="B121" s="54"/>
       <c r="C121" s="54"/>
       <c r="D121" s="54"/>
-      <c r="E121" s="54"/>
-      <c r="F121" s="54"/>
-      <c r="G121" s="54"/>
-      <c r="H121" s="54"/>
+      <c r="E121" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F121" s="67">
+        <v>0.10972222222222222</v>
+      </c>
+      <c r="G121" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H121" s="67">
+        <v>0.015196759259259259</v>
+      </c>
       <c r="I121" s="54"/>
       <c r="J121" s="54"/>
       <c r="K121" s="54"/>
@@ -5083,8 +5150,12 @@
       <c r="B122" s="54"/>
       <c r="C122" s="54"/>
       <c r="D122" s="54"/>
-      <c r="E122" s="54"/>
-      <c r="F122" s="54"/>
+      <c r="E122" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" s="67">
+        <v>0.10972222222222222</v>
+      </c>
       <c r="G122" s="54"/>
       <c r="H122" s="54"/>
       <c r="I122" s="54"/>
@@ -5294,7 +5365,7 @@
       </c>
       <c r="B137" s="69">
         <f>SUM(B116:B136)</f>
-        <v>0.2935185185</v>
+        <v>0.3587962963</v>
       </c>
       <c r="C137" s="68"/>
       <c r="D137" s="69">
@@ -5302,16 +5373,19 @@
         <v>0.2292361111</v>
       </c>
       <c r="E137" s="68"/>
-      <c r="F137" s="68"/>
+      <c r="F137" s="70">
+        <f>SUM(F117:F135)</f>
+        <v>1.383240741</v>
+      </c>
       <c r="G137" s="68"/>
       <c r="H137" s="69">
         <f>SUM(H116:H135)</f>
-        <v>0.02300925926</v>
+        <v>0.4480324074</v>
       </c>
       <c r="I137" s="68"/>
       <c r="J137" s="69">
         <f>SUM(J116:J136)</f>
-        <v>0.2292361111</v>
+        <v>0.4821180556</v>
       </c>
       <c r="K137" s="68"/>
       <c r="L137" s="69">
@@ -6226,123 +6300,123 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="70" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>88</v>
+      <c r="C3" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="71" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="71">
+      <c r="B4" s="72">
         <v>1.0</v>
       </c>
-      <c r="C4" s="72">
+      <c r="C4" s="73">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="73">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="71">
+      <c r="B5" s="72">
         <v>2.0</v>
       </c>
-      <c r="C5" s="72">
+      <c r="C5" s="73">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="73">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="71">
+      <c r="B6" s="72">
         <v>3.0</v>
       </c>
-      <c r="C6" s="72">
+      <c r="C6" s="73">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="73">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="71">
+      <c r="B7" s="72">
         <v>4.0</v>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="73">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="73">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="71">
+      <c r="B8" s="72">
         <v>5.0</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="73">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="73">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="71">
+      <c r="B9" s="72">
         <v>6.0</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="73">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="72">
+      <c r="D9" s="73">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="71">
+      <c r="B10" s="72">
         <v>7.0</v>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="73">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="74">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="71">
+      <c r="B11" s="72">
         <v>8.0</v>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="74">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="74">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="71">
+      <c r="B12" s="72">
         <v>9.0</v>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="74">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="74">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="71">
+      <c r="B13" s="72">
         <v>10.0</v>
       </c>
-      <c r="C13" s="73">
+      <c r="C13" s="74">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="73">
         <v>45965.0</v>
       </c>
     </row>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="eWdMrhJoTS4M4QFoS5GozNlFDlzJzdV0I1r1+OHyOmg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="bl2uqCJVoNfeO6CgraTRhAj+M3kdyVVGkVn0x8CSVRg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="102">
   <si>
     <t>Semana</t>
   </si>
@@ -294,6 +294,30 @@
   </si>
   <si>
     <t>Revisión casos de prueba</t>
+  </si>
+  <si>
+    <t>Semana 10</t>
+  </si>
+  <si>
+    <t>Especificación de CU15: Visualizar tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU07: crear etapa</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de Prueba Primera tanda</t>
+  </si>
+  <si>
+    <t>Reunión 30/10</t>
+  </si>
+  <si>
+    <t>Cierre de Iteración</t>
+  </si>
+  <si>
+    <t>Priorización de CU's 2da tanda</t>
+  </si>
+  <si>
+    <t>Revisión documento de CU's priorizados 2da tanda</t>
   </si>
   <si>
     <t>Fecha de inicio</t>
@@ -311,7 +335,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -377,13 +401,18 @@
       <name val="Docs-Roboto"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,6 +435,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -491,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -529,35 +570,42 @@
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="46" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -577,7 +625,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -587,7 +635,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -663,7 +711,26 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="8" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -741,7 +808,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I11" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I12" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="Semana" id="1"/>
     <tableColumn name="Análisis" id="2"/>
@@ -1271,27 +1338,27 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="5">
-        <f>Registro!B137</f>
+        <f>Registro!B125</f>
         <v>0.3587962963</v>
       </c>
       <c r="C10" s="5">
-        <f>Registro!D137</f>
+        <f>Registro!D125</f>
         <v>0.2292361111</v>
       </c>
       <c r="D10" s="5">
-        <f>Registro!F137</f>
+        <f>Registro!F125</f>
         <v>1.383240741</v>
       </c>
       <c r="E10" s="5">
-        <f>Registro!H137</f>
+        <f>Registro!H125</f>
         <v>0.4480324074</v>
       </c>
       <c r="F10" s="5">
-        <f>Registro!J137</f>
+        <f>Registro!J125</f>
         <v>0.4821180556</v>
       </c>
       <c r="G10" s="5">
-        <f>Registro!L137</f>
+        <f>Registro!L125</f>
         <v>0.3020833333</v>
       </c>
       <c r="H10" s="5">
@@ -1303,45 +1370,75 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="15">
+        <f>Registro!B146</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <f>Registro!D146</f>
+        <v>0.04717592593</v>
+      </c>
+      <c r="D11" s="15">
+        <f>Registro!F146</f>
+        <v>0.1041666667</v>
+      </c>
+      <c r="E11" s="15">
+        <f>Registro!H146</f>
+        <v>0.4132986111</v>
+      </c>
+      <c r="F11" s="15">
+        <f>Registro!J146</f>
+        <v>0.2320023148</v>
+      </c>
+      <c r="G11" s="15">
+        <f>Registro!L146</f>
+        <v>0.1041666667</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="15">
-        <f t="shared" ref="B11:G11" si="2">SUM(B2:B10)</f>
+      <c r="B12" s="18">
+        <f>SUM(B2:B10)</f>
         <v>3.201782407</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C12" s="18">
+        <f t="shared" ref="C12:G12" si="2">SUM(C2:C11)</f>
+        <v>4.134155093</v>
+      </c>
+      <c r="D12" s="18">
         <f t="shared" si="2"/>
-        <v>4.086979167</v>
-      </c>
-      <c r="D11" s="15">
+        <v>3.690138889</v>
+      </c>
+      <c r="E12" s="18">
         <f t="shared" si="2"/>
-        <v>3.585972222</v>
-      </c>
-      <c r="E11" s="15">
+        <v>1.384479167</v>
+      </c>
+      <c r="F12" s="18">
         <f t="shared" si="2"/>
-        <v>0.9711805556</v>
-      </c>
-      <c r="F11" s="15">
+        <v>2.838298611</v>
+      </c>
+      <c r="G12" s="18">
         <f t="shared" si="2"/>
-        <v>2.606296296</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" si="2"/>
-        <v>1.26537037</v>
-      </c>
-      <c r="H11" s="15">
-        <f>SUM(Total!$B11:$G11)</f>
-        <v>15.71758102</v>
-      </c>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1"/>
+        <v>1.369537037</v>
+      </c>
+      <c r="H12" s="18">
+        <f>SUM(Total!$B12:$G12)</f>
+        <v>16.6183912</v>
+      </c>
+      <c r="I12" s="19"/>
+    </row>
     <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="14" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="H15" s="20"/>
+    </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
@@ -2330,6 +2427,7 @@
     <row r="1001" ht="14.25" customHeight="1"/>
     <row r="1002" ht="14.25" customHeight="1"/>
     <row r="1003" ht="14.25" customHeight="1"/>
+    <row r="1004" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -2354,7 +2452,7 @@
     <col customWidth="1" min="4" max="4" width="39.5"/>
     <col customWidth="1" min="5" max="5" width="27.63"/>
     <col customWidth="1" min="6" max="6" width="17.75"/>
-    <col customWidth="1" min="7" max="7" width="40.25"/>
+    <col customWidth="1" min="7" max="7" width="44.75"/>
     <col customWidth="1" min="8" max="8" width="27.63"/>
     <col customWidth="1" min="9" max="9" width="54.63"/>
     <col customWidth="1" min="10" max="10" width="27.63"/>
@@ -2364,292 +2462,292 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="18"/>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="19" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="21" t="s">
+      <c r="I1" s="25"/>
+      <c r="J1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="21" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="26" t="s">
+      <c r="D2" s="30"/>
+      <c r="E2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="26" t="s">
+      <c r="F2" s="30"/>
+      <c r="G2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="26" t="s">
+      <c r="H2" s="30"/>
+      <c r="I2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="26" t="s">
+      <c r="J2" s="30"/>
+      <c r="K2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="27"/>
+      <c r="L2" s="30"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="6">
         <v>0.05783564814814815</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="10" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="9">
         <v>0.03487268518518519</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="10" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="K3" s="30"/>
+      <c r="K3" s="33"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="5">
         <v>1.1574074074074075E-4</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="7">
         <v>0.06111111111111111</v>
       </c>
-      <c r="K4" s="30"/>
+      <c r="K4" s="33"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="5">
         <v>0.04273148148148148</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
       <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7">
         <v>0.019791666666666666</v>
       </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="5">
         <v>0.002939814814814815</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
       <c r="I6" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7">
         <v>0.039780092592592596</v>
       </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="5">
         <v>0.06607638888888889</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
       <c r="I7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="9">
         <v>0.0798611111111111</v>
       </c>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="5">
         <v>0.06518518518518518</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="31" t="s">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="34" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="13">
         <v>0.03515046296296296</v>
       </c>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>0.0798611111111111</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J9" s="7">
         <v>0.06607638888888889</v>
       </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="5">
         <v>0.019791666666666666</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="9">
         <v>0.05783564814814815</v>
       </c>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="5">
         <v>0.039780092592592596</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="5">
         <v>0.028356481481481483</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="31" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="5">
         <v>0.013148148148148148</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="10" t="s">
@@ -2658,108 +2756,108 @@
       <c r="B14" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="38">
         <f>SUM(B3:B14)</f>
         <v>0.4929050926</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="36">
+      <c r="F15" s="39">
         <f>SUM(F3:F14)</f>
         <v>0.03487268519</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="36">
+      <c r="J15" s="39">
         <f>SUM(J3:J14)</f>
         <v>0.4366898148</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="36">
+      <c r="L15" s="39">
         <f>SUM(L3:L14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="24"/>
-      <c r="B16" s="21" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="21" t="s">
+      <c r="C16" s="29"/>
+      <c r="D16" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="21" t="s">
+      <c r="E16" s="29"/>
+      <c r="F16" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="21" t="s">
+      <c r="G16" s="29"/>
+      <c r="H16" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="21" t="s">
+      <c r="I16" s="29"/>
+      <c r="J16" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="21" t="s">
+      <c r="K16" s="29"/>
+      <c r="L16" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="26" t="s">
+      <c r="D17" s="30"/>
+      <c r="E17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="26" t="s">
+      <c r="F17" s="30"/>
+      <c r="G17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="27"/>
-      <c r="I17" s="26" t="s">
+      <c r="H17" s="30"/>
+      <c r="I17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="26" t="s">
+      <c r="J17" s="30"/>
+      <c r="K17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="27"/>
+      <c r="L17" s="30"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
@@ -2772,20 +2870,20 @@
       <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
@@ -2802,7 +2900,7 @@
       <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="K19" s="38" t="s">
+      <c r="K19" s="41" t="s">
         <v>35</v>
       </c>
       <c r="L19" s="7">
@@ -2810,29 +2908,29 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
       <c r="G20" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="42" t="s">
         <v>36</v>
       </c>
       <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="K20" s="38" t="s">
+      <c r="K20" s="41" t="s">
         <v>35</v>
       </c>
       <c r="L20" s="7">
@@ -2840,411 +2938,411 @@
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B37" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="39">
         <f>SUM(B18:B37)</f>
         <v>0.4042824074</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40">
+      <c r="E38" s="43"/>
+      <c r="F38" s="43">
         <f>SUM(F17:F36)</f>
         <v>0.689375</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="36">
+      <c r="H38" s="39">
         <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40">
+      <c r="I38" s="43"/>
+      <c r="J38" s="43">
         <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40">
+      <c r="K38" s="43"/>
+      <c r="L38" s="43">
         <f>SUM(L18:L36)</f>
         <v>0.03163194444</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="24"/>
-      <c r="B39" s="21" t="s">
+      <c r="A39" s="27"/>
+      <c r="B39" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="26"/>
-      <c r="D39" s="21" t="s">
+      <c r="C39" s="29"/>
+      <c r="D39" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="29"/>
+      <c r="F39" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="26"/>
-      <c r="H39" s="21" t="s">
+      <c r="G39" s="29"/>
+      <c r="H39" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="21" t="s">
+      <c r="I39" s="29"/>
+      <c r="J39" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="26"/>
-      <c r="L39" s="21" t="s">
+      <c r="K39" s="29"/>
+      <c r="L39" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="26" t="s">
+      <c r="D40" s="30"/>
+      <c r="E40" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="26" t="s">
+      <c r="F40" s="30"/>
+      <c r="G40" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="27"/>
-      <c r="I40" s="26" t="s">
+      <c r="H40" s="30"/>
+      <c r="I40" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J40" s="27"/>
-      <c r="K40" s="26" t="s">
+      <c r="J40" s="30"/>
+      <c r="K40" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L40" s="27"/>
+      <c r="L40" s="30"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6">
         <v>0.23333333333333334</v>
       </c>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
       <c r="I41" s="10" t="s">
         <v>38</v>
       </c>
@@ -3259,18 +3357,18 @@
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="10" t="s">
         <v>38</v>
       </c>
@@ -3285,18 +3383,18 @@
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
       <c r="I43" s="10" t="s">
         <v>38</v>
       </c>
@@ -3311,317 +3409,317 @@
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
       <c r="I44" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
       <c r="I45" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
       <c r="I46" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
       <c r="I47" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
       <c r="I48" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
       <c r="I49" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="28" t="s">
+      <c r="A50" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
       <c r="I50" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
       <c r="I51" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="43"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
-      <c r="K53" s="43"/>
-      <c r="L53" s="44"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="46"/>
+      <c r="K53" s="46"/>
+      <c r="L53" s="47"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="32"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="34" t="s">
+      <c r="A59" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="36">
+      <c r="B59" s="39">
         <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="40">
+      <c r="F59" s="43">
         <f>SUM(F41:F58)</f>
         <v>0.2333333333</v>
       </c>
@@ -3631,72 +3729,72 @@
         <v>0</v>
       </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="36">
+      <c r="J59" s="39">
         <f>SUM(J41:J58)</f>
         <v>0.218587963</v>
       </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="36">
+      <c r="L59" s="39">
         <f>SUM(L41:L58)</f>
         <v>0.161875</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="24"/>
-      <c r="B60" s="21" t="s">
+      <c r="A60" s="27"/>
+      <c r="B60" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="26"/>
-      <c r="D60" s="21" t="s">
+      <c r="C60" s="29"/>
+      <c r="D60" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="26"/>
-      <c r="F60" s="21" t="s">
+      <c r="E60" s="29"/>
+      <c r="F60" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="26"/>
-      <c r="H60" s="21" t="s">
+      <c r="G60" s="29"/>
+      <c r="H60" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="26"/>
-      <c r="J60" s="21" t="s">
+      <c r="I60" s="29"/>
+      <c r="J60" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="26"/>
-      <c r="L60" s="21" t="s">
+      <c r="K60" s="29"/>
+      <c r="L60" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B61" s="41" t="s">
+      <c r="B61" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="26" t="s">
+      <c r="D61" s="30"/>
+      <c r="E61" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="27"/>
-      <c r="G61" s="26" t="s">
+      <c r="F61" s="30"/>
+      <c r="G61" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H61" s="27"/>
-      <c r="I61" s="26" t="s">
+      <c r="H61" s="30"/>
+      <c r="I61" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J61" s="27"/>
-      <c r="K61" s="26" t="s">
+      <c r="J61" s="30"/>
+      <c r="K61" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L61" s="27"/>
+      <c r="L61" s="30"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="28" t="s">
+      <c r="A62" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="7">
@@ -3722,20 +3820,20 @@
       <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="K62" s="29"/>
-      <c r="L62" s="29"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
       <c r="G63" s="10" t="s">
         <v>43</v>
       </c>
@@ -3748,316 +3846,316 @@
       <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="28" t="s">
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="31" t="s">
         <v>44</v>
       </c>
       <c r="J64" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="28" t="s">
+      <c r="A65" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="29"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="29"/>
-      <c r="K65" s="29"/>
-      <c r="L65" s="29"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="32"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="31" t="s">
         <v>44</v>
       </c>
       <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="32"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="28" t="s">
+      <c r="A71" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="28" t="s">
+      <c r="A72" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="29"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="28" t="s">
+      <c r="A73" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="29"/>
-      <c r="L73" s="29"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
+      <c r="L73" s="32"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="28" t="s">
+      <c r="A74" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="29"/>
-      <c r="L74" s="29"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="32"/>
+      <c r="L74" s="32"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="34" t="s">
+      <c r="A75" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B75" s="36">
+      <c r="B75" s="39">
         <f>SUM(B62:B74)</f>
         <v>0.6286805556</v>
       </c>
-      <c r="C75" s="45"/>
-      <c r="D75" s="35">
+      <c r="C75" s="48"/>
+      <c r="D75" s="38">
         <f>SUM(D62:D74)</f>
         <v>0.0244212963</v>
       </c>
-      <c r="E75" s="46"/>
-      <c r="F75" s="36">
+      <c r="E75" s="49"/>
+      <c r="F75" s="39">
         <f>SUM(F62:F74)</f>
         <v>0.09237268519</v>
       </c>
-      <c r="G75" s="46"/>
-      <c r="H75" s="36">
+      <c r="G75" s="49"/>
+      <c r="H75" s="39">
         <f>SUM(H62:H74)</f>
         <v>0.1780092593</v>
       </c>
-      <c r="I75" s="46"/>
-      <c r="J75" s="36">
+      <c r="I75" s="49"/>
+      <c r="J75" s="39">
         <f>SUM(J62:J74)</f>
         <v>0.2304861111</v>
       </c>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
+      <c r="K75" s="49"/>
+      <c r="L75" s="49"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="24"/>
-      <c r="B76" s="21" t="s">
+      <c r="A76" s="27"/>
+      <c r="B76" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C76" s="26"/>
-      <c r="D76" s="21" t="s">
+      <c r="C76" s="29"/>
+      <c r="D76" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="26"/>
-      <c r="F76" s="21" t="s">
+      <c r="E76" s="29"/>
+      <c r="F76" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="26"/>
-      <c r="H76" s="21" t="s">
+      <c r="G76" s="29"/>
+      <c r="H76" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="26"/>
-      <c r="J76" s="21" t="s">
+      <c r="I76" s="29"/>
+      <c r="J76" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="26"/>
-      <c r="L76" s="21" t="s">
+      <c r="K76" s="29"/>
+      <c r="L76" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="24" t="s">
+      <c r="A77" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="41" t="s">
+      <c r="B77" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="26" t="s">
+      <c r="C77" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="27"/>
-      <c r="E77" s="26" t="s">
+      <c r="D77" s="30"/>
+      <c r="E77" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F77" s="27"/>
-      <c r="G77" s="26" t="s">
+      <c r="F77" s="30"/>
+      <c r="G77" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H77" s="27"/>
-      <c r="I77" s="26" t="s">
+      <c r="H77" s="30"/>
+      <c r="I77" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J77" s="27"/>
-      <c r="K77" s="26" t="s">
+      <c r="J77" s="30"/>
+      <c r="K77" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L77" s="27"/>
+      <c r="L77" s="30"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="28" t="s">
+      <c r="A78" s="31" t="s">
         <v>46</v>
       </c>
       <c r="B78" s="7">
         <v>0.125</v>
       </c>
-      <c r="C78" s="47" t="s">
+      <c r="C78" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="D78" s="48">
+      <c r="D78" s="51">
         <v>0.11513888888888889</v>
       </c>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48">
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="51"/>
+      <c r="H78" s="51">
         <v>0.013888888888888888</v>
       </c>
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="31" t="s">
         <v>48</v>
       </c>
       <c r="J78" s="7">
@@ -4071,232 +4169,232 @@
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="28" t="s">
+      <c r="A79" s="31" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="7">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C79" s="47" t="s">
+      <c r="C79" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="48">
+      <c r="D79" s="51">
         <v>0.5638888888888889</v>
       </c>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="28" t="s">
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="J79" s="50">
+      <c r="J79" s="53">
         <v>0.09305555555555556</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="32" t="s">
+      <c r="A80" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B80" s="51">
+      <c r="B80" s="54">
         <v>0.0625</v>
       </c>
-      <c r="C80" s="47" t="s">
+      <c r="C80" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="55">
         <v>0.19444444444444445</v>
       </c>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="31" t="s">
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="34" t="s">
         <v>51</v>
       </c>
       <c r="J80" s="13">
         <v>0.041666666666666664</v>
       </c>
-      <c r="K80" s="49"/>
-      <c r="L80" s="49"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="52"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="32" t="s">
+      <c r="A81" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B81" s="53">
+      <c r="B81" s="56">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C81" s="48"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="49"/>
-      <c r="J81" s="49"/>
-      <c r="K81" s="48"/>
-      <c r="L81" s="48"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
+      <c r="H81" s="52"/>
+      <c r="I81" s="52"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="51"/>
+      <c r="L81" s="51"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="28" t="s">
+      <c r="A82" s="31" t="s">
         <v>52</v>
       </c>
       <c r="B82" s="9">
         <v>0.05763888888888889</v>
       </c>
-      <c r="C82" s="48"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
-      <c r="H82" s="49"/>
-      <c r="I82" s="49"/>
-      <c r="J82" s="49"/>
-      <c r="K82" s="49"/>
-      <c r="L82" s="49"/>
+      <c r="C82" s="51"/>
+      <c r="D82" s="51"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="52"/>
+      <c r="G82" s="52"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="52"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="52"/>
+      <c r="L82" s="52"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="54"/>
+      <c r="A83" s="57"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="48"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="49"/>
-      <c r="G83" s="49"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="49"/>
-      <c r="K83" s="49"/>
-      <c r="L83" s="49"/>
+      <c r="C83" s="51"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
+      <c r="H83" s="52"/>
+      <c r="I83" s="52"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="52"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="54"/>
+      <c r="A84" s="57"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="49"/>
-      <c r="J84" s="49"/>
-      <c r="K84" s="49"/>
-      <c r="L84" s="49"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
+      <c r="I84" s="52"/>
+      <c r="J84" s="52"/>
+      <c r="K84" s="52"/>
+      <c r="L84" s="52"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="54"/>
+      <c r="A85" s="57"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="55"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="G85" s="49"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="49"/>
-      <c r="J85" s="49"/>
-      <c r="K85" s="55"/>
-      <c r="L85" s="55"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
+      <c r="H85" s="52"/>
+      <c r="I85" s="52"/>
+      <c r="J85" s="52"/>
+      <c r="K85" s="58"/>
+      <c r="L85" s="58"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B86" s="40">
+      <c r="B86" s="43">
         <f>SUM(B78:B85)</f>
         <v>0.3979166667</v>
       </c>
-      <c r="C86" s="56"/>
-      <c r="D86" s="56">
+      <c r="C86" s="59"/>
+      <c r="D86" s="59">
         <f>SUM(D78:D83)</f>
         <v>0.8734722222</v>
       </c>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="35">
+      <c r="E86" s="60"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="38">
         <f>SUM(H78:H85)</f>
         <v>0.01388888889</v>
       </c>
-      <c r="I86" s="57"/>
-      <c r="J86" s="35">
+      <c r="I86" s="60"/>
+      <c r="J86" s="38">
         <f>SUM(J78:J85)</f>
         <v>0.2180555556</v>
       </c>
-      <c r="K86" s="40"/>
-      <c r="L86" s="40">
+      <c r="K86" s="43"/>
+      <c r="L86" s="43">
         <f>SUM(L78:L80)</f>
         <v>0.03333333333</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="24"/>
-      <c r="B87" s="21" t="s">
+      <c r="A87" s="27"/>
+      <c r="B87" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C87" s="26"/>
-      <c r="D87" s="21" t="s">
+      <c r="C87" s="29"/>
+      <c r="D87" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="26"/>
-      <c r="F87" s="21" t="s">
+      <c r="E87" s="29"/>
+      <c r="F87" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="26"/>
-      <c r="H87" s="21" t="s">
+      <c r="G87" s="29"/>
+      <c r="H87" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I87" s="26"/>
-      <c r="J87" s="21" t="s">
+      <c r="I87" s="29"/>
+      <c r="J87" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="26"/>
-      <c r="L87" s="21" t="s">
+      <c r="K87" s="29"/>
+      <c r="L87" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="24" t="s">
+      <c r="A88" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B88" s="41" t="s">
+      <c r="B88" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C88" s="26" t="s">
+      <c r="C88" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D88" s="27"/>
-      <c r="E88" s="26" t="s">
+      <c r="D88" s="30"/>
+      <c r="E88" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F88" s="27"/>
-      <c r="G88" s="26" t="s">
+      <c r="F88" s="30"/>
+      <c r="G88" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H88" s="27"/>
-      <c r="I88" s="26" t="s">
+      <c r="H88" s="30"/>
+      <c r="I88" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J88" s="27"/>
-      <c r="K88" s="26" t="s">
+      <c r="J88" s="30"/>
+      <c r="K88" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L88" s="27"/>
+      <c r="L88" s="30"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="54"/>
+      <c r="A89" s="57"/>
       <c r="B89" s="7">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C89" s="47" t="s">
+      <c r="C89" s="50" t="s">
         <v>54</v>
       </c>
       <c r="D89" s="13">
         <v>0.17631944444444445</v>
       </c>
-      <c r="E89" s="58" t="s">
+      <c r="E89" s="61" t="s">
         <v>55</v>
       </c>
       <c r="F89" s="7">
@@ -4322,28 +4420,28 @@
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="54"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="47" t="s">
+      <c r="A90" s="57"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="50" t="s">
         <v>59</v>
       </c>
       <c r="D90" s="13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E90" s="58" t="s">
+      <c r="E90" s="61" t="s">
         <v>55</v>
       </c>
       <c r="F90" s="7">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G90" s="39" t="s">
+      <c r="G90" s="42" t="s">
         <v>60</v>
       </c>
       <c r="H90" s="7">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I90" s="29"/>
-      <c r="J90" s="29"/>
+      <c r="I90" s="32"/>
+      <c r="J90" s="32"/>
       <c r="K90" s="10" t="s">
         <v>58</v>
       </c>
@@ -4352,15 +4450,15 @@
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="54"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="47" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="D91" s="50">
+      <c r="D91" s="53">
         <v>0.32806712962962964</v>
       </c>
-      <c r="E91" s="58" t="s">
+      <c r="E91" s="61" t="s">
         <v>55</v>
       </c>
       <c r="F91" s="7">
@@ -4372,8 +4470,8 @@
       <c r="H91" s="7">
         <v>0.06527777777777778</v>
       </c>
-      <c r="I91" s="29"/>
-      <c r="J91" s="29"/>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
       <c r="K91" s="10" t="s">
         <v>62</v>
       </c>
@@ -4382,333 +4480,333 @@
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="54"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="49"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="29"/>
-      <c r="F92" s="29"/>
-      <c r="G92" s="29"/>
-      <c r="H92" s="29"/>
-      <c r="I92" s="29"/>
-      <c r="J92" s="29"/>
-      <c r="K92" s="29"/>
-      <c r="L92" s="29"/>
+      <c r="A92" s="57"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="32"/>
+      <c r="H92" s="32"/>
+      <c r="I92" s="32"/>
+      <c r="J92" s="32"/>
+      <c r="K92" s="32"/>
+      <c r="L92" s="32"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B93" s="40">
+      <c r="B93" s="43">
         <f>SUM(B89)</f>
         <v>0.08333333333</v>
       </c>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56">
+      <c r="C93" s="59"/>
+      <c r="D93" s="59">
         <f>SUM(D89:D92)</f>
         <v>0.6710532407</v>
       </c>
-      <c r="E93" s="40"/>
-      <c r="F93" s="40">
+      <c r="E93" s="43"/>
+      <c r="F93" s="43">
         <f>SUM(F89:F91)</f>
         <v>0.8770833333</v>
       </c>
-      <c r="G93" s="40"/>
-      <c r="H93" s="40">
+      <c r="G93" s="43"/>
+      <c r="H93" s="43">
         <f>SUM(H89:H91)</f>
         <v>0.3071064815</v>
       </c>
-      <c r="I93" s="40"/>
-      <c r="J93" s="40">
+      <c r="I93" s="43"/>
+      <c r="J93" s="43">
         <f>SUM(J89)</f>
         <v>0.003472222222</v>
       </c>
-      <c r="K93" s="40"/>
-      <c r="L93" s="40">
+      <c r="K93" s="43"/>
+      <c r="L93" s="43">
         <f>SUM(L89:L91)</f>
         <v>0.4239467593</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="24"/>
-      <c r="B94" s="21" t="s">
+      <c r="A94" s="27"/>
+      <c r="B94" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C94" s="26"/>
-      <c r="D94" s="21" t="s">
+      <c r="C94" s="29"/>
+      <c r="D94" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E94" s="26"/>
-      <c r="F94" s="21" t="s">
+      <c r="E94" s="29"/>
+      <c r="F94" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="26"/>
-      <c r="H94" s="21" t="s">
+      <c r="G94" s="29"/>
+      <c r="H94" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="26"/>
-      <c r="J94" s="21" t="s">
+      <c r="I94" s="29"/>
+      <c r="J94" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="26"/>
-      <c r="L94" s="21" t="s">
+      <c r="K94" s="29"/>
+      <c r="L94" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="59" t="s">
+      <c r="A95" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="60" t="s">
+      <c r="B95" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="C95" s="61" t="s">
+      <c r="C95" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D95" s="29"/>
-      <c r="E95" s="61" t="s">
+      <c r="D95" s="32"/>
+      <c r="E95" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="F95" s="29"/>
-      <c r="G95" s="61" t="s">
+      <c r="F95" s="32"/>
+      <c r="G95" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="H95" s="29"/>
-      <c r="I95" s="61" t="s">
+      <c r="H95" s="32"/>
+      <c r="I95" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J95" s="29"/>
-      <c r="K95" s="61" t="s">
+      <c r="J95" s="32"/>
+      <c r="K95" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="L95" s="29"/>
+      <c r="L95" s="32"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="28" t="s">
+      <c r="A96" s="31" t="s">
         <v>64</v>
       </c>
       <c r="B96" s="9">
         <v>0.020833333333333332</v>
       </c>
-      <c r="C96" s="47" t="s">
+      <c r="C96" s="50" t="s">
         <v>65</v>
       </c>
       <c r="D96" s="13">
         <v>0.5</v>
       </c>
-      <c r="E96" s="29"/>
-      <c r="F96" s="29"/>
-      <c r="G96" s="29"/>
-      <c r="H96" s="29"/>
+      <c r="E96" s="32"/>
+      <c r="F96" s="32"/>
+      <c r="G96" s="32"/>
+      <c r="H96" s="32"/>
       <c r="I96" s="10" t="s">
         <v>66</v>
       </c>
       <c r="J96" s="9">
         <v>0.022222222222222223</v>
       </c>
-      <c r="K96" s="29"/>
-      <c r="L96" s="29"/>
+      <c r="K96" s="32"/>
+      <c r="L96" s="32"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="28" t="s">
+      <c r="A97" s="31" t="s">
         <v>67</v>
       </c>
       <c r="B97" s="9">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C97" s="47" t="s">
+      <c r="C97" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D97" s="50">
+      <c r="D97" s="53">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="29"/>
-      <c r="H97" s="29"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="32"/>
+      <c r="H97" s="32"/>
       <c r="I97" s="10" t="s">
         <v>69</v>
       </c>
       <c r="J97" s="9">
         <v>0.06859953703703704</v>
       </c>
-      <c r="K97" s="29"/>
-      <c r="L97" s="29"/>
+      <c r="K97" s="32"/>
+      <c r="L97" s="32"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="54"/>
+      <c r="A98" s="57"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="47" t="s">
+      <c r="C98" s="50" t="s">
         <v>68</v>
       </c>
       <c r="D98" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
-      <c r="G98" s="29"/>
-      <c r="H98" s="29"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
       <c r="I98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="J98" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="K98" s="29"/>
-      <c r="L98" s="29"/>
+      <c r="K98" s="32"/>
+      <c r="L98" s="32"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="54"/>
+      <c r="A99" s="57"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="47" t="s">
+      <c r="C99" s="50" t="s">
         <v>68</v>
       </c>
       <c r="D99" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E99" s="29"/>
-      <c r="F99" s="29"/>
-      <c r="G99" s="29"/>
-      <c r="H99" s="29"/>
-      <c r="I99" s="31" t="s">
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J99" s="50">
+      <c r="J99" s="53">
         <v>0.03420138888888889</v>
       </c>
-      <c r="K99" s="29"/>
-      <c r="L99" s="29"/>
+      <c r="K99" s="32"/>
+      <c r="L99" s="32"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="28"/>
+      <c r="A100" s="31"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="47" t="s">
+      <c r="C100" s="50" t="s">
         <v>70</v>
       </c>
       <c r="D100" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="E100" s="29"/>
-      <c r="F100" s="29"/>
-      <c r="G100" s="29"/>
-      <c r="H100" s="29"/>
-      <c r="I100" s="31" t="s">
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="34" t="s">
         <v>68</v>
       </c>
       <c r="J100" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K100" s="29"/>
-      <c r="L100" s="29"/>
+      <c r="K100" s="32"/>
+      <c r="L100" s="32"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="28"/>
+      <c r="A101" s="31"/>
       <c r="B101" s="9"/>
-      <c r="C101" s="49"/>
-      <c r="D101" s="62"/>
-      <c r="E101" s="29"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="29"/>
-      <c r="H101" s="29"/>
-      <c r="I101" s="31" t="s">
+      <c r="C101" s="52"/>
+      <c r="D101" s="65"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="34" t="s">
         <v>68</v>
       </c>
       <c r="J101" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K101" s="29"/>
-      <c r="L101" s="29"/>
+      <c r="K101" s="32"/>
+      <c r="L101" s="32"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="34" t="s">
+      <c r="A102" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B102" s="36">
+      <c r="B102" s="39">
         <f>SUM(B96:B101)</f>
         <v>0.06805555556</v>
       </c>
-      <c r="C102" s="45"/>
-      <c r="D102" s="35">
+      <c r="C102" s="48"/>
+      <c r="D102" s="38">
         <f>SUM(D96:D101)</f>
         <v>0.8178472222</v>
       </c>
-      <c r="E102" s="46"/>
-      <c r="F102" s="46"/>
-      <c r="G102" s="46"/>
-      <c r="H102" s="46"/>
-      <c r="I102" s="46"/>
-      <c r="J102" s="36">
+      <c r="E102" s="49"/>
+      <c r="F102" s="49"/>
+      <c r="G102" s="49"/>
+      <c r="H102" s="49"/>
+      <c r="I102" s="49"/>
+      <c r="J102" s="39">
         <f>SUM(J96:J101)</f>
         <v>0.4086689815</v>
       </c>
-      <c r="K102" s="46"/>
-      <c r="L102" s="46"/>
+      <c r="K102" s="49"/>
+      <c r="L102" s="49"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="24"/>
-      <c r="B103" s="21" t="s">
+      <c r="A103" s="27"/>
+      <c r="B103" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C103" s="26"/>
-      <c r="D103" s="21" t="s">
+      <c r="C103" s="29"/>
+      <c r="D103" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E103" s="26"/>
-      <c r="F103" s="21" t="s">
+      <c r="E103" s="29"/>
+      <c r="F103" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G103" s="26"/>
-      <c r="H103" s="21" t="s">
+      <c r="G103" s="29"/>
+      <c r="H103" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I103" s="26"/>
-      <c r="J103" s="21" t="s">
+      <c r="I103" s="29"/>
+      <c r="J103" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K103" s="26"/>
-      <c r="L103" s="21" t="s">
+      <c r="K103" s="29"/>
+      <c r="L103" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="59" t="s">
+      <c r="A104" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B104" s="60" t="s">
+      <c r="B104" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="C104" s="61" t="s">
+      <c r="C104" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="D104" s="29"/>
-      <c r="E104" s="61" t="s">
+      <c r="D104" s="32"/>
+      <c r="E104" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="F104" s="63"/>
-      <c r="G104" s="61" t="s">
+      <c r="F104" s="66"/>
+      <c r="G104" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="H104" s="29"/>
-      <c r="I104" s="61" t="s">
+      <c r="H104" s="32"/>
+      <c r="I104" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J104" s="29"/>
-      <c r="K104" s="61" t="s">
+      <c r="J104" s="32"/>
+      <c r="K104" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="L104" s="29"/>
+      <c r="L104" s="32"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="28" t="s">
+      <c r="A105" s="31" t="s">
         <v>67</v>
       </c>
       <c r="B105" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C105" s="47" t="s">
+      <c r="C105" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D105" s="50">
+      <c r="D105" s="53">
         <v>0.03420138888888889</v>
       </c>
       <c r="E105" s="10" t="s">
@@ -4717,12 +4815,12 @@
       <c r="F105" s="6">
         <v>0.27569444444444446</v>
       </c>
-      <c r="G105" s="29"/>
-      <c r="H105" s="29"/>
-      <c r="I105" s="31" t="s">
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
+      <c r="I105" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="J105" s="50">
+      <c r="J105" s="53">
         <v>0.1909722222222222</v>
       </c>
       <c r="K105" s="9"/>
@@ -4731,18 +4829,18 @@
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="28"/>
+      <c r="A106" s="31"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="47" t="s">
+      <c r="C106" s="50" t="s">
         <v>68</v>
       </c>
       <c r="D106" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E106" s="29"/>
-      <c r="F106" s="29"/>
-      <c r="G106" s="29"/>
-      <c r="H106" s="29"/>
+      <c r="E106" s="32"/>
+      <c r="F106" s="32"/>
+      <c r="G106" s="32"/>
+      <c r="H106" s="32"/>
       <c r="I106" s="10" t="s">
         <v>73</v>
       </c>
@@ -4757,26 +4855,26 @@
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="28" t="s">
+      <c r="A107" s="31" t="s">
         <v>75</v>
       </c>
       <c r="B107" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C107" s="47" t="s">
+      <c r="C107" s="50" t="s">
         <v>68</v>
       </c>
       <c r="D107" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E107" s="29"/>
-      <c r="F107" s="29"/>
-      <c r="G107" s="29"/>
-      <c r="H107" s="29"/>
-      <c r="I107" s="31" t="s">
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="32"/>
+      <c r="H107" s="32"/>
+      <c r="I107" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="J107" s="50">
+      <c r="J107" s="53">
         <v>0.03420138888888889</v>
       </c>
       <c r="K107" s="10" t="s">
@@ -4787,209 +4885,209 @@
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="54"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="47" t="s">
+      <c r="A108" s="57"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="50" t="s">
         <v>77</v>
       </c>
       <c r="D108" s="13">
         <v>0.3076388888888889</v>
       </c>
-      <c r="E108" s="29"/>
-      <c r="F108" s="29"/>
-      <c r="G108" s="29"/>
-      <c r="H108" s="29"/>
-      <c r="I108" s="31" t="s">
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+      <c r="I108" s="34" t="s">
         <v>68</v>
       </c>
       <c r="J108" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K108" s="29"/>
-      <c r="L108" s="29"/>
+      <c r="K108" s="32"/>
+      <c r="L108" s="32"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="54"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="47" t="s">
+      <c r="A109" s="57"/>
+      <c r="B109" s="32"/>
+      <c r="C109" s="50" t="s">
         <v>77</v>
       </c>
       <c r="D109" s="13">
         <v>0.24097222222222223</v>
       </c>
-      <c r="E109" s="29"/>
-      <c r="F109" s="29"/>
-      <c r="G109" s="29"/>
-      <c r="H109" s="29"/>
-      <c r="I109" s="31" t="s">
+      <c r="E109" s="32"/>
+      <c r="F109" s="32"/>
+      <c r="G109" s="32"/>
+      <c r="H109" s="32"/>
+      <c r="I109" s="34" t="s">
         <v>68</v>
       </c>
       <c r="J109" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K109" s="29"/>
-      <c r="L109" s="29"/>
+      <c r="K109" s="32"/>
+      <c r="L109" s="32"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="54"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="47" t="s">
+      <c r="A110" s="57"/>
+      <c r="B110" s="32"/>
+      <c r="C110" s="50" t="s">
         <v>78</v>
       </c>
       <c r="D110" s="13">
         <v>0.10609953703703703</v>
       </c>
-      <c r="E110" s="29"/>
-      <c r="F110" s="29"/>
-      <c r="G110" s="29"/>
-      <c r="H110" s="29"/>
-      <c r="I110" s="28" t="s">
+      <c r="E110" s="32"/>
+      <c r="F110" s="32"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="32"/>
+      <c r="I110" s="31" t="s">
         <v>75</v>
       </c>
       <c r="J110" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="K110" s="29"/>
-      <c r="L110" s="29"/>
+      <c r="K110" s="32"/>
+      <c r="L110" s="32"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="54"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="49"/>
-      <c r="D111" s="49"/>
-      <c r="E111" s="29"/>
-      <c r="F111" s="29"/>
-      <c r="G111" s="29"/>
-      <c r="H111" s="29"/>
-      <c r="I111" s="29"/>
-      <c r="J111" s="29"/>
-      <c r="K111" s="29"/>
-      <c r="L111" s="29"/>
+      <c r="A111" s="57"/>
+      <c r="B111" s="32"/>
+      <c r="C111" s="52"/>
+      <c r="D111" s="52"/>
+      <c r="E111" s="32"/>
+      <c r="F111" s="32"/>
+      <c r="G111" s="32"/>
+      <c r="H111" s="32"/>
+      <c r="I111" s="32"/>
+      <c r="J111" s="32"/>
+      <c r="K111" s="32"/>
+      <c r="L111" s="32"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="54"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="49"/>
-      <c r="D112" s="49"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-      <c r="J112" s="29"/>
-      <c r="K112" s="29"/>
-      <c r="L112" s="29"/>
+      <c r="A112" s="57"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="52"/>
+      <c r="D112" s="52"/>
+      <c r="E112" s="32"/>
+      <c r="F112" s="32"/>
+      <c r="G112" s="32"/>
+      <c r="H112" s="32"/>
+      <c r="I112" s="32"/>
+      <c r="J112" s="32"/>
+      <c r="K112" s="32"/>
+      <c r="L112" s="32"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="34" t="s">
+      <c r="A113" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="40">
+      <c r="B113" s="43">
         <f>SUM(B105:B112)</f>
         <v>0.2798611111</v>
       </c>
-      <c r="C113" s="45"/>
-      <c r="D113" s="56">
+      <c r="C113" s="48"/>
+      <c r="D113" s="59">
         <f>SUM(D105:D112)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="E113" s="46"/>
-      <c r="F113" s="40">
+      <c r="E113" s="49"/>
+      <c r="F113" s="43">
         <f>SUM(F105:F112)</f>
         <v>0.2756944444</v>
       </c>
-      <c r="G113" s="46"/>
-      <c r="H113" s="46"/>
-      <c r="I113" s="46"/>
-      <c r="J113" s="40">
+      <c r="G113" s="49"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="49"/>
+      <c r="J113" s="43">
         <f>SUM(J105:J112)</f>
         <v>0.5817361111</v>
       </c>
-      <c r="K113" s="46"/>
-      <c r="L113" s="36">
+      <c r="K113" s="49"/>
+      <c r="L113" s="39">
         <f>SUM(L105:L112)</f>
         <v>0.3125</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="24"/>
-      <c r="B114" s="21" t="s">
+      <c r="A114" s="27"/>
+      <c r="B114" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C114" s="26"/>
-      <c r="D114" s="21" t="s">
+      <c r="C114" s="29"/>
+      <c r="D114" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E114" s="26"/>
-      <c r="F114" s="21" t="s">
+      <c r="E114" s="29"/>
+      <c r="F114" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G114" s="26"/>
-      <c r="H114" s="21" t="s">
+      <c r="G114" s="29"/>
+      <c r="H114" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I114" s="26"/>
-      <c r="J114" s="21" t="s">
+      <c r="I114" s="29"/>
+      <c r="J114" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K114" s="26"/>
-      <c r="L114" s="21" t="s">
+      <c r="K114" s="29"/>
+      <c r="L114" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B115" s="41" t="s">
+      <c r="B115" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="C115" s="26" t="s">
+      <c r="C115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D115" s="27"/>
-      <c r="E115" s="26" t="s">
+      <c r="D115" s="30"/>
+      <c r="E115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F115" s="27"/>
-      <c r="G115" s="26" t="s">
+      <c r="F115" s="30"/>
+      <c r="G115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="H115" s="27"/>
-      <c r="I115" s="26" t="s">
+      <c r="H115" s="30"/>
+      <c r="I115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J115" s="27"/>
-      <c r="K115" s="26" t="s">
+      <c r="J115" s="30"/>
+      <c r="K115" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L115" s="27"/>
+      <c r="L115" s="30"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="28" t="s">
+      <c r="A116" s="31" t="s">
         <v>75</v>
       </c>
       <c r="B116" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C116" s="28" t="s">
+      <c r="C116" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D116" s="64">
+      <c r="D116" s="67">
         <v>0.09930555555555555</v>
       </c>
-      <c r="E116" s="54"/>
-      <c r="F116" s="54"/>
-      <c r="G116" s="65" t="s">
+      <c r="E116" s="57"/>
+      <c r="F116" s="57"/>
+      <c r="G116" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="H116" s="66">
+      <c r="H116" s="69">
         <v>0.008726851851851852</v>
       </c>
-      <c r="I116" s="28" t="s">
+      <c r="I116" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="J116" s="64">
+      <c r="J116" s="67">
         <v>0.09930555555555555</v>
       </c>
       <c r="K116" s="10" t="s">
@@ -5000,34 +5098,34 @@
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="28" t="s">
+      <c r="A117" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B117" s="64">
+      <c r="B117" s="67">
         <v>0.06087962962962963</v>
       </c>
-      <c r="C117" s="28" t="s">
+      <c r="C117" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D117" s="67">
+      <c r="D117" s="70">
         <v>0.05625</v>
       </c>
-      <c r="E117" s="28" t="s">
+      <c r="E117" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="F117" s="67">
+      <c r="F117" s="70">
         <v>0.6346296296296297</v>
       </c>
-      <c r="G117" s="32" t="s">
+      <c r="G117" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="H117" s="67">
+      <c r="H117" s="70">
         <v>0.014282407407407407</v>
       </c>
-      <c r="I117" s="28" t="s">
+      <c r="I117" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="J117" s="67">
+      <c r="J117" s="70">
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
@@ -5038,370 +5136,572 @@
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="28" t="s">
+      <c r="A118" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B118" s="64">
+      <c r="B118" s="67">
         <v>0.06527777777777778</v>
       </c>
-      <c r="C118" s="28" t="s">
+      <c r="C118" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D118" s="64">
+      <c r="D118" s="67">
         <v>0.07368055555555555</v>
       </c>
-      <c r="E118" s="28" t="s">
+      <c r="E118" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="F118" s="67">
+      <c r="F118" s="70">
         <v>0.04513888888888889</v>
       </c>
-      <c r="G118" s="28" t="s">
+      <c r="G118" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="H118" s="67">
+      <c r="H118" s="70">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I118" s="28" t="s">
+      <c r="I118" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="J118" s="64">
+      <c r="J118" s="67">
         <v>0.07368055555555555</v>
       </c>
-      <c r="K118" s="54"/>
-      <c r="L118" s="54"/>
+      <c r="K118" s="57"/>
+      <c r="L118" s="57"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="54"/>
-      <c r="B119" s="54"/>
-      <c r="C119" s="54"/>
-      <c r="D119" s="54"/>
-      <c r="E119" s="28" t="s">
+      <c r="A119" s="57"/>
+      <c r="B119" s="57"/>
+      <c r="C119" s="57"/>
+      <c r="D119" s="57"/>
+      <c r="E119" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="F119" s="67">
+      <c r="F119" s="70">
         <v>0.225</v>
       </c>
-      <c r="G119" s="28" t="s">
+      <c r="G119" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="H119" s="67">
+      <c r="H119" s="70">
         <v>0.08680555555555555</v>
       </c>
-      <c r="I119" s="28" t="s">
+      <c r="I119" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="J119" s="67">
+      <c r="J119" s="70">
         <v>0.18760416666666666</v>
       </c>
-      <c r="K119" s="54"/>
-      <c r="L119" s="54"/>
+      <c r="K119" s="57"/>
+      <c r="L119" s="57"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="54"/>
-      <c r="B120" s="54"/>
-      <c r="C120" s="54"/>
-      <c r="D120" s="54"/>
-      <c r="E120" s="28" t="s">
+      <c r="A120" s="57"/>
+      <c r="B120" s="57"/>
+      <c r="C120" s="57"/>
+      <c r="D120" s="57"/>
+      <c r="E120" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="F120" s="67">
+      <c r="F120" s="70">
         <v>0.2590277777777778</v>
       </c>
-      <c r="G120" s="28" t="s">
+      <c r="G120" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="H120" s="67">
+      <c r="H120" s="70">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I120" s="28" t="s">
+      <c r="I120" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="J120" s="64">
+      <c r="J120" s="67">
         <v>0.06527777777777778</v>
       </c>
-      <c r="K120" s="54"/>
-      <c r="L120" s="54"/>
+      <c r="K120" s="57"/>
+      <c r="L120" s="57"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="54"/>
-      <c r="B121" s="54"/>
-      <c r="C121" s="54"/>
-      <c r="D121" s="54"/>
-      <c r="E121" s="28" t="s">
+      <c r="A121" s="57"/>
+      <c r="B121" s="57"/>
+      <c r="C121" s="57"/>
+      <c r="D121" s="57"/>
+      <c r="E121" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="F121" s="67">
+      <c r="F121" s="70">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G121" s="28" t="s">
+      <c r="G121" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="H121" s="67">
+      <c r="H121" s="70">
         <v>0.015196759259259259</v>
       </c>
-      <c r="I121" s="54"/>
-      <c r="J121" s="54"/>
-      <c r="K121" s="54"/>
-      <c r="L121" s="54"/>
+      <c r="I121" s="57"/>
+      <c r="J121" s="57"/>
+      <c r="K121" s="57"/>
+      <c r="L121" s="57"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="54"/>
-      <c r="B122" s="54"/>
-      <c r="C122" s="54"/>
-      <c r="D122" s="54"/>
-      <c r="E122" s="28" t="s">
+      <c r="A122" s="57"/>
+      <c r="B122" s="57"/>
+      <c r="C122" s="57"/>
+      <c r="D122" s="57"/>
+      <c r="E122" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="F122" s="67">
+      <c r="F122" s="70">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G122" s="54"/>
-      <c r="H122" s="54"/>
-      <c r="I122" s="54"/>
-      <c r="J122" s="54"/>
-      <c r="K122" s="54"/>
-      <c r="L122" s="54"/>
+      <c r="G122" s="57"/>
+      <c r="H122" s="57"/>
+      <c r="I122" s="57"/>
+      <c r="J122" s="57"/>
+      <c r="K122" s="57"/>
+      <c r="L122" s="57"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="54"/>
-      <c r="B123" s="54"/>
-      <c r="C123" s="54"/>
-      <c r="D123" s="54"/>
-      <c r="E123" s="54"/>
-      <c r="F123" s="54"/>
-      <c r="G123" s="54"/>
-      <c r="H123" s="54"/>
-      <c r="I123" s="54"/>
-      <c r="J123" s="54"/>
-      <c r="K123" s="54"/>
-      <c r="L123" s="54"/>
+      <c r="A123" s="57"/>
+      <c r="B123" s="57"/>
+      <c r="C123" s="57"/>
+      <c r="D123" s="57"/>
+      <c r="E123" s="57"/>
+      <c r="F123" s="57"/>
+      <c r="G123" s="57"/>
+      <c r="H123" s="57"/>
+      <c r="I123" s="57"/>
+      <c r="J123" s="57"/>
+      <c r="K123" s="57"/>
+      <c r="L123" s="57"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="54"/>
-      <c r="B124" s="54"/>
-      <c r="C124" s="54"/>
-      <c r="D124" s="54"/>
-      <c r="E124" s="54"/>
-      <c r="F124" s="54"/>
-      <c r="G124" s="54"/>
-      <c r="H124" s="54"/>
-      <c r="I124" s="54"/>
-      <c r="J124" s="54"/>
-      <c r="K124" s="54"/>
-      <c r="L124" s="54"/>
+      <c r="A124" s="71"/>
+      <c r="B124" s="71"/>
+      <c r="C124" s="71"/>
+      <c r="D124" s="71"/>
+      <c r="E124" s="71"/>
+      <c r="F124" s="71"/>
+      <c r="G124" s="71"/>
+      <c r="H124" s="71"/>
+      <c r="I124" s="71"/>
+      <c r="J124" s="71"/>
+      <c r="K124" s="71"/>
+      <c r="L124" s="71"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="54"/>
-      <c r="B125" s="54"/>
-      <c r="C125" s="54"/>
-      <c r="D125" s="54"/>
-      <c r="E125" s="54"/>
-      <c r="F125" s="54"/>
-      <c r="G125" s="54"/>
-      <c r="H125" s="54"/>
-      <c r="I125" s="54"/>
-      <c r="J125" s="54"/>
-      <c r="K125" s="54"/>
-      <c r="L125" s="54"/>
-    </row>
-    <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="54"/>
-      <c r="B126" s="54"/>
-      <c r="C126" s="54"/>
-      <c r="D126" s="54"/>
-      <c r="E126" s="54"/>
-      <c r="F126" s="54"/>
-      <c r="G126" s="54"/>
-      <c r="H126" s="54"/>
-      <c r="I126" s="54"/>
-      <c r="J126" s="54"/>
-      <c r="K126" s="54"/>
-      <c r="L126" s="54"/>
-    </row>
-    <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="54"/>
-      <c r="B127" s="54"/>
-      <c r="C127" s="54"/>
-      <c r="D127" s="54"/>
-      <c r="E127" s="54"/>
-      <c r="F127" s="54"/>
-      <c r="G127" s="54"/>
-      <c r="H127" s="54"/>
-      <c r="I127" s="54"/>
-      <c r="J127" s="54"/>
-      <c r="K127" s="54"/>
-      <c r="L127" s="54"/>
-    </row>
-    <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="54"/>
-      <c r="B128" s="54"/>
-      <c r="C128" s="54"/>
-      <c r="D128" s="54"/>
-      <c r="E128" s="54"/>
-      <c r="F128" s="54"/>
-      <c r="G128" s="54"/>
-      <c r="H128" s="54"/>
-      <c r="I128" s="54"/>
-      <c r="J128" s="54"/>
-      <c r="K128" s="54"/>
-      <c r="L128" s="54"/>
-    </row>
-    <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="54"/>
-      <c r="B129" s="54"/>
-      <c r="C129" s="54"/>
-      <c r="D129" s="54"/>
-      <c r="E129" s="54"/>
-      <c r="F129" s="54"/>
-      <c r="G129" s="54"/>
-      <c r="H129" s="54"/>
-      <c r="I129" s="54"/>
-      <c r="J129" s="54"/>
-      <c r="K129" s="54"/>
-      <c r="L129" s="54"/>
-    </row>
-    <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="54"/>
-      <c r="B130" s="54"/>
-      <c r="C130" s="54"/>
-      <c r="D130" s="54"/>
-      <c r="E130" s="54"/>
-      <c r="F130" s="54"/>
-      <c r="G130" s="54"/>
-      <c r="H130" s="54"/>
-      <c r="I130" s="54"/>
-      <c r="J130" s="54"/>
-      <c r="K130" s="54"/>
-      <c r="L130" s="54"/>
-    </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="54"/>
-      <c r="B131" s="54"/>
-      <c r="C131" s="54"/>
-      <c r="D131" s="54"/>
-      <c r="E131" s="54"/>
-      <c r="F131" s="54"/>
-      <c r="G131" s="54"/>
-      <c r="H131" s="54"/>
-      <c r="I131" s="54"/>
-      <c r="J131" s="54"/>
-      <c r="K131" s="54"/>
-      <c r="L131" s="54"/>
-    </row>
-    <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="54"/>
-      <c r="B132" s="54"/>
-      <c r="C132" s="54"/>
-      <c r="D132" s="54"/>
-      <c r="E132" s="54"/>
-      <c r="F132" s="54"/>
-      <c r="G132" s="54"/>
-      <c r="H132" s="54"/>
-      <c r="I132" s="54"/>
-      <c r="J132" s="54"/>
-      <c r="K132" s="54"/>
-      <c r="L132" s="54"/>
-    </row>
-    <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="54"/>
-      <c r="B133" s="54"/>
-      <c r="C133" s="54"/>
-      <c r="D133" s="54"/>
-      <c r="E133" s="54"/>
-      <c r="F133" s="54"/>
-      <c r="G133" s="54"/>
-      <c r="H133" s="54"/>
-      <c r="I133" s="54"/>
-      <c r="J133" s="54"/>
-      <c r="K133" s="54"/>
-      <c r="L133" s="54"/>
-    </row>
-    <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="54"/>
-      <c r="B134" s="54"/>
-      <c r="C134" s="54"/>
-      <c r="D134" s="54"/>
-      <c r="E134" s="54"/>
-      <c r="F134" s="54"/>
-      <c r="G134" s="54"/>
-      <c r="H134" s="54"/>
-      <c r="I134" s="54"/>
-      <c r="J134" s="54"/>
-      <c r="K134" s="54"/>
-      <c r="L134" s="54"/>
-    </row>
-    <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="54"/>
-      <c r="B135" s="54"/>
-      <c r="C135" s="54"/>
-      <c r="D135" s="54"/>
-      <c r="E135" s="54"/>
-      <c r="F135" s="54"/>
-      <c r="G135" s="54"/>
-      <c r="H135" s="54"/>
-      <c r="I135" s="54"/>
-      <c r="J135" s="54"/>
-      <c r="K135" s="54"/>
-      <c r="L135" s="54"/>
-    </row>
-    <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="68"/>
-      <c r="B136" s="68"/>
-      <c r="C136" s="68"/>
-      <c r="D136" s="68"/>
-      <c r="E136" s="68"/>
-      <c r="F136" s="68"/>
-      <c r="G136" s="68"/>
-      <c r="H136" s="68"/>
-      <c r="I136" s="68"/>
-      <c r="J136" s="68"/>
-      <c r="K136" s="68"/>
-      <c r="L136" s="68"/>
-    </row>
-    <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="34" t="s">
+      <c r="A125" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B137" s="69">
-        <f>SUM(B116:B136)</f>
+      <c r="B125" s="72">
+        <f>SUM(B116:B124)</f>
         <v>0.3587962963</v>
       </c>
-      <c r="C137" s="68"/>
-      <c r="D137" s="69">
+      <c r="C125" s="71"/>
+      <c r="D125" s="72">
         <f>SUM(D116:D118)</f>
         <v>0.2292361111</v>
       </c>
-      <c r="E137" s="68"/>
-      <c r="F137" s="70">
-        <f>SUM(F117:F135)</f>
+      <c r="E125" s="71"/>
+      <c r="F125" s="73">
+        <f>SUM(F117:F123)</f>
         <v>1.383240741</v>
       </c>
-      <c r="G137" s="68"/>
-      <c r="H137" s="69">
-        <f>SUM(H116:H135)</f>
+      <c r="G125" s="71"/>
+      <c r="H125" s="72">
+        <f>SUM(H116:H123)</f>
         <v>0.4480324074</v>
       </c>
-      <c r="I137" s="68"/>
-      <c r="J137" s="69">
-        <f>SUM(J116:J136)</f>
+      <c r="I125" s="71"/>
+      <c r="J125" s="72">
+        <f>SUM(J116:J124)</f>
         <v>0.4821180556</v>
       </c>
-      <c r="K137" s="68"/>
-      <c r="L137" s="69">
-        <f>SUM(L116:L135)</f>
+      <c r="K125" s="71"/>
+      <c r="L125" s="72">
+        <f>SUM(L116:L123)</f>
         <v>0.3020833333</v>
       </c>
     </row>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1">
+      <c r="A126" s="27"/>
+      <c r="B126" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126" s="29"/>
+      <c r="D126" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E126" s="29"/>
+      <c r="F126" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G126" s="29"/>
+      <c r="H126" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I126" s="29"/>
+      <c r="J126" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="K126" s="29"/>
+      <c r="L126" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" ht="14.25" customHeight="1">
+      <c r="A127" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C127" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="30"/>
+      <c r="E127" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="30"/>
+      <c r="G127" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" s="30"/>
+      <c r="I127" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="J127" s="30"/>
+      <c r="K127" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="L127" s="30"/>
+    </row>
+    <row r="128" ht="14.25" customHeight="1">
+      <c r="A128" s="21"/>
+      <c r="B128" s="21"/>
+      <c r="C128" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="D128" s="75">
+        <v>0.04717592592592593</v>
+      </c>
+      <c r="E128" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="F128" s="76">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="G128" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H128" s="77">
+        <v>0.08680555555555555</v>
+      </c>
+      <c r="I128" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="J128" s="78">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="K128" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="L128" s="76">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" customHeight="1">
+      <c r="A129" s="21"/>
+      <c r="B129" s="21"/>
+      <c r="C129" s="21"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="21"/>
+      <c r="G129" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H129" s="78">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="I129" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="J129" s="79">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="K129" s="21"/>
+      <c r="L129" s="21"/>
+    </row>
+    <row r="130" ht="14.25" customHeight="1">
+      <c r="A130" s="21"/>
+      <c r="B130" s="21"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+      <c r="E130" s="21"/>
+      <c r="F130" s="21"/>
+      <c r="G130" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H130" s="77">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I130" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="J130" s="79">
+        <v>0.01662037037037037</v>
+      </c>
+      <c r="K130" s="21"/>
+      <c r="L130" s="21"/>
+    </row>
+    <row r="131" ht="14.25" customHeight="1">
+      <c r="A131" s="21"/>
+      <c r="B131" s="21"/>
+      <c r="C131" s="21"/>
+      <c r="D131" s="21"/>
+      <c r="E131" s="21"/>
+      <c r="F131" s="21"/>
+      <c r="G131" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="H131" s="79">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="J131" s="80"/>
+      <c r="K131" s="21"/>
+      <c r="L131" s="21"/>
+    </row>
+    <row r="132" ht="14.25" customHeight="1">
+      <c r="A132" s="21"/>
+      <c r="B132" s="21"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="21"/>
+      <c r="E132" s="21"/>
+      <c r="F132" s="21"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="21"/>
+      <c r="I132" s="21"/>
+      <c r="J132" s="21"/>
+      <c r="K132" s="21"/>
+      <c r="L132" s="21"/>
+    </row>
+    <row r="133" ht="14.25" customHeight="1">
+      <c r="A133" s="21"/>
+      <c r="B133" s="21"/>
+      <c r="C133" s="21"/>
+      <c r="D133" s="21"/>
+      <c r="E133" s="21"/>
+      <c r="F133" s="21"/>
+      <c r="G133" s="21"/>
+      <c r="H133" s="21"/>
+      <c r="I133" s="21"/>
+      <c r="J133" s="21"/>
+      <c r="K133" s="21"/>
+      <c r="L133" s="21"/>
+    </row>
+    <row r="134" ht="14.25" customHeight="1">
+      <c r="A134" s="21"/>
+      <c r="B134" s="21"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="21"/>
+      <c r="E134" s="21"/>
+      <c r="F134" s="21"/>
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
+      <c r="I134" s="21"/>
+      <c r="J134" s="21"/>
+      <c r="K134" s="21"/>
+      <c r="L134" s="21"/>
+    </row>
+    <row r="135" ht="14.25" customHeight="1">
+      <c r="A135" s="21"/>
+      <c r="B135" s="21"/>
+      <c r="C135" s="21"/>
+      <c r="D135" s="21"/>
+      <c r="E135" s="21"/>
+      <c r="F135" s="21"/>
+      <c r="G135" s="21"/>
+      <c r="H135" s="21"/>
+      <c r="I135" s="21"/>
+      <c r="J135" s="21"/>
+      <c r="K135" s="21"/>
+      <c r="L135" s="21"/>
+    </row>
+    <row r="136" ht="14.25" customHeight="1">
+      <c r="A136" s="21"/>
+      <c r="B136" s="21"/>
+      <c r="C136" s="21"/>
+      <c r="D136" s="21"/>
+      <c r="E136" s="21"/>
+      <c r="F136" s="21"/>
+      <c r="G136" s="21"/>
+      <c r="H136" s="21"/>
+      <c r="I136" s="21"/>
+      <c r="J136" s="21"/>
+      <c r="K136" s="21"/>
+      <c r="L136" s="21"/>
+    </row>
+    <row r="137" ht="14.25" customHeight="1">
+      <c r="A137" s="21"/>
+      <c r="B137" s="21"/>
+      <c r="C137" s="21"/>
+      <c r="D137" s="21"/>
+      <c r="E137" s="21"/>
+      <c r="F137" s="21"/>
+      <c r="G137" s="21"/>
+      <c r="H137" s="21"/>
+      <c r="I137" s="21"/>
+      <c r="J137" s="21"/>
+      <c r="K137" s="21"/>
+      <c r="L137" s="21"/>
+    </row>
+    <row r="138" ht="14.25" customHeight="1">
+      <c r="A138" s="21"/>
+      <c r="B138" s="21"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="21"/>
+      <c r="J138" s="21"/>
+      <c r="K138" s="21"/>
+      <c r="L138" s="21"/>
+    </row>
+    <row r="139" ht="14.25" customHeight="1">
+      <c r="A139" s="21"/>
+      <c r="B139" s="21"/>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
+      <c r="I139" s="21"/>
+      <c r="J139" s="21"/>
+      <c r="K139" s="21"/>
+      <c r="L139" s="21"/>
+    </row>
+    <row r="140" ht="14.25" customHeight="1">
+      <c r="A140" s="21"/>
+      <c r="B140" s="21"/>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
+      <c r="I140" s="21"/>
+      <c r="J140" s="21"/>
+      <c r="K140" s="21"/>
+      <c r="L140" s="21"/>
+    </row>
+    <row r="141" ht="14.25" customHeight="1">
+      <c r="A141" s="21"/>
+      <c r="B141" s="21"/>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+      <c r="E141" s="21"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
+      <c r="I141" s="21"/>
+      <c r="J141" s="21"/>
+      <c r="K141" s="21"/>
+      <c r="L141" s="21"/>
+    </row>
+    <row r="142" ht="14.25" customHeight="1">
+      <c r="A142" s="21"/>
+      <c r="B142" s="21"/>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+      <c r="E142" s="21"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
+      <c r="I142" s="21"/>
+      <c r="J142" s="21"/>
+      <c r="K142" s="21"/>
+      <c r="L142" s="21"/>
+    </row>
+    <row r="143" ht="14.25" customHeight="1">
+      <c r="A143" s="21"/>
+      <c r="B143" s="21"/>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+      <c r="E143" s="21"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
+      <c r="I143" s="21"/>
+      <c r="J143" s="21"/>
+      <c r="K143" s="21"/>
+      <c r="L143" s="21"/>
+    </row>
+    <row r="144" ht="14.25" customHeight="1">
+      <c r="A144" s="21"/>
+      <c r="B144" s="21"/>
+      <c r="C144" s="21"/>
+      <c r="D144" s="21"/>
+      <c r="E144" s="21"/>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21"/>
+      <c r="I144" s="21"/>
+      <c r="J144" s="21"/>
+      <c r="K144" s="21"/>
+      <c r="L144" s="21"/>
+    </row>
+    <row r="145" ht="14.25" customHeight="1">
+      <c r="A145" s="21"/>
+      <c r="B145" s="21"/>
+      <c r="C145" s="21"/>
+      <c r="D145" s="21"/>
+      <c r="E145" s="21"/>
+      <c r="F145" s="21"/>
+      <c r="G145" s="21"/>
+      <c r="H145" s="21"/>
+      <c r="I145" s="21"/>
+      <c r="J145" s="21"/>
+      <c r="K145" s="21"/>
+      <c r="L145" s="21"/>
+    </row>
+    <row r="146" ht="14.25" customHeight="1">
+      <c r="A146" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="71">
+        <f>SUM(B128:B145)</f>
+        <v>0</v>
+      </c>
+      <c r="C146" s="71"/>
+      <c r="D146" s="73">
+        <f>SUM(D128:D145)</f>
+        <v>0.04717592593</v>
+      </c>
+      <c r="E146" s="71"/>
+      <c r="F146" s="73">
+        <f>SUM(F128:F145)</f>
+        <v>0.1041666667</v>
+      </c>
+      <c r="G146" s="71"/>
+      <c r="H146" s="73">
+        <f>SUM(H128:H145)</f>
+        <v>0.4132986111</v>
+      </c>
+      <c r="I146" s="71"/>
+      <c r="J146" s="73">
+        <f>SUM(J128:J145)</f>
+        <v>0.2320023148</v>
+      </c>
+      <c r="K146" s="71"/>
+      <c r="L146" s="73">
+        <f>SUM(L128:L145)</f>
+        <v>0.1041666667</v>
+      </c>
+    </row>
     <row r="147" ht="14.25" customHeight="1"/>
     <row r="148" ht="14.25" customHeight="1"/>
     <row r="149" ht="14.25" customHeight="1"/>
@@ -6266,18 +6566,6 @@
     <row r="1008" ht="14.25" customHeight="1"/>
     <row r="1009" ht="14.25" customHeight="1"/>
     <row r="1010" ht="14.25" customHeight="1"/>
-    <row r="1011" ht="14.25" customHeight="1"/>
-    <row r="1012" ht="14.25" customHeight="1"/>
-    <row r="1013" ht="14.25" customHeight="1"/>
-    <row r="1014" ht="14.25" customHeight="1"/>
-    <row r="1015" ht="14.25" customHeight="1"/>
-    <row r="1016" ht="14.25" customHeight="1"/>
-    <row r="1017" ht="14.25" customHeight="1"/>
-    <row r="1018" ht="14.25" customHeight="1"/>
-    <row r="1019" ht="14.25" customHeight="1"/>
-    <row r="1020" ht="14.25" customHeight="1"/>
-    <row r="1021" ht="14.25" customHeight="1"/>
-    <row r="1022" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A53:L53"/>
@@ -6300,130 +6588,130 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>93</v>
+      <c r="C3" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="81" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="72">
+      <c r="B4" s="82">
         <v>1.0</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="83">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="83">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="72">
+      <c r="B5" s="82">
         <v>2.0</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="83">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="83">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="72">
+      <c r="B6" s="82">
         <v>3.0</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="83">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="83">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="72">
+      <c r="B7" s="82">
         <v>4.0</v>
       </c>
-      <c r="C7" s="73">
+      <c r="C7" s="83">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="83">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="72">
+      <c r="B8" s="82">
         <v>5.0</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="83">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="83">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="72">
+      <c r="B9" s="82">
         <v>6.0</v>
       </c>
-      <c r="C9" s="73">
+      <c r="C9" s="83">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="83">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="72">
+      <c r="B10" s="82">
         <v>7.0</v>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="83">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="84">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="72">
+      <c r="B11" s="82">
         <v>8.0</v>
       </c>
-      <c r="C11" s="74">
+      <c r="C11" s="84">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="84">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="72">
+      <c r="B12" s="82">
         <v>9.0</v>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="84">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="84">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="72">
+      <c r="B13" s="82">
         <v>10.0</v>
       </c>
-      <c r="C13" s="74">
+      <c r="C13" s="84">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="73">
+      <c r="D13" s="83">
         <v>45965.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -412,7 +412,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,20 +457,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -532,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -582,30 +576,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="46" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -625,7 +616,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -635,7 +626,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -678,7 +669,7 @@
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -711,26 +702,17 @@
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="4" fontId="13" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="8" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="1" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -740,6 +722,15 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2478,276 +2469,276 @@
       <c r="H1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="25"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="26"/>
+      <c r="K1" s="25"/>
       <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="29" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="29" t="s">
+      <c r="F2" s="29"/>
+      <c r="G2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="29" t="s">
+      <c r="H2" s="29"/>
+      <c r="I2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="29" t="s">
+      <c r="J2" s="29"/>
+      <c r="K2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="30"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="6">
         <v>0.05783564814814815</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="10" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="9">
         <v>0.03487268518518519</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
       <c r="I3" s="10" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="K3" s="33"/>
+      <c r="K3" s="32"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="5">
         <v>1.1574074074074075E-4</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
       <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="7">
         <v>0.06111111111111111</v>
       </c>
-      <c r="K4" s="33"/>
+      <c r="K4" s="32"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="5">
         <v>0.04273148148148148</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
       <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="7">
         <v>0.019791666666666666</v>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="5">
         <v>0.002939814814814815</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
       <c r="I6" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="7">
         <v>0.039780092592592596</v>
       </c>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="5">
         <v>0.06607638888888889</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
       <c r="I7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="9">
         <v>0.0798611111111111</v>
       </c>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="5">
         <v>0.06518518518518518</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="34" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="33" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="13">
         <v>0.03515046296296296</v>
       </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="30" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>0.0798611111111111</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
       <c r="I9" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J9" s="7">
         <v>0.06607638888888889</v>
       </c>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="5">
         <v>0.019791666666666666</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
       <c r="I10" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="9">
         <v>0.05783564814814815</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="5">
         <v>0.039780092592592596</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="5">
         <v>0.028356481481481483</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="30" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="5">
         <v>0.013148148148148148</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="10" t="s">
@@ -2756,108 +2747,108 @@
       <c r="B14" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="37">
         <f>SUM(B3:B14)</f>
         <v>0.4929050926</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="39">
+      <c r="F15" s="38">
         <f>SUM(F3:F14)</f>
         <v>0.03487268519</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="39">
+      <c r="J15" s="38">
         <f>SUM(J3:J14)</f>
         <v>0.4366898148</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="39">
+      <c r="L15" s="38">
         <f>SUM(L3:L14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="27"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="29"/>
+      <c r="C16" s="28"/>
       <c r="D16" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="29"/>
+      <c r="E16" s="28"/>
       <c r="F16" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="29"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="29"/>
+      <c r="I16" s="28"/>
       <c r="J16" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="29"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="29" t="s">
+      <c r="D17" s="29"/>
+      <c r="E17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="29" t="s">
+      <c r="F17" s="29"/>
+      <c r="G17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="30"/>
-      <c r="I17" s="29" t="s">
+      <c r="H17" s="29"/>
+      <c r="I17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="29" t="s">
+      <c r="J17" s="29"/>
+      <c r="K17" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="30"/>
+      <c r="L17" s="29"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
@@ -2870,20 +2861,20 @@
       <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="10" t="s">
         <v>34</v>
       </c>
@@ -2900,7 +2891,7 @@
       <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="K19" s="41" t="s">
+      <c r="K19" s="40" t="s">
         <v>35</v>
       </c>
       <c r="L19" s="7">
@@ -2908,29 +2899,29 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="10" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="I20" s="42" t="s">
+      <c r="I20" s="41" t="s">
         <v>36</v>
       </c>
       <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="K20" s="41" t="s">
+      <c r="K20" s="40" t="s">
         <v>35</v>
       </c>
       <c r="L20" s="7">
@@ -2938,411 +2929,411 @@
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B37" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="37" t="s">
+      <c r="A38" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="39">
+      <c r="B38" s="38">
         <f>SUM(B18:B37)</f>
         <v>0.4042824074</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43">
+      <c r="E38" s="42"/>
+      <c r="F38" s="42">
         <f>SUM(F17:F36)</f>
         <v>0.689375</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="39">
+      <c r="H38" s="38">
         <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43">
+      <c r="I38" s="42"/>
+      <c r="J38" s="42">
         <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43">
+      <c r="K38" s="42"/>
+      <c r="L38" s="42">
         <f>SUM(L18:L36)</f>
         <v>0.03163194444</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="27"/>
+      <c r="A39" s="26"/>
       <c r="B39" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="29"/>
+      <c r="C39" s="28"/>
       <c r="D39" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="29"/>
+      <c r="E39" s="28"/>
       <c r="F39" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="29"/>
+      <c r="G39" s="28"/>
       <c r="H39" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="29"/>
+      <c r="I39" s="28"/>
       <c r="J39" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="29"/>
+      <c r="K39" s="28"/>
       <c r="L39" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="29" t="s">
+      <c r="D40" s="29"/>
+      <c r="E40" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="29" t="s">
+      <c r="F40" s="29"/>
+      <c r="G40" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="30"/>
-      <c r="I40" s="29" t="s">
+      <c r="H40" s="29"/>
+      <c r="I40" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J40" s="30"/>
-      <c r="K40" s="29" t="s">
+      <c r="J40" s="29"/>
+      <c r="K40" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L40" s="30"/>
+      <c r="L40" s="29"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6">
         <v>0.23333333333333334</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
       <c r="I41" s="10" t="s">
         <v>38</v>
       </c>
@@ -3357,18 +3348,18 @@
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
       <c r="I42" s="10" t="s">
         <v>38</v>
       </c>
@@ -3383,18 +3374,18 @@
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
       <c r="I43" s="10" t="s">
         <v>38</v>
       </c>
@@ -3409,317 +3400,317 @@
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
       <c r="I44" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
       <c r="I45" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
       <c r="I46" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="K46" s="32"/>
-      <c r="L46" s="32"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
       <c r="I47" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="K47" s="32"/>
-      <c r="L47" s="32"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
       <c r="I48" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="K48" s="32"/>
-      <c r="L48" s="32"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
       <c r="I49" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
       <c r="I50" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
       <c r="I51" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="K51" s="32"/>
-      <c r="L51" s="32"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="46"/>
-      <c r="J53" s="46"/>
-      <c r="K53" s="46"/>
-      <c r="L53" s="47"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="46"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="32"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="37" t="s">
+      <c r="A59" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="39">
+      <c r="B59" s="38">
         <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="43">
+      <c r="F59" s="42">
         <f>SUM(F41:F58)</f>
         <v>0.2333333333</v>
       </c>
@@ -3729,72 +3720,72 @@
         <v>0</v>
       </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="39">
+      <c r="J59" s="38">
         <f>SUM(J41:J58)</f>
         <v>0.218587963</v>
       </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="39">
+      <c r="L59" s="38">
         <f>SUM(L41:L58)</f>
         <v>0.161875</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="27"/>
+      <c r="A60" s="26"/>
       <c r="B60" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="29"/>
+      <c r="C60" s="28"/>
       <c r="D60" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="29"/>
+      <c r="E60" s="28"/>
       <c r="F60" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="29"/>
+      <c r="G60" s="28"/>
       <c r="H60" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="29"/>
+      <c r="I60" s="28"/>
       <c r="J60" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="29"/>
+      <c r="K60" s="28"/>
       <c r="L60" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B61" s="44" t="s">
+      <c r="B61" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="30"/>
-      <c r="E61" s="29" t="s">
+      <c r="D61" s="29"/>
+      <c r="E61" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="30"/>
-      <c r="G61" s="29" t="s">
+      <c r="F61" s="29"/>
+      <c r="G61" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H61" s="30"/>
-      <c r="I61" s="29" t="s">
+      <c r="H61" s="29"/>
+      <c r="I61" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J61" s="30"/>
-      <c r="K61" s="29" t="s">
+      <c r="J61" s="29"/>
+      <c r="K61" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L61" s="30"/>
+      <c r="L61" s="29"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="7">
@@ -3820,20 +3811,20 @@
       <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
+      <c r="K62" s="31"/>
+      <c r="L62" s="31"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
       <c r="G63" s="10" t="s">
         <v>43</v>
       </c>
@@ -3846,316 +3837,316 @@
       <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
+      <c r="K63" s="31"/>
+      <c r="L63" s="31"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="31" t="s">
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="30" t="s">
         <v>44</v>
       </c>
       <c r="J64" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="32"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="31"/>
+      <c r="I65" s="31"/>
+      <c r="J65" s="31"/>
+      <c r="K65" s="31"/>
+      <c r="L65" s="31"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="30" t="s">
         <v>44</v>
       </c>
       <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="32"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="32"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="31"/>
+      <c r="J68" s="31"/>
+      <c r="K68" s="31"/>
+      <c r="L68" s="31"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="31"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="31" t="s">
+      <c r="A73" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="31"/>
+      <c r="J73" s="31"/>
+      <c r="K73" s="31"/>
+      <c r="L73" s="31"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="37" t="s">
+      <c r="A75" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B75" s="39">
+      <c r="B75" s="38">
         <f>SUM(B62:B74)</f>
         <v>0.6286805556</v>
       </c>
-      <c r="C75" s="48"/>
-      <c r="D75" s="38">
+      <c r="C75" s="47"/>
+      <c r="D75" s="37">
         <f>SUM(D62:D74)</f>
         <v>0.0244212963</v>
       </c>
-      <c r="E75" s="49"/>
-      <c r="F75" s="39">
+      <c r="E75" s="48"/>
+      <c r="F75" s="38">
         <f>SUM(F62:F74)</f>
         <v>0.09237268519</v>
       </c>
-      <c r="G75" s="49"/>
-      <c r="H75" s="39">
+      <c r="G75" s="48"/>
+      <c r="H75" s="38">
         <f>SUM(H62:H74)</f>
         <v>0.1780092593</v>
       </c>
-      <c r="I75" s="49"/>
-      <c r="J75" s="39">
+      <c r="I75" s="48"/>
+      <c r="J75" s="38">
         <f>SUM(J62:J74)</f>
         <v>0.2304861111</v>
       </c>
-      <c r="K75" s="49"/>
-      <c r="L75" s="49"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="27"/>
+      <c r="A76" s="26"/>
       <c r="B76" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C76" s="29"/>
+      <c r="C76" s="28"/>
       <c r="D76" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="29"/>
+      <c r="E76" s="28"/>
       <c r="F76" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="29"/>
+      <c r="G76" s="28"/>
       <c r="H76" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="29"/>
+      <c r="I76" s="28"/>
       <c r="J76" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="29"/>
+      <c r="K76" s="28"/>
       <c r="L76" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="27" t="s">
+      <c r="A77" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="44" t="s">
+      <c r="B77" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D77" s="30"/>
-      <c r="E77" s="29" t="s">
+      <c r="D77" s="29"/>
+      <c r="E77" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F77" s="30"/>
-      <c r="G77" s="29" t="s">
+      <c r="F77" s="29"/>
+      <c r="G77" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H77" s="30"/>
-      <c r="I77" s="29" t="s">
+      <c r="H77" s="29"/>
+      <c r="I77" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J77" s="30"/>
-      <c r="K77" s="29" t="s">
+      <c r="J77" s="29"/>
+      <c r="K77" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L77" s="30"/>
+      <c r="L77" s="29"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="31" t="s">
+      <c r="A78" s="30" t="s">
         <v>46</v>
       </c>
       <c r="B78" s="7">
         <v>0.125</v>
       </c>
-      <c r="C78" s="50" t="s">
+      <c r="C78" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D78" s="51">
+      <c r="D78" s="50">
         <v>0.11513888888888889</v>
       </c>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="51">
+      <c r="E78" s="51"/>
+      <c r="F78" s="51"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="50">
         <v>0.013888888888888888</v>
       </c>
-      <c r="I78" s="31" t="s">
+      <c r="I78" s="30" t="s">
         <v>48</v>
       </c>
       <c r="J78" s="7">
@@ -4169,232 +4160,232 @@
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="31" t="s">
+      <c r="A79" s="30" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="7">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="51">
+      <c r="D79" s="50">
         <v>0.5638888888888889</v>
       </c>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="31" t="s">
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="51"/>
+      <c r="H79" s="51"/>
+      <c r="I79" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="J79" s="53">
+      <c r="J79" s="52">
         <v>0.09305555555555556</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B80" s="54">
+      <c r="B80" s="53">
         <v>0.0625</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C80" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D80" s="55">
+      <c r="D80" s="54">
         <v>0.19444444444444445</v>
       </c>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="34" t="s">
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="51"/>
+      <c r="H80" s="51"/>
+      <c r="I80" s="33" t="s">
         <v>51</v>
       </c>
       <c r="J80" s="13">
         <v>0.041666666666666664</v>
       </c>
-      <c r="K80" s="52"/>
-      <c r="L80" s="52"/>
+      <c r="K80" s="51"/>
+      <c r="L80" s="51"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="35" t="s">
+      <c r="A81" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B81" s="56">
+      <c r="B81" s="55">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
-      <c r="H81" s="52"/>
-      <c r="I81" s="52"/>
-      <c r="J81" s="52"/>
-      <c r="K81" s="51"/>
-      <c r="L81" s="51"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+      <c r="H81" s="51"/>
+      <c r="I81" s="51"/>
+      <c r="J81" s="51"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="30" t="s">
         <v>52</v>
       </c>
       <c r="B82" s="9">
         <v>0.05763888888888889</v>
       </c>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
-      <c r="H82" s="52"/>
-      <c r="I82" s="52"/>
-      <c r="J82" s="52"/>
-      <c r="K82" s="52"/>
-      <c r="L82" s="52"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="51"/>
+      <c r="F82" s="51"/>
+      <c r="G82" s="51"/>
+      <c r="H82" s="51"/>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="51"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="57"/>
+      <c r="A83" s="56"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="52"/>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
-      <c r="L83" s="52"/>
+      <c r="C83" s="50"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="51"/>
+      <c r="G83" s="51"/>
+      <c r="H83" s="51"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
+      <c r="K83" s="51"/>
+      <c r="L83" s="51"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="57"/>
+      <c r="A84" s="56"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
-      <c r="J84" s="52"/>
-      <c r="K84" s="52"/>
-      <c r="L84" s="52"/>
+      <c r="C84" s="50"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="51"/>
+      <c r="K84" s="51"/>
+      <c r="L84" s="51"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="57"/>
+      <c r="A85" s="56"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
-      <c r="I85" s="52"/>
-      <c r="J85" s="52"/>
-      <c r="K85" s="58"/>
-      <c r="L85" s="58"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="51"/>
+      <c r="I85" s="51"/>
+      <c r="J85" s="51"/>
+      <c r="K85" s="57"/>
+      <c r="L85" s="57"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B86" s="43">
+      <c r="B86" s="42">
         <f>SUM(B78:B85)</f>
         <v>0.3979166667</v>
       </c>
-      <c r="C86" s="59"/>
-      <c r="D86" s="59">
+      <c r="C86" s="58"/>
+      <c r="D86" s="58">
         <f>SUM(D78:D83)</f>
         <v>0.8734722222</v>
       </c>
-      <c r="E86" s="60"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="60"/>
-      <c r="H86" s="38">
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="37">
         <f>SUM(H78:H85)</f>
         <v>0.01388888889</v>
       </c>
-      <c r="I86" s="60"/>
-      <c r="J86" s="38">
+      <c r="I86" s="59"/>
+      <c r="J86" s="37">
         <f>SUM(J78:J85)</f>
         <v>0.2180555556</v>
       </c>
-      <c r="K86" s="43"/>
-      <c r="L86" s="43">
+      <c r="K86" s="42"/>
+      <c r="L86" s="42">
         <f>SUM(L78:L80)</f>
         <v>0.03333333333</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="27"/>
+      <c r="A87" s="26"/>
       <c r="B87" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C87" s="29"/>
+      <c r="C87" s="28"/>
       <c r="D87" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="29"/>
+      <c r="E87" s="28"/>
       <c r="F87" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="29"/>
+      <c r="G87" s="28"/>
       <c r="H87" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I87" s="29"/>
+      <c r="I87" s="28"/>
       <c r="J87" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="29"/>
+      <c r="K87" s="28"/>
       <c r="L87" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="27" t="s">
+      <c r="A88" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B88" s="44" t="s">
+      <c r="B88" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D88" s="30"/>
-      <c r="E88" s="29" t="s">
+      <c r="D88" s="29"/>
+      <c r="E88" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F88" s="30"/>
-      <c r="G88" s="29" t="s">
+      <c r="F88" s="29"/>
+      <c r="G88" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H88" s="30"/>
-      <c r="I88" s="29" t="s">
+      <c r="H88" s="29"/>
+      <c r="I88" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J88" s="30"/>
-      <c r="K88" s="29" t="s">
+      <c r="J88" s="29"/>
+      <c r="K88" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L88" s="30"/>
+      <c r="L88" s="29"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="57"/>
+      <c r="A89" s="56"/>
       <c r="B89" s="7">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C89" s="50" t="s">
+      <c r="C89" s="49" t="s">
         <v>54</v>
       </c>
       <c r="D89" s="13">
         <v>0.17631944444444445</v>
       </c>
-      <c r="E89" s="61" t="s">
+      <c r="E89" s="60" t="s">
         <v>55</v>
       </c>
       <c r="F89" s="7">
@@ -4420,28 +4411,28 @@
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="57"/>
-      <c r="B90" s="32"/>
-      <c r="C90" s="50" t="s">
+      <c r="A90" s="56"/>
+      <c r="B90" s="31"/>
+      <c r="C90" s="49" t="s">
         <v>59</v>
       </c>
       <c r="D90" s="13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E90" s="61" t="s">
+      <c r="E90" s="60" t="s">
         <v>55</v>
       </c>
       <c r="F90" s="7">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G90" s="42" t="s">
+      <c r="G90" s="41" t="s">
         <v>60</v>
       </c>
       <c r="H90" s="7">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
+      <c r="I90" s="31"/>
+      <c r="J90" s="31"/>
       <c r="K90" s="10" t="s">
         <v>58</v>
       </c>
@@ -4450,15 +4441,15 @@
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="57"/>
-      <c r="B91" s="32"/>
-      <c r="C91" s="50" t="s">
+      <c r="A91" s="56"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="D91" s="53">
+      <c r="D91" s="52">
         <v>0.32806712962962964</v>
       </c>
-      <c r="E91" s="61" t="s">
+      <c r="E91" s="60" t="s">
         <v>55</v>
       </c>
       <c r="F91" s="7">
@@ -4470,8 +4461,8 @@
       <c r="H91" s="7">
         <v>0.06527777777777778</v>
       </c>
-      <c r="I91" s="32"/>
-      <c r="J91" s="32"/>
+      <c r="I91" s="31"/>
+      <c r="J91" s="31"/>
       <c r="K91" s="10" t="s">
         <v>62</v>
       </c>
@@ -4480,333 +4471,333 @@
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="57"/>
-      <c r="B92" s="32"/>
-      <c r="C92" s="52"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="32"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="32"/>
-      <c r="I92" s="32"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="32"/>
-      <c r="L92" s="32"/>
+      <c r="A92" s="56"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31"/>
+      <c r="G92" s="31"/>
+      <c r="H92" s="31"/>
+      <c r="I92" s="31"/>
+      <c r="J92" s="31"/>
+      <c r="K92" s="31"/>
+      <c r="L92" s="31"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B93" s="43">
+      <c r="B93" s="42">
         <f>SUM(B89)</f>
         <v>0.08333333333</v>
       </c>
-      <c r="C93" s="59"/>
-      <c r="D93" s="59">
+      <c r="C93" s="58"/>
+      <c r="D93" s="58">
         <f>SUM(D89:D92)</f>
         <v>0.6710532407</v>
       </c>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43">
+      <c r="E93" s="42"/>
+      <c r="F93" s="42">
         <f>SUM(F89:F91)</f>
         <v>0.8770833333</v>
       </c>
-      <c r="G93" s="43"/>
-      <c r="H93" s="43">
+      <c r="G93" s="42"/>
+      <c r="H93" s="42">
         <f>SUM(H89:H91)</f>
         <v>0.3071064815</v>
       </c>
-      <c r="I93" s="43"/>
-      <c r="J93" s="43">
+      <c r="I93" s="42"/>
+      <c r="J93" s="42">
         <f>SUM(J89)</f>
         <v>0.003472222222</v>
       </c>
-      <c r="K93" s="43"/>
-      <c r="L93" s="43">
+      <c r="K93" s="42"/>
+      <c r="L93" s="42">
         <f>SUM(L89:L91)</f>
         <v>0.4239467593</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="27"/>
+      <c r="A94" s="26"/>
       <c r="B94" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C94" s="29"/>
+      <c r="C94" s="28"/>
       <c r="D94" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E94" s="29"/>
+      <c r="E94" s="28"/>
       <c r="F94" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="29"/>
+      <c r="G94" s="28"/>
       <c r="H94" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="29"/>
+      <c r="I94" s="28"/>
       <c r="J94" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="29"/>
+      <c r="K94" s="28"/>
       <c r="L94" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="62" t="s">
+      <c r="A95" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="63" t="s">
+      <c r="B95" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C95" s="64" t="s">
+      <c r="C95" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D95" s="32"/>
-      <c r="E95" s="64" t="s">
+      <c r="D95" s="31"/>
+      <c r="E95" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="F95" s="32"/>
-      <c r="G95" s="64" t="s">
+      <c r="F95" s="31"/>
+      <c r="G95" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H95" s="32"/>
-      <c r="I95" s="64" t="s">
+      <c r="H95" s="31"/>
+      <c r="I95" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J95" s="32"/>
-      <c r="K95" s="64" t="s">
+      <c r="J95" s="31"/>
+      <c r="K95" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="L95" s="32"/>
+      <c r="L95" s="31"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="31" t="s">
+      <c r="A96" s="30" t="s">
         <v>64</v>
       </c>
       <c r="B96" s="9">
         <v>0.020833333333333332</v>
       </c>
-      <c r="C96" s="50" t="s">
+      <c r="C96" s="49" t="s">
         <v>65</v>
       </c>
       <c r="D96" s="13">
         <v>0.5</v>
       </c>
-      <c r="E96" s="32"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="32"/>
+      <c r="E96" s="31"/>
+      <c r="F96" s="31"/>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31"/>
       <c r="I96" s="10" t="s">
         <v>66</v>
       </c>
       <c r="J96" s="9">
         <v>0.022222222222222223</v>
       </c>
-      <c r="K96" s="32"/>
-      <c r="L96" s="32"/>
+      <c r="K96" s="31"/>
+      <c r="L96" s="31"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="31" t="s">
+      <c r="A97" s="30" t="s">
         <v>67</v>
       </c>
       <c r="B97" s="9">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C97" s="50" t="s">
+      <c r="C97" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="D97" s="53">
+      <c r="D97" s="52">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E97" s="32"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="32"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
       <c r="I97" s="10" t="s">
         <v>69</v>
       </c>
       <c r="J97" s="9">
         <v>0.06859953703703704</v>
       </c>
-      <c r="K97" s="32"/>
-      <c r="L97" s="32"/>
+      <c r="K97" s="31"/>
+      <c r="L97" s="31"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="57"/>
+      <c r="A98" s="56"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="50" t="s">
+      <c r="C98" s="49" t="s">
         <v>68</v>
       </c>
       <c r="D98" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E98" s="32"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
+      <c r="E98" s="31"/>
+      <c r="F98" s="31"/>
+      <c r="G98" s="31"/>
+      <c r="H98" s="31"/>
       <c r="I98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="J98" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="K98" s="32"/>
-      <c r="L98" s="32"/>
+      <c r="K98" s="31"/>
+      <c r="L98" s="31"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="57"/>
+      <c r="A99" s="56"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="50" t="s">
+      <c r="C99" s="49" t="s">
         <v>68</v>
       </c>
       <c r="D99" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="32"/>
-      <c r="I99" s="34" t="s">
+      <c r="E99" s="31"/>
+      <c r="F99" s="31"/>
+      <c r="G99" s="31"/>
+      <c r="H99" s="31"/>
+      <c r="I99" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="J99" s="53">
+      <c r="J99" s="52">
         <v>0.03420138888888889</v>
       </c>
-      <c r="K99" s="32"/>
-      <c r="L99" s="32"/>
+      <c r="K99" s="31"/>
+      <c r="L99" s="31"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="31"/>
+      <c r="A100" s="30"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="50" t="s">
+      <c r="C100" s="49" t="s">
         <v>70</v>
       </c>
       <c r="D100" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="34" t="s">
+      <c r="E100" s="31"/>
+      <c r="F100" s="31"/>
+      <c r="G100" s="31"/>
+      <c r="H100" s="31"/>
+      <c r="I100" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J100" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K100" s="32"/>
-      <c r="L100" s="32"/>
+      <c r="K100" s="31"/>
+      <c r="L100" s="31"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="31"/>
+      <c r="A101" s="30"/>
       <c r="B101" s="9"/>
-      <c r="C101" s="52"/>
-      <c r="D101" s="65"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="34" t="s">
+      <c r="C101" s="51"/>
+      <c r="D101" s="64"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="31"/>
+      <c r="G101" s="31"/>
+      <c r="H101" s="31"/>
+      <c r="I101" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J101" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K101" s="32"/>
-      <c r="L101" s="32"/>
+      <c r="K101" s="31"/>
+      <c r="L101" s="31"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="37" t="s">
+      <c r="A102" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B102" s="39">
+      <c r="B102" s="38">
         <f>SUM(B96:B101)</f>
         <v>0.06805555556</v>
       </c>
-      <c r="C102" s="48"/>
-      <c r="D102" s="38">
+      <c r="C102" s="47"/>
+      <c r="D102" s="37">
         <f>SUM(D96:D101)</f>
         <v>0.8178472222</v>
       </c>
-      <c r="E102" s="49"/>
-      <c r="F102" s="49"/>
-      <c r="G102" s="49"/>
-      <c r="H102" s="49"/>
-      <c r="I102" s="49"/>
-      <c r="J102" s="39">
+      <c r="E102" s="48"/>
+      <c r="F102" s="48"/>
+      <c r="G102" s="48"/>
+      <c r="H102" s="48"/>
+      <c r="I102" s="48"/>
+      <c r="J102" s="38">
         <f>SUM(J96:J101)</f>
         <v>0.4086689815</v>
       </c>
-      <c r="K102" s="49"/>
-      <c r="L102" s="49"/>
+      <c r="K102" s="48"/>
+      <c r="L102" s="48"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="27"/>
+      <c r="A103" s="26"/>
       <c r="B103" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C103" s="29"/>
+      <c r="C103" s="28"/>
       <c r="D103" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E103" s="29"/>
+      <c r="E103" s="28"/>
       <c r="F103" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G103" s="29"/>
+      <c r="G103" s="28"/>
       <c r="H103" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I103" s="29"/>
+      <c r="I103" s="28"/>
       <c r="J103" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K103" s="29"/>
+      <c r="K103" s="28"/>
       <c r="L103" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="62" t="s">
+      <c r="A104" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B104" s="63" t="s">
+      <c r="B104" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="C104" s="64" t="s">
+      <c r="C104" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D104" s="32"/>
-      <c r="E104" s="64" t="s">
+      <c r="D104" s="31"/>
+      <c r="E104" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="F104" s="66"/>
-      <c r="G104" s="64" t="s">
+      <c r="F104" s="65"/>
+      <c r="G104" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H104" s="32"/>
-      <c r="I104" s="64" t="s">
+      <c r="H104" s="31"/>
+      <c r="I104" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J104" s="32"/>
-      <c r="K104" s="64" t="s">
+      <c r="J104" s="31"/>
+      <c r="K104" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="L104" s="32"/>
+      <c r="L104" s="31"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="31" t="s">
+      <c r="A105" s="30" t="s">
         <v>67</v>
       </c>
       <c r="B105" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C105" s="50" t="s">
+      <c r="C105" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="D105" s="53">
+      <c r="D105" s="52">
         <v>0.03420138888888889</v>
       </c>
       <c r="E105" s="10" t="s">
@@ -4815,12 +4806,12 @@
       <c r="F105" s="6">
         <v>0.27569444444444446</v>
       </c>
-      <c r="G105" s="32"/>
-      <c r="H105" s="32"/>
-      <c r="I105" s="34" t="s">
+      <c r="G105" s="31"/>
+      <c r="H105" s="31"/>
+      <c r="I105" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="J105" s="53">
+      <c r="J105" s="52">
         <v>0.1909722222222222</v>
       </c>
       <c r="K105" s="9"/>
@@ -4829,18 +4820,18 @@
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="31"/>
+      <c r="A106" s="30"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="50" t="s">
+      <c r="C106" s="49" t="s">
         <v>68</v>
       </c>
       <c r="D106" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E106" s="32"/>
-      <c r="F106" s="32"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="32"/>
+      <c r="E106" s="31"/>
+      <c r="F106" s="31"/>
+      <c r="G106" s="31"/>
+      <c r="H106" s="31"/>
       <c r="I106" s="10" t="s">
         <v>73</v>
       </c>
@@ -4855,26 +4846,26 @@
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="31" t="s">
+      <c r="A107" s="30" t="s">
         <v>75</v>
       </c>
       <c r="B107" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C107" s="50" t="s">
+      <c r="C107" s="49" t="s">
         <v>68</v>
       </c>
       <c r="D107" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E107" s="32"/>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32"/>
-      <c r="H107" s="32"/>
-      <c r="I107" s="34" t="s">
+      <c r="E107" s="31"/>
+      <c r="F107" s="31"/>
+      <c r="G107" s="31"/>
+      <c r="H107" s="31"/>
+      <c r="I107" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="J107" s="53">
+      <c r="J107" s="52">
         <v>0.03420138888888889</v>
       </c>
       <c r="K107" s="10" t="s">
@@ -4885,209 +4876,209 @@
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="57"/>
-      <c r="B108" s="32"/>
-      <c r="C108" s="50" t="s">
+      <c r="A108" s="56"/>
+      <c r="B108" s="31"/>
+      <c r="C108" s="49" t="s">
         <v>77</v>
       </c>
       <c r="D108" s="13">
         <v>0.3076388888888889</v>
       </c>
-      <c r="E108" s="32"/>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
-      <c r="I108" s="34" t="s">
+      <c r="E108" s="31"/>
+      <c r="F108" s="31"/>
+      <c r="G108" s="31"/>
+      <c r="H108" s="31"/>
+      <c r="I108" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J108" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K108" s="32"/>
-      <c r="L108" s="32"/>
+      <c r="K108" s="31"/>
+      <c r="L108" s="31"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="57"/>
-      <c r="B109" s="32"/>
-      <c r="C109" s="50" t="s">
+      <c r="A109" s="56"/>
+      <c r="B109" s="31"/>
+      <c r="C109" s="49" t="s">
         <v>77</v>
       </c>
       <c r="D109" s="13">
         <v>0.24097222222222223</v>
       </c>
-      <c r="E109" s="32"/>
-      <c r="F109" s="32"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="32"/>
-      <c r="I109" s="34" t="s">
+      <c r="E109" s="31"/>
+      <c r="F109" s="31"/>
+      <c r="G109" s="31"/>
+      <c r="H109" s="31"/>
+      <c r="I109" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J109" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K109" s="32"/>
-      <c r="L109" s="32"/>
+      <c r="K109" s="31"/>
+      <c r="L109" s="31"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="57"/>
-      <c r="B110" s="32"/>
-      <c r="C110" s="50" t="s">
+      <c r="A110" s="56"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="49" t="s">
         <v>78</v>
       </c>
       <c r="D110" s="13">
         <v>0.10609953703703703</v>
       </c>
-      <c r="E110" s="32"/>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
-      <c r="I110" s="31" t="s">
+      <c r="E110" s="31"/>
+      <c r="F110" s="31"/>
+      <c r="G110" s="31"/>
+      <c r="H110" s="31"/>
+      <c r="I110" s="30" t="s">
         <v>75</v>
       </c>
       <c r="J110" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="K110" s="32"/>
-      <c r="L110" s="32"/>
+      <c r="K110" s="31"/>
+      <c r="L110" s="31"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="57"/>
-      <c r="B111" s="32"/>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="32"/>
-      <c r="I111" s="32"/>
-      <c r="J111" s="32"/>
-      <c r="K111" s="32"/>
-      <c r="L111" s="32"/>
+      <c r="A111" s="56"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="51"/>
+      <c r="D111" s="51"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="31"/>
+      <c r="G111" s="31"/>
+      <c r="H111" s="31"/>
+      <c r="I111" s="31"/>
+      <c r="J111" s="31"/>
+      <c r="K111" s="31"/>
+      <c r="L111" s="31"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="57"/>
-      <c r="B112" s="32"/>
-      <c r="C112" s="52"/>
-      <c r="D112" s="52"/>
-      <c r="E112" s="32"/>
-      <c r="F112" s="32"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="32"/>
-      <c r="I112" s="32"/>
-      <c r="J112" s="32"/>
-      <c r="K112" s="32"/>
-      <c r="L112" s="32"/>
+      <c r="A112" s="56"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
+      <c r="H112" s="31"/>
+      <c r="I112" s="31"/>
+      <c r="J112" s="31"/>
+      <c r="K112" s="31"/>
+      <c r="L112" s="31"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="37" t="s">
+      <c r="A113" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="43">
+      <c r="B113" s="42">
         <f>SUM(B105:B112)</f>
         <v>0.2798611111</v>
       </c>
-      <c r="C113" s="48"/>
-      <c r="D113" s="59">
+      <c r="C113" s="47"/>
+      <c r="D113" s="58">
         <f>SUM(D105:D112)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="E113" s="49"/>
-      <c r="F113" s="43">
+      <c r="E113" s="48"/>
+      <c r="F113" s="42">
         <f>SUM(F105:F112)</f>
         <v>0.2756944444</v>
       </c>
-      <c r="G113" s="49"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="49"/>
-      <c r="J113" s="43">
+      <c r="G113" s="48"/>
+      <c r="H113" s="48"/>
+      <c r="I113" s="48"/>
+      <c r="J113" s="42">
         <f>SUM(J105:J112)</f>
         <v>0.5817361111</v>
       </c>
-      <c r="K113" s="49"/>
-      <c r="L113" s="39">
+      <c r="K113" s="48"/>
+      <c r="L113" s="38">
         <f>SUM(L105:L112)</f>
         <v>0.3125</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="27"/>
+      <c r="A114" s="26"/>
       <c r="B114" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C114" s="29"/>
+      <c r="C114" s="28"/>
       <c r="D114" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E114" s="29"/>
+      <c r="E114" s="28"/>
       <c r="F114" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G114" s="29"/>
+      <c r="G114" s="28"/>
       <c r="H114" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I114" s="29"/>
+      <c r="I114" s="28"/>
       <c r="J114" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K114" s="29"/>
+      <c r="K114" s="28"/>
       <c r="L114" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B115" s="44" t="s">
+      <c r="B115" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D115" s="30"/>
-      <c r="E115" s="29" t="s">
+      <c r="D115" s="29"/>
+      <c r="E115" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F115" s="30"/>
-      <c r="G115" s="29" t="s">
+      <c r="F115" s="29"/>
+      <c r="G115" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H115" s="30"/>
-      <c r="I115" s="29" t="s">
+      <c r="H115" s="29"/>
+      <c r="I115" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J115" s="30"/>
-      <c r="K115" s="29" t="s">
+      <c r="J115" s="29"/>
+      <c r="K115" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L115" s="30"/>
+      <c r="L115" s="29"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="31" t="s">
+      <c r="A116" s="30" t="s">
         <v>75</v>
       </c>
       <c r="B116" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C116" s="31" t="s">
+      <c r="C116" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D116" s="67">
+      <c r="D116" s="66">
         <v>0.09930555555555555</v>
       </c>
-      <c r="E116" s="57"/>
-      <c r="F116" s="57"/>
-      <c r="G116" s="68" t="s">
+      <c r="E116" s="56"/>
+      <c r="F116" s="56"/>
+      <c r="G116" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="H116" s="69">
+      <c r="H116" s="68">
         <v>0.008726851851851852</v>
       </c>
-      <c r="I116" s="31" t="s">
+      <c r="I116" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="J116" s="67">
+      <c r="J116" s="66">
         <v>0.09930555555555555</v>
       </c>
       <c r="K116" s="10" t="s">
@@ -5098,34 +5089,34 @@
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="31" t="s">
+      <c r="A117" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B117" s="67">
+      <c r="B117" s="66">
         <v>0.06087962962962963</v>
       </c>
-      <c r="C117" s="31" t="s">
+      <c r="C117" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D117" s="70">
+      <c r="D117" s="69">
         <v>0.05625</v>
       </c>
-      <c r="E117" s="31" t="s">
+      <c r="E117" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F117" s="70">
+      <c r="F117" s="69">
         <v>0.6346296296296297</v>
       </c>
-      <c r="G117" s="35" t="s">
+      <c r="G117" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="H117" s="70">
+      <c r="H117" s="69">
         <v>0.014282407407407407</v>
       </c>
-      <c r="I117" s="31" t="s">
+      <c r="I117" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="J117" s="70">
+      <c r="J117" s="69">
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
@@ -5136,568 +5127,569 @@
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="31" t="s">
+      <c r="A118" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B118" s="67">
+      <c r="B118" s="66">
         <v>0.06527777777777778</v>
       </c>
-      <c r="C118" s="31" t="s">
+      <c r="C118" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D118" s="67">
+      <c r="D118" s="66">
         <v>0.07368055555555555</v>
       </c>
-      <c r="E118" s="31" t="s">
+      <c r="E118" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F118" s="70">
+      <c r="F118" s="69">
         <v>0.04513888888888889</v>
       </c>
-      <c r="G118" s="31" t="s">
+      <c r="G118" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="H118" s="70">
+      <c r="H118" s="69">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I118" s="31" t="s">
+      <c r="I118" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="J118" s="67">
+      <c r="J118" s="66">
         <v>0.07368055555555555</v>
       </c>
-      <c r="K118" s="57"/>
-      <c r="L118" s="57"/>
+      <c r="K118" s="56"/>
+      <c r="L118" s="56"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="57"/>
-      <c r="B119" s="57"/>
-      <c r="C119" s="57"/>
-      <c r="D119" s="57"/>
-      <c r="E119" s="31" t="s">
+      <c r="A119" s="56"/>
+      <c r="B119" s="56"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="56"/>
+      <c r="E119" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F119" s="70">
+      <c r="F119" s="69">
         <v>0.225</v>
       </c>
-      <c r="G119" s="31" t="s">
+      <c r="G119" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="H119" s="70">
+      <c r="H119" s="69">
         <v>0.08680555555555555</v>
       </c>
-      <c r="I119" s="31" t="s">
+      <c r="I119" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J119" s="70">
+      <c r="J119" s="69">
         <v>0.18760416666666666</v>
       </c>
-      <c r="K119" s="57"/>
-      <c r="L119" s="57"/>
+      <c r="K119" s="56"/>
+      <c r="L119" s="56"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="57"/>
-      <c r="B120" s="57"/>
-      <c r="C120" s="57"/>
-      <c r="D120" s="57"/>
-      <c r="E120" s="31" t="s">
+      <c r="A120" s="56"/>
+      <c r="B120" s="56"/>
+      <c r="C120" s="56"/>
+      <c r="D120" s="56"/>
+      <c r="E120" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F120" s="70">
+      <c r="F120" s="69">
         <v>0.2590277777777778</v>
       </c>
-      <c r="G120" s="31" t="s">
+      <c r="G120" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="H120" s="70">
+      <c r="H120" s="69">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I120" s="31" t="s">
+      <c r="I120" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="J120" s="67">
+      <c r="J120" s="66">
         <v>0.06527777777777778</v>
       </c>
-      <c r="K120" s="57"/>
-      <c r="L120" s="57"/>
+      <c r="K120" s="56"/>
+      <c r="L120" s="56"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="57"/>
-      <c r="B121" s="57"/>
-      <c r="C121" s="57"/>
-      <c r="D121" s="57"/>
-      <c r="E121" s="31" t="s">
+      <c r="A121" s="56"/>
+      <c r="B121" s="56"/>
+      <c r="C121" s="56"/>
+      <c r="D121" s="56"/>
+      <c r="E121" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F121" s="70">
+      <c r="F121" s="69">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G121" s="31" t="s">
+      <c r="G121" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="H121" s="70">
+      <c r="H121" s="69">
         <v>0.015196759259259259</v>
       </c>
-      <c r="I121" s="57"/>
-      <c r="J121" s="57"/>
-      <c r="K121" s="57"/>
-      <c r="L121" s="57"/>
+      <c r="I121" s="56"/>
+      <c r="J121" s="56"/>
+      <c r="K121" s="56"/>
+      <c r="L121" s="56"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="57"/>
-      <c r="B122" s="57"/>
-      <c r="C122" s="57"/>
-      <c r="D122" s="57"/>
-      <c r="E122" s="31" t="s">
+      <c r="A122" s="56"/>
+      <c r="B122" s="56"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F122" s="70">
+      <c r="F122" s="69">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G122" s="57"/>
-      <c r="H122" s="57"/>
-      <c r="I122" s="57"/>
-      <c r="J122" s="57"/>
-      <c r="K122" s="57"/>
-      <c r="L122" s="57"/>
+      <c r="G122" s="56"/>
+      <c r="H122" s="56"/>
+      <c r="I122" s="56"/>
+      <c r="J122" s="56"/>
+      <c r="K122" s="56"/>
+      <c r="L122" s="56"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="57"/>
-      <c r="B123" s="57"/>
-      <c r="C123" s="57"/>
-      <c r="D123" s="57"/>
-      <c r="E123" s="57"/>
-      <c r="F123" s="57"/>
-      <c r="G123" s="57"/>
-      <c r="H123" s="57"/>
-      <c r="I123" s="57"/>
-      <c r="J123" s="57"/>
-      <c r="K123" s="57"/>
-      <c r="L123" s="57"/>
+      <c r="A123" s="56"/>
+      <c r="B123" s="56"/>
+      <c r="C123" s="56"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="56"/>
+      <c r="F123" s="56"/>
+      <c r="G123" s="56"/>
+      <c r="H123" s="56"/>
+      <c r="I123" s="56"/>
+      <c r="J123" s="56"/>
+      <c r="K123" s="56"/>
+      <c r="L123" s="56"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="71"/>
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" s="71"/>
-      <c r="E124" s="71"/>
-      <c r="F124" s="71"/>
-      <c r="G124" s="71"/>
-      <c r="H124" s="71"/>
-      <c r="I124" s="71"/>
-      <c r="J124" s="71"/>
-      <c r="K124" s="71"/>
-      <c r="L124" s="71"/>
+      <c r="A124" s="70"/>
+      <c r="B124" s="70"/>
+      <c r="C124" s="70"/>
+      <c r="D124" s="70"/>
+      <c r="E124" s="70"/>
+      <c r="F124" s="70"/>
+      <c r="G124" s="70"/>
+      <c r="H124" s="70"/>
+      <c r="I124" s="70"/>
+      <c r="J124" s="70"/>
+      <c r="K124" s="70"/>
+      <c r="L124" s="70"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="37" t="s">
+      <c r="A125" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B125" s="72">
+      <c r="B125" s="71">
         <f>SUM(B116:B124)</f>
         <v>0.3587962963</v>
       </c>
-      <c r="C125" s="71"/>
-      <c r="D125" s="72">
+      <c r="C125" s="70"/>
+      <c r="D125" s="71">
         <f>SUM(D116:D118)</f>
         <v>0.2292361111</v>
       </c>
-      <c r="E125" s="71"/>
-      <c r="F125" s="73">
+      <c r="E125" s="70"/>
+      <c r="F125" s="72">
         <f>SUM(F117:F123)</f>
         <v>1.383240741</v>
       </c>
-      <c r="G125" s="71"/>
-      <c r="H125" s="72">
+      <c r="G125" s="70"/>
+      <c r="H125" s="71">
         <f>SUM(H116:H123)</f>
         <v>0.4480324074</v>
       </c>
-      <c r="I125" s="71"/>
-      <c r="J125" s="72">
+      <c r="I125" s="70"/>
+      <c r="J125" s="71">
         <f>SUM(J116:J124)</f>
         <v>0.4821180556</v>
       </c>
-      <c r="K125" s="71"/>
-      <c r="L125" s="72">
+      <c r="K125" s="70"/>
+      <c r="L125" s="71">
         <f>SUM(L116:L123)</f>
         <v>0.3020833333</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="27"/>
+      <c r="A126" s="26"/>
       <c r="B126" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C126" s="29"/>
+      <c r="C126" s="28"/>
       <c r="D126" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E126" s="29"/>
+      <c r="E126" s="28"/>
       <c r="F126" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G126" s="29"/>
+      <c r="G126" s="28"/>
       <c r="H126" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I126" s="29"/>
+      <c r="I126" s="28"/>
       <c r="J126" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="K126" s="29"/>
+      <c r="K126" s="28"/>
       <c r="L126" s="24" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="27" t="s">
+      <c r="A127" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B127" s="44" t="s">
+      <c r="B127" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="C127" s="29" t="s">
+      <c r="C127" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D127" s="30"/>
-      <c r="E127" s="29" t="s">
+      <c r="D127" s="29"/>
+      <c r="E127" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F127" s="30"/>
-      <c r="G127" s="29" t="s">
+      <c r="F127" s="29"/>
+      <c r="G127" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H127" s="30"/>
-      <c r="I127" s="29" t="s">
+      <c r="H127" s="29"/>
+      <c r="I127" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J127" s="30"/>
-      <c r="K127" s="29" t="s">
+      <c r="J127" s="29"/>
+      <c r="K127" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L127" s="30"/>
+      <c r="L127" s="29"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="21"/>
-      <c r="B128" s="21"/>
-      <c r="C128" s="74" t="s">
+      <c r="A128" s="56"/>
+      <c r="B128" s="56"/>
+      <c r="C128" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="D128" s="75">
+      <c r="D128" s="73">
         <v>0.04717592592592593</v>
       </c>
-      <c r="E128" s="74" t="s">
+      <c r="E128" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="F128" s="76">
+      <c r="F128" s="55">
         <v>0.10416666666666667</v>
       </c>
-      <c r="G128" s="74" t="s">
+      <c r="G128" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="H128" s="77">
+      <c r="H128" s="74">
         <v>0.08680555555555555</v>
       </c>
-      <c r="I128" s="31" t="s">
+      <c r="I128" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J128" s="78">
+      <c r="J128" s="53">
         <v>0.18760416666666666</v>
       </c>
-      <c r="K128" s="74" t="s">
+      <c r="K128" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="L128" s="76">
+      <c r="L128" s="55">
         <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="21"/>
-      <c r="B129" s="21"/>
-      <c r="C129" s="21"/>
-      <c r="D129" s="21"/>
-      <c r="E129" s="21"/>
-      <c r="F129" s="21"/>
-      <c r="G129" s="31" t="s">
+      <c r="A129" s="56"/>
+      <c r="B129" s="56"/>
+      <c r="C129" s="56"/>
+      <c r="D129" s="56"/>
+      <c r="E129" s="56"/>
+      <c r="F129" s="56"/>
+      <c r="G129" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="H129" s="78">
+      <c r="H129" s="53">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I129" s="74" t="s">
+      <c r="I129" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="J129" s="79">
+      <c r="J129" s="75">
         <v>0.027777777777777776</v>
       </c>
-      <c r="K129" s="21"/>
-      <c r="L129" s="21"/>
+      <c r="K129" s="56"/>
+      <c r="L129" s="56"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="21"/>
-      <c r="B130" s="21"/>
-      <c r="C130" s="21"/>
-      <c r="D130" s="21"/>
-      <c r="E130" s="21"/>
-      <c r="F130" s="21"/>
-      <c r="G130" s="31" t="s">
+      <c r="A130" s="56"/>
+      <c r="B130" s="56"/>
+      <c r="C130" s="56"/>
+      <c r="D130" s="56"/>
+      <c r="E130" s="56"/>
+      <c r="F130" s="56"/>
+      <c r="G130" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="H130" s="77">
+      <c r="H130" s="74">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I130" s="74" t="s">
+      <c r="I130" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="J130" s="79">
+      <c r="J130" s="75">
         <v>0.01662037037037037</v>
       </c>
-      <c r="K130" s="21"/>
-      <c r="L130" s="21"/>
+      <c r="K130" s="56"/>
+      <c r="L130" s="56"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="21"/>
-      <c r="B131" s="21"/>
-      <c r="C131" s="21"/>
-      <c r="D131" s="21"/>
-      <c r="E131" s="21"/>
-      <c r="F131" s="21"/>
-      <c r="G131" s="74" t="s">
+      <c r="A131" s="56"/>
+      <c r="B131" s="56"/>
+      <c r="C131" s="56"/>
+      <c r="D131" s="56"/>
+      <c r="E131" s="56"/>
+      <c r="F131" s="56"/>
+      <c r="G131" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="H131" s="79">
+      <c r="H131" s="75">
         <v>0.003472222222222222</v>
       </c>
-      <c r="J131" s="80"/>
-      <c r="K131" s="21"/>
-      <c r="L131" s="21"/>
+      <c r="I131" s="32"/>
+      <c r="J131" s="76"/>
+      <c r="K131" s="56"/>
+      <c r="L131" s="56"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="21"/>
-      <c r="B132" s="21"/>
-      <c r="C132" s="21"/>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="21"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21"/>
-      <c r="I132" s="21"/>
-      <c r="J132" s="21"/>
-      <c r="K132" s="21"/>
-      <c r="L132" s="21"/>
+      <c r="A132" s="56"/>
+      <c r="B132" s="56"/>
+      <c r="C132" s="56"/>
+      <c r="D132" s="56"/>
+      <c r="E132" s="56"/>
+      <c r="F132" s="56"/>
+      <c r="G132" s="56"/>
+      <c r="H132" s="56"/>
+      <c r="I132" s="56"/>
+      <c r="J132" s="56"/>
+      <c r="K132" s="56"/>
+      <c r="L132" s="56"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="21"/>
-      <c r="B133" s="21"/>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-      <c r="I133" s="21"/>
-      <c r="J133" s="21"/>
-      <c r="K133" s="21"/>
-      <c r="L133" s="21"/>
+      <c r="A133" s="56"/>
+      <c r="B133" s="56"/>
+      <c r="C133" s="56"/>
+      <c r="D133" s="56"/>
+      <c r="E133" s="56"/>
+      <c r="F133" s="56"/>
+      <c r="G133" s="56"/>
+      <c r="H133" s="56"/>
+      <c r="I133" s="56"/>
+      <c r="J133" s="56"/>
+      <c r="K133" s="56"/>
+      <c r="L133" s="56"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="21"/>
-      <c r="B134" s="21"/>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21"/>
-      <c r="K134" s="21"/>
-      <c r="L134" s="21"/>
+      <c r="A134" s="56"/>
+      <c r="B134" s="56"/>
+      <c r="C134" s="56"/>
+      <c r="D134" s="56"/>
+      <c r="E134" s="56"/>
+      <c r="F134" s="56"/>
+      <c r="G134" s="56"/>
+      <c r="H134" s="56"/>
+      <c r="I134" s="56"/>
+      <c r="J134" s="56"/>
+      <c r="K134" s="56"/>
+      <c r="L134" s="56"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="21"/>
-      <c r="B135" s="21"/>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
-      <c r="I135" s="21"/>
-      <c r="J135" s="21"/>
-      <c r="K135" s="21"/>
-      <c r="L135" s="21"/>
+      <c r="A135" s="56"/>
+      <c r="B135" s="56"/>
+      <c r="C135" s="56"/>
+      <c r="D135" s="56"/>
+      <c r="E135" s="56"/>
+      <c r="F135" s="56"/>
+      <c r="G135" s="56"/>
+      <c r="H135" s="56"/>
+      <c r="I135" s="56"/>
+      <c r="J135" s="56"/>
+      <c r="K135" s="56"/>
+      <c r="L135" s="56"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="21"/>
-      <c r="B136" s="21"/>
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="21"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="21"/>
-      <c r="I136" s="21"/>
-      <c r="J136" s="21"/>
-      <c r="K136" s="21"/>
-      <c r="L136" s="21"/>
+      <c r="A136" s="56"/>
+      <c r="B136" s="56"/>
+      <c r="C136" s="56"/>
+      <c r="D136" s="56"/>
+      <c r="E136" s="56"/>
+      <c r="F136" s="56"/>
+      <c r="G136" s="56"/>
+      <c r="H136" s="56"/>
+      <c r="I136" s="56"/>
+      <c r="J136" s="56"/>
+      <c r="K136" s="56"/>
+      <c r="L136" s="56"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="21"/>
-      <c r="B137" s="21"/>
-      <c r="C137" s="21"/>
-      <c r="D137" s="21"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="21"/>
-      <c r="G137" s="21"/>
-      <c r="H137" s="21"/>
-      <c r="I137" s="21"/>
-      <c r="J137" s="21"/>
-      <c r="K137" s="21"/>
-      <c r="L137" s="21"/>
+      <c r="A137" s="56"/>
+      <c r="B137" s="56"/>
+      <c r="C137" s="56"/>
+      <c r="D137" s="56"/>
+      <c r="E137" s="56"/>
+      <c r="F137" s="56"/>
+      <c r="G137" s="56"/>
+      <c r="H137" s="56"/>
+      <c r="I137" s="56"/>
+      <c r="J137" s="56"/>
+      <c r="K137" s="56"/>
+      <c r="L137" s="56"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="21"/>
-      <c r="B138" s="21"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="21"/>
-      <c r="F138" s="21"/>
-      <c r="G138" s="21"/>
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
-      <c r="J138" s="21"/>
-      <c r="K138" s="21"/>
-      <c r="L138" s="21"/>
+      <c r="A138" s="56"/>
+      <c r="B138" s="56"/>
+      <c r="C138" s="56"/>
+      <c r="D138" s="56"/>
+      <c r="E138" s="56"/>
+      <c r="F138" s="56"/>
+      <c r="G138" s="56"/>
+      <c r="H138" s="56"/>
+      <c r="I138" s="56"/>
+      <c r="J138" s="56"/>
+      <c r="K138" s="56"/>
+      <c r="L138" s="56"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="21"/>
-      <c r="B139" s="21"/>
-      <c r="C139" s="21"/>
-      <c r="D139" s="21"/>
-      <c r="E139" s="21"/>
-      <c r="F139" s="21"/>
-      <c r="G139" s="21"/>
-      <c r="H139" s="21"/>
-      <c r="I139" s="21"/>
-      <c r="J139" s="21"/>
-      <c r="K139" s="21"/>
-      <c r="L139" s="21"/>
+      <c r="A139" s="56"/>
+      <c r="B139" s="56"/>
+      <c r="C139" s="56"/>
+      <c r="D139" s="56"/>
+      <c r="E139" s="56"/>
+      <c r="F139" s="56"/>
+      <c r="G139" s="56"/>
+      <c r="H139" s="56"/>
+      <c r="I139" s="56"/>
+      <c r="J139" s="56"/>
+      <c r="K139" s="56"/>
+      <c r="L139" s="56"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="21"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="21"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="21"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
-      <c r="I140" s="21"/>
-      <c r="J140" s="21"/>
-      <c r="K140" s="21"/>
-      <c r="L140" s="21"/>
+      <c r="A140" s="56"/>
+      <c r="B140" s="56"/>
+      <c r="C140" s="56"/>
+      <c r="D140" s="56"/>
+      <c r="E140" s="56"/>
+      <c r="F140" s="56"/>
+      <c r="G140" s="56"/>
+      <c r="H140" s="56"/>
+      <c r="I140" s="56"/>
+      <c r="J140" s="56"/>
+      <c r="K140" s="56"/>
+      <c r="L140" s="56"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="21"/>
-      <c r="B141" s="21"/>
-      <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="21"/>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-      <c r="H141" s="21"/>
-      <c r="I141" s="21"/>
-      <c r="J141" s="21"/>
-      <c r="K141" s="21"/>
-      <c r="L141" s="21"/>
+      <c r="A141" s="56"/>
+      <c r="B141" s="56"/>
+      <c r="C141" s="56"/>
+      <c r="D141" s="56"/>
+      <c r="E141" s="56"/>
+      <c r="F141" s="56"/>
+      <c r="G141" s="56"/>
+      <c r="H141" s="56"/>
+      <c r="I141" s="56"/>
+      <c r="J141" s="56"/>
+      <c r="K141" s="56"/>
+      <c r="L141" s="56"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="21"/>
-      <c r="B142" s="21"/>
-      <c r="C142" s="21"/>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21"/>
-      <c r="I142" s="21"/>
-      <c r="J142" s="21"/>
-      <c r="K142" s="21"/>
-      <c r="L142" s="21"/>
+      <c r="A142" s="56"/>
+      <c r="B142" s="56"/>
+      <c r="C142" s="56"/>
+      <c r="D142" s="56"/>
+      <c r="E142" s="56"/>
+      <c r="F142" s="56"/>
+      <c r="G142" s="56"/>
+      <c r="H142" s="56"/>
+      <c r="I142" s="56"/>
+      <c r="J142" s="56"/>
+      <c r="K142" s="56"/>
+      <c r="L142" s="56"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="21"/>
-      <c r="B143" s="21"/>
-      <c r="C143" s="21"/>
-      <c r="D143" s="21"/>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
-      <c r="I143" s="21"/>
-      <c r="J143" s="21"/>
-      <c r="K143" s="21"/>
-      <c r="L143" s="21"/>
+      <c r="A143" s="56"/>
+      <c r="B143" s="56"/>
+      <c r="C143" s="56"/>
+      <c r="D143" s="56"/>
+      <c r="E143" s="56"/>
+      <c r="F143" s="56"/>
+      <c r="G143" s="56"/>
+      <c r="H143" s="56"/>
+      <c r="I143" s="56"/>
+      <c r="J143" s="56"/>
+      <c r="K143" s="56"/>
+      <c r="L143" s="56"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="21"/>
-      <c r="B144" s="21"/>
-      <c r="C144" s="21"/>
-      <c r="D144" s="21"/>
-      <c r="E144" s="21"/>
-      <c r="F144" s="21"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21"/>
-      <c r="I144" s="21"/>
-      <c r="J144" s="21"/>
-      <c r="K144" s="21"/>
-      <c r="L144" s="21"/>
+      <c r="A144" s="56"/>
+      <c r="B144" s="56"/>
+      <c r="C144" s="56"/>
+      <c r="D144" s="56"/>
+      <c r="E144" s="56"/>
+      <c r="F144" s="56"/>
+      <c r="G144" s="56"/>
+      <c r="H144" s="56"/>
+      <c r="I144" s="56"/>
+      <c r="J144" s="56"/>
+      <c r="K144" s="56"/>
+      <c r="L144" s="56"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="21"/>
-      <c r="B145" s="21"/>
-      <c r="C145" s="21"/>
-      <c r="D145" s="21"/>
-      <c r="E145" s="21"/>
-      <c r="F145" s="21"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21"/>
-      <c r="I145" s="21"/>
-      <c r="J145" s="21"/>
-      <c r="K145" s="21"/>
-      <c r="L145" s="21"/>
+      <c r="A145" s="56"/>
+      <c r="B145" s="56"/>
+      <c r="C145" s="56"/>
+      <c r="D145" s="56"/>
+      <c r="E145" s="56"/>
+      <c r="F145" s="56"/>
+      <c r="G145" s="56"/>
+      <c r="H145" s="56"/>
+      <c r="I145" s="56"/>
+      <c r="J145" s="56"/>
+      <c r="K145" s="56"/>
+      <c r="L145" s="56"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="37" t="s">
+      <c r="A146" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B146" s="71">
+      <c r="B146" s="70">
         <f>SUM(B128:B145)</f>
         <v>0</v>
       </c>
-      <c r="C146" s="71"/>
-      <c r="D146" s="73">
+      <c r="C146" s="70"/>
+      <c r="D146" s="72">
         <f>SUM(D128:D145)</f>
         <v>0.04717592593</v>
       </c>
-      <c r="E146" s="71"/>
-      <c r="F146" s="73">
+      <c r="E146" s="70"/>
+      <c r="F146" s="72">
         <f>SUM(F128:F145)</f>
         <v>0.1041666667</v>
       </c>
-      <c r="G146" s="71"/>
-      <c r="H146" s="73">
+      <c r="G146" s="70"/>
+      <c r="H146" s="72">
         <f>SUM(H128:H145)</f>
         <v>0.4132986111</v>
       </c>
-      <c r="I146" s="71"/>
-      <c r="J146" s="73">
+      <c r="I146" s="70"/>
+      <c r="J146" s="72">
         <f>SUM(J128:J145)</f>
         <v>0.2320023148</v>
       </c>
-      <c r="K146" s="71"/>
-      <c r="L146" s="73">
+      <c r="K146" s="70"/>
+      <c r="L146" s="72">
         <f>SUM(L128:L145)</f>
         <v>0.1041666667</v>
       </c>
@@ -6588,130 +6580,169 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="77" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="82">
+      <c r="B4" s="78">
         <v>1.0</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4" s="79">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="83">
+      <c r="D4" s="79">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="82">
+      <c r="B5" s="78">
         <v>2.0</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5" s="79">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="79">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="82">
+      <c r="B6" s="78">
         <v>3.0</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="79">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="83">
+      <c r="D6" s="79">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="82">
+      <c r="B7" s="78">
         <v>4.0</v>
       </c>
-      <c r="C7" s="83">
+      <c r="C7" s="79">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="83">
+      <c r="D7" s="79">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="82">
+      <c r="B8" s="78">
         <v>5.0</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="79">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="83">
+      <c r="D8" s="79">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="82">
+      <c r="B9" s="78">
         <v>6.0</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="79">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="79">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="82">
+      <c r="B10" s="78">
         <v>7.0</v>
       </c>
-      <c r="C10" s="83">
+      <c r="C10" s="79">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="80">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="82">
+      <c r="B11" s="78">
         <v>8.0</v>
       </c>
-      <c r="C11" s="84">
+      <c r="C11" s="80">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="80">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="82">
+      <c r="B12" s="78">
         <v>9.0</v>
       </c>
-      <c r="C12" s="84">
+      <c r="C12" s="80">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="84">
+      <c r="D12" s="80">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="82">
+      <c r="B13" s="78">
         <v>10.0</v>
       </c>
-      <c r="C13" s="84">
+      <c r="C13" s="80">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="83">
+      <c r="D13" s="79">
         <v>45965.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="B14" s="81">
+        <v>11.0</v>
+      </c>
+      <c r="C14" s="82">
+        <v>45965.0</v>
+      </c>
+      <c r="D14" s="83">
+        <v>45972.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="81">
+        <v>12.0</v>
+      </c>
+      <c r="C15" s="83">
+        <v>45941.0</v>
+      </c>
+      <c r="D15" s="83">
+        <v>45979.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="81">
+        <v>13.0</v>
+      </c>
+      <c r="C16" s="83">
+        <v>45979.0</v>
+      </c>
+      <c r="D16" s="83">
+        <v>45986.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="81">
+        <v>14.0</v>
+      </c>
+      <c r="C17" s="83">
+        <v>45986.0</v>
+      </c>
+      <c r="D17" s="83">
+        <v>45989.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="107">
   <si>
     <t>Semana</t>
   </si>
@@ -65,6 +65,9 @@
     <t>Construcción-Iteración 1</t>
   </si>
   <si>
+    <t>Construcción-Iteración 2</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -299,7 +302,7 @@
     <t>Semana 10</t>
   </si>
   <si>
-    <t>Especificación de CU15: Visualizar tarea</t>
+    <t>Especificación de CU15,CU16</t>
   </si>
   <si>
     <t>Implementación CU07: crear etapa</t>
@@ -311,7 +314,19 @@
     <t>Reunión 30/10</t>
   </si>
   <si>
+    <t>Especificación de CU13,CU14</t>
+  </si>
+  <si>
+    <t>Implementación CU08: crear iteración</t>
+  </si>
+  <si>
     <t>Cierre de Iteración</t>
+  </si>
+  <si>
+    <t>Especificación de CU08</t>
+  </si>
+  <si>
+    <t>Implementacion CU16: Comentar tarea</t>
   </si>
   <si>
     <t>Priorización de CU's 2da tanda</t>
@@ -565,16 +580,11 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="3" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="46" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="8" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -705,13 +715,18 @@
     <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="13" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -1370,11 +1385,11 @@
       </c>
       <c r="C11" s="15">
         <f>Registro!D146</f>
-        <v>0.04717592593</v>
+        <v>0.251087963</v>
       </c>
       <c r="D11" s="15">
         <f>Registro!F146</f>
-        <v>0.1041666667</v>
+        <v>0.7051273148</v>
       </c>
       <c r="E11" s="15">
         <f>Registro!H146</f>
@@ -1382,53 +1397,55 @@
       </c>
       <c r="F11" s="15">
         <f>Registro!J146</f>
-        <v>0.2320023148</v>
+        <v>0.4830902778</v>
       </c>
       <c r="G11" s="15">
         <f>Registro!L146</f>
         <v>0.1041666667</v>
       </c>
       <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
+      <c r="I11" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="18">
+      <c r="A12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="17">
         <f>SUM(B2:B10)</f>
         <v>3.201782407</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <f t="shared" ref="C12:G12" si="2">SUM(C2:C11)</f>
-        <v>4.134155093</v>
-      </c>
-      <c r="D12" s="18">
+        <v>4.33806713</v>
+      </c>
+      <c r="D12" s="17">
         <f t="shared" si="2"/>
-        <v>3.690138889</v>
-      </c>
-      <c r="E12" s="18">
+        <v>4.291099537</v>
+      </c>
+      <c r="E12" s="17">
         <f t="shared" si="2"/>
         <v>1.384479167</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f t="shared" si="2"/>
-        <v>2.838298611</v>
-      </c>
-      <c r="G12" s="18">
+        <v>3.089386574</v>
+      </c>
+      <c r="G12" s="17">
         <f t="shared" si="2"/>
         <v>1.369537037</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <f>SUM(Total!$B12:$G12)</f>
-        <v>16.6183912</v>
-      </c>
-      <c r="I12" s="19"/>
+        <v>17.67435185</v>
+      </c>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" ht="14.25" customHeight="1"/>
     <row r="14" ht="14.25" customHeight="1"/>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="H15" s="20"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
@@ -2441,7 +2458,7 @@
     <col customWidth="1" min="2" max="2" width="24.88"/>
     <col customWidth="1" min="3" max="3" width="39.38"/>
     <col customWidth="1" min="4" max="4" width="39.5"/>
-    <col customWidth="1" min="5" max="5" width="27.63"/>
+    <col customWidth="1" min="5" max="5" width="37.0"/>
     <col customWidth="1" min="6" max="6" width="17.75"/>
     <col customWidth="1" min="7" max="7" width="44.75"/>
     <col customWidth="1" min="8" max="8" width="27.63"/>
@@ -2453,436 +2470,436 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="20"/>
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="22" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="24" t="s">
+      <c r="I1" s="22"/>
+      <c r="J1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="24" t="s">
+      <c r="K1" s="24"/>
+      <c r="L1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="29"/>
+      <c r="B2" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="28"/>
+      <c r="G2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="28"/>
+      <c r="I2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="28"/>
+      <c r="K2" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="30" t="s">
-        <v>18</v>
+      <c r="A3" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="6">
         <v>0.05783564814814815</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="9">
         <v>0.03487268518518519</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="K3" s="32"/>
+      <c r="K3" s="31"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>18</v>
+      <c r="A4" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="B4" s="5">
         <v>1.1574074074074075E-4</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="7">
         <v>0.06111111111111111</v>
       </c>
-      <c r="K4" s="32"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>22</v>
+      <c r="A5" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B5" s="5">
         <v>0.04273148148148148</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
       <c r="I5" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="7">
         <v>0.019791666666666666</v>
       </c>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>22</v>
+      <c r="A6" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B6" s="5">
         <v>0.002939814814814815</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
       <c r="I6" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" s="7">
         <v>0.039780092592592596</v>
       </c>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="30" t="s">
-        <v>24</v>
+      <c r="A7" s="29" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="5">
         <v>0.06607638888888889</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" s="9">
         <v>0.0798611111111111</v>
       </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>26</v>
+      <c r="A8" s="29" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="5">
         <v>0.06518518518518518</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="33" t="s">
-        <v>27</v>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="J8" s="13">
         <v>0.03515046296296296</v>
       </c>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>25</v>
+      <c r="A9" s="29" t="s">
+        <v>26</v>
       </c>
       <c r="B9" s="5">
         <v>0.0798611111111111</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J9" s="7">
         <v>0.06607638888888889</v>
       </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>23</v>
+      <c r="A10" s="29" t="s">
+        <v>24</v>
       </c>
       <c r="B10" s="5">
         <v>0.019791666666666666</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="9">
         <v>0.05783564814814815</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="34" t="s">
-        <v>23</v>
+      <c r="A11" s="33" t="s">
+        <v>24</v>
       </c>
       <c r="B11" s="5">
         <v>0.039780092592592596</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>28</v>
+      <c r="A12" s="29" t="s">
+        <v>29</v>
       </c>
       <c r="B12" s="5">
         <v>0.028356481481481483</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="30" t="s">
-        <v>29</v>
+      <c r="A13" s="29" t="s">
+        <v>30</v>
       </c>
       <c r="B13" s="5">
         <v>0.013148148148148148</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="37">
+      <c r="A15" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="36">
         <f>SUM(B3:B14)</f>
         <v>0.4929050926</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="38">
+      <c r="F15" s="37">
         <f>SUM(F3:F14)</f>
         <v>0.03487268519</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="38">
+      <c r="J15" s="37">
         <f>SUM(J3:J14)</f>
         <v>0.4366898148</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="38">
+      <c r="L15" s="37">
         <f>SUM(L3:L14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="26"/>
-      <c r="B16" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="24" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="24" t="s">
+      <c r="E16" s="27"/>
+      <c r="F16" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="24" t="s">
+      <c r="G16" s="27"/>
+      <c r="H16" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="24" t="s">
+      <c r="I16" s="27"/>
+      <c r="J16" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="28"/>
-      <c r="L16" s="24" t="s">
+      <c r="K16" s="27"/>
+      <c r="L16" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="29"/>
-      <c r="G17" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" s="29"/>
+      <c r="A17" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="28"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="30" t="s">
-        <v>18</v>
+      <c r="A18" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
       <c r="E18" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="7">
         <v>0.08034722222222222</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="30" t="s">
-        <v>22</v>
+      <c r="A19" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F19" s="9">
         <v>0.6090277777777777</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="7">
         <v>0.003414351851851852</v>
@@ -2891,826 +2908,826 @@
       <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="K19" s="40" t="s">
-        <v>35</v>
+      <c r="K19" s="39" t="s">
+        <v>36</v>
       </c>
       <c r="L19" s="7">
         <v>0.03150462962962963</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>22</v>
+      <c r="A20" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
       <c r="G20" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="I20" s="41" t="s">
-        <v>36</v>
+      <c r="I20" s="40" t="s">
+        <v>37</v>
       </c>
       <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="K20" s="40" t="s">
-        <v>35</v>
+      <c r="K20" s="39" t="s">
+        <v>36</v>
       </c>
       <c r="L20" s="7">
         <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>22</v>
+      <c r="A21" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>22</v>
+      <c r="A22" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>22</v>
+      <c r="A23" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>22</v>
+      <c r="A24" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>22</v>
+      <c r="A25" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>22</v>
+      <c r="A26" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>22</v>
+      <c r="A27" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>22</v>
+      <c r="A28" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>22</v>
+      <c r="A29" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>22</v>
+      <c r="A30" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>22</v>
+      <c r="A31" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>22</v>
+      <c r="A32" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>22</v>
+      <c r="A33" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>22</v>
+      <c r="A34" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>22</v>
+      <c r="A35" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>22</v>
+      <c r="A36" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>18</v>
+      <c r="A37" s="29" t="s">
+        <v>19</v>
       </c>
       <c r="B37" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="38">
+      <c r="A38" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="37">
         <f>SUM(B18:B37)</f>
         <v>0.4042824074</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42">
+      <c r="E38" s="41"/>
+      <c r="F38" s="41">
         <f>SUM(F17:F36)</f>
         <v>0.689375</v>
       </c>
       <c r="G38" s="3"/>
-      <c r="H38" s="38">
+      <c r="H38" s="37">
         <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42">
+      <c r="I38" s="41"/>
+      <c r="J38" s="41">
         <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="K38" s="42"/>
-      <c r="L38" s="42">
+      <c r="K38" s="41"/>
+      <c r="L38" s="41">
         <f>SUM(L18:L36)</f>
         <v>0.03163194444</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="26"/>
-      <c r="B39" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="24" t="s">
+      <c r="A39" s="25"/>
+      <c r="B39" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="27"/>
+      <c r="D39" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="24" t="s">
+      <c r="E39" s="27"/>
+      <c r="F39" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="28"/>
-      <c r="H39" s="24" t="s">
+      <c r="G39" s="27"/>
+      <c r="H39" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="28"/>
-      <c r="J39" s="24" t="s">
+      <c r="I39" s="27"/>
+      <c r="J39" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="28"/>
-      <c r="L39" s="24" t="s">
+      <c r="K39" s="27"/>
+      <c r="L39" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="29"/>
-      <c r="E40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" s="29"/>
-      <c r="G40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="29"/>
-      <c r="I40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="29"/>
-      <c r="K40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L40" s="29"/>
+      <c r="A40" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="28"/>
+      <c r="I40" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="28"/>
+      <c r="K40" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40" s="28"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>22</v>
+      <c r="A41" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6">
         <v>0.23333333333333334</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
       <c r="I41" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J41" s="7">
         <v>0.0575462962962963</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L41" s="7">
         <v>0.016446759259259258</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>22</v>
+      <c r="A42" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
       <c r="I42" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" s="7">
         <v>0.019178240740740742</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L42" s="7">
         <v>0.10934027777777777</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="30" t="s">
-        <v>22</v>
+      <c r="A43" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
       <c r="I43" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J43" s="7">
         <v>0.01525462962962963</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L43" s="7">
         <v>0.03608796296296296</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>22</v>
+      <c r="A44" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
       <c r="I44" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>22</v>
+      <c r="A45" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
       <c r="I45" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>22</v>
+      <c r="A46" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
       <c r="I46" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>22</v>
+      <c r="A47" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
       <c r="I47" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>22</v>
+      <c r="A48" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
       <c r="I48" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>22</v>
+      <c r="A49" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
       <c r="I49" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>22</v>
+      <c r="A50" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
       <c r="I50" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>22</v>
+      <c r="A51" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
       <c r="I51" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>22</v>
+      <c r="A52" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="46"/>
+      <c r="A53" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="45"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>22</v>
+      <c r="A54" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>22</v>
+      <c r="A55" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>22</v>
+      <c r="A56" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="31"/>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>22</v>
+      <c r="A57" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>22</v>
+      <c r="A58" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="38">
+      <c r="A59" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="37">
         <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="42">
+      <c r="F59" s="41">
         <f>SUM(F41:F58)</f>
         <v>0.2333333333</v>
       </c>
@@ -3720,73 +3737,73 @@
         <v>0</v>
       </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="38">
+      <c r="J59" s="37">
         <f>SUM(J41:J58)</f>
         <v>0.218587963</v>
       </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="38">
+      <c r="L59" s="37">
         <f>SUM(L41:L58)</f>
         <v>0.161875</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="26"/>
-      <c r="B60" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C60" s="28"/>
-      <c r="D60" s="24" t="s">
+      <c r="A60" s="25"/>
+      <c r="B60" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="27"/>
+      <c r="D60" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="28"/>
-      <c r="F60" s="24" t="s">
+      <c r="E60" s="27"/>
+      <c r="F60" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="28"/>
-      <c r="H60" s="24" t="s">
+      <c r="G60" s="27"/>
+      <c r="H60" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="28"/>
-      <c r="J60" s="24" t="s">
+      <c r="I60" s="27"/>
+      <c r="J60" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="28"/>
-      <c r="L60" s="24" t="s">
+      <c r="K60" s="27"/>
+      <c r="L60" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B61" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" s="29"/>
-      <c r="G61" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="29"/>
-      <c r="I61" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="29"/>
-      <c r="K61" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L61" s="29"/>
+      <c r="A61" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="28"/>
+      <c r="E61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="28"/>
+      <c r="G61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" s="28"/>
+      <c r="I61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="28"/>
+      <c r="K61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L61" s="28"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>22</v>
+      <c r="A62" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B62" s="7">
         <v>0.0028703703703703703</v>
@@ -3800,1018 +3817,1018 @@
         <v>0.09237268518518518</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="7">
         <v>0.16012731481481482</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>22</v>
+      <c r="A63" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
       <c r="G63" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H63" s="7">
         <v>0.017881944444444443</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>22</v>
+      <c r="A64" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="30" t="s">
-        <v>44</v>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="J64" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>22</v>
+      <c r="A65" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>44</v>
+      <c r="A66" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>22</v>
+      <c r="A67" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>22</v>
+      <c r="A68" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="31"/>
-      <c r="L68" s="31"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>22</v>
+      <c r="A69" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>22</v>
+      <c r="A70" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>22</v>
+      <c r="A71" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>22</v>
+      <c r="A72" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="30" t="s">
-        <v>22</v>
+      <c r="A73" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="31"/>
-      <c r="K73" s="31"/>
-      <c r="L73" s="31"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="30" t="s">
-        <v>22</v>
+      <c r="A74" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="31"/>
-      <c r="L74" s="31"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" s="38">
+      <c r="A75" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="37">
         <f>SUM(B62:B74)</f>
         <v>0.6286805556</v>
       </c>
-      <c r="C75" s="47"/>
-      <c r="D75" s="37">
+      <c r="C75" s="46"/>
+      <c r="D75" s="36">
         <f>SUM(D62:D74)</f>
         <v>0.0244212963</v>
       </c>
-      <c r="E75" s="48"/>
-      <c r="F75" s="38">
+      <c r="E75" s="47"/>
+      <c r="F75" s="37">
         <f>SUM(F62:F74)</f>
         <v>0.09237268519</v>
       </c>
-      <c r="G75" s="48"/>
-      <c r="H75" s="38">
+      <c r="G75" s="47"/>
+      <c r="H75" s="37">
         <f>SUM(H62:H74)</f>
         <v>0.1780092593</v>
       </c>
-      <c r="I75" s="48"/>
-      <c r="J75" s="38">
+      <c r="I75" s="47"/>
+      <c r="J75" s="37">
         <f>SUM(J62:J74)</f>
         <v>0.2304861111</v>
       </c>
-      <c r="K75" s="48"/>
-      <c r="L75" s="48"/>
+      <c r="K75" s="47"/>
+      <c r="L75" s="47"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="26"/>
-      <c r="B76" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C76" s="28"/>
-      <c r="D76" s="24" t="s">
+      <c r="A76" s="25"/>
+      <c r="B76" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="27"/>
+      <c r="D76" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="24" t="s">
+      <c r="E76" s="27"/>
+      <c r="F76" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="28"/>
-      <c r="H76" s="24" t="s">
+      <c r="G76" s="27"/>
+      <c r="H76" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="28"/>
-      <c r="J76" s="24" t="s">
+      <c r="I76" s="27"/>
+      <c r="J76" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="28"/>
-      <c r="L76" s="24" t="s">
+      <c r="K76" s="27"/>
+      <c r="L76" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B77" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" s="29"/>
-      <c r="E77" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" s="29"/>
-      <c r="G77" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" s="29"/>
-      <c r="I77" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="29"/>
-      <c r="K77" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L77" s="29"/>
+      <c r="A77" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="28"/>
+      <c r="E77" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="28"/>
+      <c r="G77" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="28"/>
+      <c r="I77" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="28"/>
+      <c r="K77" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" s="28"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="30" t="s">
-        <v>46</v>
+      <c r="A78" s="29" t="s">
+        <v>47</v>
       </c>
       <c r="B78" s="7">
         <v>0.125</v>
       </c>
-      <c r="C78" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="D78" s="50">
+      <c r="C78" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" s="49">
         <v>0.11513888888888889</v>
       </c>
-      <c r="E78" s="51"/>
-      <c r="F78" s="51"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50">
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49">
         <v>0.013888888888888888</v>
       </c>
-      <c r="I78" s="30" t="s">
-        <v>48</v>
+      <c r="I78" s="29" t="s">
+        <v>49</v>
       </c>
       <c r="J78" s="7">
         <v>0.08333333333333333</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L78" s="9">
         <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="30" t="s">
-        <v>50</v>
+      <c r="A79" s="29" t="s">
+        <v>51</v>
       </c>
       <c r="B79" s="7">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C79" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="D79" s="50">
+      <c r="C79" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" s="49">
         <v>0.5638888888888889</v>
       </c>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="51"/>
-      <c r="I79" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="J79" s="52">
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J79" s="51">
         <v>0.09305555555555556</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B80" s="53">
+      <c r="A80" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80" s="52">
         <v>0.0625</v>
       </c>
-      <c r="C80" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="D80" s="54">
+      <c r="C80" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="53">
         <v>0.19444444444444445</v>
       </c>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="51"/>
-      <c r="I80" s="33" t="s">
-        <v>51</v>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="32" t="s">
+        <v>52</v>
       </c>
       <c r="J80" s="13">
         <v>0.041666666666666664</v>
       </c>
-      <c r="K80" s="51"/>
-      <c r="L80" s="51"/>
+      <c r="K80" s="50"/>
+      <c r="L80" s="50"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B81" s="55">
+      <c r="A81" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B81" s="54">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C81" s="50"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="51"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="51"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="50"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="49"/>
+      <c r="L81" s="49"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="30" t="s">
-        <v>52</v>
+      <c r="A82" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="B82" s="9">
         <v>0.05763888888888889</v>
       </c>
-      <c r="C82" s="50"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="51"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="51"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="51"/>
-      <c r="L82" s="51"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="49"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="50"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="56"/>
+      <c r="A83" s="55"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="51"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="51"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="51"/>
-      <c r="L83" s="51"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="50"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="50"/>
+      <c r="L83" s="50"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="56"/>
+      <c r="A84" s="55"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="50"/>
-      <c r="D84" s="50"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="51"/>
-      <c r="J84" s="51"/>
-      <c r="K84" s="51"/>
-      <c r="L84" s="51"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="50"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="50"/>
+      <c r="L84" s="50"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="56"/>
+      <c r="A85" s="55"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="51"/>
-      <c r="K85" s="57"/>
-      <c r="L85" s="57"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="50"/>
+      <c r="I85" s="50"/>
+      <c r="J85" s="50"/>
+      <c r="K85" s="56"/>
+      <c r="L85" s="56"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" s="42">
+        <v>16</v>
+      </c>
+      <c r="B86" s="41">
         <f>SUM(B78:B85)</f>
         <v>0.3979166667</v>
       </c>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58">
+      <c r="C86" s="57"/>
+      <c r="D86" s="57">
         <f>SUM(D78:D83)</f>
         <v>0.8734722222</v>
       </c>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="37">
+      <c r="E86" s="58"/>
+      <c r="F86" s="58"/>
+      <c r="G86" s="58"/>
+      <c r="H86" s="36">
         <f>SUM(H78:H85)</f>
         <v>0.01388888889</v>
       </c>
-      <c r="I86" s="59"/>
-      <c r="J86" s="37">
+      <c r="I86" s="58"/>
+      <c r="J86" s="36">
         <f>SUM(J78:J85)</f>
         <v>0.2180555556</v>
       </c>
-      <c r="K86" s="42"/>
-      <c r="L86" s="42">
+      <c r="K86" s="41"/>
+      <c r="L86" s="41">
         <f>SUM(L78:L80)</f>
         <v>0.03333333333</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="26"/>
-      <c r="B87" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C87" s="28"/>
-      <c r="D87" s="24" t="s">
+      <c r="A87" s="25"/>
+      <c r="B87" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="27"/>
+      <c r="D87" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="28"/>
-      <c r="F87" s="24" t="s">
+      <c r="E87" s="27"/>
+      <c r="F87" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="28"/>
-      <c r="H87" s="24" t="s">
+      <c r="G87" s="27"/>
+      <c r="H87" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I87" s="28"/>
-      <c r="J87" s="24" t="s">
+      <c r="I87" s="27"/>
+      <c r="J87" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="28"/>
-      <c r="L87" s="24" t="s">
+      <c r="K87" s="27"/>
+      <c r="L87" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B88" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C88" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="29"/>
-      <c r="E88" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F88" s="29"/>
-      <c r="G88" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H88" s="29"/>
-      <c r="I88" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="29"/>
-      <c r="K88" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L88" s="29"/>
+      <c r="A88" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C88" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="28"/>
+      <c r="E88" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="28"/>
+      <c r="G88" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="28"/>
+      <c r="I88" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="28"/>
+      <c r="K88" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L88" s="28"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="56"/>
+      <c r="A89" s="55"/>
       <c r="B89" s="7">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C89" s="49" t="s">
-        <v>54</v>
+      <c r="C89" s="48" t="s">
+        <v>55</v>
       </c>
       <c r="D89" s="13">
         <v>0.17631944444444445</v>
       </c>
-      <c r="E89" s="60" t="s">
-        <v>55</v>
+      <c r="E89" s="59" t="s">
+        <v>56</v>
       </c>
       <c r="F89" s="7">
         <v>0.39791666666666664</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H89" s="7">
         <v>0.10641203703703704</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J89" s="7">
         <v>0.003472222222222222</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L89" s="7">
         <v>0.125</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="56"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="49" t="s">
-        <v>59</v>
+      <c r="A90" s="55"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="48" t="s">
+        <v>60</v>
       </c>
       <c r="D90" s="13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E90" s="60" t="s">
-        <v>55</v>
+      <c r="E90" s="59" t="s">
+        <v>56</v>
       </c>
       <c r="F90" s="7">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G90" s="41" t="s">
-        <v>60</v>
+      <c r="G90" s="40" t="s">
+        <v>61</v>
       </c>
       <c r="H90" s="7">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I90" s="31"/>
-      <c r="J90" s="31"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
       <c r="K90" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L90" s="7">
         <v>0.0625</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="56"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D91" s="52">
+      <c r="A91" s="55"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="51">
         <v>0.32806712962962964</v>
       </c>
-      <c r="E91" s="60" t="s">
-        <v>55</v>
+      <c r="E91" s="59" t="s">
+        <v>56</v>
       </c>
       <c r="F91" s="7">
         <v>0.125</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H91" s="7">
         <v>0.06527777777777778</v>
       </c>
-      <c r="I91" s="31"/>
-      <c r="J91" s="31"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="30"/>
       <c r="K91" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L91" s="9">
         <v>0.23644675925925926</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="56"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="31"/>
-      <c r="G92" s="31"/>
-      <c r="H92" s="31"/>
-      <c r="I92" s="31"/>
-      <c r="J92" s="31"/>
-      <c r="K92" s="31"/>
-      <c r="L92" s="31"/>
+      <c r="A92" s="55"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="50"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="30"/>
+      <c r="K92" s="30"/>
+      <c r="L92" s="30"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="42">
+        <v>16</v>
+      </c>
+      <c r="B93" s="41">
         <f>SUM(B89)</f>
         <v>0.08333333333</v>
       </c>
-      <c r="C93" s="58"/>
-      <c r="D93" s="58">
+      <c r="C93" s="57"/>
+      <c r="D93" s="57">
         <f>SUM(D89:D92)</f>
         <v>0.6710532407</v>
       </c>
-      <c r="E93" s="42"/>
-      <c r="F93" s="42">
+      <c r="E93" s="41"/>
+      <c r="F93" s="41">
         <f>SUM(F89:F91)</f>
         <v>0.8770833333</v>
       </c>
-      <c r="G93" s="42"/>
-      <c r="H93" s="42">
+      <c r="G93" s="41"/>
+      <c r="H93" s="41">
         <f>SUM(H89:H91)</f>
         <v>0.3071064815</v>
       </c>
-      <c r="I93" s="42"/>
-      <c r="J93" s="42">
+      <c r="I93" s="41"/>
+      <c r="J93" s="41">
         <f>SUM(J89)</f>
         <v>0.003472222222</v>
       </c>
-      <c r="K93" s="42"/>
-      <c r="L93" s="42">
+      <c r="K93" s="41"/>
+      <c r="L93" s="41">
         <f>SUM(L89:L91)</f>
         <v>0.4239467593</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="26"/>
-      <c r="B94" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C94" s="28"/>
-      <c r="D94" s="24" t="s">
+      <c r="A94" s="25"/>
+      <c r="B94" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="27"/>
+      <c r="D94" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="24" t="s">
+      <c r="E94" s="27"/>
+      <c r="F94" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="28"/>
-      <c r="H94" s="24" t="s">
+      <c r="G94" s="27"/>
+      <c r="H94" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="28"/>
-      <c r="J94" s="24" t="s">
+      <c r="I94" s="27"/>
+      <c r="J94" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="28"/>
-      <c r="L94" s="24" t="s">
+      <c r="K94" s="27"/>
+      <c r="L94" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="B95" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="C95" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="31"/>
-      <c r="E95" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" s="31"/>
-      <c r="G95" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H95" s="31"/>
-      <c r="I95" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="31"/>
-      <c r="K95" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="L95" s="31"/>
+      <c r="A95" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C95" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="30"/>
+      <c r="E95" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="30"/>
+      <c r="G95" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" s="30"/>
+      <c r="I95" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="30"/>
+      <c r="K95" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95" s="30"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="30" t="s">
-        <v>64</v>
+      <c r="A96" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="B96" s="9">
         <v>0.020833333333333332</v>
       </c>
-      <c r="C96" s="49" t="s">
-        <v>65</v>
+      <c r="C96" s="48" t="s">
+        <v>66</v>
       </c>
       <c r="D96" s="13">
         <v>0.5</v>
       </c>
-      <c r="E96" s="31"/>
-      <c r="F96" s="31"/>
-      <c r="G96" s="31"/>
-      <c r="H96" s="31"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
       <c r="I96" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J96" s="9">
         <v>0.022222222222222223</v>
       </c>
-      <c r="K96" s="31"/>
-      <c r="L96" s="31"/>
+      <c r="K96" s="30"/>
+      <c r="L96" s="30"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="30" t="s">
-        <v>67</v>
+      <c r="A97" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="B97" s="9">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C97" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D97" s="52">
+      <c r="C97" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" s="51">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E97" s="31"/>
-      <c r="F97" s="31"/>
-      <c r="G97" s="31"/>
-      <c r="H97" s="31"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
       <c r="I97" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J97" s="9">
         <v>0.06859953703703704</v>
       </c>
-      <c r="K97" s="31"/>
-      <c r="L97" s="31"/>
+      <c r="K97" s="30"/>
+      <c r="L97" s="30"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="56"/>
+      <c r="A98" s="55"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="49" t="s">
-        <v>68</v>
+      <c r="C98" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="D98" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E98" s="31"/>
-      <c r="F98" s="31"/>
-      <c r="G98" s="31"/>
-      <c r="H98" s="31"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
       <c r="I98" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J98" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="K98" s="31"/>
-      <c r="L98" s="31"/>
+      <c r="K98" s="30"/>
+      <c r="L98" s="30"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="56"/>
+      <c r="A99" s="55"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="49" t="s">
-        <v>68</v>
+      <c r="C99" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="D99" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E99" s="31"/>
-      <c r="F99" s="31"/>
-      <c r="G99" s="31"/>
-      <c r="H99" s="31"/>
-      <c r="I99" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="J99" s="52">
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="J99" s="51">
         <v>0.03420138888888889</v>
       </c>
-      <c r="K99" s="31"/>
-      <c r="L99" s="31"/>
+      <c r="K99" s="30"/>
+      <c r="L99" s="30"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="30"/>
+      <c r="A100" s="29"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="49" t="s">
-        <v>70</v>
+      <c r="C100" s="48" t="s">
+        <v>71</v>
       </c>
       <c r="D100" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="E100" s="31"/>
-      <c r="F100" s="31"/>
-      <c r="G100" s="31"/>
-      <c r="H100" s="31"/>
-      <c r="I100" s="33" t="s">
-        <v>68</v>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="32" t="s">
+        <v>69</v>
       </c>
       <c r="J100" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K100" s="31"/>
-      <c r="L100" s="31"/>
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="30"/>
+      <c r="A101" s="29"/>
       <c r="B101" s="9"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="64"/>
-      <c r="E101" s="31"/>
-      <c r="F101" s="31"/>
-      <c r="G101" s="31"/>
-      <c r="H101" s="31"/>
-      <c r="I101" s="33" t="s">
-        <v>68</v>
+      <c r="C101" s="50"/>
+      <c r="D101" s="63"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="32" t="s">
+        <v>69</v>
       </c>
       <c r="J101" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K101" s="31"/>
-      <c r="L101" s="31"/>
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" s="38">
+      <c r="A102" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B102" s="37">
         <f>SUM(B96:B101)</f>
         <v>0.06805555556</v>
       </c>
-      <c r="C102" s="47"/>
-      <c r="D102" s="37">
+      <c r="C102" s="46"/>
+      <c r="D102" s="36">
         <f>SUM(D96:D101)</f>
         <v>0.8178472222</v>
       </c>
-      <c r="E102" s="48"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="48"/>
-      <c r="I102" s="48"/>
-      <c r="J102" s="38">
+      <c r="E102" s="47"/>
+      <c r="F102" s="47"/>
+      <c r="G102" s="47"/>
+      <c r="H102" s="47"/>
+      <c r="I102" s="47"/>
+      <c r="J102" s="37">
         <f>SUM(J96:J101)</f>
         <v>0.4086689815</v>
       </c>
-      <c r="K102" s="48"/>
-      <c r="L102" s="48"/>
+      <c r="K102" s="47"/>
+      <c r="L102" s="47"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="26"/>
-      <c r="B103" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C103" s="28"/>
-      <c r="D103" s="24" t="s">
+      <c r="A103" s="25"/>
+      <c r="B103" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="27"/>
+      <c r="D103" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E103" s="28"/>
-      <c r="F103" s="24" t="s">
+      <c r="E103" s="27"/>
+      <c r="F103" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G103" s="28"/>
-      <c r="H103" s="24" t="s">
+      <c r="G103" s="27"/>
+      <c r="H103" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I103" s="28"/>
-      <c r="J103" s="24" t="s">
+      <c r="I103" s="27"/>
+      <c r="J103" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K103" s="28"/>
-      <c r="L103" s="24" t="s">
+      <c r="K103" s="27"/>
+      <c r="L103" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="61" t="s">
-        <v>16</v>
-      </c>
-      <c r="B104" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="C104" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="D104" s="31"/>
-      <c r="E104" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F104" s="65"/>
-      <c r="G104" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="H104" s="31"/>
-      <c r="I104" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="J104" s="31"/>
-      <c r="K104" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="L104" s="31"/>
+      <c r="A104" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="30"/>
+      <c r="E104" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="64"/>
+      <c r="G104" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H104" s="30"/>
+      <c r="I104" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="30"/>
+      <c r="K104" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104" s="30"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="30" t="s">
-        <v>67</v>
+      <c r="A105" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="B105" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C105" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D105" s="52">
+      <c r="C105" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D105" s="51">
         <v>0.03420138888888889</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F105" s="6">
         <v>0.27569444444444446</v>
       </c>
-      <c r="G105" s="31"/>
-      <c r="H105" s="31"/>
-      <c r="I105" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="J105" s="52">
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="J105" s="51">
         <v>0.1909722222222222</v>
       </c>
       <c r="K105" s="9"/>
@@ -4820,876 +4837,904 @@
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="30"/>
+      <c r="A106" s="29"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="49" t="s">
-        <v>68</v>
+      <c r="C106" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="D106" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E106" s="31"/>
-      <c r="F106" s="31"/>
-      <c r="G106" s="31"/>
-      <c r="H106" s="31"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
       <c r="I106" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J106" s="9">
         <v>0.03125</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L106" s="9">
         <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="30" t="s">
-        <v>75</v>
+      <c r="A107" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="B107" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C107" s="49" t="s">
-        <v>68</v>
+      <c r="C107" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="D107" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E107" s="31"/>
-      <c r="F107" s="31"/>
-      <c r="G107" s="31"/>
-      <c r="H107" s="31"/>
-      <c r="I107" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="J107" s="52">
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+      <c r="H107" s="30"/>
+      <c r="I107" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="J107" s="51">
         <v>0.03420138888888889</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L107" s="9">
         <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="56"/>
-      <c r="B108" s="31"/>
-      <c r="C108" s="49" t="s">
-        <v>77</v>
+      <c r="A108" s="55"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="48" t="s">
+        <v>78</v>
       </c>
       <c r="D108" s="13">
         <v>0.3076388888888889</v>
       </c>
-      <c r="E108" s="31"/>
-      <c r="F108" s="31"/>
-      <c r="G108" s="31"/>
-      <c r="H108" s="31"/>
-      <c r="I108" s="33" t="s">
-        <v>68</v>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="30"/>
+      <c r="H108" s="30"/>
+      <c r="I108" s="32" t="s">
+        <v>69</v>
       </c>
       <c r="J108" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K108" s="31"/>
-      <c r="L108" s="31"/>
+      <c r="K108" s="30"/>
+      <c r="L108" s="30"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="56"/>
-      <c r="B109" s="31"/>
-      <c r="C109" s="49" t="s">
-        <v>77</v>
+      <c r="A109" s="55"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="48" t="s">
+        <v>78</v>
       </c>
       <c r="D109" s="13">
         <v>0.24097222222222223</v>
       </c>
-      <c r="E109" s="31"/>
-      <c r="F109" s="31"/>
-      <c r="G109" s="31"/>
-      <c r="H109" s="31"/>
-      <c r="I109" s="33" t="s">
-        <v>68</v>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
+      <c r="I109" s="32" t="s">
+        <v>69</v>
       </c>
       <c r="J109" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K109" s="31"/>
-      <c r="L109" s="31"/>
+      <c r="K109" s="30"/>
+      <c r="L109" s="30"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="56"/>
-      <c r="B110" s="31"/>
-      <c r="C110" s="49" t="s">
-        <v>78</v>
+      <c r="A110" s="55"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="48" t="s">
+        <v>79</v>
       </c>
       <c r="D110" s="13">
         <v>0.10609953703703703</v>
       </c>
-      <c r="E110" s="31"/>
-      <c r="F110" s="31"/>
-      <c r="G110" s="31"/>
-      <c r="H110" s="31"/>
-      <c r="I110" s="30" t="s">
-        <v>75</v>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+      <c r="H110" s="30"/>
+      <c r="I110" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="J110" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="K110" s="31"/>
-      <c r="L110" s="31"/>
+      <c r="K110" s="30"/>
+      <c r="L110" s="30"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="56"/>
-      <c r="B111" s="31"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="31"/>
-      <c r="F111" s="31"/>
-      <c r="G111" s="31"/>
-      <c r="H111" s="31"/>
-      <c r="I111" s="31"/>
-      <c r="J111" s="31"/>
-      <c r="K111" s="31"/>
-      <c r="L111" s="31"/>
+      <c r="A111" s="55"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="50"/>
+      <c r="D111" s="50"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
+      <c r="I111" s="30"/>
+      <c r="J111" s="30"/>
+      <c r="K111" s="30"/>
+      <c r="L111" s="30"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="56"/>
-      <c r="B112" s="31"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="31"/>
-      <c r="F112" s="31"/>
-      <c r="G112" s="31"/>
-      <c r="H112" s="31"/>
-      <c r="I112" s="31"/>
-      <c r="J112" s="31"/>
-      <c r="K112" s="31"/>
-      <c r="L112" s="31"/>
+      <c r="A112" s="55"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="50"/>
+      <c r="D112" s="50"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
+      <c r="G112" s="30"/>
+      <c r="H112" s="30"/>
+      <c r="I112" s="30"/>
+      <c r="J112" s="30"/>
+      <c r="K112" s="30"/>
+      <c r="L112" s="30"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" s="42">
+      <c r="A113" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113" s="41">
         <f>SUM(B105:B112)</f>
         <v>0.2798611111</v>
       </c>
-      <c r="C113" s="47"/>
-      <c r="D113" s="58">
+      <c r="C113" s="46"/>
+      <c r="D113" s="57">
         <f>SUM(D105:D112)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="E113" s="48"/>
-      <c r="F113" s="42">
+      <c r="E113" s="47"/>
+      <c r="F113" s="41">
         <f>SUM(F105:F112)</f>
         <v>0.2756944444</v>
       </c>
-      <c r="G113" s="48"/>
-      <c r="H113" s="48"/>
-      <c r="I113" s="48"/>
-      <c r="J113" s="42">
+      <c r="G113" s="47"/>
+      <c r="H113" s="47"/>
+      <c r="I113" s="47"/>
+      <c r="J113" s="41">
         <f>SUM(J105:J112)</f>
         <v>0.5817361111</v>
       </c>
-      <c r="K113" s="48"/>
-      <c r="L113" s="38">
+      <c r="K113" s="47"/>
+      <c r="L113" s="37">
         <f>SUM(L105:L112)</f>
         <v>0.3125</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="26"/>
-      <c r="B114" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C114" s="28"/>
-      <c r="D114" s="24" t="s">
+      <c r="A114" s="25"/>
+      <c r="B114" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="27"/>
+      <c r="D114" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E114" s="28"/>
-      <c r="F114" s="24" t="s">
+      <c r="E114" s="27"/>
+      <c r="F114" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G114" s="28"/>
-      <c r="H114" s="24" t="s">
+      <c r="G114" s="27"/>
+      <c r="H114" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I114" s="28"/>
-      <c r="J114" s="24" t="s">
+      <c r="I114" s="27"/>
+      <c r="J114" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K114" s="28"/>
-      <c r="L114" s="24" t="s">
+      <c r="K114" s="27"/>
+      <c r="L114" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B115" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C115" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D115" s="29"/>
-      <c r="E115" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F115" s="29"/>
-      <c r="G115" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H115" s="29"/>
-      <c r="I115" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J115" s="29"/>
-      <c r="K115" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L115" s="29"/>
+      <c r="A115" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="28"/>
+      <c r="E115" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" s="28"/>
+      <c r="G115" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H115" s="28"/>
+      <c r="I115" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" s="28"/>
+      <c r="K115" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115" s="28"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="30" t="s">
-        <v>75</v>
+      <c r="A116" s="29" t="s">
+        <v>76</v>
       </c>
       <c r="B116" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C116" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D116" s="66">
+      <c r="C116" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D116" s="65">
         <v>0.09930555555555555</v>
       </c>
-      <c r="E116" s="56"/>
-      <c r="F116" s="56"/>
-      <c r="G116" s="67" t="s">
+      <c r="E116" s="55"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="H116" s="67">
+        <v>0.008726851851851852</v>
+      </c>
+      <c r="I116" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="H116" s="68">
-        <v>0.008726851851851852</v>
-      </c>
-      <c r="I116" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="J116" s="66">
+      <c r="J116" s="65">
         <v>0.09930555555555555</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L116" s="9">
         <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B117" s="66">
+      <c r="A117" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" s="65">
         <v>0.06087962962962963</v>
       </c>
-      <c r="C117" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D117" s="69">
+      <c r="C117" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D117" s="68">
         <v>0.05625</v>
       </c>
-      <c r="E117" s="30" t="s">
+      <c r="E117" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F117" s="68">
+        <v>0.6346296296296297</v>
+      </c>
+      <c r="G117" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H117" s="68">
+        <v>0.014282407407407407</v>
+      </c>
+      <c r="I117" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="F117" s="69">
-        <v>0.6346296296296297</v>
-      </c>
-      <c r="G117" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H117" s="69">
-        <v>0.014282407407407407</v>
-      </c>
-      <c r="I117" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="J117" s="69">
+      <c r="J117" s="68">
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L117" s="9">
         <v>0.1076388888888889</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B118" s="66">
+      <c r="A118" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B118" s="65">
         <v>0.06527777777777778</v>
       </c>
-      <c r="C118" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D118" s="66">
+      <c r="C118" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D118" s="65">
         <v>0.07368055555555555</v>
       </c>
-      <c r="E118" s="30" t="s">
+      <c r="E118" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F118" s="68">
+        <v>0.04513888888888889</v>
+      </c>
+      <c r="G118" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="H118" s="68">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="I118" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="F118" s="69">
-        <v>0.04513888888888889</v>
-      </c>
-      <c r="G118" s="30" t="s">
+      <c r="J118" s="65">
+        <v>0.07368055555555555</v>
+      </c>
+      <c r="K118" s="55"/>
+      <c r="L118" s="55"/>
+    </row>
+    <row r="119" ht="14.25" customHeight="1">
+      <c r="A119" s="55"/>
+      <c r="B119" s="55"/>
+      <c r="C119" s="55"/>
+      <c r="D119" s="55"/>
+      <c r="E119" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="H118" s="69">
+      <c r="F119" s="68">
+        <v>0.225</v>
+      </c>
+      <c r="G119" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H119" s="68">
+        <v>0.08680555555555555</v>
+      </c>
+      <c r="I119" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J119" s="68">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I118" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="J118" s="66">
-        <v>0.07368055555555555</v>
-      </c>
-      <c r="K118" s="56"/>
-      <c r="L118" s="56"/>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="56"/>
-      <c r="B119" s="56"/>
-      <c r="C119" s="56"/>
-      <c r="D119" s="56"/>
-      <c r="E119" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F119" s="69">
-        <v>0.225</v>
-      </c>
-      <c r="G119" s="30" t="s">
+      <c r="K119" s="55"/>
+      <c r="L119" s="55"/>
+    </row>
+    <row r="120" ht="14.25" customHeight="1">
+      <c r="A120" s="55"/>
+      <c r="B120" s="55"/>
+      <c r="C120" s="55"/>
+      <c r="D120" s="55"/>
+      <c r="E120" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F120" s="68">
+        <v>0.2590277777777778</v>
+      </c>
+      <c r="G120" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="H119" s="69">
-        <v>0.08680555555555555</v>
-      </c>
-      <c r="I119" s="30" t="s">
+      <c r="H120" s="68">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I120" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="J120" s="65">
+        <v>0.06527777777777778</v>
+      </c>
+      <c r="K120" s="55"/>
+      <c r="L120" s="55"/>
+    </row>
+    <row r="121" ht="14.25" customHeight="1">
+      <c r="A121" s="55"/>
+      <c r="B121" s="55"/>
+      <c r="C121" s="55"/>
+      <c r="D121" s="55"/>
+      <c r="E121" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="J119" s="69">
-        <v>0.18760416666666666</v>
-      </c>
-      <c r="K119" s="56"/>
-      <c r="L119" s="56"/>
-    </row>
-    <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="56"/>
-      <c r="B120" s="56"/>
-      <c r="C120" s="56"/>
-      <c r="D120" s="56"/>
-      <c r="E120" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F120" s="69">
-        <v>0.2590277777777778</v>
-      </c>
-      <c r="G120" s="30" t="s">
+      <c r="F121" s="68">
+        <v>0.10972222222222222</v>
+      </c>
+      <c r="G121" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H121" s="68">
+        <v>0.015196759259259259</v>
+      </c>
+      <c r="I121" s="55"/>
+      <c r="J121" s="55"/>
+      <c r="K121" s="55"/>
+      <c r="L121" s="55"/>
+    </row>
+    <row r="122" ht="14.25" customHeight="1">
+      <c r="A122" s="55"/>
+      <c r="B122" s="55"/>
+      <c r="C122" s="55"/>
+      <c r="D122" s="55"/>
+      <c r="E122" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="H120" s="69">
-        <v>0.13541666666666666</v>
-      </c>
-      <c r="I120" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="J120" s="66">
-        <v>0.06527777777777778</v>
-      </c>
-      <c r="K120" s="56"/>
-      <c r="L120" s="56"/>
-    </row>
-    <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="56"/>
-      <c r="B121" s="56"/>
-      <c r="C121" s="56"/>
-      <c r="D121" s="56"/>
-      <c r="E121" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F121" s="69">
+      <c r="F122" s="68">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G121" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="H121" s="69">
-        <v>0.015196759259259259</v>
-      </c>
-      <c r="I121" s="56"/>
-      <c r="J121" s="56"/>
-      <c r="K121" s="56"/>
-      <c r="L121" s="56"/>
-    </row>
-    <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="56"/>
-      <c r="B122" s="56"/>
-      <c r="C122" s="56"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="F122" s="69">
-        <v>0.10972222222222222</v>
-      </c>
-      <c r="G122" s="56"/>
-      <c r="H122" s="56"/>
-      <c r="I122" s="56"/>
-      <c r="J122" s="56"/>
-      <c r="K122" s="56"/>
-      <c r="L122" s="56"/>
+      <c r="G122" s="55"/>
+      <c r="H122" s="55"/>
+      <c r="I122" s="55"/>
+      <c r="J122" s="55"/>
+      <c r="K122" s="55"/>
+      <c r="L122" s="55"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="56"/>
-      <c r="B123" s="56"/>
-      <c r="C123" s="56"/>
-      <c r="D123" s="56"/>
-      <c r="E123" s="56"/>
-      <c r="F123" s="56"/>
-      <c r="G123" s="56"/>
-      <c r="H123" s="56"/>
-      <c r="I123" s="56"/>
-      <c r="J123" s="56"/>
-      <c r="K123" s="56"/>
-      <c r="L123" s="56"/>
+      <c r="A123" s="55"/>
+      <c r="B123" s="55"/>
+      <c r="C123" s="55"/>
+      <c r="D123" s="55"/>
+      <c r="E123" s="55"/>
+      <c r="F123" s="55"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="55"/>
+      <c r="I123" s="55"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="55"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="70"/>
-      <c r="B124" s="70"/>
-      <c r="C124" s="70"/>
-      <c r="D124" s="70"/>
-      <c r="E124" s="70"/>
-      <c r="F124" s="70"/>
-      <c r="G124" s="70"/>
-      <c r="H124" s="70"/>
-      <c r="I124" s="70"/>
-      <c r="J124" s="70"/>
-      <c r="K124" s="70"/>
-      <c r="L124" s="70"/>
+      <c r="A124" s="69"/>
+      <c r="B124" s="69"/>
+      <c r="C124" s="69"/>
+      <c r="D124" s="69"/>
+      <c r="E124" s="69"/>
+      <c r="F124" s="69"/>
+      <c r="G124" s="69"/>
+      <c r="H124" s="69"/>
+      <c r="I124" s="69"/>
+      <c r="J124" s="69"/>
+      <c r="K124" s="69"/>
+      <c r="L124" s="69"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" s="71">
+      <c r="A125" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B125" s="70">
         <f>SUM(B116:B124)</f>
         <v>0.3587962963</v>
       </c>
-      <c r="C125" s="70"/>
-      <c r="D125" s="71">
+      <c r="C125" s="69"/>
+      <c r="D125" s="70">
         <f>SUM(D116:D118)</f>
         <v>0.2292361111</v>
       </c>
-      <c r="E125" s="70"/>
-      <c r="F125" s="72">
+      <c r="E125" s="69"/>
+      <c r="F125" s="71">
         <f>SUM(F117:F123)</f>
         <v>1.383240741</v>
       </c>
-      <c r="G125" s="70"/>
-      <c r="H125" s="71">
+      <c r="G125" s="69"/>
+      <c r="H125" s="70">
         <f>SUM(H116:H123)</f>
         <v>0.4480324074</v>
       </c>
-      <c r="I125" s="70"/>
-      <c r="J125" s="71">
+      <c r="I125" s="69"/>
+      <c r="J125" s="70">
         <f>SUM(J116:J124)</f>
         <v>0.4821180556</v>
       </c>
-      <c r="K125" s="70"/>
-      <c r="L125" s="71">
+      <c r="K125" s="69"/>
+      <c r="L125" s="70">
         <f>SUM(L116:L123)</f>
         <v>0.3020833333</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="26"/>
-      <c r="B126" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C126" s="28"/>
-      <c r="D126" s="24" t="s">
+      <c r="A126" s="25"/>
+      <c r="B126" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C126" s="27"/>
+      <c r="D126" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E126" s="28"/>
-      <c r="F126" s="24" t="s">
+      <c r="E126" s="27"/>
+      <c r="F126" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="G126" s="28"/>
-      <c r="H126" s="24" t="s">
+      <c r="G126" s="27"/>
+      <c r="H126" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I126" s="28"/>
-      <c r="J126" s="24" t="s">
+      <c r="I126" s="27"/>
+      <c r="J126" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K126" s="28"/>
-      <c r="L126" s="24" t="s">
+      <c r="K126" s="27"/>
+      <c r="L126" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B127" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C127" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D127" s="29"/>
-      <c r="E127" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" s="29"/>
-      <c r="G127" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="H127" s="29"/>
-      <c r="I127" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J127" s="29"/>
-      <c r="K127" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="L127" s="29"/>
+      <c r="A127" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B127" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" s="28"/>
+      <c r="E127" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127" s="28"/>
+      <c r="G127" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" s="28"/>
+      <c r="I127" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="28"/>
+      <c r="K127" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L127" s="28"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="56"/>
-      <c r="B128" s="56"/>
-      <c r="C128" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D128" s="73">
-        <v>0.04717592592592593</v>
-      </c>
-      <c r="E128" s="30" t="s">
+      <c r="A128" s="55"/>
+      <c r="B128" s="55"/>
+      <c r="C128" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="F128" s="55">
-        <v>0.10416666666666667</v>
-      </c>
-      <c r="G128" s="30" t="s">
+      <c r="D128" s="72">
+        <v>0.1557060185185185</v>
+      </c>
+      <c r="E128" s="29" t="s">
         <v>95</v>
+      </c>
+      <c r="F128" s="73">
+        <v>0.1875</v>
+      </c>
+      <c r="G128" s="29" t="s">
+        <v>96</v>
       </c>
       <c r="H128" s="74">
         <v>0.08680555555555555</v>
       </c>
-      <c r="I128" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="J128" s="53">
+      <c r="I128" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J128" s="52">
         <v>0.18760416666666666</v>
       </c>
-      <c r="K128" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="L128" s="55">
+      <c r="K128" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="L128" s="54">
         <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="56"/>
-      <c r="B129" s="56"/>
-      <c r="C129" s="56"/>
-      <c r="D129" s="56"/>
-      <c r="E129" s="56"/>
-      <c r="F129" s="56"/>
-      <c r="G129" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="H129" s="53">
+      <c r="A129" s="55"/>
+      <c r="B129" s="55"/>
+      <c r="C129" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D129" s="52">
+        <v>0.07152777777777777</v>
+      </c>
+      <c r="E129" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F129" s="75">
+        <v>0.22569444444444445</v>
+      </c>
+      <c r="G129" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="H129" s="52">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I129" s="30" t="s">
-        <v>97</v>
+      <c r="I129" s="29" t="s">
+        <v>100</v>
       </c>
       <c r="J129" s="75">
         <v>0.027777777777777776</v>
       </c>
-      <c r="K129" s="56"/>
-      <c r="L129" s="56"/>
+      <c r="K129" s="55"/>
+      <c r="L129" s="55"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="56"/>
-      <c r="B130" s="56"/>
-      <c r="C130" s="56"/>
-      <c r="D130" s="56"/>
-      <c r="E130" s="56"/>
-      <c r="F130" s="56"/>
-      <c r="G130" s="30" t="s">
-        <v>89</v>
+      <c r="A130" s="55"/>
+      <c r="B130" s="55"/>
+      <c r="C130" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D130" s="52">
+        <v>0.023854166666666666</v>
+      </c>
+      <c r="E130" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F130" s="52">
+        <v>0.29193287037037036</v>
+      </c>
+      <c r="G130" s="29" t="s">
+        <v>90</v>
       </c>
       <c r="H130" s="74">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I130" s="30" t="s">
-        <v>98</v>
+      <c r="I130" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="J130" s="75">
         <v>0.01662037037037037</v>
       </c>
-      <c r="K130" s="56"/>
-      <c r="L130" s="56"/>
+      <c r="K130" s="55"/>
+      <c r="L130" s="55"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="56"/>
-      <c r="B131" s="56"/>
-      <c r="C131" s="56"/>
-      <c r="D131" s="56"/>
-      <c r="E131" s="56"/>
-      <c r="F131" s="56"/>
-      <c r="G131" s="30" t="s">
-        <v>99</v>
+      <c r="A131" s="55"/>
+      <c r="B131" s="55"/>
+      <c r="C131" s="55"/>
+      <c r="D131" s="55"/>
+      <c r="E131" s="55"/>
+      <c r="F131" s="55"/>
+      <c r="G131" s="29" t="s">
+        <v>104</v>
       </c>
       <c r="H131" s="75">
         <v>0.003472222222222222</v>
       </c>
-      <c r="I131" s="32"/>
-      <c r="J131" s="76"/>
-      <c r="K131" s="56"/>
-      <c r="L131" s="56"/>
+      <c r="I131" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="J131" s="52">
+        <v>0.1557060185185185</v>
+      </c>
+      <c r="K131" s="55"/>
+      <c r="L131" s="55"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="56"/>
-      <c r="B132" s="56"/>
-      <c r="C132" s="56"/>
-      <c r="D132" s="56"/>
-      <c r="E132" s="56"/>
-      <c r="F132" s="56"/>
-      <c r="G132" s="56"/>
-      <c r="H132" s="56"/>
-      <c r="I132" s="56"/>
-      <c r="J132" s="56"/>
-      <c r="K132" s="56"/>
-      <c r="L132" s="56"/>
+      <c r="A132" s="55"/>
+      <c r="B132" s="55"/>
+      <c r="C132" s="55"/>
+      <c r="D132" s="55"/>
+      <c r="E132" s="55"/>
+      <c r="F132" s="55"/>
+      <c r="G132" s="55"/>
+      <c r="H132" s="55"/>
+      <c r="I132" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J132" s="52">
+        <v>0.07152777777777777</v>
+      </c>
+      <c r="K132" s="55"/>
+      <c r="L132" s="55"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="56"/>
-      <c r="B133" s="56"/>
-      <c r="C133" s="56"/>
-      <c r="D133" s="56"/>
-      <c r="E133" s="56"/>
-      <c r="F133" s="56"/>
-      <c r="G133" s="56"/>
-      <c r="H133" s="56"/>
-      <c r="I133" s="56"/>
-      <c r="J133" s="56"/>
-      <c r="K133" s="56"/>
-      <c r="L133" s="56"/>
+      <c r="A133" s="55"/>
+      <c r="B133" s="55"/>
+      <c r="C133" s="55"/>
+      <c r="D133" s="55"/>
+      <c r="E133" s="55"/>
+      <c r="F133" s="55"/>
+      <c r="G133" s="55"/>
+      <c r="H133" s="55"/>
+      <c r="I133" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="J133" s="52">
+        <v>0.023854166666666666</v>
+      </c>
+      <c r="K133" s="55"/>
+      <c r="L133" s="55"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="56"/>
-      <c r="B134" s="56"/>
-      <c r="C134" s="56"/>
-      <c r="D134" s="56"/>
-      <c r="E134" s="56"/>
-      <c r="F134" s="56"/>
-      <c r="G134" s="56"/>
-      <c r="H134" s="56"/>
-      <c r="I134" s="56"/>
-      <c r="J134" s="56"/>
-      <c r="K134" s="56"/>
-      <c r="L134" s="56"/>
+      <c r="A134" s="55"/>
+      <c r="B134" s="55"/>
+      <c r="C134" s="55"/>
+      <c r="D134" s="55"/>
+      <c r="E134" s="55"/>
+      <c r="F134" s="55"/>
+      <c r="G134" s="55"/>
+      <c r="H134" s="55"/>
+      <c r="I134" s="55"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="55"/>
+      <c r="L134" s="55"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="56"/>
-      <c r="B135" s="56"/>
-      <c r="C135" s="56"/>
-      <c r="D135" s="56"/>
-      <c r="E135" s="56"/>
-      <c r="F135" s="56"/>
-      <c r="G135" s="56"/>
-      <c r="H135" s="56"/>
-      <c r="I135" s="56"/>
-      <c r="J135" s="56"/>
-      <c r="K135" s="56"/>
-      <c r="L135" s="56"/>
+      <c r="A135" s="55"/>
+      <c r="B135" s="55"/>
+      <c r="C135" s="55"/>
+      <c r="D135" s="55"/>
+      <c r="E135" s="55"/>
+      <c r="F135" s="55"/>
+      <c r="G135" s="55"/>
+      <c r="H135" s="55"/>
+      <c r="I135" s="55"/>
+      <c r="J135" s="55"/>
+      <c r="K135" s="55"/>
+      <c r="L135" s="55"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="56"/>
-      <c r="B136" s="56"/>
-      <c r="C136" s="56"/>
-      <c r="D136" s="56"/>
-      <c r="E136" s="56"/>
-      <c r="F136" s="56"/>
-      <c r="G136" s="56"/>
-      <c r="H136" s="56"/>
-      <c r="I136" s="56"/>
-      <c r="J136" s="56"/>
-      <c r="K136" s="56"/>
-      <c r="L136" s="56"/>
+      <c r="A136" s="55"/>
+      <c r="B136" s="55"/>
+      <c r="C136" s="55"/>
+      <c r="D136" s="55"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="56"/>
-      <c r="B137" s="56"/>
-      <c r="C137" s="56"/>
-      <c r="D137" s="56"/>
-      <c r="E137" s="56"/>
-      <c r="F137" s="56"/>
-      <c r="G137" s="56"/>
-      <c r="H137" s="56"/>
-      <c r="I137" s="56"/>
-      <c r="J137" s="56"/>
-      <c r="K137" s="56"/>
-      <c r="L137" s="56"/>
+      <c r="A137" s="55"/>
+      <c r="B137" s="55"/>
+      <c r="C137" s="55"/>
+      <c r="D137" s="55"/>
+      <c r="E137" s="55"/>
+      <c r="F137" s="55"/>
+      <c r="G137" s="55"/>
+      <c r="H137" s="55"/>
+      <c r="I137" s="55"/>
+      <c r="J137" s="55"/>
+      <c r="K137" s="55"/>
+      <c r="L137" s="55"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="56"/>
-      <c r="B138" s="56"/>
-      <c r="C138" s="56"/>
-      <c r="D138" s="56"/>
-      <c r="E138" s="56"/>
-      <c r="F138" s="56"/>
-      <c r="G138" s="56"/>
-      <c r="H138" s="56"/>
-      <c r="I138" s="56"/>
-      <c r="J138" s="56"/>
-      <c r="K138" s="56"/>
-      <c r="L138" s="56"/>
+      <c r="A138" s="55"/>
+      <c r="B138" s="55"/>
+      <c r="C138" s="55"/>
+      <c r="D138" s="55"/>
+      <c r="E138" s="55"/>
+      <c r="F138" s="55"/>
+      <c r="G138" s="55"/>
+      <c r="H138" s="55"/>
+      <c r="I138" s="55"/>
+      <c r="J138" s="55"/>
+      <c r="K138" s="55"/>
+      <c r="L138" s="55"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="56"/>
-      <c r="B139" s="56"/>
-      <c r="C139" s="56"/>
-      <c r="D139" s="56"/>
-      <c r="E139" s="56"/>
-      <c r="F139" s="56"/>
-      <c r="G139" s="56"/>
-      <c r="H139" s="56"/>
-      <c r="I139" s="56"/>
-      <c r="J139" s="56"/>
-      <c r="K139" s="56"/>
-      <c r="L139" s="56"/>
+      <c r="A139" s="55"/>
+      <c r="B139" s="55"/>
+      <c r="C139" s="55"/>
+      <c r="D139" s="55"/>
+      <c r="E139" s="55"/>
+      <c r="F139" s="55"/>
+      <c r="G139" s="55"/>
+      <c r="H139" s="55"/>
+      <c r="I139" s="55"/>
+      <c r="J139" s="55"/>
+      <c r="K139" s="55"/>
+      <c r="L139" s="55"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="56"/>
-      <c r="B140" s="56"/>
-      <c r="C140" s="56"/>
-      <c r="D140" s="56"/>
-      <c r="E140" s="56"/>
-      <c r="F140" s="56"/>
-      <c r="G140" s="56"/>
-      <c r="H140" s="56"/>
-      <c r="I140" s="56"/>
-      <c r="J140" s="56"/>
-      <c r="K140" s="56"/>
-      <c r="L140" s="56"/>
+      <c r="A140" s="55"/>
+      <c r="B140" s="55"/>
+      <c r="C140" s="55"/>
+      <c r="D140" s="55"/>
+      <c r="E140" s="55"/>
+      <c r="F140" s="55"/>
+      <c r="G140" s="55"/>
+      <c r="H140" s="55"/>
+      <c r="I140" s="55"/>
+      <c r="J140" s="55"/>
+      <c r="K140" s="55"/>
+      <c r="L140" s="55"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="56"/>
-      <c r="B141" s="56"/>
-      <c r="C141" s="56"/>
-      <c r="D141" s="56"/>
-      <c r="E141" s="56"/>
-      <c r="F141" s="56"/>
-      <c r="G141" s="56"/>
-      <c r="H141" s="56"/>
-      <c r="I141" s="56"/>
-      <c r="J141" s="56"/>
-      <c r="K141" s="56"/>
-      <c r="L141" s="56"/>
+      <c r="A141" s="55"/>
+      <c r="B141" s="55"/>
+      <c r="C141" s="55"/>
+      <c r="D141" s="55"/>
+      <c r="E141" s="55"/>
+      <c r="F141" s="55"/>
+      <c r="G141" s="55"/>
+      <c r="H141" s="55"/>
+      <c r="I141" s="55"/>
+      <c r="J141" s="55"/>
+      <c r="K141" s="55"/>
+      <c r="L141" s="55"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="56"/>
-      <c r="B142" s="56"/>
-      <c r="C142" s="56"/>
-      <c r="D142" s="56"/>
-      <c r="E142" s="56"/>
-      <c r="F142" s="56"/>
-      <c r="G142" s="56"/>
-      <c r="H142" s="56"/>
-      <c r="I142" s="56"/>
-      <c r="J142" s="56"/>
-      <c r="K142" s="56"/>
-      <c r="L142" s="56"/>
+      <c r="A142" s="55"/>
+      <c r="B142" s="55"/>
+      <c r="C142" s="55"/>
+      <c r="D142" s="55"/>
+      <c r="E142" s="55"/>
+      <c r="F142" s="55"/>
+      <c r="G142" s="55"/>
+      <c r="H142" s="55"/>
+      <c r="I142" s="55"/>
+      <c r="J142" s="55"/>
+      <c r="K142" s="55"/>
+      <c r="L142" s="55"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="56"/>
-      <c r="B143" s="56"/>
-      <c r="C143" s="56"/>
-      <c r="D143" s="56"/>
-      <c r="E143" s="56"/>
-      <c r="F143" s="56"/>
-      <c r="G143" s="56"/>
-      <c r="H143" s="56"/>
-      <c r="I143" s="56"/>
-      <c r="J143" s="56"/>
-      <c r="K143" s="56"/>
-      <c r="L143" s="56"/>
+      <c r="A143" s="55"/>
+      <c r="B143" s="55"/>
+      <c r="C143" s="55"/>
+      <c r="D143" s="55"/>
+      <c r="E143" s="55"/>
+      <c r="F143" s="55"/>
+      <c r="G143" s="55"/>
+      <c r="H143" s="55"/>
+      <c r="I143" s="55"/>
+      <c r="J143" s="55"/>
+      <c r="K143" s="55"/>
+      <c r="L143" s="55"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="56"/>
-      <c r="B144" s="56"/>
-      <c r="C144" s="56"/>
-      <c r="D144" s="56"/>
-      <c r="E144" s="56"/>
-      <c r="F144" s="56"/>
-      <c r="G144" s="56"/>
-      <c r="H144" s="56"/>
-      <c r="I144" s="56"/>
-      <c r="J144" s="56"/>
-      <c r="K144" s="56"/>
-      <c r="L144" s="56"/>
+      <c r="A144" s="55"/>
+      <c r="B144" s="55"/>
+      <c r="C144" s="55"/>
+      <c r="D144" s="55"/>
+      <c r="E144" s="55"/>
+      <c r="F144" s="55"/>
+      <c r="G144" s="55"/>
+      <c r="H144" s="55"/>
+      <c r="I144" s="55"/>
+      <c r="J144" s="55"/>
+      <c r="K144" s="55"/>
+      <c r="L144" s="55"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="56"/>
-      <c r="B145" s="56"/>
-      <c r="C145" s="56"/>
-      <c r="D145" s="56"/>
-      <c r="E145" s="56"/>
-      <c r="F145" s="56"/>
-      <c r="G145" s="56"/>
-      <c r="H145" s="56"/>
-      <c r="I145" s="56"/>
-      <c r="J145" s="56"/>
-      <c r="K145" s="56"/>
-      <c r="L145" s="56"/>
+      <c r="A145" s="55"/>
+      <c r="B145" s="55"/>
+      <c r="C145" s="55"/>
+      <c r="D145" s="55"/>
+      <c r="E145" s="55"/>
+      <c r="F145" s="55"/>
+      <c r="G145" s="55"/>
+      <c r="H145" s="55"/>
+      <c r="I145" s="55"/>
+      <c r="J145" s="55"/>
+      <c r="K145" s="55"/>
+      <c r="L145" s="55"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" s="70">
+      <c r="A146" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146" s="69">
         <f>SUM(B128:B145)</f>
         <v>0</v>
       </c>
-      <c r="C146" s="70"/>
-      <c r="D146" s="72">
+      <c r="C146" s="69"/>
+      <c r="D146" s="71">
         <f>SUM(D128:D145)</f>
-        <v>0.04717592593</v>
-      </c>
-      <c r="E146" s="70"/>
-      <c r="F146" s="72">
+        <v>0.251087963</v>
+      </c>
+      <c r="E146" s="69"/>
+      <c r="F146" s="71">
         <f>SUM(F128:F145)</f>
-        <v>0.1041666667</v>
-      </c>
-      <c r="G146" s="70"/>
-      <c r="H146" s="72">
+        <v>0.7051273148</v>
+      </c>
+      <c r="G146" s="69"/>
+      <c r="H146" s="71">
         <f>SUM(H128:H145)</f>
         <v>0.4132986111</v>
       </c>
-      <c r="I146" s="70"/>
-      <c r="J146" s="72">
+      <c r="I146" s="69"/>
+      <c r="J146" s="71">
         <f>SUM(J128:J145)</f>
-        <v>0.2320023148</v>
-      </c>
-      <c r="K146" s="70"/>
-      <c r="L146" s="72">
+        <v>0.4830902778</v>
+      </c>
+      <c r="K146" s="69"/>
+      <c r="L146" s="71">
         <f>SUM(L128:L145)</f>
         <v>0.1041666667</v>
       </c>
@@ -6584,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="77" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D3" s="77" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="bl2uqCJVoNfeO6CgraTRhAj+M3kdyVVGkVn0x8CSVRg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="8kN9tO6DfeTlf9RVY7KekZua9O+zJbptoO/f8MpKWFk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="121">
   <si>
     <t>Semana</t>
   </si>
@@ -333,6 +333,48 @@
   </si>
   <si>
     <t>Revisión documento de CU's priorizados 2da tanda</t>
+  </si>
+  <si>
+    <t>Semana 11</t>
+  </si>
+  <si>
+    <t>Especificación CU07: Crear etapa</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU15: Visualizar Tarea / CU16: Comentar Tarea</t>
+  </si>
+  <si>
+    <t>Ajustar documentos rama main</t>
+  </si>
+  <si>
+    <t>Revisión Especificación CU13 y CU14</t>
+  </si>
+  <si>
+    <t>Reunión 6/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ejecución de Casos de prueba de CU07: Crear Etapa</t>
+  </si>
+  <si>
+    <t>Implementación CU13 Asignar dependencia</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU13: Asignar dependencia / CU14: Modificar estado de tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU14 Modificar estado tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU15 Visualizar tarea</t>
+  </si>
+  <si>
+    <t>Ejecución de Casos de prueba de CU21: Registrar tiempo manual</t>
+  </si>
+  <si>
+    <t>Implementación CU16 Comentar tarea</t>
+  </si>
+  <si>
+    <t>Implementación CU21: Registrar tiempo manual</t>
   </si>
   <si>
     <t>Fecha de inicio</t>
@@ -541,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="90">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -727,6 +769,24 @@
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="13" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -814,7 +874,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I12" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I13" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="9">
     <tableColumn name="Semana" id="1"/>
     <tableColumn name="Análisis" id="2"/>
@@ -1299,7 +1359,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <f t="shared" ref="H8:H10" si="1">SUM(B8:G8)</f>
+        <f t="shared" ref="H8:H12" si="1">SUM(B8:G8)</f>
         <v>1.294571759</v>
       </c>
       <c r="I8" s="8" t="s">
@@ -1380,74 +1440,112 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="15">
-        <f>Registro!B146</f>
+        <f>Registro!B134</f>
         <v>0</v>
       </c>
       <c r="C11" s="15">
-        <f>Registro!D146</f>
+        <f>Registro!D134</f>
         <v>0.251087963</v>
       </c>
       <c r="D11" s="15">
-        <f>Registro!F146</f>
+        <f>Registro!F134</f>
         <v>0.7051273148</v>
       </c>
       <c r="E11" s="15">
-        <f>Registro!H146</f>
+        <f>Registro!H134</f>
         <v>0.4132986111</v>
       </c>
       <c r="F11" s="15">
-        <f>Registro!J146</f>
+        <f>Registro!J134</f>
         <v>0.4830902778</v>
       </c>
       <c r="G11" s="15">
-        <f>Registro!L146</f>
+        <f>Registro!L134</f>
         <v>0.1041666667</v>
       </c>
-      <c r="H11" s="15"/>
+      <c r="H11" s="15">
+        <f t="shared" si="1"/>
+        <v>1.956770833</v>
+      </c>
       <c r="I11" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="5">
+        <f>Registro!B145</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <f>Registro!D145</f>
+        <v>0.04395833333</v>
+      </c>
+      <c r="D12" s="5">
+        <f>Registro!F145</f>
+        <v>1.610740741</v>
+      </c>
+      <c r="E12" s="5">
+        <f>Registro!H145</f>
+        <v>0.3412847222</v>
+      </c>
+      <c r="F12" s="5">
+        <f>Registro!J145</f>
+        <v>0.04395833333</v>
+      </c>
+      <c r="G12" s="5">
+        <f>Registro!L145</f>
+        <v>0.1111111111</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="1"/>
+        <v>2.151053241</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="17">
-        <f>SUM(B2:B10)</f>
+      <c r="B13" s="17">
+        <f t="shared" ref="B13:G13" si="2">SUM(B2:B12)</f>
         <v>3.201782407</v>
       </c>
-      <c r="C12" s="17">
-        <f t="shared" ref="C12:G12" si="2">SUM(C2:C11)</f>
-        <v>4.33806713</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="C13" s="17">
         <f t="shared" si="2"/>
-        <v>4.291099537</v>
-      </c>
-      <c r="E12" s="17">
+        <v>4.382025463</v>
+      </c>
+      <c r="D13" s="17">
         <f t="shared" si="2"/>
-        <v>1.384479167</v>
-      </c>
-      <c r="F12" s="17">
+        <v>5.901840278</v>
+      </c>
+      <c r="E13" s="17">
         <f t="shared" si="2"/>
-        <v>3.089386574</v>
-      </c>
-      <c r="G12" s="17">
+        <v>1.725763889</v>
+      </c>
+      <c r="F13" s="17">
         <f t="shared" si="2"/>
-        <v>1.369537037</v>
-      </c>
-      <c r="H12" s="17">
-        <f>SUM(Total!$B12:$G12)</f>
-        <v>17.67435185</v>
-      </c>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1"/>
+        <v>3.133344907</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="2"/>
+        <v>1.480648148</v>
+      </c>
+      <c r="H13" s="17">
+        <f>SUM(Total!$B13:$G13)</f>
+        <v>19.82540509</v>
+      </c>
+      <c r="I13" s="18"/>
+    </row>
     <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1"/>
+    <row r="15" ht="14.25" customHeight="1"/>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="H16" s="19"/>
+    </row>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -2436,6 +2534,7 @@
     <row r="1002" ht="14.25" customHeight="1"/>
     <row r="1003" ht="14.25" customHeight="1"/>
     <row r="1004" ht="14.25" customHeight="1"/>
+    <row r="1005" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -2458,9 +2557,9 @@
     <col customWidth="1" min="2" max="2" width="24.88"/>
     <col customWidth="1" min="3" max="3" width="39.38"/>
     <col customWidth="1" min="4" max="4" width="39.5"/>
-    <col customWidth="1" min="5" max="5" width="37.0"/>
+    <col customWidth="1" min="5" max="5" width="41.63"/>
     <col customWidth="1" min="6" max="6" width="17.75"/>
-    <col customWidth="1" min="7" max="7" width="44.75"/>
+    <col customWidth="1" min="7" max="7" width="63.25"/>
     <col customWidth="1" min="8" max="8" width="27.63"/>
     <col customWidth="1" min="9" max="9" width="54.63"/>
     <col customWidth="1" min="10" max="10" width="27.63"/>
@@ -5538,86 +5637,172 @@
       <c r="L133" s="55"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="55"/>
-      <c r="B134" s="55"/>
-      <c r="C134" s="55"/>
-      <c r="D134" s="55"/>
-      <c r="E134" s="55"/>
-      <c r="F134" s="55"/>
-      <c r="G134" s="55"/>
-      <c r="H134" s="55"/>
-      <c r="I134" s="55"/>
-      <c r="J134" s="55"/>
-      <c r="K134" s="55"/>
-      <c r="L134" s="55"/>
+      <c r="A134" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134" s="69">
+        <f>SUM(B128:B133)</f>
+        <v>0</v>
+      </c>
+      <c r="C134" s="69"/>
+      <c r="D134" s="71">
+        <f>SUM(D128:D133)</f>
+        <v>0.251087963</v>
+      </c>
+      <c r="E134" s="69"/>
+      <c r="F134" s="71">
+        <f>SUM(F128:F133)</f>
+        <v>0.7051273148</v>
+      </c>
+      <c r="G134" s="69"/>
+      <c r="H134" s="71">
+        <f>SUM(H128:H133)</f>
+        <v>0.4132986111</v>
+      </c>
+      <c r="I134" s="69"/>
+      <c r="J134" s="71">
+        <f>SUM(J128:J133)</f>
+        <v>0.4830902778</v>
+      </c>
+      <c r="K134" s="69"/>
+      <c r="L134" s="71">
+        <f>SUM(L128:L133)</f>
+        <v>0.1041666667</v>
+      </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="55"/>
-      <c r="B135" s="55"/>
-      <c r="C135" s="55"/>
-      <c r="D135" s="55"/>
-      <c r="E135" s="55"/>
-      <c r="F135" s="55"/>
-      <c r="G135" s="55"/>
-      <c r="H135" s="55"/>
-      <c r="I135" s="55"/>
-      <c r="J135" s="55"/>
-      <c r="K135" s="55"/>
-      <c r="L135" s="55"/>
+      <c r="A135" s="25"/>
+      <c r="B135" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" s="27"/>
+      <c r="D135" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E135" s="27"/>
+      <c r="F135" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G135" s="27"/>
+      <c r="H135" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I135" s="27"/>
+      <c r="J135" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="K135" s="27"/>
+      <c r="L135" s="23" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="55"/>
-      <c r="B136" s="55"/>
-      <c r="C136" s="55"/>
-      <c r="D136" s="55"/>
-      <c r="E136" s="55"/>
-      <c r="F136" s="55"/>
-      <c r="G136" s="55"/>
-      <c r="H136" s="55"/>
-      <c r="I136" s="55"/>
-      <c r="J136" s="55"/>
-      <c r="K136" s="55"/>
-      <c r="L136" s="55"/>
+      <c r="A136" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B136" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" s="28"/>
+      <c r="E136" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="28"/>
+      <c r="G136" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H136" s="28"/>
+      <c r="I136" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="28"/>
+      <c r="K136" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L136" s="28"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="55"/>
       <c r="B137" s="55"/>
-      <c r="C137" s="55"/>
-      <c r="D137" s="55"/>
-      <c r="E137" s="55"/>
-      <c r="F137" s="55"/>
-      <c r="G137" s="55"/>
-      <c r="H137" s="55"/>
-      <c r="I137" s="55"/>
-      <c r="J137" s="55"/>
-      <c r="K137" s="55"/>
-      <c r="L137" s="55"/>
+      <c r="C137" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" s="77">
+        <v>0.043958333333333335</v>
+      </c>
+      <c r="E137" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F137" s="73">
+        <v>0.2708333333333333</v>
+      </c>
+      <c r="G137" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="H137" s="79">
+        <v>0.11635416666666666</v>
+      </c>
+      <c r="I137" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="J137" s="52">
+        <v>0.043958333333333335</v>
+      </c>
+      <c r="K137" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="L137" s="54">
+        <v>0.006944444444444444</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="55"/>
       <c r="B138" s="55"/>
-      <c r="C138" s="55"/>
-      <c r="D138" s="55"/>
-      <c r="E138" s="55"/>
-      <c r="F138" s="55"/>
-      <c r="G138" s="55"/>
-      <c r="H138" s="55"/>
-      <c r="I138" s="55"/>
-      <c r="J138" s="55"/>
-      <c r="K138" s="55"/>
-      <c r="L138" s="55"/>
+      <c r="C138" s="29"/>
+      <c r="D138" s="52"/>
+      <c r="E138" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F138" s="75">
+        <v>0.22569444444444445</v>
+      </c>
+      <c r="G138" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="H138" s="52">
+        <v>0.004097222222222223</v>
+      </c>
+      <c r="I138" s="78"/>
+      <c r="J138" s="79"/>
+      <c r="K138" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L138" s="54">
+        <v>0.10416666666666667</v>
+      </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="55"/>
       <c r="B139" s="55"/>
-      <c r="C139" s="55"/>
-      <c r="D139" s="55"/>
-      <c r="E139" s="55"/>
-      <c r="F139" s="55"/>
-      <c r="G139" s="55"/>
-      <c r="H139" s="55"/>
-      <c r="I139" s="55"/>
-      <c r="J139" s="55"/>
+      <c r="C139" s="29"/>
+      <c r="D139" s="52"/>
+      <c r="E139" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F139" s="52">
+        <v>0.29193287037037036</v>
+      </c>
+      <c r="G139" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="H139" s="74">
+        <v>0.06458333333333334</v>
+      </c>
+      <c r="I139" s="29"/>
+      <c r="J139" s="75"/>
       <c r="K139" s="55"/>
       <c r="L139" s="55"/>
     </row>
@@ -5626,12 +5811,20 @@
       <c r="B140" s="55"/>
       <c r="C140" s="55"/>
       <c r="D140" s="55"/>
-      <c r="E140" s="55"/>
-      <c r="F140" s="55"/>
-      <c r="G140" s="55"/>
-      <c r="H140" s="55"/>
-      <c r="I140" s="55"/>
-      <c r="J140" s="55"/>
+      <c r="E140" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F140" s="68">
+        <v>0.1913425925925926</v>
+      </c>
+      <c r="G140" s="80" t="s">
+        <v>113</v>
+      </c>
+      <c r="H140" s="75">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="I140" s="76"/>
+      <c r="J140" s="52"/>
       <c r="K140" s="55"/>
       <c r="L140" s="55"/>
     </row>
@@ -5640,12 +5833,16 @@
       <c r="B141" s="55"/>
       <c r="C141" s="55"/>
       <c r="D141" s="55"/>
-      <c r="E141" s="55"/>
-      <c r="F141" s="55"/>
-      <c r="G141" s="55"/>
-      <c r="H141" s="55"/>
-      <c r="I141" s="55"/>
-      <c r="J141" s="55"/>
+      <c r="E141" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="F141" s="68">
+        <v>0.14575231481481482</v>
+      </c>
+      <c r="G141" s="29"/>
+      <c r="H141" s="79"/>
+      <c r="I141" s="33"/>
+      <c r="J141" s="52"/>
       <c r="K141" s="55"/>
       <c r="L141" s="55"/>
     </row>
@@ -5654,91 +5851,94 @@
       <c r="B142" s="55"/>
       <c r="C142" s="55"/>
       <c r="D142" s="55"/>
-      <c r="E142" s="55"/>
-      <c r="F142" s="55"/>
-      <c r="G142" s="55"/>
-      <c r="H142" s="55"/>
-      <c r="I142" s="55"/>
-      <c r="J142" s="55"/>
+      <c r="E142" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="F142" s="68">
+        <v>0.1932523148148148</v>
+      </c>
+      <c r="G142" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="H142" s="75">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="I142" s="33"/>
+      <c r="J142" s="52"/>
       <c r="K142" s="55"/>
       <c r="L142" s="55"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="55"/>
-      <c r="B143" s="55"/>
-      <c r="C143" s="55"/>
-      <c r="D143" s="55"/>
-      <c r="E143" s="55"/>
-      <c r="F143" s="55"/>
-      <c r="G143" s="55"/>
-      <c r="H143" s="55"/>
-      <c r="I143" s="55"/>
-      <c r="J143" s="55"/>
-      <c r="K143" s="55"/>
-      <c r="L143" s="55"/>
+      <c r="A143" s="35"/>
+      <c r="B143" s="69"/>
+      <c r="C143" s="69"/>
+      <c r="D143" s="69"/>
+      <c r="E143" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F143" s="81">
+        <v>0.29193287037037036</v>
+      </c>
+      <c r="G143" s="69"/>
+      <c r="H143" s="69"/>
+      <c r="I143" s="69"/>
+      <c r="J143" s="69"/>
+      <c r="K143" s="69"/>
+      <c r="L143" s="69"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="55"/>
-      <c r="B144" s="55"/>
-      <c r="C144" s="55"/>
-      <c r="D144" s="55"/>
-      <c r="E144" s="55"/>
-      <c r="F144" s="55"/>
-      <c r="G144" s="55"/>
-      <c r="H144" s="55"/>
-      <c r="I144" s="55"/>
-      <c r="J144" s="55"/>
-      <c r="K144" s="55"/>
-      <c r="L144" s="55"/>
+      <c r="A144" s="35"/>
+      <c r="B144" s="69"/>
+      <c r="C144" s="69"/>
+      <c r="D144" s="69"/>
+      <c r="E144" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="F144" s="81">
+        <v>0.4636689814814815</v>
+      </c>
+      <c r="G144" s="69"/>
+      <c r="H144" s="69"/>
+      <c r="I144" s="69"/>
+      <c r="J144" s="69"/>
+      <c r="K144" s="69"/>
+      <c r="L144" s="69"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="55"/>
-      <c r="B145" s="55"/>
-      <c r="C145" s="55"/>
-      <c r="D145" s="55"/>
-      <c r="E145" s="55"/>
-      <c r="F145" s="55"/>
-      <c r="G145" s="55"/>
-      <c r="H145" s="55"/>
-      <c r="I145" s="55"/>
-      <c r="J145" s="55"/>
-      <c r="K145" s="55"/>
-      <c r="L145" s="55"/>
-    </row>
-    <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="35" t="s">
+      <c r="A145" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B146" s="69">
-        <f>SUM(B128:B145)</f>
+      <c r="B145" s="69">
+        <f>SUM(B137:B142)</f>
         <v>0</v>
       </c>
-      <c r="C146" s="69"/>
-      <c r="D146" s="71">
-        <f>SUM(D128:D145)</f>
-        <v>0.251087963</v>
-      </c>
-      <c r="E146" s="69"/>
-      <c r="F146" s="71">
-        <f>SUM(F128:F145)</f>
-        <v>0.7051273148</v>
-      </c>
-      <c r="G146" s="69"/>
-      <c r="H146" s="71">
-        <f>SUM(H128:H145)</f>
-        <v>0.4132986111</v>
-      </c>
-      <c r="I146" s="69"/>
-      <c r="J146" s="71">
-        <f>SUM(J128:J145)</f>
-        <v>0.4830902778</v>
-      </c>
-      <c r="K146" s="69"/>
-      <c r="L146" s="71">
-        <f>SUM(L128:L145)</f>
-        <v>0.1041666667</v>
-      </c>
-    </row>
+      <c r="C145" s="69"/>
+      <c r="D145" s="71">
+        <f>SUM(D137:D142)</f>
+        <v>0.04395833333</v>
+      </c>
+      <c r="E145" s="69"/>
+      <c r="F145" s="71">
+        <f>SUM(F137:F143)</f>
+        <v>1.610740741</v>
+      </c>
+      <c r="G145" s="69"/>
+      <c r="H145" s="71">
+        <f>SUM(H137:H142)</f>
+        <v>0.3412847222</v>
+      </c>
+      <c r="I145" s="69"/>
+      <c r="J145" s="71">
+        <f>SUM(J137:J142)</f>
+        <v>0.04395833333</v>
+      </c>
+      <c r="K145" s="69"/>
+      <c r="L145" s="71">
+        <f>SUM(L137:L142)</f>
+        <v>0.1111111111</v>
+      </c>
+    </row>
+    <row r="146" ht="14.25" customHeight="1"/>
     <row r="147" ht="14.25" customHeight="1"/>
     <row r="148" ht="14.25" customHeight="1"/>
     <row r="149" ht="14.25" customHeight="1"/>
@@ -6593,16 +6793,6 @@
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
-    <row r="1001" ht="14.25" customHeight="1"/>
-    <row r="1002" ht="14.25" customHeight="1"/>
-    <row r="1003" ht="14.25" customHeight="1"/>
-    <row r="1004" ht="14.25" customHeight="1"/>
-    <row r="1005" ht="14.25" customHeight="1"/>
-    <row r="1006" ht="14.25" customHeight="1"/>
-    <row r="1007" ht="14.25" customHeight="1"/>
-    <row r="1008" ht="14.25" customHeight="1"/>
-    <row r="1009" ht="14.25" customHeight="1"/>
-    <row r="1010" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A53:L53"/>
@@ -6625,167 +6815,167 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="77" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>106</v>
+      <c r="C3" s="83" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="83" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="78">
+      <c r="B4" s="84">
         <v>1.0</v>
       </c>
-      <c r="C4" s="79">
+      <c r="C4" s="85">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="85">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="78">
+      <c r="B5" s="84">
         <v>2.0</v>
       </c>
-      <c r="C5" s="79">
+      <c r="C5" s="85">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="85">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="78">
+      <c r="B6" s="84">
         <v>3.0</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="85">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="85">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="78">
+      <c r="B7" s="84">
         <v>4.0</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="85">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="85">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="78">
+      <c r="B8" s="84">
         <v>5.0</v>
       </c>
-      <c r="C8" s="79">
+      <c r="C8" s="85">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="85">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="78">
+      <c r="B9" s="84">
         <v>6.0</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="85">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="85">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="78">
+      <c r="B10" s="84">
         <v>7.0</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="85">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="86">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="78">
+      <c r="B11" s="84">
         <v>8.0</v>
       </c>
-      <c r="C11" s="80">
+      <c r="C11" s="86">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="86">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="78">
+      <c r="B12" s="84">
         <v>9.0</v>
       </c>
-      <c r="C12" s="80">
+      <c r="C12" s="86">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="86">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="78">
+      <c r="B13" s="84">
         <v>10.0</v>
       </c>
-      <c r="C13" s="80">
+      <c r="C13" s="86">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="85">
         <v>45965.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="81">
+      <c r="B14" s="87">
         <v>11.0</v>
       </c>
-      <c r="C14" s="82">
+      <c r="C14" s="88">
         <v>45965.0</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="89">
         <v>45972.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="81">
+      <c r="B15" s="87">
         <v>12.0</v>
       </c>
-      <c r="C15" s="83">
+      <c r="C15" s="89">
         <v>45941.0</v>
       </c>
-      <c r="D15" s="83">
+      <c r="D15" s="89">
         <v>45979.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="81">
+      <c r="B16" s="87">
         <v>13.0</v>
       </c>
-      <c r="C16" s="83">
+      <c r="C16" s="89">
         <v>45979.0</v>
       </c>
-      <c r="D16" s="83">
+      <c r="D16" s="89">
         <v>45986.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="81">
+      <c r="B17" s="87">
         <v>14.0</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17" s="89">
         <v>45986.0</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="89">
         <v>45989.0</v>
       </c>
     </row>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="Wo0tMkqL7epBl/5yZbS97Jrk/nOx096iC+qc9Jtft6c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="hqo43g689y9bFPjeJIeefgbwFrAenGT8UpUDkpKDr10="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="153">
   <si>
     <t>Semana</t>
   </si>
@@ -72,18 +72,24 @@
     <t>Construcción-Iteración 3</t>
   </si>
   <si>
+    <t>Cierre de cursada</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
     <t>Total x semana</t>
   </si>
   <si>
-    <t>total etapa</t>
+    <t>total x etapa</t>
   </si>
   <si>
     <t>FASE</t>
   </si>
   <si>
+    <t>Total si se junta las etapas de elaboración / construcción</t>
+  </si>
+  <si>
     <t>INICIO</t>
   </si>
   <si>
@@ -447,10 +453,16 @@
     <t>Cierre de iteracion</t>
   </si>
   <si>
+    <t>Reunión 20/11</t>
+  </si>
+  <si>
     <t>Codificación CU 03, 04, 17 y 23</t>
   </si>
   <si>
     <t>Ejecución casos de prueba CU03 Asignar Rol</t>
+  </si>
+  <si>
+    <t>Planificación post-cursada</t>
   </si>
   <si>
     <t>Codificación CU 05 y 06</t>
@@ -477,7 +489,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -553,8 +565,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,8 +633,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC1E4F5"/>
         <bgColor rgb="FFC1E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E7CC3"/>
+        <bgColor rgb="FF8E7CC3"/>
       </patternFill>
     </fill>
     <fill>
@@ -627,19 +661,35 @@
         <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -665,6 +715,22 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -676,6 +742,24 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -684,25 +768,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+    </border>
+    <border>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -722,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="118">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -770,52 +840,70 @@
     <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="7" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="10" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="10" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="7" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="10" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="11" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="5" fillId="11" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="10" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="12" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="5" fillId="13" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="14" fontId="5" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="15" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="12" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="13" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="15" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="15" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="15" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -836,7 +924,7 @@
     </xf>
     <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="1" numFmtId="21" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="13" fontId="9" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="11" fontId="9" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -846,14 +934,13 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="1" numFmtId="46" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="13" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
@@ -910,7 +997,7 @@
     <xf borderId="1" fillId="4" fontId="10" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="13" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -960,7 +1047,10 @@
     <xf borderId="1" fillId="4" fontId="10" numFmtId="46" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="15" numFmtId="46" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1739,21 +1829,23 @@
       </c>
       <c r="F14" s="5">
         <f>Registro!J162</f>
-        <v>0.02430555556</v>
+        <v>0.1076388889</v>
       </c>
       <c r="G14" s="5">
         <f>Registro!L162</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="8"/>
+      <c r="I14" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="16">
-        <f t="shared" ref="B15:G15" si="2">SUM(B2:B13)</f>
+        <f t="shared" ref="B15:G15" si="2">SUM(B2:B14)</f>
         <v>3.201782407</v>
       </c>
       <c r="C15" s="16">
@@ -1762,23 +1854,23 @@
       </c>
       <c r="D15" s="16">
         <f t="shared" si="2"/>
-        <v>7.181493056</v>
+        <v>9.780798611</v>
       </c>
       <c r="E15" s="16">
         <f t="shared" si="2"/>
-        <v>1.725763889</v>
+        <v>2.276030093</v>
       </c>
       <c r="F15" s="16">
         <f t="shared" si="2"/>
-        <v>3.346099537</v>
+        <v>3.453738426</v>
       </c>
       <c r="G15" s="16">
         <f t="shared" si="2"/>
-        <v>1.584814815</v>
+        <v>1.709814815</v>
       </c>
       <c r="H15" s="16">
         <f>SUM(Total!$B15:$G15)</f>
-        <v>21.54060185</v>
+        <v>24.9228125</v>
       </c>
       <c r="I15" s="17"/>
     </row>
@@ -2802,10 +2894,11 @@
     <col customWidth="1" min="6" max="6" width="20.5"/>
     <col customWidth="1" min="7" max="7" width="23.13"/>
     <col customWidth="1" min="8" max="8" width="14.38"/>
-    <col customWidth="1" min="9" max="9" width="41.75"/>
-    <col customWidth="1" min="10" max="10" width="21.75"/>
-    <col customWidth="1" min="11" max="11" width="45.13"/>
-    <col customWidth="1" min="12" max="26" width="10.63"/>
+    <col customWidth="1" min="9" max="9" width="21.75"/>
+    <col customWidth="1" min="10" max="10" width="45.13"/>
+    <col customWidth="1" min="11" max="11" width="10.63"/>
+    <col customWidth="1" min="12" max="12" width="49.25"/>
+    <col customWidth="1" min="13" max="25" width="10.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -2831,17 +2924,18 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="I1" s="19" t="s">
         <v>20</v>
       </c>
+      <c r="J1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3">
@@ -2875,16 +2969,18 @@
         <f>SUM('Total x etapas del proyecto'!$B2:$G2)</f>
         <v>0.9644675926</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="21">
+      <c r="I2" s="23">
         <f>SUM(H2+H3)</f>
         <v>2.140381944</v>
       </c>
-      <c r="K2" s="22" t="s">
-        <v>21</v>
-      </c>
+      <c r="J2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="25">
+        <f>I2</f>
+        <v>2.140381944</v>
+      </c>
+      <c r="L2" s="26"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3">
@@ -2917,11 +3013,10 @@
         <f>SUM('Total x etapas del proyecto'!$B3:$G3)</f>
         <v>1.175914352</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="24"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="30"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3">
@@ -2955,16 +3050,18 @@
         <f>SUM('Total x etapas del proyecto'!$B4:$G4)</f>
         <v>1.101747685</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="25">
+      <c r="I4" s="31">
         <f>SUM(H4:H5)</f>
         <v>2.255717593</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>22</v>
-      </c>
+      <c r="J4" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="32">
+        <f>SUM(I4,I6)</f>
+        <v>8.142314815</v>
+      </c>
+      <c r="L4" s="26"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3">
@@ -2995,11 +3092,10 @@
         <f>SUM('Total x etapas del proyecto'!$B5:$G5)</f>
         <v>1.153969907</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="34"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3">
@@ -3028,16 +3124,15 @@
         <f>SUM('Total x etapas del proyecto'!$B6:$G6)</f>
         <v>2.226030093</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="21">
+      <c r="I6" s="23">
         <f>SUM(H6:H8)</f>
         <v>5.886597222</v>
       </c>
-      <c r="K6" s="22" t="s">
-        <v>23</v>
-      </c>
+      <c r="J6" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="33"/>
+      <c r="L6" s="34"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3">
@@ -3071,11 +3166,10 @@
         <f>SUM('Total x etapas del proyecto'!$B7:$G7)</f>
         <v>2.36599537</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="27"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="34"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="12">
@@ -3097,14 +3191,13 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <f t="shared" ref="H8:H13" si="1">SUM(B8:G8)</f>
+        <f t="shared" ref="H8:H14" si="1">SUM(B8:G8)</f>
         <v>1.294571759</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>13</v>
-      </c>
+      <c r="I8" s="37"/>
       <c r="J8" s="28"/>
-      <c r="K8" s="24"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="30"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="12">
@@ -3135,16 +3228,18 @@
         <f t="shared" si="1"/>
         <v>2.231377315</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="21">
+      <c r="I9" s="23">
         <f>SUM(H9:H10)</f>
         <v>5.434884259</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>24</v>
-      </c>
+      <c r="J9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="38">
+        <f>SUM(I9,I11,I13)</f>
+        <v>11.25790509</v>
+      </c>
+      <c r="L9" s="26"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="12">
@@ -3178,11 +3273,10 @@
         <f t="shared" si="1"/>
         <v>3.203506944</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="I10" s="37"/>
       <c r="J10" s="28"/>
-      <c r="K10" s="24"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="34"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="12">
@@ -3216,16 +3310,15 @@
         <f t="shared" si="1"/>
         <v>1.956770833</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="21">
+      <c r="I11" s="23">
         <f>SUM(H11:H12)</f>
         <v>4.107824074</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>25</v>
-      </c>
+      <c r="J11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="33"/>
+      <c r="L11" s="34"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="12">
@@ -3259,11 +3352,10 @@
         <f t="shared" si="1"/>
         <v>2.151053241</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="I12" s="37"/>
       <c r="J12" s="28"/>
-      <c r="K12" s="24"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="34"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="12">
@@ -3297,16 +3389,15 @@
         <f t="shared" si="1"/>
         <v>1.715196759</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="29">
+      <c r="I13" s="39">
         <f>H13</f>
         <v>1.715196759</v>
       </c>
-      <c r="K13" s="30" t="s">
-        <v>26</v>
-      </c>
+      <c r="J13" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="12">
@@ -3330,23 +3421,35 @@
       </c>
       <c r="F14" s="5">
         <f>Registro!J162</f>
-        <v>0.02430555556</v>
+        <v>0.1076388889</v>
       </c>
       <c r="G14" s="5">
         <f>Registro!L162</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="32"/>
+        <v>0.125</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="1"/>
+        <v>3.382210648</v>
+      </c>
+      <c r="I14" s="39">
+        <f>SUM(B14:G14)</f>
+        <v>3.382210648</v>
+      </c>
+      <c r="J14" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="41">
+        <f>I14</f>
+        <v>3.382210648</v>
+      </c>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="16">
-        <f t="shared" ref="B15:G15" si="2">SUM(B2:B13)</f>
+        <f t="shared" ref="B15:G15" si="2">SUM(B2:B14)</f>
         <v>3.201782407</v>
       </c>
       <c r="C15" s="16">
@@ -3355,27 +3458,26 @@
       </c>
       <c r="D15" s="16">
         <f t="shared" si="2"/>
-        <v>7.181493056</v>
+        <v>9.780798611</v>
       </c>
       <c r="E15" s="16">
         <f t="shared" si="2"/>
-        <v>1.725763889</v>
+        <v>2.276030093</v>
       </c>
       <c r="F15" s="16">
         <f t="shared" si="2"/>
-        <v>3.346099537</v>
+        <v>3.453738426</v>
       </c>
       <c r="G15" s="16">
         <f t="shared" si="2"/>
-        <v>1.584814815</v>
+        <v>1.709814815</v>
       </c>
       <c r="H15" s="16">
         <f>SUM('Total x etapas del proyecto'!$B15:$G15)</f>
-        <v>21.54060185</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="32"/>
+        <v>24.9228125</v>
+      </c>
+      <c r="I15" s="42"/>
+      <c r="J15" s="43"/>
     </row>
     <row r="16" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
@@ -4372,17 +4474,22 @@
     <row r="1006" ht="14.25" customHeight="1"/>
     <row r="1007" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="K9:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:L8"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="K11:K12"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4414,436 +4521,436 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
+      <c r="A1" s="44"/>
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="46"/>
+      <c r="H1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37" t="s">
+      <c r="I1" s="46"/>
+      <c r="J1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="38"/>
-      <c r="L1" s="37" t="s">
+      <c r="K1" s="48"/>
+      <c r="L1" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="42"/>
-      <c r="G2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="42"/>
+      <c r="A2" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="52"/>
+      <c r="E2" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="52"/>
+      <c r="G2" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="52"/>
+      <c r="I2" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="52"/>
+      <c r="K2" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="52"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="43" t="s">
-        <v>29</v>
+      <c r="A3" s="53" t="s">
+        <v>31</v>
       </c>
       <c r="B3" s="6">
         <v>0.05783564814814815</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="9">
         <v>0.03487268518518519</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
       <c r="I3" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J3" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="K3" s="45"/>
+      <c r="K3" s="55"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="43" t="s">
-        <v>29</v>
+      <c r="A4" s="53" t="s">
+        <v>31</v>
       </c>
       <c r="B4" s="5">
         <v>1.1574074074074075E-4</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
       <c r="I4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" s="7">
         <v>0.06111111111111111</v>
       </c>
-      <c r="K4" s="45"/>
+      <c r="K4" s="55"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>33</v>
+      <c r="A5" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B5" s="5">
         <v>0.04273148148148148</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
       <c r="I5" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5" s="7">
         <v>0.019791666666666666</v>
       </c>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="43" t="s">
-        <v>33</v>
+      <c r="A6" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B6" s="5">
         <v>0.002939814814814815</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
       <c r="I6" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6" s="7">
         <v>0.039780092592592596</v>
       </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>35</v>
+      <c r="A7" s="53" t="s">
+        <v>37</v>
       </c>
       <c r="B7" s="5">
         <v>0.06607638888888889</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
       <c r="I7" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J7" s="9">
         <v>0.0798611111111111</v>
       </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="43" t="s">
-        <v>37</v>
+      <c r="A8" s="53" t="s">
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>0.06518518518518518</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="46" t="s">
-        <v>38</v>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="56" t="s">
+        <v>40</v>
       </c>
       <c r="J8" s="13">
         <v>0.03515046296296296</v>
       </c>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>36</v>
+      <c r="A9" s="53" t="s">
+        <v>38</v>
       </c>
       <c r="B9" s="5">
         <v>0.0798611111111111</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
       <c r="I9" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J9" s="7">
         <v>0.06607638888888889</v>
       </c>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="43" t="s">
-        <v>34</v>
+      <c r="A10" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="B10" s="5">
         <v>0.019791666666666666</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
       <c r="I10" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J10" s="9">
         <v>0.05783564814814815</v>
       </c>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="47" t="s">
-        <v>34</v>
+      <c r="A11" s="57" t="s">
+        <v>36</v>
       </c>
       <c r="B11" s="5">
         <v>0.039780092592592596</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="43" t="s">
-        <v>39</v>
+      <c r="A12" s="53" t="s">
+        <v>41</v>
       </c>
       <c r="B12" s="5">
         <v>0.028356481481481483</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>40</v>
+      <c r="A13" s="53" t="s">
+        <v>42</v>
       </c>
       <c r="B13" s="5">
         <v>0.013148148148148148</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7">
         <v>0.07708333333333334</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="50">
+      <c r="A15" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="60">
         <f>SUM(B3:B14)</f>
         <v>0.4929050926</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52">
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="62">
         <f>SUM(F3:F14)</f>
         <v>0.03487268519</v>
       </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="52">
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="62">
         <f>SUM(J3:J14)</f>
         <v>0.4366898148</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="52">
+      <c r="K15" s="61"/>
+      <c r="L15" s="62">
         <f>SUM(L3:L14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="37" t="s">
+      <c r="A16" s="49"/>
+      <c r="B16" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="37" t="s">
+      <c r="E16" s="51"/>
+      <c r="F16" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="37" t="s">
+      <c r="G16" s="51"/>
+      <c r="H16" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="41"/>
-      <c r="J16" s="37" t="s">
+      <c r="I16" s="51"/>
+      <c r="J16" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="37" t="s">
+      <c r="K16" s="51"/>
+      <c r="L16" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="42"/>
+      <c r="A17" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="52"/>
+      <c r="E17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="52"/>
+      <c r="I17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="52"/>
+      <c r="K17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="52"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="43" t="s">
-        <v>29</v>
+      <c r="A18" s="53" t="s">
+        <v>31</v>
       </c>
       <c r="B18" s="7">
         <v>0.03831018518518518</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
       <c r="E18" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18" s="7">
         <v>0.08034722222222222</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H18" s="7">
         <v>0.003981481481481482</v>
       </c>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="54"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="43" t="s">
-        <v>33</v>
+      <c r="A19" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B19" s="7">
         <v>0.02244212962962963</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
       <c r="E19" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F19" s="9">
         <v>0.6090277777777777</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="7">
         <v>0.003414351851851852</v>
@@ -4852,902 +4959,902 @@
       <c r="J19" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="K19" s="54" t="s">
-        <v>46</v>
+      <c r="K19" s="64" t="s">
+        <v>48</v>
       </c>
       <c r="L19" s="7">
         <v>0.03150462962962963</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="43" t="s">
-        <v>33</v>
+      <c r="A20" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B20" s="7">
         <v>0.016608796296296295</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H20" s="7">
         <v>0.016747685185185185</v>
       </c>
-      <c r="I20" s="55" t="s">
-        <v>47</v>
+      <c r="I20" s="65" t="s">
+        <v>49</v>
       </c>
       <c r="J20" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="K20" s="54" t="s">
-        <v>46</v>
+      <c r="K20" s="64" t="s">
+        <v>48</v>
       </c>
       <c r="L20" s="7">
         <v>1.273148148148148E-4</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="43" t="s">
-        <v>33</v>
+      <c r="A21" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B21" s="7">
         <v>0.018761574074074073</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="43" t="s">
-        <v>33</v>
+      <c r="A22" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B22" s="7">
         <v>0.07424768518518518</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="43" t="s">
-        <v>33</v>
+      <c r="A23" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B23" s="7">
         <v>0.047789351851851854</v>
       </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="43" t="s">
-        <v>33</v>
+      <c r="A24" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B24" s="7">
         <v>0.0350462962962963</v>
       </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="43" t="s">
-        <v>33</v>
+      <c r="A25" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B25" s="7">
         <v>0.008020833333333333</v>
       </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="54"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="43" t="s">
-        <v>33</v>
+      <c r="A26" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B26" s="7">
         <v>0.010416666666666666</v>
       </c>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="43" t="s">
-        <v>33</v>
+      <c r="A27" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>0.013125</v>
       </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="43" t="s">
-        <v>33</v>
+      <c r="A28" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B28" s="7">
         <v>0.019143518518518518</v>
       </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="54"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="43" t="s">
-        <v>33</v>
+      <c r="A29" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B29" s="7">
         <v>0.009305555555555555</v>
       </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="43" t="s">
-        <v>33</v>
+      <c r="A30" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B30" s="7">
         <v>0.04144675925925926</v>
       </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="43" t="s">
-        <v>33</v>
+      <c r="A31" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B31" s="7">
         <v>0.0016782407407407408</v>
       </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="43" t="s">
-        <v>33</v>
+      <c r="A32" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B32" s="7">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="43" t="s">
-        <v>33</v>
+      <c r="A33" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B33" s="7">
         <v>6.944444444444444E-5</v>
       </c>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="44"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="43" t="s">
-        <v>33</v>
+      <c r="A34" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B34" s="7">
         <v>5.439814814814814E-4</v>
       </c>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="43" t="s">
-        <v>33</v>
+      <c r="A35" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B35" s="7">
         <v>0.023078703703703702</v>
       </c>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="44"/>
-      <c r="L35" s="44"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="43" t="s">
-        <v>33</v>
+      <c r="A36" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B36" s="7">
         <v>0.007060185185185185</v>
       </c>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="44"/>
-      <c r="L36" s="44"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="43" t="s">
-        <v>29</v>
+      <c r="A37" s="53" t="s">
+        <v>31</v>
       </c>
       <c r="B37" s="9">
         <v>0.017175925925925924</v>
       </c>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="52">
+      <c r="A38" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="62">
         <f>SUM(B18:B37)</f>
         <v>0.4042824074</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56">
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66">
         <f>SUM(F17:F36)</f>
         <v>0.689375</v>
       </c>
-      <c r="G38" s="51"/>
-      <c r="H38" s="52">
+      <c r="G38" s="61"/>
+      <c r="H38" s="62">
         <f>SUM(H18:H36)</f>
         <v>0.02414351852</v>
       </c>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56">
+      <c r="I38" s="66"/>
+      <c r="J38" s="66">
         <f>SUM(J18:J36)</f>
         <v>0.02648148148</v>
       </c>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56">
+      <c r="K38" s="66"/>
+      <c r="L38" s="66">
         <f>SUM(L18:L36)</f>
         <v>0.03163194444</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="39"/>
-      <c r="B39" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="37" t="s">
+      <c r="A39" s="49"/>
+      <c r="B39" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="51"/>
+      <c r="D39" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="37" t="s">
+      <c r="E39" s="51"/>
+      <c r="F39" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="41"/>
-      <c r="H39" s="37" t="s">
+      <c r="G39" s="51"/>
+      <c r="H39" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I39" s="41"/>
-      <c r="J39" s="37" t="s">
+      <c r="I39" s="51"/>
+      <c r="J39" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="41"/>
-      <c r="L39" s="37" t="s">
+      <c r="K39" s="51"/>
+      <c r="L39" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="42"/>
-      <c r="E40" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="42"/>
-      <c r="I40" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J40" s="42"/>
-      <c r="K40" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L40" s="42"/>
+      <c r="A40" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="52"/>
+      <c r="E40" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="52"/>
+      <c r="G40" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" s="52"/>
+      <c r="I40" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="52"/>
+      <c r="K40" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="52"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="43" t="s">
-        <v>33</v>
+      <c r="A41" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B41" s="7">
         <v>0.04128472222222222</v>
       </c>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6">
         <v>0.23333333333333334</v>
       </c>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
       <c r="I41" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J41" s="7">
         <v>0.0575462962962963</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L41" s="7">
         <v>0.016446759259259258</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="43" t="s">
-        <v>33</v>
+      <c r="A42" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B42" s="7">
         <v>0.04113425925925926</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
       <c r="I42" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J42" s="7">
         <v>0.019178240740740742</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L42" s="7">
         <v>0.10934027777777777</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="43" t="s">
-        <v>33</v>
+      <c r="A43" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B43" s="7">
         <v>0.03423611111111111</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
       <c r="I43" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J43" s="7">
         <v>0.01525462962962963</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L43" s="7">
         <v>0.03608796296296296</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="43" t="s">
-        <v>33</v>
+      <c r="A44" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B44" s="7">
         <v>0.029768518518518517</v>
       </c>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
       <c r="I44" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J44" s="7">
         <v>0.004722222222222222</v>
       </c>
-      <c r="K44" s="44"/>
-      <c r="L44" s="44"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="54"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="43" t="s">
-        <v>33</v>
+      <c r="A45" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B45" s="7">
         <v>0.0078125</v>
       </c>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
       <c r="I45" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J45" s="7">
         <v>1.6203703703703703E-4</v>
       </c>
-      <c r="K45" s="44"/>
-      <c r="L45" s="44"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="54"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="43" t="s">
-        <v>33</v>
+      <c r="A46" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B46" s="7">
         <v>0.01810185185185185</v>
       </c>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
       <c r="I46" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J46" s="7">
         <v>0.0046875</v>
       </c>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="54"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="43" t="s">
-        <v>33</v>
+      <c r="A47" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B47" s="7">
         <v>1.5046296296296297E-4</v>
       </c>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
       <c r="I47" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J47" s="7">
         <v>0.012094907407407407</v>
       </c>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="43" t="s">
-        <v>33</v>
+      <c r="A48" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B48" s="7">
         <v>2.4305555555555555E-4</v>
       </c>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
       <c r="I48" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J48" s="7">
         <v>0.02900462962962963</v>
       </c>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="54"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="43" t="s">
-        <v>33</v>
+      <c r="A49" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B49" s="7">
         <v>0.011412037037037037</v>
       </c>
-      <c r="C49" s="44"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="44"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
       <c r="I49" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J49" s="7">
         <v>0.027962962962962964</v>
       </c>
-      <c r="K49" s="44"/>
-      <c r="L49" s="44"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="43" t="s">
-        <v>33</v>
+      <c r="A50" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B50" s="7">
         <v>0.019131944444444444</v>
       </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
       <c r="I50" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J50" s="7">
         <v>0.016400462962962964</v>
       </c>
-      <c r="K50" s="44"/>
-      <c r="L50" s="44"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="43" t="s">
-        <v>33</v>
+      <c r="A51" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B51" s="7">
         <v>0.026516203703703705</v>
       </c>
-      <c r="C51" s="44"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="44"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="44"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
       <c r="I51" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J51" s="7">
         <v>0.031574074074074074</v>
       </c>
-      <c r="K51" s="44"/>
-      <c r="L51" s="44"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="54"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="43" t="s">
-        <v>33</v>
+      <c r="A52" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B52" s="7">
         <v>0.04517361111111111</v>
       </c>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="44"/>
-      <c r="L52" s="44"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="54"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="54"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="59"/>
-      <c r="C53" s="59"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="59"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="59"/>
-      <c r="J53" s="59"/>
-      <c r="K53" s="59"/>
-      <c r="L53" s="60"/>
+      <c r="A53" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="69"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="69"/>
+      <c r="F53" s="69"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="69"/>
+      <c r="I53" s="69"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="69"/>
+      <c r="L53" s="22"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="43" t="s">
-        <v>33</v>
+      <c r="A54" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B54" s="7">
         <v>0.1352662037037037</v>
       </c>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="44"/>
-      <c r="K54" s="44"/>
-      <c r="L54" s="44"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="43" t="s">
-        <v>33</v>
+      <c r="A55" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B55" s="7">
         <v>0.03125</v>
       </c>
-      <c r="C55" s="44"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="44"/>
-      <c r="I55" s="44"/>
-      <c r="J55" s="44"/>
-      <c r="K55" s="44"/>
-      <c r="L55" s="44"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="43" t="s">
-        <v>33</v>
+      <c r="A56" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B56" s="7">
         <v>0.027662037037037037</v>
       </c>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="44"/>
-      <c r="K56" s="44"/>
-      <c r="L56" s="44"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="43" t="s">
-        <v>33</v>
+      <c r="A57" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B57" s="7">
         <v>2.662037037037037E-4</v>
       </c>
-      <c r="C57" s="44"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="44"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="44"/>
-      <c r="J57" s="44"/>
-      <c r="K57" s="44"/>
-      <c r="L57" s="44"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="54"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="43" t="s">
-        <v>33</v>
+      <c r="A58" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B58" s="7">
         <v>0.018541666666666668</v>
       </c>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="44"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="54"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="52">
+      <c r="A59" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="62">
         <f>SUM(B41:B58)</f>
         <v>0.4879513889</v>
       </c>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="56">
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="66">
         <f>SUM(F41:F58)</f>
         <v>0.2333333333</v>
       </c>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51">
+      <c r="G59" s="61"/>
+      <c r="H59" s="61">
         <f>SUM(H41:H51)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="51"/>
-      <c r="J59" s="52">
+      <c r="I59" s="61"/>
+      <c r="J59" s="62">
         <f>SUM(J41:J58)</f>
         <v>0.218587963</v>
       </c>
-      <c r="K59" s="51"/>
-      <c r="L59" s="52">
+      <c r="K59" s="61"/>
+      <c r="L59" s="62">
         <f>SUM(L41:L58)</f>
         <v>0.161875</v>
       </c>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="39"/>
-      <c r="B60" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="41"/>
-      <c r="D60" s="37" t="s">
+      <c r="A60" s="49"/>
+      <c r="B60" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="51"/>
+      <c r="D60" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="41"/>
-      <c r="F60" s="37" t="s">
+      <c r="E60" s="51"/>
+      <c r="F60" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="41"/>
-      <c r="H60" s="37" t="s">
+      <c r="G60" s="51"/>
+      <c r="H60" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I60" s="41"/>
-      <c r="J60" s="37" t="s">
+      <c r="I60" s="51"/>
+      <c r="J60" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="41"/>
-      <c r="L60" s="37" t="s">
+      <c r="K60" s="51"/>
+      <c r="L60" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C61" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="42"/>
-      <c r="E61" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="42"/>
-      <c r="G61" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H61" s="42"/>
-      <c r="I61" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J61" s="42"/>
-      <c r="K61" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L61" s="42"/>
+      <c r="A61" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="52"/>
+      <c r="E61" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61" s="52"/>
+      <c r="G61" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" s="52"/>
+      <c r="I61" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J61" s="52"/>
+      <c r="K61" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" s="52"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="43" t="s">
-        <v>33</v>
+      <c r="A62" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B62" s="7">
         <v>0.0028703703703703703</v>
@@ -5761,1018 +5868,1018 @@
         <v>0.09237268518518518</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H62" s="7">
         <v>0.16012731481481482</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J62" s="7">
         <v>0.1171412037037037</v>
       </c>
-      <c r="K62" s="44"/>
-      <c r="L62" s="44"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="54"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="43" t="s">
-        <v>33</v>
+      <c r="A63" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B63" s="7">
         <v>0.16708333333333333</v>
       </c>
-      <c r="C63" s="44"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
       <c r="G63" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H63" s="7">
         <v>0.017881944444444443</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J63" s="7">
         <v>0.05094907407407408</v>
       </c>
-      <c r="K63" s="44"/>
-      <c r="L63" s="44"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="54"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="43" t="s">
-        <v>33</v>
+      <c r="A64" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B64" s="7">
         <v>0.01716435185185185</v>
       </c>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="43" t="s">
-        <v>55</v>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="53" t="s">
+        <v>57</v>
       </c>
       <c r="J64" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="K64" s="44"/>
-      <c r="L64" s="44"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="54"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="43" t="s">
-        <v>33</v>
+      <c r="A65" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B65" s="7">
         <v>0.014085648148148147</v>
       </c>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="44"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="54"/>
+      <c r="L65" s="54"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="43" t="s">
-        <v>55</v>
+      <c r="A66" s="53" t="s">
+        <v>57</v>
       </c>
       <c r="B66" s="7">
         <v>0.06239583333333333</v>
       </c>
-      <c r="C66" s="44"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="44"/>
-      <c r="L66" s="44"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
+      <c r="H66" s="54"/>
+      <c r="I66" s="54"/>
+      <c r="J66" s="54"/>
+      <c r="K66" s="54"/>
+      <c r="L66" s="54"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="43" t="s">
-        <v>33</v>
+      <c r="A67" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B67" s="7">
         <v>0.10212962962962963</v>
       </c>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
-      <c r="J67" s="44"/>
-      <c r="K67" s="44"/>
-      <c r="L67" s="44"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
+      <c r="K67" s="54"/>
+      <c r="L67" s="54"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="43" t="s">
-        <v>33</v>
+      <c r="A68" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B68" s="7">
         <v>0.02273148148148148</v>
       </c>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
-      <c r="I68" s="44"/>
-      <c r="J68" s="44"/>
-      <c r="K68" s="44"/>
-      <c r="L68" s="44"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="54"/>
+      <c r="L68" s="54"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="43" t="s">
-        <v>33</v>
+      <c r="A69" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B69" s="7">
         <v>3.8194444444444446E-4</v>
       </c>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
-      <c r="H69" s="44"/>
-      <c r="I69" s="44"/>
-      <c r="J69" s="44"/>
-      <c r="K69" s="44"/>
-      <c r="L69" s="44"/>
+      <c r="C69" s="54"/>
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
+      <c r="K69" s="54"/>
+      <c r="L69" s="54"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="43" t="s">
-        <v>33</v>
+      <c r="A70" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B70" s="7">
         <v>0.011099537037037036</v>
       </c>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="44"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="44"/>
-      <c r="L70" s="44"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
+      <c r="K70" s="54"/>
+      <c r="L70" s="54"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="43" t="s">
-        <v>33</v>
+      <c r="A71" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B71" s="7">
         <v>0.019965277777777776</v>
       </c>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="44"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
+      <c r="H71" s="54"/>
+      <c r="I71" s="54"/>
+      <c r="J71" s="54"/>
+      <c r="K71" s="54"/>
+      <c r="L71" s="54"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="43" t="s">
-        <v>33</v>
+      <c r="A72" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B72" s="7">
         <v>0.10784722222222222</v>
       </c>
-      <c r="C72" s="44"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="44"/>
-      <c r="I72" s="44"/>
-      <c r="J72" s="44"/>
-      <c r="K72" s="44"/>
-      <c r="L72" s="44"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="54"/>
+      <c r="K72" s="54"/>
+      <c r="L72" s="54"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="43" t="s">
-        <v>33</v>
+      <c r="A73" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B73" s="7">
         <v>0.04087962962962963</v>
       </c>
-      <c r="C73" s="44"/>
-      <c r="D73" s="44"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="44"/>
-      <c r="H73" s="44"/>
-      <c r="I73" s="44"/>
-      <c r="J73" s="44"/>
-      <c r="K73" s="44"/>
-      <c r="L73" s="44"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="54"/>
+      <c r="I73" s="54"/>
+      <c r="J73" s="54"/>
+      <c r="K73" s="54"/>
+      <c r="L73" s="54"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="43" t="s">
-        <v>33</v>
+      <c r="A74" s="53" t="s">
+        <v>35</v>
       </c>
       <c r="B74" s="7">
         <v>0.0600462962962963</v>
       </c>
-      <c r="C74" s="44"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="44"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="44"/>
-      <c r="I74" s="44"/>
-      <c r="J74" s="44"/>
-      <c r="K74" s="44"/>
-      <c r="L74" s="44"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54"/>
+      <c r="L74" s="54"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="52">
+      <c r="A75" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" s="62">
         <f>SUM(B62:B74)</f>
         <v>0.6286805556</v>
       </c>
-      <c r="C75" s="61"/>
-      <c r="D75" s="50">
+      <c r="C75" s="70"/>
+      <c r="D75" s="60">
         <f>SUM(D62:D74)</f>
         <v>0.0244212963</v>
       </c>
-      <c r="E75" s="62"/>
-      <c r="F75" s="52">
+      <c r="E75" s="71"/>
+      <c r="F75" s="62">
         <f>SUM(F62:F74)</f>
         <v>0.09237268519</v>
       </c>
-      <c r="G75" s="62"/>
-      <c r="H75" s="52">
+      <c r="G75" s="71"/>
+      <c r="H75" s="62">
         <f>SUM(H62:H74)</f>
         <v>0.1780092593</v>
       </c>
-      <c r="I75" s="62"/>
-      <c r="J75" s="52">
+      <c r="I75" s="71"/>
+      <c r="J75" s="62">
         <f>SUM(J62:J74)</f>
         <v>0.2304861111</v>
       </c>
-      <c r="K75" s="62"/>
-      <c r="L75" s="62"/>
+      <c r="K75" s="71"/>
+      <c r="L75" s="71"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="39"/>
-      <c r="B76" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C76" s="41"/>
-      <c r="D76" s="37" t="s">
+      <c r="A76" s="49"/>
+      <c r="B76" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76" s="51"/>
+      <c r="D76" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="41"/>
-      <c r="F76" s="37" t="s">
+      <c r="E76" s="51"/>
+      <c r="F76" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G76" s="41"/>
-      <c r="H76" s="37" t="s">
+      <c r="G76" s="51"/>
+      <c r="H76" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="41"/>
-      <c r="J76" s="37" t="s">
+      <c r="I76" s="51"/>
+      <c r="J76" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="41"/>
-      <c r="L76" s="37" t="s">
+      <c r="K76" s="51"/>
+      <c r="L76" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B77" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="C77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D77" s="42"/>
-      <c r="E77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" s="42"/>
-      <c r="G77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="42"/>
-      <c r="I77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J77" s="42"/>
-      <c r="K77" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L77" s="42"/>
+      <c r="A77" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" s="52"/>
+      <c r="E77" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" s="52"/>
+      <c r="G77" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" s="52"/>
+      <c r="I77" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J77" s="52"/>
+      <c r="K77" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L77" s="52"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="43" t="s">
-        <v>57</v>
+      <c r="A78" s="53" t="s">
+        <v>59</v>
       </c>
       <c r="B78" s="7">
         <v>0.125</v>
       </c>
-      <c r="C78" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="D78" s="64">
+      <c r="C78" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D78" s="73">
         <v>0.11513888888888889</v>
       </c>
-      <c r="E78" s="65"/>
-      <c r="F78" s="65"/>
-      <c r="G78" s="64"/>
-      <c r="H78" s="64">
+      <c r="E78" s="74"/>
+      <c r="F78" s="74"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="73">
         <v>0.013888888888888888</v>
       </c>
-      <c r="I78" s="43" t="s">
-        <v>59</v>
+      <c r="I78" s="53" t="s">
+        <v>61</v>
       </c>
       <c r="J78" s="7">
         <v>0.08333333333333333</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L78" s="9">
         <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="43" t="s">
-        <v>61</v>
+      <c r="A79" s="53" t="s">
+        <v>63</v>
       </c>
       <c r="B79" s="7">
         <v>0.06944444444444445</v>
       </c>
-      <c r="C79" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="D79" s="64">
+      <c r="C79" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D79" s="73">
         <v>0.5638888888888889</v>
       </c>
-      <c r="E79" s="65"/>
-      <c r="F79" s="65"/>
-      <c r="G79" s="65"/>
-      <c r="H79" s="65"/>
-      <c r="I79" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="J79" s="66">
+      <c r="E79" s="74"/>
+      <c r="F79" s="74"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="74"/>
+      <c r="I79" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J79" s="75">
         <v>0.09305555555555556</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B80" s="67">
+      <c r="A80" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="76">
         <v>0.0625</v>
       </c>
-      <c r="C80" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="D80" s="68">
+      <c r="C80" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" s="77">
         <v>0.19444444444444445</v>
       </c>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="46" t="s">
-        <v>62</v>
+      <c r="E80" s="74"/>
+      <c r="F80" s="74"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="56" t="s">
+        <v>64</v>
       </c>
       <c r="J80" s="13">
         <v>0.041666666666666664</v>
       </c>
-      <c r="K80" s="65"/>
-      <c r="L80" s="65"/>
+      <c r="K80" s="74"/>
+      <c r="L80" s="74"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B81" s="69">
+      <c r="A81" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" s="78">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C81" s="64"/>
-      <c r="D81" s="64"/>
-      <c r="E81" s="65"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="65"/>
-      <c r="H81" s="65"/>
-      <c r="I81" s="65"/>
-      <c r="J81" s="65"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="74"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="74"/>
+      <c r="K81" s="73"/>
+      <c r="L81" s="73"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="43" t="s">
-        <v>63</v>
+      <c r="A82" s="53" t="s">
+        <v>65</v>
       </c>
       <c r="B82" s="9">
         <v>0.05763888888888889</v>
       </c>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
-      <c r="E82" s="65"/>
-      <c r="F82" s="65"/>
-      <c r="G82" s="65"/>
-      <c r="H82" s="65"/>
-      <c r="I82" s="65"/>
-      <c r="J82" s="65"/>
-      <c r="K82" s="65"/>
-      <c r="L82" s="65"/>
+      <c r="C82" s="73"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="74"/>
+      <c r="F82" s="74"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="74"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="74"/>
+      <c r="K82" s="74"/>
+      <c r="L82" s="74"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="70"/>
+      <c r="A83" s="79"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="64"/>
-      <c r="D83" s="64"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="65"/>
-      <c r="H83" s="65"/>
-      <c r="I83" s="65"/>
-      <c r="J83" s="65"/>
-      <c r="K83" s="65"/>
-      <c r="L83" s="65"/>
+      <c r="C83" s="73"/>
+      <c r="D83" s="73"/>
+      <c r="E83" s="74"/>
+      <c r="F83" s="74"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="74"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="74"/>
+      <c r="L83" s="74"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="70"/>
+      <c r="A84" s="79"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="64"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="65"/>
-      <c r="F84" s="65"/>
-      <c r="G84" s="65"/>
-      <c r="H84" s="65"/>
-      <c r="I84" s="65"/>
-      <c r="J84" s="65"/>
-      <c r="K84" s="65"/>
-      <c r="L84" s="65"/>
+      <c r="C84" s="73"/>
+      <c r="D84" s="73"/>
+      <c r="E84" s="74"/>
+      <c r="F84" s="74"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="74"/>
+      <c r="L84" s="74"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="70"/>
+      <c r="A85" s="79"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="71"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="65"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="65"/>
-      <c r="H85" s="65"/>
-      <c r="I85" s="65"/>
-      <c r="J85" s="65"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
+      <c r="C85" s="80"/>
+      <c r="D85" s="80"/>
+      <c r="E85" s="74"/>
+      <c r="F85" s="74"/>
+      <c r="G85" s="74"/>
+      <c r="H85" s="74"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="74"/>
+      <c r="K85" s="80"/>
+      <c r="L85" s="80"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B86" s="56">
+      <c r="A86" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" s="66">
         <f>SUM(B78:B85)</f>
         <v>0.3979166667</v>
       </c>
-      <c r="C86" s="72"/>
-      <c r="D86" s="72">
+      <c r="C86" s="81"/>
+      <c r="D86" s="81">
         <f>SUM(D78:D83)</f>
         <v>0.8734722222</v>
       </c>
-      <c r="E86" s="73"/>
-      <c r="F86" s="73"/>
-      <c r="G86" s="73"/>
-      <c r="H86" s="50">
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="60">
         <f>SUM(H78:H85)</f>
         <v>0.01388888889</v>
       </c>
-      <c r="I86" s="73"/>
-      <c r="J86" s="50">
+      <c r="I86" s="82"/>
+      <c r="J86" s="60">
         <f>SUM(J78:J85)</f>
         <v>0.2180555556</v>
       </c>
-      <c r="K86" s="56"/>
-      <c r="L86" s="56">
+      <c r="K86" s="66"/>
+      <c r="L86" s="66">
         <f>SUM(L78:L80)</f>
         <v>0.03333333333</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="39"/>
-      <c r="B87" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C87" s="41"/>
-      <c r="D87" s="37" t="s">
+      <c r="A87" s="49"/>
+      <c r="B87" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" s="51"/>
+      <c r="D87" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="41"/>
-      <c r="F87" s="37" t="s">
+      <c r="E87" s="51"/>
+      <c r="F87" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="41"/>
-      <c r="H87" s="37" t="s">
+      <c r="G87" s="51"/>
+      <c r="H87" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I87" s="41"/>
-      <c r="J87" s="37" t="s">
+      <c r="I87" s="51"/>
+      <c r="J87" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="41"/>
-      <c r="L87" s="37" t="s">
+      <c r="K87" s="51"/>
+      <c r="L87" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B88" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="C88" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" s="42"/>
-      <c r="E88" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="42"/>
-      <c r="G88" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" s="42"/>
-      <c r="I88" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J88" s="42"/>
-      <c r="K88" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L88" s="42"/>
+      <c r="A88" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="52"/>
+      <c r="E88" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="52"/>
+      <c r="G88" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H88" s="52"/>
+      <c r="I88" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J88" s="52"/>
+      <c r="K88" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L88" s="52"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="70"/>
+      <c r="A89" s="79"/>
       <c r="B89" s="7">
         <v>0.08333333333333333</v>
       </c>
-      <c r="C89" s="63" t="s">
-        <v>65</v>
+      <c r="C89" s="72" t="s">
+        <v>67</v>
       </c>
       <c r="D89" s="13">
         <v>0.17631944444444445</v>
       </c>
-      <c r="E89" s="74" t="s">
-        <v>66</v>
+      <c r="E89" s="83" t="s">
+        <v>68</v>
       </c>
       <c r="F89" s="7">
         <v>0.39791666666666664</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H89" s="7">
         <v>0.10641203703703704</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J89" s="7">
         <v>0.003472222222222222</v>
       </c>
       <c r="K89" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L89" s="7">
         <v>0.125</v>
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="70"/>
-      <c r="B90" s="44"/>
-      <c r="C90" s="63" t="s">
-        <v>70</v>
+      <c r="A90" s="79"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="72" t="s">
+        <v>72</v>
       </c>
       <c r="D90" s="13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="E90" s="74" t="s">
-        <v>66</v>
+      <c r="E90" s="83" t="s">
+        <v>68</v>
       </c>
       <c r="F90" s="7">
         <v>0.3541666666666667</v>
       </c>
-      <c r="G90" s="55" t="s">
-        <v>71</v>
+      <c r="G90" s="65" t="s">
+        <v>73</v>
       </c>
       <c r="H90" s="7">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I90" s="44"/>
-      <c r="J90" s="44"/>
+      <c r="I90" s="54"/>
+      <c r="J90" s="54"/>
       <c r="K90" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L90" s="7">
         <v>0.0625</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="70"/>
-      <c r="B91" s="44"/>
-      <c r="C91" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="D91" s="66">
+      <c r="A91" s="79"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="D91" s="75">
         <v>0.32806712962962964</v>
       </c>
-      <c r="E91" s="74" t="s">
-        <v>66</v>
+      <c r="E91" s="83" t="s">
+        <v>68</v>
       </c>
       <c r="F91" s="7">
         <v>0.125</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H91" s="7">
         <v>0.06527777777777778</v>
       </c>
-      <c r="I91" s="44"/>
-      <c r="J91" s="44"/>
+      <c r="I91" s="54"/>
+      <c r="J91" s="54"/>
       <c r="K91" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L91" s="9">
         <v>0.23644675925925926</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="70"/>
-      <c r="B92" s="44"/>
-      <c r="C92" s="65"/>
-      <c r="D92" s="65"/>
-      <c r="E92" s="44"/>
-      <c r="F92" s="44"/>
-      <c r="G92" s="44"/>
-      <c r="H92" s="44"/>
-      <c r="I92" s="44"/>
-      <c r="J92" s="44"/>
-      <c r="K92" s="44"/>
-      <c r="L92" s="44"/>
+      <c r="A92" s="79"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="74"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="54"/>
+      <c r="I92" s="54"/>
+      <c r="J92" s="54"/>
+      <c r="K92" s="54"/>
+      <c r="L92" s="54"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="56">
+      <c r="A93" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" s="66">
         <f>SUM(B89)</f>
         <v>0.08333333333</v>
       </c>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72">
+      <c r="C93" s="81"/>
+      <c r="D93" s="81">
         <f>SUM(D89:D92)</f>
         <v>0.6710532407</v>
       </c>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56">
+      <c r="E93" s="66"/>
+      <c r="F93" s="66">
         <f>SUM(F89:F91)</f>
         <v>0.8770833333</v>
       </c>
-      <c r="G93" s="56"/>
-      <c r="H93" s="56">
+      <c r="G93" s="66"/>
+      <c r="H93" s="66">
         <f>SUM(H89:H91)</f>
         <v>0.3071064815</v>
       </c>
-      <c r="I93" s="56"/>
-      <c r="J93" s="56">
+      <c r="I93" s="66"/>
+      <c r="J93" s="66">
         <f>SUM(J89)</f>
         <v>0.003472222222</v>
       </c>
-      <c r="K93" s="56"/>
-      <c r="L93" s="56">
+      <c r="K93" s="66"/>
+      <c r="L93" s="66">
         <f>SUM(L89:L91)</f>
         <v>0.4239467593</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="39"/>
-      <c r="B94" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C94" s="41"/>
-      <c r="D94" s="37" t="s">
+      <c r="A94" s="49"/>
+      <c r="B94" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C94" s="51"/>
+      <c r="D94" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E94" s="41"/>
-      <c r="F94" s="37" t="s">
+      <c r="E94" s="51"/>
+      <c r="F94" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="41"/>
-      <c r="H94" s="37" t="s">
+      <c r="G94" s="51"/>
+      <c r="H94" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="41"/>
-      <c r="J94" s="37" t="s">
+      <c r="I94" s="51"/>
+      <c r="J94" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="41"/>
-      <c r="L94" s="37" t="s">
+      <c r="K94" s="51"/>
+      <c r="L94" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="B95" s="76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="D95" s="44"/>
-      <c r="E95" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F95" s="44"/>
-      <c r="G95" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="H95" s="44"/>
-      <c r="I95" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="J95" s="44"/>
-      <c r="K95" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="L95" s="44"/>
+      <c r="A95" s="84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B95" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="C95" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" s="54"/>
+      <c r="E95" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="54"/>
+      <c r="G95" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="H95" s="54"/>
+      <c r="I95" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="J95" s="54"/>
+      <c r="K95" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="L95" s="54"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="43" t="s">
-        <v>75</v>
+      <c r="A96" s="53" t="s">
+        <v>77</v>
       </c>
       <c r="B96" s="9">
         <v>0.020833333333333332</v>
       </c>
-      <c r="C96" s="63" t="s">
-        <v>76</v>
+      <c r="C96" s="72" t="s">
+        <v>78</v>
       </c>
       <c r="D96" s="13">
         <v>0.5</v>
       </c>
-      <c r="E96" s="44"/>
-      <c r="F96" s="44"/>
-      <c r="G96" s="44"/>
-      <c r="H96" s="44"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="54"/>
       <c r="I96" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J96" s="9">
         <v>0.022222222222222223</v>
       </c>
-      <c r="K96" s="44"/>
-      <c r="L96" s="44"/>
+      <c r="K96" s="54"/>
+      <c r="L96" s="54"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="43" t="s">
-        <v>78</v>
+      <c r="A97" s="53" t="s">
+        <v>80</v>
       </c>
       <c r="B97" s="9">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C97" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D97" s="66">
+      <c r="C97" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="D97" s="75">
         <v>0.03420138888888889</v>
       </c>
-      <c r="E97" s="44"/>
-      <c r="F97" s="44"/>
-      <c r="G97" s="44"/>
-      <c r="H97" s="44"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="54"/>
+      <c r="H97" s="54"/>
       <c r="I97" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J97" s="9">
         <v>0.06859953703703704</v>
       </c>
-      <c r="K97" s="44"/>
-      <c r="L97" s="44"/>
+      <c r="K97" s="54"/>
+      <c r="L97" s="54"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="70"/>
+      <c r="A98" s="79"/>
       <c r="B98" s="9"/>
-      <c r="C98" s="63" t="s">
-        <v>79</v>
+      <c r="C98" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="D98" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E98" s="44"/>
-      <c r="F98" s="44"/>
-      <c r="G98" s="44"/>
-      <c r="H98" s="44"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
       <c r="I98" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J98" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="K98" s="44"/>
-      <c r="L98" s="44"/>
+      <c r="K98" s="54"/>
+      <c r="L98" s="54"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="70"/>
+      <c r="A99" s="79"/>
       <c r="B99" s="9"/>
-      <c r="C99" s="63" t="s">
-        <v>79</v>
+      <c r="C99" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="D99" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E99" s="44"/>
-      <c r="F99" s="44"/>
-      <c r="G99" s="44"/>
-      <c r="H99" s="44"/>
-      <c r="I99" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J99" s="66">
+      <c r="E99" s="54"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="54"/>
+      <c r="H99" s="54"/>
+      <c r="I99" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" s="75">
         <v>0.03420138888888889</v>
       </c>
-      <c r="K99" s="44"/>
-      <c r="L99" s="44"/>
+      <c r="K99" s="54"/>
+      <c r="L99" s="54"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="43"/>
+      <c r="A100" s="53"/>
       <c r="B100" s="9"/>
-      <c r="C100" s="63" t="s">
-        <v>81</v>
+      <c r="C100" s="72" t="s">
+        <v>83</v>
       </c>
       <c r="D100" s="6">
         <v>0.1909722222222222</v>
       </c>
-      <c r="E100" s="44"/>
-      <c r="F100" s="44"/>
-      <c r="G100" s="44"/>
-      <c r="H100" s="44"/>
-      <c r="I100" s="46" t="s">
-        <v>79</v>
+      <c r="E100" s="54"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="54"/>
+      <c r="I100" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="J100" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K100" s="44"/>
-      <c r="L100" s="44"/>
+      <c r="K100" s="54"/>
+      <c r="L100" s="54"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="43"/>
+      <c r="A101" s="53"/>
       <c r="B101" s="9"/>
-      <c r="C101" s="65"/>
-      <c r="D101" s="78"/>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44"/>
-      <c r="G101" s="44"/>
-      <c r="H101" s="44"/>
-      <c r="I101" s="46" t="s">
-        <v>79</v>
+      <c r="C101" s="74"/>
+      <c r="D101" s="87"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="54"/>
+      <c r="H101" s="54"/>
+      <c r="I101" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="J101" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K101" s="44"/>
-      <c r="L101" s="44"/>
+      <c r="K101" s="54"/>
+      <c r="L101" s="54"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B102" s="52">
+      <c r="A102" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102" s="62">
         <f>SUM(B96:B101)</f>
         <v>0.06805555556</v>
       </c>
-      <c r="C102" s="61"/>
-      <c r="D102" s="50">
+      <c r="C102" s="70"/>
+      <c r="D102" s="60">
         <f>SUM(D96:D101)</f>
         <v>0.8178472222</v>
       </c>
-      <c r="E102" s="62"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="62"/>
-      <c r="H102" s="62"/>
-      <c r="I102" s="62"/>
-      <c r="J102" s="52">
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
+      <c r="G102" s="71"/>
+      <c r="H102" s="71"/>
+      <c r="I102" s="71"/>
+      <c r="J102" s="62">
         <f>SUM(J96:J101)</f>
         <v>0.4086689815</v>
       </c>
-      <c r="K102" s="62"/>
-      <c r="L102" s="62"/>
+      <c r="K102" s="71"/>
+      <c r="L102" s="71"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="39"/>
-      <c r="B103" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C103" s="41"/>
-      <c r="D103" s="37" t="s">
+      <c r="A103" s="49"/>
+      <c r="B103" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C103" s="51"/>
+      <c r="D103" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E103" s="41"/>
-      <c r="F103" s="37" t="s">
+      <c r="E103" s="51"/>
+      <c r="F103" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G103" s="41"/>
-      <c r="H103" s="37" t="s">
+      <c r="G103" s="51"/>
+      <c r="H103" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I103" s="41"/>
-      <c r="J103" s="37" t="s">
+      <c r="I103" s="51"/>
+      <c r="J103" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K103" s="41"/>
-      <c r="L103" s="37" t="s">
+      <c r="K103" s="51"/>
+      <c r="L103" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="B104" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="C104" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="D104" s="44"/>
-      <c r="E104" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F104" s="79"/>
-      <c r="G104" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="H104" s="44"/>
-      <c r="I104" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="J104" s="44"/>
-      <c r="K104" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="L104" s="44"/>
+      <c r="A104" s="84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C104" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="54"/>
+      <c r="E104" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104" s="88"/>
+      <c r="G104" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="H104" s="54"/>
+      <c r="I104" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="J104" s="54"/>
+      <c r="K104" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="L104" s="54"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="43" t="s">
-        <v>78</v>
+      <c r="A105" s="53" t="s">
+        <v>80</v>
       </c>
       <c r="B105" s="6">
         <v>0.04722222222222222</v>
       </c>
-      <c r="C105" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D105" s="66">
+      <c r="C105" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="D105" s="75">
         <v>0.03420138888888889</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F105" s="6">
         <v>0.27569444444444446</v>
       </c>
-      <c r="G105" s="44"/>
-      <c r="H105" s="44"/>
-      <c r="I105" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="J105" s="66">
+      <c r="G105" s="54"/>
+      <c r="H105" s="54"/>
+      <c r="I105" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="J105" s="75">
         <v>0.1909722222222222</v>
       </c>
       <c r="K105" s="9"/>
@@ -6781,1380 +6888,1388 @@
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="43"/>
+      <c r="A106" s="53"/>
       <c r="B106" s="9"/>
-      <c r="C106" s="63" t="s">
-        <v>79</v>
+      <c r="C106" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="D106" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="E106" s="44"/>
-      <c r="F106" s="44"/>
-      <c r="G106" s="44"/>
-      <c r="H106" s="44"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="54"/>
+      <c r="H106" s="54"/>
       <c r="I106" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J106" s="9">
         <v>0.03125</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L106" s="9">
         <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="43" t="s">
-        <v>86</v>
+      <c r="A107" s="53" t="s">
+        <v>88</v>
       </c>
       <c r="B107" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C107" s="63" t="s">
-        <v>79</v>
+      <c r="C107" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="D107" s="13">
         <v>0.0625</v>
       </c>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="44"/>
-      <c r="I107" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J107" s="66">
+      <c r="E107" s="54"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="54"/>
+      <c r="H107" s="54"/>
+      <c r="I107" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J107" s="75">
         <v>0.03420138888888889</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L107" s="9">
         <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="70"/>
-      <c r="B108" s="44"/>
-      <c r="C108" s="63" t="s">
-        <v>88</v>
+      <c r="A108" s="79"/>
+      <c r="B108" s="54"/>
+      <c r="C108" s="72" t="s">
+        <v>90</v>
       </c>
       <c r="D108" s="13">
         <v>0.3076388888888889</v>
       </c>
-      <c r="E108" s="44"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="44"/>
-      <c r="H108" s="44"/>
-      <c r="I108" s="46" t="s">
-        <v>79</v>
+      <c r="E108" s="54"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="54"/>
+      <c r="I108" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="J108" s="13">
         <v>0.03017361111111111</v>
       </c>
-      <c r="K108" s="44"/>
-      <c r="L108" s="44"/>
+      <c r="K108" s="54"/>
+      <c r="L108" s="54"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="70"/>
-      <c r="B109" s="44"/>
-      <c r="C109" s="63" t="s">
-        <v>88</v>
+      <c r="A109" s="79"/>
+      <c r="B109" s="54"/>
+      <c r="C109" s="72" t="s">
+        <v>90</v>
       </c>
       <c r="D109" s="13">
         <v>0.24097222222222223</v>
       </c>
-      <c r="E109" s="44"/>
-      <c r="F109" s="44"/>
-      <c r="G109" s="44"/>
-      <c r="H109" s="44"/>
-      <c r="I109" s="46" t="s">
-        <v>79</v>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="54"/>
+      <c r="I109" s="56" t="s">
+        <v>81</v>
       </c>
       <c r="J109" s="13">
         <v>0.0625</v>
       </c>
-      <c r="K109" s="44"/>
-      <c r="L109" s="44"/>
+      <c r="K109" s="54"/>
+      <c r="L109" s="54"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="70"/>
-      <c r="B110" s="44"/>
-      <c r="C110" s="63" t="s">
-        <v>89</v>
+      <c r="A110" s="79"/>
+      <c r="B110" s="54"/>
+      <c r="C110" s="72" t="s">
+        <v>91</v>
       </c>
       <c r="D110" s="13">
         <v>0.10609953703703703</v>
       </c>
-      <c r="E110" s="44"/>
-      <c r="F110" s="44"/>
-      <c r="G110" s="44"/>
-      <c r="H110" s="44"/>
-      <c r="I110" s="43" t="s">
-        <v>86</v>
+      <c r="E110" s="54"/>
+      <c r="F110" s="54"/>
+      <c r="G110" s="54"/>
+      <c r="H110" s="54"/>
+      <c r="I110" s="53" t="s">
+        <v>88</v>
       </c>
       <c r="J110" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="K110" s="44"/>
-      <c r="L110" s="44"/>
+      <c r="K110" s="54"/>
+      <c r="L110" s="54"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="70"/>
-      <c r="B111" s="44"/>
-      <c r="C111" s="65"/>
-      <c r="D111" s="65"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="44"/>
-      <c r="I111" s="44"/>
-      <c r="J111" s="44"/>
-      <c r="K111" s="44"/>
-      <c r="L111" s="44"/>
+      <c r="A111" s="79"/>
+      <c r="B111" s="54"/>
+      <c r="C111" s="74"/>
+      <c r="D111" s="74"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="54"/>
+      <c r="H111" s="54"/>
+      <c r="I111" s="54"/>
+      <c r="J111" s="54"/>
+      <c r="K111" s="54"/>
+      <c r="L111" s="54"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="70"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="65"/>
-      <c r="D112" s="65"/>
-      <c r="E112" s="44"/>
-      <c r="F112" s="44"/>
-      <c r="G112" s="44"/>
-      <c r="H112" s="44"/>
-      <c r="I112" s="44"/>
-      <c r="J112" s="44"/>
-      <c r="K112" s="44"/>
-      <c r="L112" s="44"/>
+      <c r="A112" s="79"/>
+      <c r="B112" s="54"/>
+      <c r="C112" s="74"/>
+      <c r="D112" s="74"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="54"/>
+      <c r="J112" s="54"/>
+      <c r="K112" s="54"/>
+      <c r="L112" s="54"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B113" s="56">
+      <c r="A113" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" s="66">
         <f>SUM(B105:B112)</f>
         <v>0.2798611111</v>
       </c>
-      <c r="C113" s="61"/>
-      <c r="D113" s="72">
+      <c r="C113" s="70"/>
+      <c r="D113" s="81">
         <f>SUM(D105:D112)</f>
         <v>0.7815856481</v>
       </c>
-      <c r="E113" s="62"/>
-      <c r="F113" s="56">
+      <c r="E113" s="71"/>
+      <c r="F113" s="66">
         <f>SUM(F105:F112)</f>
         <v>0.2756944444</v>
       </c>
-      <c r="G113" s="62"/>
-      <c r="H113" s="62"/>
-      <c r="I113" s="62"/>
-      <c r="J113" s="56">
+      <c r="G113" s="71"/>
+      <c r="H113" s="71"/>
+      <c r="I113" s="71"/>
+      <c r="J113" s="66">
         <f>SUM(J105:J112)</f>
         <v>0.5817361111</v>
       </c>
-      <c r="K113" s="62"/>
-      <c r="L113" s="52">
+      <c r="K113" s="71"/>
+      <c r="L113" s="62">
         <f>SUM(L105:L112)</f>
         <v>0.3125</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="39"/>
-      <c r="B114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="37" t="s">
+      <c r="A114" s="49"/>
+      <c r="B114" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" s="51"/>
+      <c r="D114" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E114" s="41"/>
-      <c r="F114" s="37" t="s">
+      <c r="E114" s="51"/>
+      <c r="F114" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G114" s="41"/>
-      <c r="H114" s="37" t="s">
+      <c r="G114" s="51"/>
+      <c r="H114" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I114" s="41"/>
-      <c r="J114" s="37" t="s">
+      <c r="I114" s="51"/>
+      <c r="J114" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K114" s="41"/>
-      <c r="L114" s="37" t="s">
+      <c r="K114" s="51"/>
+      <c r="L114" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B115" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C115" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D115" s="42"/>
-      <c r="E115" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F115" s="42"/>
-      <c r="G115" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H115" s="42"/>
-      <c r="I115" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J115" s="42"/>
-      <c r="K115" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L115" s="42"/>
+      <c r="A115" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B115" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="C115" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" s="52"/>
+      <c r="E115" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" s="52"/>
+      <c r="G115" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H115" s="52"/>
+      <c r="I115" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J115" s="52"/>
+      <c r="K115" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L115" s="52"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="43" t="s">
-        <v>86</v>
+      <c r="A116" s="53" t="s">
+        <v>88</v>
       </c>
       <c r="B116" s="9">
         <v>0.2326388888888889</v>
       </c>
-      <c r="C116" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D116" s="80">
+      <c r="C116" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="D116" s="89">
         <v>0.09930555555555555</v>
       </c>
-      <c r="E116" s="70"/>
-      <c r="F116" s="70"/>
-      <c r="G116" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="H116" s="82">
+      <c r="E116" s="79"/>
+      <c r="F116" s="79"/>
+      <c r="G116" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="H116" s="91">
         <v>0.008726851851851852</v>
       </c>
-      <c r="I116" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="J116" s="80">
+      <c r="I116" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="J116" s="89">
         <v>0.09930555555555555</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L116" s="9">
         <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B117" s="80">
+      <c r="A117" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="89">
         <v>0.06087962962962963</v>
       </c>
-      <c r="C117" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="D117" s="83">
+      <c r="C117" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D117" s="92">
         <v>0.05625</v>
       </c>
-      <c r="E117" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="F117" s="83">
+      <c r="E117" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F117" s="92">
         <v>0.6346296296296297</v>
       </c>
-      <c r="G117" s="47" t="s">
+      <c r="G117" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="H117" s="92">
+        <v>0.014282407407407407</v>
+      </c>
+      <c r="I117" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="H117" s="83">
-        <v>0.014282407407407407</v>
-      </c>
-      <c r="I117" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J117" s="83">
+      <c r="J117" s="92">
         <v>0.05625</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L117" s="9">
         <v>0.1076388888888889</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="B118" s="80">
+      <c r="A118" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" s="89">
         <v>0.06527777777777778</v>
       </c>
-      <c r="C118" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D118" s="80">
+      <c r="C118" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="89">
         <v>0.07368055555555555</v>
       </c>
-      <c r="E118" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F118" s="83">
+      <c r="E118" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F118" s="92">
         <v>0.04513888888888889</v>
       </c>
-      <c r="G118" s="43" t="s">
+      <c r="G118" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="H118" s="92">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="I118" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="H118" s="83">
+      <c r="J118" s="89">
+        <v>0.07368055555555555</v>
+      </c>
+      <c r="K118" s="79"/>
+      <c r="L118" s="79"/>
+    </row>
+    <row r="119" ht="14.25" customHeight="1">
+      <c r="A119" s="79"/>
+      <c r="B119" s="79"/>
+      <c r="C119" s="79"/>
+      <c r="D119" s="79"/>
+      <c r="E119" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F119" s="92">
+        <v>0.225</v>
+      </c>
+      <c r="G119" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="H119" s="92">
+        <v>0.08680555555555555</v>
+      </c>
+      <c r="I119" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="J119" s="92">
         <v>0.18760416666666666</v>
       </c>
-      <c r="I118" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="J118" s="80">
-        <v>0.07368055555555555</v>
-      </c>
-      <c r="K118" s="70"/>
-      <c r="L118" s="70"/>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="70"/>
-      <c r="B119" s="70"/>
-      <c r="C119" s="70"/>
-      <c r="D119" s="70"/>
-      <c r="E119" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F119" s="83">
-        <v>0.225</v>
-      </c>
-      <c r="G119" s="43" t="s">
+      <c r="K119" s="79"/>
+      <c r="L119" s="79"/>
+    </row>
+    <row r="120" ht="14.25" customHeight="1">
+      <c r="A120" s="79"/>
+      <c r="B120" s="79"/>
+      <c r="C120" s="79"/>
+      <c r="D120" s="79"/>
+      <c r="E120" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="H119" s="83">
-        <v>0.08680555555555555</v>
-      </c>
-      <c r="I119" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="J119" s="83">
-        <v>0.18760416666666666</v>
-      </c>
-      <c r="K119" s="70"/>
-      <c r="L119" s="70"/>
-    </row>
-    <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="70"/>
-      <c r="B120" s="70"/>
-      <c r="C120" s="70"/>
-      <c r="D120" s="70"/>
-      <c r="E120" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F120" s="83">
+      <c r="F120" s="92">
         <v>0.2590277777777778</v>
       </c>
-      <c r="G120" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="H120" s="83">
+      <c r="G120" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="H120" s="92">
         <v>0.13541666666666666</v>
       </c>
-      <c r="I120" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="J120" s="80">
+      <c r="I120" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J120" s="89">
         <v>0.06527777777777778</v>
       </c>
-      <c r="K120" s="70"/>
-      <c r="L120" s="70"/>
+      <c r="K120" s="79"/>
+      <c r="L120" s="79"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="70"/>
-      <c r="B121" s="70"/>
-      <c r="C121" s="70"/>
-      <c r="D121" s="70"/>
-      <c r="E121" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F121" s="83">
+      <c r="A121" s="79"/>
+      <c r="B121" s="79"/>
+      <c r="C121" s="79"/>
+      <c r="D121" s="79"/>
+      <c r="E121" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F121" s="92">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G121" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="H121" s="83">
+      <c r="G121" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="H121" s="92">
         <v>0.015196759259259259</v>
       </c>
-      <c r="I121" s="70"/>
-      <c r="J121" s="70"/>
-      <c r="K121" s="70"/>
-      <c r="L121" s="70"/>
+      <c r="I121" s="79"/>
+      <c r="J121" s="79"/>
+      <c r="K121" s="79"/>
+      <c r="L121" s="79"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="70"/>
-      <c r="B122" s="70"/>
-      <c r="C122" s="70"/>
-      <c r="D122" s="70"/>
-      <c r="E122" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F122" s="83">
+      <c r="A122" s="79"/>
+      <c r="B122" s="79"/>
+      <c r="C122" s="79"/>
+      <c r="D122" s="79"/>
+      <c r="E122" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F122" s="92">
         <v>0.10972222222222222</v>
       </c>
-      <c r="G122" s="70"/>
-      <c r="H122" s="70"/>
-      <c r="I122" s="70"/>
-      <c r="J122" s="70"/>
-      <c r="K122" s="70"/>
-      <c r="L122" s="70"/>
+      <c r="G122" s="79"/>
+      <c r="H122" s="79"/>
+      <c r="I122" s="79"/>
+      <c r="J122" s="79"/>
+      <c r="K122" s="79"/>
+      <c r="L122" s="79"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="70"/>
-      <c r="B123" s="70"/>
-      <c r="C123" s="70"/>
-      <c r="D123" s="70"/>
-      <c r="E123" s="70"/>
-      <c r="F123" s="70"/>
-      <c r="G123" s="70"/>
-      <c r="H123" s="70"/>
-      <c r="I123" s="70"/>
-      <c r="J123" s="70"/>
-      <c r="K123" s="70"/>
-      <c r="L123" s="70"/>
+      <c r="A123" s="79"/>
+      <c r="B123" s="79"/>
+      <c r="C123" s="79"/>
+      <c r="D123" s="79"/>
+      <c r="E123" s="79"/>
+      <c r="F123" s="79"/>
+      <c r="G123" s="79"/>
+      <c r="H123" s="79"/>
+      <c r="I123" s="79"/>
+      <c r="J123" s="79"/>
+      <c r="K123" s="79"/>
+      <c r="L123" s="79"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="84"/>
-      <c r="B124" s="84"/>
-      <c r="C124" s="84"/>
-      <c r="D124" s="84"/>
-      <c r="E124" s="84"/>
-      <c r="F124" s="84"/>
-      <c r="G124" s="84"/>
-      <c r="H124" s="84"/>
-      <c r="I124" s="84"/>
-      <c r="J124" s="84"/>
-      <c r="K124" s="84"/>
-      <c r="L124" s="84"/>
+      <c r="A124" s="93"/>
+      <c r="B124" s="93"/>
+      <c r="C124" s="93"/>
+      <c r="D124" s="93"/>
+      <c r="E124" s="93"/>
+      <c r="F124" s="93"/>
+      <c r="G124" s="93"/>
+      <c r="H124" s="93"/>
+      <c r="I124" s="93"/>
+      <c r="J124" s="93"/>
+      <c r="K124" s="93"/>
+      <c r="L124" s="93"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B125" s="85">
+      <c r="A125" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B125" s="94">
         <f>SUM(B116:B124)</f>
         <v>0.3587962963</v>
       </c>
-      <c r="C125" s="84"/>
-      <c r="D125" s="85">
+      <c r="C125" s="93"/>
+      <c r="D125" s="94">
         <f>SUM(D116:D118)</f>
         <v>0.2292361111</v>
       </c>
-      <c r="E125" s="84"/>
-      <c r="F125" s="86">
+      <c r="E125" s="93"/>
+      <c r="F125" s="95">
         <f>SUM(F117:F123)</f>
         <v>1.383240741</v>
       </c>
-      <c r="G125" s="84"/>
-      <c r="H125" s="85">
+      <c r="G125" s="93"/>
+      <c r="H125" s="94">
         <f>SUM(H116:H123)</f>
         <v>0.4480324074</v>
       </c>
-      <c r="I125" s="84"/>
-      <c r="J125" s="85">
+      <c r="I125" s="93"/>
+      <c r="J125" s="94">
         <f>SUM(J116:J124)</f>
         <v>0.4821180556</v>
       </c>
-      <c r="K125" s="84"/>
-      <c r="L125" s="85">
+      <c r="K125" s="93"/>
+      <c r="L125" s="94">
         <f>SUM(L116:L123)</f>
         <v>0.3020833333</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="39"/>
-      <c r="B126" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C126" s="41"/>
-      <c r="D126" s="37" t="s">
+      <c r="A126" s="49"/>
+      <c r="B126" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C126" s="51"/>
+      <c r="D126" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E126" s="41"/>
-      <c r="F126" s="37" t="s">
+      <c r="E126" s="51"/>
+      <c r="F126" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G126" s="41"/>
-      <c r="H126" s="37" t="s">
+      <c r="G126" s="51"/>
+      <c r="H126" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I126" s="41"/>
-      <c r="J126" s="37" t="s">
+      <c r="I126" s="51"/>
+      <c r="J126" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K126" s="41"/>
-      <c r="L126" s="37" t="s">
+      <c r="K126" s="51"/>
+      <c r="L126" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B127" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="C127" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D127" s="42"/>
-      <c r="E127" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F127" s="42"/>
-      <c r="G127" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H127" s="42"/>
-      <c r="I127" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J127" s="42"/>
-      <c r="K127" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L127" s="42"/>
+      <c r="A127" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B127" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="C127" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" s="52"/>
+      <c r="E127" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127" s="52"/>
+      <c r="G127" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H127" s="52"/>
+      <c r="I127" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J127" s="52"/>
+      <c r="K127" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L127" s="52"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="70"/>
-      <c r="B128" s="70"/>
-      <c r="C128" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D128" s="87">
+      <c r="A128" s="79"/>
+      <c r="B128" s="79"/>
+      <c r="C128" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128" s="96">
         <v>0.1557060185185185</v>
       </c>
-      <c r="E128" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="F128" s="88">
+      <c r="E128" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F128" s="97">
         <v>0.1875</v>
       </c>
-      <c r="G128" s="43" t="s">
+      <c r="G128" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="H128" s="98">
+        <v>0.08680555555555555</v>
+      </c>
+      <c r="I128" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="J128" s="76">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="K128" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="L128" s="78">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" customHeight="1">
+      <c r="A129" s="79"/>
+      <c r="B129" s="79"/>
+      <c r="C129" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D129" s="76">
+        <v>0.07152777777777777</v>
+      </c>
+      <c r="E129" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F129" s="99">
+        <v>0.22569444444444445</v>
+      </c>
+      <c r="G129" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="H129" s="76">
+        <v>0.18760416666666666</v>
+      </c>
+      <c r="I129" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="J129" s="99">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="K129" s="79"/>
+      <c r="L129" s="79"/>
+    </row>
+    <row r="130" ht="14.25" customHeight="1">
+      <c r="A130" s="79"/>
+      <c r="B130" s="79"/>
+      <c r="C130" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D130" s="76">
+        <v>0.023854166666666666</v>
+      </c>
+      <c r="E130" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F130" s="76">
+        <v>0.29193287037037036</v>
+      </c>
+      <c r="G130" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="H130" s="98">
+        <v>0.13541666666666666</v>
+      </c>
+      <c r="I130" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="J130" s="99">
+        <v>0.01662037037037037</v>
+      </c>
+      <c r="K130" s="79"/>
+      <c r="L130" s="79"/>
+    </row>
+    <row r="131" ht="14.25" customHeight="1">
+      <c r="A131" s="79"/>
+      <c r="B131" s="79"/>
+      <c r="C131" s="79"/>
+      <c r="D131" s="79"/>
+      <c r="E131" s="79"/>
+      <c r="F131" s="79"/>
+      <c r="G131" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="H131" s="99">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="I131" s="100" t="s">
         <v>106</v>
       </c>
-      <c r="H128" s="89">
-        <v>0.08680555555555555</v>
-      </c>
-      <c r="I128" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="J128" s="67">
-        <v>0.18760416666666666</v>
-      </c>
-      <c r="K128" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="L128" s="69">
-        <v>0.10416666666666667</v>
-      </c>
-    </row>
-    <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="70"/>
-      <c r="B129" s="70"/>
-      <c r="C129" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="D129" s="67">
+      <c r="J131" s="76">
+        <v>0.1557060185185185</v>
+      </c>
+      <c r="K131" s="79"/>
+      <c r="L131" s="79"/>
+    </row>
+    <row r="132" ht="14.25" customHeight="1">
+      <c r="A132" s="79"/>
+      <c r="B132" s="79"/>
+      <c r="C132" s="79"/>
+      <c r="D132" s="79"/>
+      <c r="E132" s="79"/>
+      <c r="F132" s="79"/>
+      <c r="G132" s="79"/>
+      <c r="H132" s="79"/>
+      <c r="I132" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="J132" s="76">
         <v>0.07152777777777777</v>
       </c>
-      <c r="E129" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="F129" s="90">
-        <v>0.22569444444444445</v>
-      </c>
-      <c r="G129" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="H129" s="67">
-        <v>0.18760416666666666</v>
-      </c>
-      <c r="I129" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="J129" s="90">
-        <v>0.027777777777777776</v>
-      </c>
-      <c r="K129" s="70"/>
-      <c r="L129" s="70"/>
-    </row>
-    <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="70"/>
-      <c r="B130" s="70"/>
-      <c r="C130" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="D130" s="67">
+      <c r="K132" s="79"/>
+      <c r="L132" s="79"/>
+    </row>
+    <row r="133" ht="14.25" customHeight="1">
+      <c r="A133" s="79"/>
+      <c r="B133" s="79"/>
+      <c r="C133" s="79"/>
+      <c r="D133" s="79"/>
+      <c r="E133" s="79"/>
+      <c r="F133" s="79"/>
+      <c r="G133" s="79"/>
+      <c r="H133" s="79"/>
+      <c r="I133" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="J133" s="76">
         <v>0.023854166666666666</v>
       </c>
-      <c r="E130" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="F130" s="67">
-        <v>0.29193287037037036</v>
-      </c>
-      <c r="G130" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="H130" s="89">
-        <v>0.13541666666666666</v>
-      </c>
-      <c r="I130" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="J130" s="90">
-        <v>0.01662037037037037</v>
-      </c>
-      <c r="K130" s="70"/>
-      <c r="L130" s="70"/>
-    </row>
-    <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="70"/>
-      <c r="B131" s="70"/>
-      <c r="C131" s="70"/>
-      <c r="D131" s="70"/>
-      <c r="E131" s="70"/>
-      <c r="F131" s="70"/>
-      <c r="G131" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="H131" s="90">
-        <v>0.003472222222222222</v>
-      </c>
-      <c r="I131" s="91" t="s">
-        <v>104</v>
-      </c>
-      <c r="J131" s="67">
-        <v>0.1557060185185185</v>
-      </c>
-      <c r="K131" s="70"/>
-      <c r="L131" s="70"/>
-    </row>
-    <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="70"/>
-      <c r="B132" s="70"/>
-      <c r="C132" s="70"/>
-      <c r="D132" s="70"/>
-      <c r="E132" s="70"/>
-      <c r="F132" s="70"/>
-      <c r="G132" s="70"/>
-      <c r="H132" s="70"/>
-      <c r="I132" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="J132" s="67">
-        <v>0.07152777777777777</v>
-      </c>
-      <c r="K132" s="70"/>
-      <c r="L132" s="70"/>
-    </row>
-    <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="70"/>
-      <c r="B133" s="70"/>
-      <c r="C133" s="70"/>
-      <c r="D133" s="70"/>
-      <c r="E133" s="70"/>
-      <c r="F133" s="70"/>
-      <c r="G133" s="70"/>
-      <c r="H133" s="70"/>
-      <c r="I133" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="J133" s="67">
-        <v>0.023854166666666666</v>
-      </c>
-      <c r="K133" s="70"/>
-      <c r="L133" s="70"/>
+      <c r="K133" s="79"/>
+      <c r="L133" s="79"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B134" s="84">
+      <c r="A134" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B134" s="93">
         <f>SUM(B128:B133)</f>
         <v>0</v>
       </c>
-      <c r="C134" s="84"/>
-      <c r="D134" s="86">
+      <c r="C134" s="93"/>
+      <c r="D134" s="95">
         <f>SUM(D128:D133)</f>
         <v>0.251087963</v>
       </c>
-      <c r="E134" s="84"/>
-      <c r="F134" s="86">
+      <c r="E134" s="93"/>
+      <c r="F134" s="95">
         <f>SUM(F128:F133)</f>
         <v>0.7051273148</v>
       </c>
-      <c r="G134" s="84"/>
-      <c r="H134" s="86">
+      <c r="G134" s="93"/>
+      <c r="H134" s="95">
         <f>SUM(H128:H133)</f>
         <v>0.4132986111</v>
       </c>
-      <c r="I134" s="84"/>
-      <c r="J134" s="86">
+      <c r="I134" s="93"/>
+      <c r="J134" s="95">
         <f>SUM(J128:J133)</f>
         <v>0.4830902778</v>
       </c>
-      <c r="K134" s="84"/>
-      <c r="L134" s="86">
+      <c r="K134" s="93"/>
+      <c r="L134" s="95">
         <f>SUM(L128:L133)</f>
         <v>0.1041666667</v>
       </c>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="39"/>
-      <c r="B135" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C135" s="41"/>
-      <c r="D135" s="37" t="s">
+      <c r="A135" s="49"/>
+      <c r="B135" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C135" s="51"/>
+      <c r="D135" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E135" s="41"/>
-      <c r="F135" s="37" t="s">
+      <c r="E135" s="51"/>
+      <c r="F135" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G135" s="41"/>
-      <c r="H135" s="37" t="s">
+      <c r="G135" s="51"/>
+      <c r="H135" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="I135" s="41"/>
-      <c r="J135" s="37" t="s">
+      <c r="I135" s="51"/>
+      <c r="J135" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="K135" s="41"/>
-      <c r="L135" s="37" t="s">
+      <c r="K135" s="51"/>
+      <c r="L135" s="47" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B136" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="C136" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D136" s="42"/>
-      <c r="E136" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F136" s="42"/>
-      <c r="G136" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H136" s="42"/>
-      <c r="I136" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="J136" s="42"/>
-      <c r="K136" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L136" s="42"/>
+      <c r="A136" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="C136" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D136" s="52"/>
+      <c r="E136" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="52"/>
+      <c r="G136" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H136" s="52"/>
+      <c r="I136" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="J136" s="52"/>
+      <c r="K136" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L136" s="52"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="70"/>
-      <c r="B137" s="70"/>
-      <c r="C137" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="D137" s="92">
+      <c r="A137" s="79"/>
+      <c r="B137" s="79"/>
+      <c r="C137" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D137" s="101">
         <v>0.043958333333333335</v>
       </c>
-      <c r="E137" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="F137" s="88">
+      <c r="E137" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F137" s="97">
         <v>0.2708333333333333</v>
       </c>
-      <c r="G137" s="93" t="s">
-        <v>117</v>
-      </c>
-      <c r="H137" s="94">
+      <c r="G137" s="102" t="s">
+        <v>119</v>
+      </c>
+      <c r="H137" s="103">
         <v>0.11635416666666666</v>
       </c>
-      <c r="I137" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="J137" s="67">
+      <c r="I137" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="J137" s="76">
         <v>0.043958333333333335</v>
       </c>
-      <c r="K137" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="L137" s="69">
+      <c r="K137" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="L137" s="78">
         <v>0.006944444444444444</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="70"/>
-      <c r="B138" s="70"/>
-      <c r="C138" s="43"/>
-      <c r="D138" s="67"/>
-      <c r="E138" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="F138" s="90">
+      <c r="A138" s="79"/>
+      <c r="B138" s="79"/>
+      <c r="C138" s="53"/>
+      <c r="D138" s="76"/>
+      <c r="E138" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="F138" s="99">
         <v>0.22569444444444445</v>
       </c>
-      <c r="G138" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="H138" s="67">
+      <c r="G138" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="H138" s="76">
         <v>0.004097222222222223</v>
       </c>
-      <c r="I138" s="93"/>
-      <c r="J138" s="94"/>
-      <c r="K138" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="L138" s="69">
+      <c r="I138" s="102"/>
+      <c r="J138" s="103"/>
+      <c r="K138" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="L138" s="78">
         <v>0.10416666666666667</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="70"/>
-      <c r="B139" s="70"/>
-      <c r="C139" s="43"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="F139" s="67">
+      <c r="A139" s="79"/>
+      <c r="B139" s="79"/>
+      <c r="C139" s="53"/>
+      <c r="D139" s="76"/>
+      <c r="E139" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F139" s="76">
         <v>0.29193287037037036</v>
       </c>
-      <c r="G139" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="H139" s="89">
+      <c r="G139" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="H139" s="98">
         <v>0.06458333333333334</v>
       </c>
-      <c r="I139" s="43"/>
-      <c r="J139" s="90"/>
-      <c r="K139" s="70"/>
-      <c r="L139" s="70"/>
+      <c r="I139" s="53"/>
+      <c r="J139" s="99"/>
+      <c r="K139" s="79"/>
+      <c r="L139" s="79"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="70"/>
-      <c r="B140" s="70"/>
-      <c r="C140" s="70"/>
-      <c r="D140" s="70"/>
-      <c r="E140" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="F140" s="83">
+      <c r="A140" s="79"/>
+      <c r="B140" s="79"/>
+      <c r="C140" s="79"/>
+      <c r="D140" s="79"/>
+      <c r="E140" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="F140" s="92">
         <v>0.1913425925925926</v>
       </c>
-      <c r="G140" s="95" t="s">
-        <v>123</v>
-      </c>
-      <c r="H140" s="90">
+      <c r="G140" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="H140" s="99">
         <v>0.11458333333333333</v>
       </c>
-      <c r="I140" s="91"/>
-      <c r="J140" s="67"/>
-      <c r="K140" s="70"/>
-      <c r="L140" s="70"/>
+      <c r="I140" s="100"/>
+      <c r="J140" s="76"/>
+      <c r="K140" s="79"/>
+      <c r="L140" s="79"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="70"/>
-      <c r="B141" s="70"/>
-      <c r="C141" s="70"/>
-      <c r="D141" s="70"/>
-      <c r="E141" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="F141" s="83">
+      <c r="A141" s="79"/>
+      <c r="B141" s="79"/>
+      <c r="C141" s="79"/>
+      <c r="D141" s="79"/>
+      <c r="E141" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F141" s="92">
         <v>0.14575231481481482</v>
       </c>
-      <c r="G141" s="43"/>
-      <c r="H141" s="94"/>
-      <c r="I141" s="47"/>
-      <c r="J141" s="67"/>
-      <c r="K141" s="70"/>
-      <c r="L141" s="70"/>
+      <c r="G141" s="53"/>
+      <c r="H141" s="103"/>
+      <c r="I141" s="57"/>
+      <c r="J141" s="76"/>
+      <c r="K141" s="79"/>
+      <c r="L141" s="79"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="70"/>
-      <c r="B142" s="70"/>
-      <c r="C142" s="70"/>
-      <c r="D142" s="70"/>
-      <c r="E142" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="F142" s="83">
+      <c r="A142" s="79"/>
+      <c r="B142" s="79"/>
+      <c r="C142" s="79"/>
+      <c r="D142" s="79"/>
+      <c r="E142" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F142" s="92">
         <v>0.1932523148148148</v>
       </c>
-      <c r="G142" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="H142" s="90">
+      <c r="G142" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="H142" s="99">
         <v>0.041666666666666664</v>
       </c>
-      <c r="I142" s="47"/>
-      <c r="J142" s="67"/>
-      <c r="K142" s="70"/>
-      <c r="L142" s="70"/>
+      <c r="I142" s="57"/>
+      <c r="J142" s="76"/>
+      <c r="K142" s="79"/>
+      <c r="L142" s="79"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="49"/>
-      <c r="B143" s="84"/>
-      <c r="C143" s="84"/>
-      <c r="D143" s="84"/>
-      <c r="E143" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="F143" s="96">
+      <c r="A143" s="59"/>
+      <c r="B143" s="93"/>
+      <c r="C143" s="93"/>
+      <c r="D143" s="93"/>
+      <c r="E143" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="F143" s="105">
         <v>0.29193287037037036</v>
       </c>
-      <c r="G143" s="84"/>
-      <c r="H143" s="84"/>
-      <c r="I143" s="84"/>
-      <c r="J143" s="84"/>
-      <c r="K143" s="84"/>
-      <c r="L143" s="84"/>
+      <c r="G143" s="93"/>
+      <c r="H143" s="93"/>
+      <c r="I143" s="93"/>
+      <c r="J143" s="93"/>
+      <c r="K143" s="93"/>
+      <c r="L143" s="93"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="49"/>
-      <c r="B144" s="84"/>
-      <c r="C144" s="84"/>
-      <c r="D144" s="84"/>
-      <c r="E144" s="97" t="s">
-        <v>128</v>
-      </c>
-      <c r="F144" s="96">
+      <c r="A144" s="59"/>
+      <c r="B144" s="93"/>
+      <c r="C144" s="93"/>
+      <c r="D144" s="93"/>
+      <c r="E144" s="106" t="s">
+        <v>130</v>
+      </c>
+      <c r="F144" s="105">
         <v>0.4636689814814815</v>
       </c>
-      <c r="G144" s="84"/>
-      <c r="H144" s="84"/>
-      <c r="I144" s="84"/>
-      <c r="J144" s="84"/>
-      <c r="K144" s="84"/>
-      <c r="L144" s="84"/>
+      <c r="G144" s="93"/>
+      <c r="H144" s="93"/>
+      <c r="I144" s="93"/>
+      <c r="J144" s="93"/>
+      <c r="K144" s="93"/>
+      <c r="L144" s="93"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B145" s="84">
+      <c r="A145" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B145" s="93">
         <f>SUM(B137:B142)</f>
         <v>0</v>
       </c>
-      <c r="C145" s="84"/>
-      <c r="D145" s="86">
+      <c r="C145" s="93"/>
+      <c r="D145" s="95">
         <f>SUM(D137:D142)</f>
         <v>0.04395833333</v>
       </c>
-      <c r="E145" s="84"/>
-      <c r="F145" s="86">
+      <c r="E145" s="93"/>
+      <c r="F145" s="95">
         <f>SUM(F137:F143)</f>
         <v>1.610740741</v>
       </c>
-      <c r="G145" s="84"/>
-      <c r="H145" s="86">
+      <c r="G145" s="93"/>
+      <c r="H145" s="95">
         <f>SUM(H137:H142)</f>
         <v>0.3412847222</v>
       </c>
-      <c r="I145" s="84"/>
-      <c r="J145" s="86">
+      <c r="I145" s="93"/>
+      <c r="J145" s="95">
         <f>SUM(J137:J142)</f>
         <v>0.04395833333</v>
       </c>
-      <c r="K145" s="84"/>
-      <c r="L145" s="86">
+      <c r="K145" s="93"/>
+      <c r="L145" s="95">
         <f>SUM(L137:L142)</f>
         <v>0.1111111111</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B146" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="C146" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D146" s="42"/>
-      <c r="E146" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F146" s="42"/>
-      <c r="G146" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H146" s="42"/>
-      <c r="I146" s="41"/>
-      <c r="J146" s="42"/>
-      <c r="K146" s="41"/>
-      <c r="L146" s="42"/>
+      <c r="A146" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B146" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C146" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D146" s="52"/>
+      <c r="E146" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146" s="52"/>
+      <c r="G146" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H146" s="52"/>
+      <c r="I146" s="51"/>
+      <c r="J146" s="52"/>
+      <c r="K146" s="51"/>
+      <c r="L146" s="52"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="70"/>
-      <c r="B147" s="70"/>
-      <c r="C147" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="D147" s="92">
+      <c r="A147" s="79"/>
+      <c r="B147" s="79"/>
+      <c r="C147" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D147" s="101">
         <v>0.03011574074074074</v>
       </c>
-      <c r="E147" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F147" s="88">
+      <c r="E147" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="F147" s="97">
         <v>0.10416666666666667</v>
       </c>
-      <c r="G147" s="93"/>
-      <c r="H147" s="94"/>
-      <c r="I147" s="43" t="s">
+      <c r="G147" s="102"/>
+      <c r="H147" s="103"/>
+      <c r="I147" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="J147" s="78">
+        <v>0.048993055555555554</v>
+      </c>
+      <c r="K147" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="L147" s="78">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="148" ht="14.25" customHeight="1">
+      <c r="A148" s="79"/>
+      <c r="B148" s="79"/>
+      <c r="C148" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D148" s="78">
+        <v>0.029479166666666667</v>
+      </c>
+      <c r="E148" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="F148" s="99">
+        <v>1.175486111111111</v>
+      </c>
+      <c r="G148" s="53"/>
+      <c r="H148" s="76"/>
+      <c r="I148" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="J148" s="98">
+        <v>0.04513888888888889</v>
+      </c>
+      <c r="K148" s="53"/>
+      <c r="L148" s="78"/>
+    </row>
+    <row r="149" ht="14.25" customHeight="1">
+      <c r="A149" s="79"/>
+      <c r="B149" s="79"/>
+      <c r="C149" s="107" t="s">
+        <v>139</v>
+      </c>
+      <c r="D149" s="108">
+        <v>0.059027777777777776</v>
+      </c>
+      <c r="E149" s="53"/>
+      <c r="F149" s="76"/>
+      <c r="G149" s="53"/>
+      <c r="H149" s="98"/>
+      <c r="I149" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="J149" s="99">
+        <v>0.029479166666666667</v>
+      </c>
+      <c r="K149" s="79"/>
+      <c r="L149" s="79"/>
+    </row>
+    <row r="150" ht="14.25" customHeight="1">
+      <c r="A150" s="79"/>
+      <c r="B150" s="79"/>
+      <c r="C150" s="79"/>
+      <c r="D150" s="79"/>
+      <c r="E150" s="53"/>
+      <c r="F150" s="92"/>
+      <c r="G150" s="104"/>
+      <c r="H150" s="99"/>
+      <c r="I150" s="107" t="s">
+        <v>139</v>
+      </c>
+      <c r="J150" s="109">
+        <v>0.059027777777777776</v>
+      </c>
+      <c r="K150" s="79"/>
+      <c r="L150" s="79"/>
+    </row>
+    <row r="151" ht="14.25" customHeight="1">
+      <c r="A151" s="79"/>
+      <c r="B151" s="79"/>
+      <c r="C151" s="79"/>
+      <c r="D151" s="79"/>
+      <c r="E151" s="53"/>
+      <c r="F151" s="92"/>
+      <c r="G151" s="104"/>
+      <c r="H151" s="99"/>
+      <c r="I151" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="J147" s="69">
-        <v>0.048993055555555554</v>
-      </c>
-      <c r="K147" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="L147" s="69">
-        <v>0.10416666666666667</v>
-      </c>
-    </row>
-    <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="70"/>
-      <c r="B148" s="70"/>
-      <c r="C148" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D148" s="69">
-        <v>0.029479166666666667</v>
-      </c>
-      <c r="E148" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="F148" s="90">
-        <v>1.175486111111111</v>
-      </c>
-      <c r="G148" s="43"/>
-      <c r="H148" s="67"/>
-      <c r="I148" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="J148" s="89">
-        <v>0.04513888888888889</v>
-      </c>
-      <c r="K148" s="43"/>
-      <c r="L148" s="69"/>
-    </row>
-    <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="70"/>
-      <c r="B149" s="70"/>
-      <c r="C149" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="D149" s="99">
-        <v>0.059027777777777776</v>
-      </c>
-      <c r="E149" s="43"/>
-      <c r="F149" s="67"/>
-      <c r="G149" s="43"/>
-      <c r="H149" s="89"/>
-      <c r="I149" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="J149" s="90">
-        <v>0.029479166666666667</v>
-      </c>
-      <c r="K149" s="70"/>
-      <c r="L149" s="70"/>
-    </row>
-    <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="70"/>
-      <c r="B150" s="70"/>
-      <c r="C150" s="70"/>
-      <c r="D150" s="70"/>
-      <c r="E150" s="43"/>
-      <c r="F150" s="83"/>
-      <c r="G150" s="95"/>
-      <c r="H150" s="90"/>
-      <c r="I150" s="98" t="s">
-        <v>137</v>
-      </c>
-      <c r="J150" s="100">
-        <v>0.059027777777777776</v>
-      </c>
-      <c r="K150" s="70"/>
-      <c r="L150" s="70"/>
-    </row>
-    <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="70"/>
-      <c r="B151" s="70"/>
-      <c r="C151" s="70"/>
-      <c r="D151" s="70"/>
-      <c r="E151" s="43"/>
-      <c r="F151" s="83"/>
-      <c r="G151" s="95"/>
-      <c r="H151" s="90"/>
-      <c r="I151" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="J151" s="92">
+      <c r="J151" s="101">
         <v>0.03011574074074074</v>
       </c>
-      <c r="K151" s="70"/>
-      <c r="L151" s="70"/>
+      <c r="K151" s="79"/>
+      <c r="L151" s="79"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B152" s="84">
+      <c r="A152" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B152" s="93">
         <f>SUM(B147:B151)</f>
         <v>0</v>
       </c>
-      <c r="C152" s="84"/>
-      <c r="D152" s="86">
+      <c r="C152" s="93"/>
+      <c r="D152" s="95">
         <f>SUM(D147:D151)</f>
         <v>0.1186226852</v>
       </c>
-      <c r="E152" s="84"/>
-      <c r="F152" s="86">
+      <c r="E152" s="93"/>
+      <c r="F152" s="95">
         <f>SUM(F147:F151)</f>
         <v>1.279652778</v>
       </c>
-      <c r="G152" s="84"/>
-      <c r="H152" s="86">
+      <c r="G152" s="93"/>
+      <c r="H152" s="95">
         <f>SUM(H147:H151)</f>
         <v>0</v>
       </c>
-      <c r="I152" s="84"/>
-      <c r="J152" s="86">
+      <c r="I152" s="93"/>
+      <c r="J152" s="95">
         <f>SUM(J147:J151)</f>
         <v>0.2127546296</v>
       </c>
-      <c r="K152" s="84"/>
-      <c r="L152" s="86">
+      <c r="K152" s="93"/>
+      <c r="L152" s="95">
         <f>SUM(L147:L151)</f>
         <v>0.1041666667</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B153" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="C153" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D153" s="42"/>
-      <c r="E153" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F153" s="42"/>
-      <c r="G153" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="H153" s="42"/>
-      <c r="I153" s="41"/>
-      <c r="J153" s="42"/>
-      <c r="K153" s="41"/>
-      <c r="L153" s="42"/>
+      <c r="A153" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B153" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="C153" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D153" s="52"/>
+      <c r="E153" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153" s="52"/>
+      <c r="G153" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="52"/>
+      <c r="I153" s="51"/>
+      <c r="J153" s="52"/>
+      <c r="K153" s="51"/>
+      <c r="L153" s="52"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="70"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="43"/>
-      <c r="D154" s="92"/>
-      <c r="E154" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="F154" s="88">
+      <c r="A154" s="79"/>
+      <c r="B154" s="79"/>
+      <c r="C154" s="53"/>
+      <c r="D154" s="101"/>
+      <c r="E154" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="F154" s="97">
         <v>0.7652777777777777</v>
       </c>
-      <c r="G154" s="95" t="s">
-        <v>140</v>
-      </c>
-      <c r="H154" s="89">
+      <c r="G154" s="104" t="s">
+        <v>142</v>
+      </c>
+      <c r="H154" s="98">
         <v>0.1423611111111111</v>
       </c>
-      <c r="I154" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="J154" s="69">
+      <c r="I154" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="J154" s="78">
         <v>0.024305555555555556</v>
       </c>
-      <c r="K154" s="43"/>
-      <c r="L154" s="69"/>
+      <c r="K154" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="L154" s="78">
+        <v>0.125</v>
+      </c>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="70"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="43"/>
-      <c r="D155" s="69"/>
-      <c r="E155" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="F155" s="90">
+      <c r="A155" s="79"/>
+      <c r="B155" s="79"/>
+      <c r="C155" s="53"/>
+      <c r="D155" s="78"/>
+      <c r="E155" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="F155" s="99">
         <v>1.1458333333333333</v>
       </c>
-      <c r="G155" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="H155" s="67">
+      <c r="G155" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="H155" s="76">
         <v>0.06079861111111111</v>
       </c>
-      <c r="I155" s="43"/>
-      <c r="J155" s="89"/>
-      <c r="K155" s="43"/>
-      <c r="L155" s="69"/>
+      <c r="I155" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="J155" s="110">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K155" s="53"/>
+      <c r="L155" s="78"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="70"/>
-      <c r="B156" s="70"/>
-      <c r="C156" s="43"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="F156" s="67">
+      <c r="A156" s="79"/>
+      <c r="B156" s="79"/>
+      <c r="C156" s="53"/>
+      <c r="D156" s="76"/>
+      <c r="E156" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F156" s="76">
         <v>0.6881944444444444</v>
       </c>
-      <c r="G156" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="H156" s="89">
+      <c r="G156" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="H156" s="98">
         <v>0.03815972222222222</v>
       </c>
-      <c r="I156" s="43"/>
-      <c r="J156" s="90"/>
-      <c r="K156" s="70"/>
-      <c r="L156" s="70"/>
+      <c r="I156" s="53"/>
+      <c r="J156" s="99"/>
+      <c r="K156" s="79"/>
+      <c r="L156" s="79"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="70"/>
-      <c r="B157" s="70"/>
-      <c r="C157" s="70"/>
-      <c r="D157" s="70"/>
-      <c r="E157" s="43"/>
-      <c r="F157" s="83"/>
-      <c r="G157" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="H157" s="90">
+      <c r="A157" s="79"/>
+      <c r="B157" s="79"/>
+      <c r="C157" s="79"/>
+      <c r="D157" s="79"/>
+      <c r="E157" s="53"/>
+      <c r="F157" s="92"/>
+      <c r="G157" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="H157" s="99">
         <v>0.30894675925925924</v>
       </c>
-      <c r="I157" s="43"/>
-      <c r="J157" s="92"/>
-      <c r="K157" s="70"/>
-      <c r="L157" s="70"/>
+      <c r="I157" s="53"/>
+      <c r="J157" s="101"/>
+      <c r="K157" s="79"/>
+      <c r="L157" s="79"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="70"/>
-      <c r="B158" s="70"/>
-      <c r="C158" s="70"/>
-      <c r="D158" s="70"/>
-      <c r="E158" s="43"/>
-      <c r="F158" s="83"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="90"/>
-      <c r="I158" s="43"/>
-      <c r="J158" s="92"/>
-      <c r="K158" s="70"/>
-      <c r="L158" s="70"/>
+      <c r="A158" s="79"/>
+      <c r="B158" s="79"/>
+      <c r="C158" s="79"/>
+      <c r="D158" s="79"/>
+      <c r="E158" s="53"/>
+      <c r="F158" s="92"/>
+      <c r="G158" s="104"/>
+      <c r="H158" s="99"/>
+      <c r="I158" s="53"/>
+      <c r="J158" s="101"/>
+      <c r="K158" s="79"/>
+      <c r="L158" s="79"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="70"/>
-      <c r="B159" s="70"/>
-      <c r="C159" s="70"/>
-      <c r="D159" s="70"/>
-      <c r="E159" s="43"/>
-      <c r="F159" s="83"/>
-      <c r="G159" s="95"/>
-      <c r="H159" s="90"/>
-      <c r="I159" s="43"/>
-      <c r="J159" s="92"/>
-      <c r="K159" s="70"/>
-      <c r="L159" s="70"/>
+      <c r="A159" s="79"/>
+      <c r="B159" s="79"/>
+      <c r="C159" s="79"/>
+      <c r="D159" s="79"/>
+      <c r="E159" s="53"/>
+      <c r="F159" s="92"/>
+      <c r="G159" s="104"/>
+      <c r="H159" s="99"/>
+      <c r="I159" s="53"/>
+      <c r="J159" s="101"/>
+      <c r="K159" s="79"/>
+      <c r="L159" s="79"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="70"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="70"/>
-      <c r="E160" s="43"/>
-      <c r="F160" s="83"/>
-      <c r="G160" s="95"/>
-      <c r="H160" s="90"/>
-      <c r="I160" s="43"/>
-      <c r="J160" s="92"/>
-      <c r="K160" s="70"/>
-      <c r="L160" s="70"/>
+      <c r="A160" s="79"/>
+      <c r="B160" s="79"/>
+      <c r="C160" s="79"/>
+      <c r="D160" s="79"/>
+      <c r="E160" s="53"/>
+      <c r="F160" s="92"/>
+      <c r="G160" s="104"/>
+      <c r="H160" s="99"/>
+      <c r="I160" s="53"/>
+      <c r="J160" s="101"/>
+      <c r="K160" s="79"/>
+      <c r="L160" s="79"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="70"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="70"/>
-      <c r="E161" s="43"/>
-      <c r="F161" s="83"/>
-      <c r="G161" s="95"/>
-      <c r="H161" s="90"/>
-      <c r="I161" s="43"/>
-      <c r="J161" s="92"/>
-      <c r="K161" s="70"/>
-      <c r="L161" s="70"/>
+      <c r="A161" s="79"/>
+      <c r="B161" s="79"/>
+      <c r="C161" s="79"/>
+      <c r="D161" s="79"/>
+      <c r="E161" s="53"/>
+      <c r="F161" s="92"/>
+      <c r="G161" s="104"/>
+      <c r="H161" s="99"/>
+      <c r="I161" s="53"/>
+      <c r="J161" s="101"/>
+      <c r="K161" s="79"/>
+      <c r="L161" s="79"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B162" s="84">
+      <c r="A162" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="93">
         <f>SUM(B154:B161)</f>
         <v>0</v>
       </c>
-      <c r="C162" s="84"/>
-      <c r="D162" s="86">
+      <c r="C162" s="93"/>
+      <c r="D162" s="95">
         <f>SUM(D154:D161)</f>
         <v>0</v>
       </c>
-      <c r="E162" s="84"/>
-      <c r="F162" s="86">
+      <c r="E162" s="93"/>
+      <c r="F162" s="95">
         <f>SUM(F154:F161)</f>
         <v>2.599305556</v>
       </c>
-      <c r="G162" s="84"/>
-      <c r="H162" s="86">
+      <c r="G162" s="93"/>
+      <c r="H162" s="95">
         <f>SUM(H154:H161)</f>
         <v>0.5502662037</v>
       </c>
-      <c r="I162" s="84"/>
-      <c r="J162" s="86">
+      <c r="I162" s="93"/>
+      <c r="J162" s="95">
         <f>SUM(J154:J161)</f>
-        <v>0.02430555556</v>
-      </c>
-      <c r="K162" s="84"/>
-      <c r="L162" s="86">
+        <v>0.1076388889</v>
+      </c>
+      <c r="K162" s="93"/>
+      <c r="L162" s="95">
         <f>SUM(L154:L161)</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1"/>
@@ -9018,156 +9133,156 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="101" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="101" t="s">
-        <v>148</v>
+      <c r="C3" s="111" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="111" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="102">
+      <c r="B4" s="112">
         <v>1.0</v>
       </c>
-      <c r="C4" s="103">
+      <c r="C4" s="113">
         <v>45895.0</v>
       </c>
-      <c r="D4" s="103">
+      <c r="D4" s="113">
         <v>45902.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="102">
+      <c r="B5" s="112">
         <v>2.0</v>
       </c>
-      <c r="C5" s="103">
+      <c r="C5" s="113">
         <v>45902.0</v>
       </c>
-      <c r="D5" s="103">
+      <c r="D5" s="113">
         <v>45909.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="102">
+      <c r="B6" s="112">
         <v>3.0</v>
       </c>
-      <c r="C6" s="103">
+      <c r="C6" s="113">
         <v>45909.0</v>
       </c>
-      <c r="D6" s="103">
+      <c r="D6" s="113">
         <v>45916.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="102">
+      <c r="B7" s="112">
         <v>4.0</v>
       </c>
-      <c r="C7" s="103">
+      <c r="C7" s="113">
         <v>45916.0</v>
       </c>
-      <c r="D7" s="103">
+      <c r="D7" s="113">
         <v>45923.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="102">
+      <c r="B8" s="112">
         <v>5.0</v>
       </c>
-      <c r="C8" s="103">
+      <c r="C8" s="113">
         <v>45923.0</v>
       </c>
-      <c r="D8" s="103">
+      <c r="D8" s="113">
         <v>45930.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="102">
+      <c r="B9" s="112">
         <v>6.0</v>
       </c>
-      <c r="C9" s="103">
+      <c r="C9" s="113">
         <v>45930.0</v>
       </c>
-      <c r="D9" s="103">
+      <c r="D9" s="113">
         <v>45937.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="102">
+      <c r="B10" s="112">
         <v>7.0</v>
       </c>
-      <c r="C10" s="103">
+      <c r="C10" s="113">
         <v>45937.0</v>
       </c>
-      <c r="D10" s="104">
+      <c r="D10" s="114">
         <v>45944.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="102">
+      <c r="B11" s="112">
         <v>8.0</v>
       </c>
-      <c r="C11" s="104">
+      <c r="C11" s="114">
         <v>45944.0</v>
       </c>
-      <c r="D11" s="104">
+      <c r="D11" s="114">
         <v>45951.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="102">
+      <c r="B12" s="112">
         <v>9.0</v>
       </c>
-      <c r="C12" s="104">
+      <c r="C12" s="114">
         <v>45951.0</v>
       </c>
-      <c r="D12" s="104">
+      <c r="D12" s="114">
         <v>45958.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="102">
+      <c r="B13" s="112">
         <v>10.0</v>
       </c>
-      <c r="C13" s="104">
+      <c r="C13" s="114">
         <v>45958.0</v>
       </c>
-      <c r="D13" s="103">
+      <c r="D13" s="113">
         <v>45965.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="105">
+      <c r="B14" s="115">
         <v>11.0</v>
       </c>
-      <c r="C14" s="106">
+      <c r="C14" s="116">
         <v>45965.0</v>
       </c>
-      <c r="D14" s="107">
+      <c r="D14" s="117">
         <v>45972.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="105">
+      <c r="B15" s="115">
         <v>12.0</v>
       </c>
-      <c r="C15" s="107">
+      <c r="C15" s="117">
         <v>45941.0</v>
       </c>
-      <c r="D15" s="107">
+      <c r="D15" s="117">
         <v>45979.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="105">
+      <c r="B16" s="115">
         <v>13.0</v>
       </c>
-      <c r="C16" s="107">
+      <c r="C16" s="117">
         <v>45979.0</v>
       </c>
-      <c r="D16" s="107">
+      <c r="D16" s="117">
         <v>45989.0</v>
       </c>
     </row>

--- a/para grafico de registro de tiempos-Kairos.xlsx
+++ b/para grafico de registro de tiempos-Kairos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="154">
   <si>
     <t>Semana</t>
   </si>
@@ -469,6 +469,9 @@
   </si>
   <si>
     <t>Ejecución casos de prueba CU04 Modificar perfil</t>
+  </si>
+  <si>
+    <t>Grabar y editar video vista miembro manual de usuario</t>
   </si>
   <si>
     <t>Casos de prueba CU06,CU18,CU19, CU22 y CU23</t>
@@ -1829,7 +1832,7 @@
       </c>
       <c r="F14" s="5">
         <f>Registro!J162</f>
-        <v>0.1076388889</v>
+        <v>0.3833333333</v>
       </c>
       <c r="G14" s="5">
         <f>Registro!L162</f>
@@ -1862,7 +1865,7 @@
       </c>
       <c r="F15" s="16">
         <f t="shared" si="2"/>
-        <v>3.453738426</v>
+        <v>3.72943287</v>
       </c>
       <c r="G15" s="16">
         <f t="shared" si="2"/>
@@ -1870,7 +1873,7 @@
       </c>
       <c r="H15" s="16">
         <f>SUM(Total!$B15:$G15)</f>
-        <v>24.9228125</v>
+        <v>25.19850694</v>
       </c>
       <c r="I15" s="17"/>
     </row>
@@ -3421,7 +3424,7 @@
       </c>
       <c r="F14" s="5">
         <f>Registro!J162</f>
-        <v>0.1076388889</v>
+        <v>0.3833333333</v>
       </c>
       <c r="G14" s="5">
         <f>Registro!L162</f>
@@ -3429,18 +3432,18 @@
       </c>
       <c r="H14" s="5">
         <f t="shared" si="1"/>
-        <v>3.382210648</v>
+        <v>3.657905093</v>
       </c>
       <c r="I14" s="39">
         <f>SUM(B14:G14)</f>
-        <v>3.382210648</v>
+        <v>3.657905093</v>
       </c>
       <c r="J14" s="40" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="41">
         <f>I14</f>
-        <v>3.382210648</v>
+        <v>3.657905093</v>
       </c>
       <c r="L14" s="22"/>
     </row>
@@ -3466,7 +3469,7 @@
       </c>
       <c r="F15" s="16">
         <f t="shared" si="2"/>
-        <v>3.453738426</v>
+        <v>3.72943287</v>
       </c>
       <c r="G15" s="16">
         <f t="shared" si="2"/>
@@ -3474,7 +3477,7 @@
       </c>
       <c r="H15" s="16">
         <f>SUM('Total x etapas del proyecto'!$B15:$G15)</f>
-        <v>24.9228125</v>
+        <v>25.19850694</v>
       </c>
       <c r="I15" s="42"/>
       <c r="J15" s="43"/>
@@ -8159,8 +8162,12 @@
       <c r="H156" s="98">
         <v>0.03815972222222222</v>
       </c>
-      <c r="I156" s="53"/>
-      <c r="J156" s="99"/>
+      <c r="I156" s="53" t="s">
+        <v>150</v>
+      </c>
+      <c r="J156" s="99">
+        <v>0.27569444444444446</v>
+      </c>
       <c r="K156" s="79"/>
       <c r="L156" s="79"/>
     </row>
@@ -8172,7 +8179,7 @@
       <c r="E157" s="53"/>
       <c r="F157" s="92"/>
       <c r="G157" s="104" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H157" s="99">
         <v>0.30894675925925924</v>
@@ -8264,7 +8271,7 @@
       <c r="I162" s="93"/>
       <c r="J162" s="95">
         <f>SUM(J154:J161)</f>
-        <v>0.1076388889</v>
+        <v>0.3833333333</v>
       </c>
       <c r="K162" s="93"/>
       <c r="L162" s="95">
@@ -9137,10 +9144,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="111" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D3" s="111" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
